--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -476,9 +476,9 @@
         <v>day1</v>
       </c>
       <c r="G3" t="str" xml:space="preserve">
-        <v xml:space="preserve">いちご_x000d_
-ブルーベリー_x000d_
-ちょこ_x000d_
+        <v xml:space="preserve">いちご_x000d__x000d_
+ブルーベリー_x000d__x000d_
+ちょこ_x000d__x000d_
 キャラメル　　※値段は未定</v>
       </c>
       <c r="H3" t="str">
@@ -713,7 +713,7 @@
         <v>both</v>
       </c>
       <c r="G12" t="str" xml:space="preserve">
-        <v xml:space="preserve">黒糖わらび餅抹茶ラテ 1杯 380円_x000d_
+        <v xml:space="preserve">黒糖わらび餅抹茶ラテ 1杯 380円_x000d__x000d_
 黒糖わらび餅ミルクティー 1杯 380円</v>
       </c>
       <c r="H12" t="str">
@@ -740,7 +740,7 @@
         <v>both</v>
       </c>
       <c r="G13" t="str" xml:space="preserve">
-        <v xml:space="preserve">黒糖わらび餅抹茶ラテ 1杯 380円_x000d_
+        <v xml:space="preserve">黒糖わらび餅抹茶ラテ 1杯 380円_x000d__x000d_
 黒糖わらび餅ミルクティー 1杯 380円</v>
       </c>
       <c r="H13" t="str">
@@ -767,9 +767,9 @@
         <v>both</v>
       </c>
       <c r="G14" t="str" xml:space="preserve">
-        <v xml:space="preserve">ソーラーランタン_x000d_
-ウォーム 1個 4,400円_x000d_
-クール 1個 4,400円_x000d_
+        <v xml:space="preserve">ソーラーランタン_x000d__x000d_
+ウォーム 1個 4,400円_x000d__x000d_
+クール 1個 4,400円_x000d__x000d_
 レインボー 1個 5,500円</v>
       </c>
       <c r="H14" t="str">
@@ -822,10 +822,10 @@
         <v>both</v>
       </c>
       <c r="G16" t="str" xml:space="preserve">
-        <v xml:space="preserve">焼き鳥（塩orタレ）_x000d_
-1本 200円_x000d_
-3本 500円_x000d_
-5本 700円_x000d_
+        <v xml:space="preserve">焼き鳥（塩orタレ）_x000d__x000d_
+1本 200円_x000d__x000d_
+3本 500円_x000d__x000d_
+5本 700円_x000d__x000d_
 缶ビール 1本 400円</v>
       </c>
       <c r="H16" t="str">
@@ -878,10 +878,10 @@
         <v>both</v>
       </c>
       <c r="G18" t="str" xml:space="preserve">
-        <v xml:space="preserve">ひとくちドーナツ_x000d_
-6個 300円_x000d_
-8個 350円_x000d_
-各種ソース ＋50円_x000d_
+        <v xml:space="preserve">ひとくちドーナツ_x000d__x000d_
+6個 300円_x000d__x000d_
+8個 350円_x000d__x000d_
+各種ソース ＋50円_x000d__x000d_
 ホイップ ＋50円</v>
       </c>
       <c r="H18" t="str">
@@ -908,8 +908,8 @@
         <v>both</v>
       </c>
       <c r="G19" t="str" xml:space="preserve">
-        <v xml:space="preserve">ホットコーヒー 1杯 200円_x000d_
-アイスコーヒー 1杯 300円_x000d_
+        <v xml:space="preserve">ホットコーヒー 1杯 200円_x000d__x000d_
+アイスコーヒー 1杯 300円_x000d__x000d_
 おかわり 1杯 100円</v>
       </c>
       <c r="H19" t="str">
@@ -1066,7 +1066,7 @@
         <v>both</v>
       </c>
       <c r="G25" t="str" xml:space="preserve">
-        <v xml:space="preserve">参加費　おひとり500円_x000d_
+        <v xml:space="preserve">参加費　おひとり500円_x000d__x000d_
 (抹茶＋和菓子)</v>
       </c>
       <c r="H25" t="str">
@@ -1074,6 +1074,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:H25"/>
   </ignoredErrors>
@@ -1453,6 +1454,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G16"/>
   </ignoredErrors>
@@ -1644,8 +1646,8 @@
         <v>both</v>
       </c>
       <c r="G8" t="str" xml:space="preserve">
-        <v xml:space="preserve">子どもから大人までだいすき_x000d_
-お得にたくさん食べられる5本セットがおすすめ_x000d_
+        <v xml:space="preserve">子どもから大人までだいすき_x000d__x000d_
+お得にたくさん食べられる5本セットがおすすめ_x000d__x000d_
 おいしい焼き鳥食べに来てね</v>
       </c>
     </row>
@@ -1949,6 +1951,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:G21"/>
   </ignoredErrors>
@@ -2012,6 +2015,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
@@ -2493,7 +2497,7 @@
         <v>8号館横 茶室</v>
       </c>
       <c r="D24" t="str">
-        <v>8号館横</v>
+        <v>茶室</v>
       </c>
       <c r="E24">
         <v>1</v>
@@ -2519,7 +2523,7 @@
         <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>204教室</v>
+        <v>204</v>
       </c>
     </row>
     <row r="26">
@@ -2539,7 +2543,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="str">
-        <v>205教室</v>
+        <v>205</v>
       </c>
     </row>
     <row r="27">
@@ -2559,7 +2563,7 @@
         <v>2</v>
       </c>
       <c r="F27" t="str">
-        <v>206教室</v>
+        <v>206</v>
       </c>
     </row>
     <row r="28">
@@ -2579,7 +2583,7 @@
         <v>1</v>
       </c>
       <c r="F28" t="str">
-        <v>101教室</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29">
@@ -2599,7 +2603,7 @@
         <v>1</v>
       </c>
       <c r="F29" t="str">
-        <v>101教室</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30">
@@ -2619,7 +2623,7 @@
         <v>1</v>
       </c>
       <c r="F30" t="str">
-        <v>102教室</v>
+        <v>102</v>
       </c>
     </row>
     <row r="31">
@@ -2639,7 +2643,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="str">
-        <v>103・105教室</v>
+        <v>103・105</v>
       </c>
     </row>
     <row r="32">
@@ -2659,7 +2663,7 @@
         <v>2</v>
       </c>
       <c r="F32" t="str">
-        <v>201教室</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33">
@@ -2679,7 +2683,7 @@
         <v>2</v>
       </c>
       <c r="F33" t="str">
-        <v>203教室</v>
+        <v>203</v>
       </c>
     </row>
     <row r="34">
@@ -2699,7 +2703,7 @@
         <v>2</v>
       </c>
       <c r="F34" t="str">
-        <v>204教室</v>
+        <v>204</v>
       </c>
     </row>
     <row r="35">
@@ -2719,7 +2723,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="str">
-        <v>205教室</v>
+        <v>205</v>
       </c>
     </row>
     <row r="36">
@@ -2739,7 +2743,7 @@
         <v>2</v>
       </c>
       <c r="F36" t="str">
-        <v>206教室</v>
+        <v>206</v>
       </c>
     </row>
     <row r="37">
@@ -2759,7 +2763,7 @@
         <v>3</v>
       </c>
       <c r="F37" t="str">
-        <v>305教室</v>
+        <v>305</v>
       </c>
     </row>
     <row r="38">
@@ -2779,7 +2783,7 @@
         <v>3</v>
       </c>
       <c r="F38" t="str">
-        <v>306教室</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39">
@@ -2819,7 +2823,7 @@
         <v>2</v>
       </c>
       <c r="F40" t="str">
-        <v>201教室</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41">
@@ -2839,7 +2843,7 @@
         <v>2</v>
       </c>
       <c r="F41" t="str">
-        <v>203教室</v>
+        <v>203</v>
       </c>
     </row>
     <row r="42">
@@ -2859,7 +2863,7 @@
         <v>3</v>
       </c>
       <c r="F42" t="str">
-        <v>301教室</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43">
@@ -2879,7 +2883,7 @@
         <v>3</v>
       </c>
       <c r="F43" t="str">
-        <v>303教室</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44">
@@ -2899,7 +2903,7 @@
         <v>4</v>
       </c>
       <c r="F44" t="str">
-        <v>401教室</v>
+        <v>401</v>
       </c>
     </row>
     <row r="45">
@@ -2919,7 +2923,7 @@
         <v>4</v>
       </c>
       <c r="F45" t="str">
-        <v>403教室</v>
+        <v>403</v>
       </c>
     </row>
     <row r="46">
@@ -3019,7 +3023,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="str">
-        <v>大礼拝堂</v>
+        <v>礼拝堂</v>
       </c>
     </row>
     <row r="51">
@@ -3063,6 +3067,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:F52"/>
   </ignoredErrors>
@@ -4162,6 +4167,7 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
     <ignoredError numberStoredAsText="1" sqref="A1:J34"/>
   </ignoredErrors>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkytw\Desktop\GitHub\Home-Page\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C1DCAA-22E2-47A4-A520-0E866A24A363}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286787FA-356A-42D6-BA5E-F91E903995A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mogiten" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="525">
   <si>
     <t>id</t>
   </si>
@@ -1578,9 +1578,6 @@
   </si>
   <si>
     <t>tt-d2-11</t>
-  </si>
-  <si>
-    <t>16:30～17:30</t>
   </si>
   <si>
     <t>17:30</t>
@@ -1641,12 +1638,61 @@
 ※ 出演者への直接のプレゼント、差し入れはできません。プレゼントボックスを設置いたします。</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>day1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>day2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF79C0FF"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>開場</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF79C0FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">15:30 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF79C0FF"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>開演</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF79C0FF"/>
+        <rFont val="Consolas"/>
+        <family val="3"/>
+      </rPr>
+      <t>16:30</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1660,6 +1706,26 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF79C0FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF79C0FF"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF79C0FF"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1682,11 +1748,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2027,9 +2097,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2055,7 +2125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2081,7 +2151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2107,7 +2177,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>23</v>
       </c>
@@ -2133,7 +2203,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>29</v>
       </c>
@@ -2159,7 +2229,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -2185,7 +2255,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>40</v>
       </c>
@@ -2211,7 +2281,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>46</v>
       </c>
@@ -2237,7 +2307,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -2263,7 +2333,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>55</v>
       </c>
@@ -2289,7 +2359,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>61</v>
       </c>
@@ -2315,7 +2385,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -2341,7 +2411,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>73</v>
       </c>
@@ -2367,7 +2437,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>75</v>
       </c>
@@ -2393,7 +2463,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>81</v>
       </c>
@@ -2419,7 +2489,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>87</v>
       </c>
@@ -2445,7 +2515,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>92</v>
       </c>
@@ -2471,7 +2541,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>98</v>
       </c>
@@ -2497,7 +2567,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>104</v>
       </c>
@@ -2523,7 +2593,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>110</v>
       </c>
@@ -2549,7 +2619,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>116</v>
       </c>
@@ -2575,7 +2645,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>122</v>
       </c>
@@ -2601,7 +2671,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>128</v>
       </c>
@@ -2627,7 +2697,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>134</v>
       </c>
@@ -2653,7 +2723,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>140</v>
       </c>
@@ -2691,9 +2761,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2716,7 +2786,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -2739,7 +2809,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>152</v>
       </c>
@@ -2762,7 +2832,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>157</v>
       </c>
@@ -2785,7 +2855,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>162</v>
       </c>
@@ -2808,7 +2878,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>167</v>
       </c>
@@ -2831,7 +2901,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>171</v>
       </c>
@@ -2854,7 +2924,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>176</v>
       </c>
@@ -2877,7 +2947,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>181</v>
       </c>
@@ -2900,7 +2970,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>185</v>
       </c>
@@ -2923,7 +2993,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>190</v>
       </c>
@@ -2946,7 +3016,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>194</v>
       </c>
@@ -2969,7 +3039,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>198</v>
       </c>
@@ -2992,7 +3062,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>202</v>
       </c>
@@ -3015,7 +3085,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>207</v>
       </c>
@@ -3038,7 +3108,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>211</v>
       </c>
@@ -3073,9 +3143,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3098,7 +3168,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>216</v>
       </c>
@@ -3121,7 +3191,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>222</v>
       </c>
@@ -3144,7 +3214,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>226</v>
       </c>
@@ -3167,7 +3237,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>230</v>
       </c>
@@ -3190,7 +3260,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>234</v>
       </c>
@@ -3213,7 +3283,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>238</v>
       </c>
@@ -3236,7 +3306,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>242</v>
       </c>
@@ -3259,7 +3329,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>246</v>
       </c>
@@ -3282,7 +3352,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>250</v>
       </c>
@@ -3305,7 +3375,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>254</v>
       </c>
@@ -3328,7 +3398,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>258</v>
       </c>
@@ -3351,7 +3421,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>263</v>
       </c>
@@ -3374,7 +3444,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>268</v>
       </c>
@@ -3397,7 +3467,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>273</v>
       </c>
@@ -3420,7 +3490,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>278</v>
       </c>
@@ -3443,7 +3513,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>283</v>
       </c>
@@ -3466,7 +3536,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>288</v>
       </c>
@@ -3489,7 +3559,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>290</v>
       </c>
@@ -3512,7 +3582,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>294</v>
       </c>
@@ -3535,7 +3605,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>296</v>
       </c>
@@ -3628,10 +3698,10 @@
         <v>137</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>521</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -4707,9 +4777,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4741,15 +4811,15 @@
         <v>419</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>238</v>
       </c>
       <c r="B2" t="s">
         <v>420</v>
       </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="C2" t="s">
+        <v>522</v>
       </c>
       <c r="D2" t="s">
         <v>261</v>
@@ -4773,15 +4843,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>216</v>
       </c>
       <c r="B3" t="s">
         <v>424</v>
       </c>
-      <c r="C3">
-        <v>1</v>
+      <c r="C3" t="s">
+        <v>522</v>
       </c>
       <c r="D3" t="s">
         <v>261</v>
@@ -4805,15 +4875,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>222</v>
       </c>
       <c r="B4" t="s">
         <v>428</v>
       </c>
-      <c r="C4">
-        <v>1</v>
+      <c r="C4" t="s">
+        <v>522</v>
       </c>
       <c r="D4" t="s">
         <v>261</v>
@@ -4837,15 +4907,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>230</v>
       </c>
       <c r="B5" t="s">
         <v>432</v>
       </c>
-      <c r="C5">
-        <v>1</v>
+      <c r="C5" t="s">
+        <v>522</v>
       </c>
       <c r="D5" t="s">
         <v>261</v>
@@ -4869,15 +4939,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>234</v>
       </c>
       <c r="B6" t="s">
         <v>436</v>
       </c>
-      <c r="C6">
-        <v>1</v>
+      <c r="C6" t="s">
+        <v>522</v>
       </c>
       <c r="D6" t="s">
         <v>261</v>
@@ -4901,15 +4971,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>226</v>
       </c>
       <c r="B7" t="s">
         <v>440</v>
       </c>
-      <c r="C7">
-        <v>1</v>
+      <c r="C7" t="s">
+        <v>522</v>
       </c>
       <c r="D7" t="s">
         <v>261</v>
@@ -4933,15 +5003,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>258</v>
       </c>
       <c r="B8" t="s">
         <v>444</v>
       </c>
-      <c r="C8">
-        <v>1</v>
+      <c r="C8" t="s">
+        <v>522</v>
       </c>
       <c r="D8" t="s">
         <v>261</v>
@@ -4965,15 +5035,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>242</v>
       </c>
       <c r="B9" t="s">
         <v>448</v>
       </c>
-      <c r="C9">
-        <v>1</v>
+      <c r="C9" t="s">
+        <v>522</v>
       </c>
       <c r="D9" t="s">
         <v>244</v>
@@ -4997,15 +5067,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>246</v>
       </c>
       <c r="B10" t="s">
         <v>452</v>
       </c>
-      <c r="C10">
-        <v>1</v>
+      <c r="C10" t="s">
+        <v>522</v>
       </c>
       <c r="D10" t="s">
         <v>244</v>
@@ -5029,15 +5099,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>250</v>
       </c>
       <c r="B11" t="s">
         <v>456</v>
       </c>
-      <c r="C11">
-        <v>1</v>
+      <c r="C11" t="s">
+        <v>522</v>
       </c>
       <c r="D11" t="s">
         <v>244</v>
@@ -5061,15 +5131,15 @@
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>254</v>
       </c>
       <c r="B12" t="s">
         <v>459</v>
       </c>
-      <c r="C12">
-        <v>1</v>
+      <c r="C12" t="s">
+        <v>522</v>
       </c>
       <c r="D12" t="s">
         <v>244</v>
@@ -5093,15 +5163,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>278</v>
       </c>
       <c r="B13" t="s">
         <v>463</v>
       </c>
-      <c r="C13">
-        <v>1</v>
+      <c r="C13" t="s">
+        <v>522</v>
       </c>
       <c r="D13" t="s">
         <v>281</v>
@@ -5125,15 +5195,15 @@
         <v>360</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>273</v>
       </c>
       <c r="B14" t="s">
         <v>466</v>
       </c>
-      <c r="C14">
-        <v>1</v>
+      <c r="C14" t="s">
+        <v>522</v>
       </c>
       <c r="D14" t="s">
         <v>276</v>
@@ -5157,15 +5227,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>283</v>
       </c>
       <c r="B15" t="s">
         <v>469</v>
       </c>
-      <c r="C15">
-        <v>1</v>
+      <c r="C15" t="s">
+        <v>522</v>
       </c>
       <c r="D15" t="s">
         <v>286</v>
@@ -5189,15 +5259,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>283</v>
       </c>
       <c r="B16" t="s">
         <v>473</v>
       </c>
-      <c r="C16">
-        <v>1</v>
+      <c r="C16" t="s">
+        <v>522</v>
       </c>
       <c r="D16" t="s">
         <v>286</v>
@@ -5221,15 +5291,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>288</v>
       </c>
       <c r="B17" t="s">
         <v>476</v>
       </c>
-      <c r="C17">
-        <v>1</v>
+      <c r="C17" t="s">
+        <v>522</v>
       </c>
       <c r="D17" t="s">
         <v>286</v>
@@ -5253,15 +5323,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>290</v>
       </c>
       <c r="B18" t="s">
         <v>480</v>
       </c>
-      <c r="C18">
-        <v>1</v>
+      <c r="C18" t="s">
+        <v>522</v>
       </c>
       <c r="D18" t="s">
         <v>286</v>
@@ -5285,15 +5355,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>238</v>
       </c>
       <c r="B19" t="s">
         <v>484</v>
       </c>
-      <c r="C19">
-        <v>2</v>
+      <c r="C19" t="s">
+        <v>523</v>
       </c>
       <c r="D19" t="s">
         <v>261</v>
@@ -5317,15 +5387,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>216</v>
       </c>
       <c r="B20" t="s">
         <v>487</v>
       </c>
-      <c r="C20">
-        <v>2</v>
+      <c r="C20" t="s">
+        <v>523</v>
       </c>
       <c r="D20" t="s">
         <v>261</v>
@@ -5349,15 +5419,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>222</v>
       </c>
       <c r="B21" t="s">
         <v>491</v>
       </c>
-      <c r="C21">
-        <v>2</v>
+      <c r="C21" t="s">
+        <v>523</v>
       </c>
       <c r="D21" t="s">
         <v>261</v>
@@ -5381,15 +5451,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>230</v>
       </c>
       <c r="B22" t="s">
         <v>494</v>
       </c>
-      <c r="C22">
-        <v>2</v>
+      <c r="C22" t="s">
+        <v>523</v>
       </c>
       <c r="D22" t="s">
         <v>261</v>
@@ -5413,15 +5483,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>234</v>
       </c>
       <c r="B23" t="s">
         <v>497</v>
       </c>
-      <c r="C23">
-        <v>2</v>
+      <c r="C23" t="s">
+        <v>523</v>
       </c>
       <c r="D23" t="s">
         <v>261</v>
@@ -5445,15 +5515,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>226</v>
       </c>
       <c r="B24" t="s">
         <v>499</v>
       </c>
-      <c r="C24">
-        <v>2</v>
+      <c r="C24" t="s">
+        <v>523</v>
       </c>
       <c r="D24" t="s">
         <v>261</v>
@@ -5477,15 +5547,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>258</v>
       </c>
       <c r="B25" t="s">
         <v>501</v>
       </c>
-      <c r="C25">
-        <v>2</v>
+      <c r="C25" t="s">
+        <v>523</v>
       </c>
       <c r="D25" t="s">
         <v>261</v>
@@ -5509,15 +5579,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>263</v>
       </c>
       <c r="B26" t="s">
         <v>504</v>
       </c>
-      <c r="C26">
-        <v>2</v>
+      <c r="C26" t="s">
+        <v>523</v>
       </c>
       <c r="D26" t="s">
         <v>261</v>
@@ -5541,15 +5611,15 @@
         <v>60</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>242</v>
       </c>
       <c r="B27" t="s">
         <v>506</v>
       </c>
-      <c r="C27">
-        <v>2</v>
+      <c r="C27" t="s">
+        <v>523</v>
       </c>
       <c r="D27" t="s">
         <v>244</v>
@@ -5573,15 +5643,15 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>254</v>
       </c>
       <c r="B28" t="s">
         <v>509</v>
       </c>
-      <c r="C28">
-        <v>2</v>
+      <c r="C28" t="s">
+        <v>523</v>
       </c>
       <c r="D28" t="s">
         <v>244</v>
@@ -5605,47 +5675,47 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>298</v>
       </c>
       <c r="B29" t="s">
         <v>510</v>
       </c>
-      <c r="C29">
-        <v>2</v>
+      <c r="C29" t="s">
+        <v>523</v>
       </c>
       <c r="D29" t="s">
         <v>244</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E29" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="G29" t="s">
         <v>511</v>
       </c>
-      <c r="F29" t="s">
-        <v>446</v>
-      </c>
-      <c r="G29" t="s">
-        <v>512</v>
-      </c>
       <c r="H29">
-        <v>990</v>
+        <v>930</v>
       </c>
       <c r="I29">
         <v>1050</v>
       </c>
       <c r="J29">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>278</v>
       </c>
       <c r="B30" t="s">
-        <v>513</v>
-      </c>
-      <c r="C30">
-        <v>2</v>
+        <v>512</v>
+      </c>
+      <c r="C30" t="s">
+        <v>523</v>
       </c>
       <c r="D30" t="s">
         <v>281</v>
@@ -5669,21 +5739,21 @@
         <v>360</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>294</v>
       </c>
       <c r="B31" t="s">
-        <v>514</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
+        <v>513</v>
+      </c>
+      <c r="C31" t="s">
+        <v>523</v>
       </c>
       <c r="D31" t="s">
         <v>286</v>
       </c>
       <c r="E31" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="F31" t="s">
         <v>431</v>
@@ -5701,15 +5771,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>294</v>
       </c>
       <c r="B32" t="s">
-        <v>516</v>
-      </c>
-      <c r="C32">
-        <v>2</v>
+        <v>515</v>
+      </c>
+      <c r="C32" t="s">
+        <v>523</v>
       </c>
       <c r="D32" t="s">
         <v>286</v>
@@ -5733,15 +5803,15 @@
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>296</v>
       </c>
       <c r="B33" t="s">
-        <v>517</v>
-      </c>
-      <c r="C33">
-        <v>2</v>
+        <v>516</v>
+      </c>
+      <c r="C33" t="s">
+        <v>523</v>
       </c>
       <c r="D33" t="s">
         <v>286</v>
@@ -5765,24 +5835,24 @@
         <v>15</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="14.4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>296</v>
       </c>
       <c r="B34" t="s">
-        <v>518</v>
-      </c>
-      <c r="C34">
-        <v>2</v>
+        <v>517</v>
+      </c>
+      <c r="C34" t="s">
+        <v>523</v>
       </c>
       <c r="D34" t="s">
         <v>286</v>
       </c>
       <c r="E34" t="s">
+        <v>518</v>
+      </c>
+      <c r="F34" t="s">
         <v>519</v>
-      </c>
-      <c r="F34" t="s">
-        <v>520</v>
       </c>
       <c r="G34" t="s">
         <v>478</v>
@@ -5801,7 +5871,7 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:J34" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:J1 A7:B7 A2:B2 D2:J2 A3:B3 D3:J3 A4:B4 D4:J4 A5:B5 D5:J5 A6:B6 D6:J6 A34:B34 A8:B8 D8:J8 D7:J7 A9:B9 D9:J9 A10:B10 D10:J10 A11:B11 D11:J11 A12:B12 D12:J12 A13:B13 D13:J13 A14:B14 D14:J14 A15:B15 D15:J15 A16:B16 D16:J16 A17:B17 D17:J17 A18:B18 D18:J18 A19:B19 D19:J19 A20:B20 D20:J20 A21:B21 D21:J21 A22:B22 D22:J22 A23:B23 D23:J23 A24:B24 D24:J24 A25:B25 D25:J25 A26:B26 D26:J26 A27:B27 D27:J27 A28:B28 D28:J28 A29:B29 D29 A30:B30 D30:J30 A31:B31 D31:J31 A32:B32 D32:J32 A33:B33 D33:J33 D34:J34 G29 I29" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkytw\Desktop\GitHub\Home-Page\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{286787FA-356A-42D6-BA5E-F91E903995A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4556A40-1A16-4524-A707-43EF2FB5C386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8376" yWindow="2676" windowWidth="12648" windowHeight="11004" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mogiten" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="timetable" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -945,9 +946,6 @@
   </si>
   <si>
     <t>宮世琉弥トークショー × 平潟祭</t>
-  </si>
-  <si>
-    <t>平潟祭実行委員会</t>
   </si>
   <si>
     <t>芸能</t>
@@ -1685,6 +1683,13 @@
       </rPr>
       <t>16:30</t>
     </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>平潟祭実行委員会 芸能</t>
+    <rPh sb="9" eb="11">
+      <t>ゲイノウ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -3686,10 +3691,10 @@
         <v>299</v>
       </c>
       <c r="C2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D2" t="s">
         <v>300</v>
-      </c>
-      <c r="D2" t="s">
-        <v>301</v>
       </c>
       <c r="E2" t="s">
         <v>244</v>
@@ -3698,17 +3703,17 @@
         <v>137</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>520</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>521</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:H1 A2:F2" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:H1 A2:B2 D2:F2" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -3730,19 +3735,19 @@
         <v>4</v>
       </c>
       <c r="B1" t="s">
+        <v>301</v>
+      </c>
+      <c r="C1" t="s">
         <v>302</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>303</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>304</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>305</v>
-      </c>
-      <c r="F1" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -3753,16 +3758,16 @@
         <v>33</v>
       </c>
       <c r="C2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D2" t="s">
         <v>307</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>308</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>309</v>
-      </c>
-      <c r="F2" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -3773,16 +3778,16 @@
         <v>33</v>
       </c>
       <c r="C3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D3" t="s">
+        <v>307</v>
+      </c>
+      <c r="E3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F3" t="s">
         <v>311</v>
-      </c>
-      <c r="D3" t="s">
-        <v>308</v>
-      </c>
-      <c r="E3" t="s">
-        <v>309</v>
-      </c>
-      <c r="F3" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -3793,16 +3798,16 @@
         <v>33</v>
       </c>
       <c r="C4" t="s">
+        <v>312</v>
+      </c>
+      <c r="D4" t="s">
+        <v>307</v>
+      </c>
+      <c r="E4" t="s">
+        <v>308</v>
+      </c>
+      <c r="F4" t="s">
         <v>313</v>
-      </c>
-      <c r="D4" t="s">
-        <v>308</v>
-      </c>
-      <c r="E4" t="s">
-        <v>309</v>
-      </c>
-      <c r="F4" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -3813,16 +3818,16 @@
         <v>33</v>
       </c>
       <c r="C5" t="s">
+        <v>314</v>
+      </c>
+      <c r="D5" t="s">
+        <v>307</v>
+      </c>
+      <c r="E5" t="s">
+        <v>308</v>
+      </c>
+      <c r="F5" t="s">
         <v>315</v>
-      </c>
-      <c r="D5" t="s">
-        <v>308</v>
-      </c>
-      <c r="E5" t="s">
-        <v>309</v>
-      </c>
-      <c r="F5" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -3833,16 +3838,16 @@
         <v>33</v>
       </c>
       <c r="C6" t="s">
+        <v>316</v>
+      </c>
+      <c r="D6" t="s">
+        <v>307</v>
+      </c>
+      <c r="E6" t="s">
+        <v>308</v>
+      </c>
+      <c r="F6" t="s">
         <v>317</v>
-      </c>
-      <c r="D6" t="s">
-        <v>308</v>
-      </c>
-      <c r="E6" t="s">
-        <v>309</v>
-      </c>
-      <c r="F6" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -3853,16 +3858,16 @@
         <v>33</v>
       </c>
       <c r="C7" t="s">
+        <v>318</v>
+      </c>
+      <c r="D7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E7" t="s">
+        <v>308</v>
+      </c>
+      <c r="F7" t="s">
         <v>319</v>
-      </c>
-      <c r="D7" t="s">
-        <v>308</v>
-      </c>
-      <c r="E7" t="s">
-        <v>309</v>
-      </c>
-      <c r="F7" t="s">
-        <v>320</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -3873,16 +3878,16 @@
         <v>33</v>
       </c>
       <c r="C8" t="s">
+        <v>320</v>
+      </c>
+      <c r="D8" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" t="s">
+        <v>308</v>
+      </c>
+      <c r="F8" t="s">
         <v>321</v>
-      </c>
-      <c r="D8" t="s">
-        <v>308</v>
-      </c>
-      <c r="E8" t="s">
-        <v>309</v>
-      </c>
-      <c r="F8" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -3893,16 +3898,16 @@
         <v>33</v>
       </c>
       <c r="C9" t="s">
+        <v>322</v>
+      </c>
+      <c r="D9" t="s">
+        <v>307</v>
+      </c>
+      <c r="E9" t="s">
+        <v>308</v>
+      </c>
+      <c r="F9" t="s">
         <v>323</v>
-      </c>
-      <c r="D9" t="s">
-        <v>308</v>
-      </c>
-      <c r="E9" t="s">
-        <v>309</v>
-      </c>
-      <c r="F9" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -3913,16 +3918,16 @@
         <v>33</v>
       </c>
       <c r="C10" t="s">
+        <v>324</v>
+      </c>
+      <c r="D10" t="s">
+        <v>307</v>
+      </c>
+      <c r="E10" t="s">
+        <v>308</v>
+      </c>
+      <c r="F10" t="s">
         <v>325</v>
-      </c>
-      <c r="D10" t="s">
-        <v>308</v>
-      </c>
-      <c r="E10" t="s">
-        <v>309</v>
-      </c>
-      <c r="F10" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -3933,16 +3938,16 @@
         <v>33</v>
       </c>
       <c r="C11" t="s">
+        <v>326</v>
+      </c>
+      <c r="D11" t="s">
+        <v>307</v>
+      </c>
+      <c r="E11" t="s">
+        <v>308</v>
+      </c>
+      <c r="F11" t="s">
         <v>327</v>
-      </c>
-      <c r="D11" t="s">
-        <v>308</v>
-      </c>
-      <c r="E11" t="s">
-        <v>309</v>
-      </c>
-      <c r="F11" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -3953,16 +3958,16 @@
         <v>33</v>
       </c>
       <c r="C12" t="s">
+        <v>328</v>
+      </c>
+      <c r="D12" t="s">
+        <v>307</v>
+      </c>
+      <c r="E12" t="s">
+        <v>308</v>
+      </c>
+      <c r="F12" t="s">
         <v>329</v>
-      </c>
-      <c r="D12" t="s">
-        <v>308</v>
-      </c>
-      <c r="E12" t="s">
-        <v>309</v>
-      </c>
-      <c r="F12" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -3973,16 +3978,16 @@
         <v>33</v>
       </c>
       <c r="C13" t="s">
+        <v>330</v>
+      </c>
+      <c r="D13" t="s">
+        <v>307</v>
+      </c>
+      <c r="E13" t="s">
+        <v>308</v>
+      </c>
+      <c r="F13" t="s">
         <v>331</v>
-      </c>
-      <c r="D13" t="s">
-        <v>308</v>
-      </c>
-      <c r="E13" t="s">
-        <v>309</v>
-      </c>
-      <c r="F13" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -3993,16 +3998,16 @@
         <v>33</v>
       </c>
       <c r="C14" t="s">
+        <v>332</v>
+      </c>
+      <c r="D14" t="s">
+        <v>307</v>
+      </c>
+      <c r="E14" t="s">
+        <v>308</v>
+      </c>
+      <c r="F14" t="s">
         <v>333</v>
-      </c>
-      <c r="D14" t="s">
-        <v>308</v>
-      </c>
-      <c r="E14" t="s">
-        <v>309</v>
-      </c>
-      <c r="F14" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -4013,16 +4018,16 @@
         <v>33</v>
       </c>
       <c r="C15" t="s">
+        <v>334</v>
+      </c>
+      <c r="D15" t="s">
+        <v>307</v>
+      </c>
+      <c r="E15" t="s">
+        <v>308</v>
+      </c>
+      <c r="F15" t="s">
         <v>335</v>
-      </c>
-      <c r="D15" t="s">
-        <v>308</v>
-      </c>
-      <c r="E15" t="s">
-        <v>309</v>
-      </c>
-      <c r="F15" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -4033,16 +4038,16 @@
         <v>33</v>
       </c>
       <c r="C16" t="s">
+        <v>336</v>
+      </c>
+      <c r="D16" t="s">
+        <v>307</v>
+      </c>
+      <c r="E16" t="s">
+        <v>308</v>
+      </c>
+      <c r="F16" t="s">
         <v>337</v>
-      </c>
-      <c r="D16" t="s">
-        <v>308</v>
-      </c>
-      <c r="E16" t="s">
-        <v>309</v>
-      </c>
-      <c r="F16" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -4053,16 +4058,16 @@
         <v>33</v>
       </c>
       <c r="C17" t="s">
+        <v>338</v>
+      </c>
+      <c r="D17" t="s">
+        <v>307</v>
+      </c>
+      <c r="E17" t="s">
+        <v>308</v>
+      </c>
+      <c r="F17" t="s">
         <v>339</v>
-      </c>
-      <c r="D17" t="s">
-        <v>308</v>
-      </c>
-      <c r="E17" t="s">
-        <v>309</v>
-      </c>
-      <c r="F17" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -4073,16 +4078,16 @@
         <v>33</v>
       </c>
       <c r="C18" t="s">
+        <v>340</v>
+      </c>
+      <c r="D18" t="s">
+        <v>307</v>
+      </c>
+      <c r="E18" t="s">
+        <v>308</v>
+      </c>
+      <c r="F18" t="s">
         <v>341</v>
-      </c>
-      <c r="D18" t="s">
-        <v>308</v>
-      </c>
-      <c r="E18" t="s">
-        <v>309</v>
-      </c>
-      <c r="F18" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -4093,16 +4098,16 @@
         <v>33</v>
       </c>
       <c r="C19" t="s">
+        <v>342</v>
+      </c>
+      <c r="D19" t="s">
+        <v>307</v>
+      </c>
+      <c r="E19" t="s">
+        <v>308</v>
+      </c>
+      <c r="F19" t="s">
         <v>343</v>
-      </c>
-      <c r="D19" t="s">
-        <v>308</v>
-      </c>
-      <c r="E19" t="s">
-        <v>309</v>
-      </c>
-      <c r="F19" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -4113,16 +4118,16 @@
         <v>33</v>
       </c>
       <c r="C20" t="s">
+        <v>344</v>
+      </c>
+      <c r="D20" t="s">
+        <v>307</v>
+      </c>
+      <c r="E20" t="s">
+        <v>308</v>
+      </c>
+      <c r="F20" t="s">
         <v>345</v>
-      </c>
-      <c r="D20" t="s">
-        <v>308</v>
-      </c>
-      <c r="E20" t="s">
-        <v>309</v>
-      </c>
-      <c r="F20" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -4133,16 +4138,16 @@
         <v>33</v>
       </c>
       <c r="C21" t="s">
+        <v>346</v>
+      </c>
+      <c r="D21" t="s">
+        <v>307</v>
+      </c>
+      <c r="E21" t="s">
+        <v>308</v>
+      </c>
+      <c r="F21" t="s">
         <v>347</v>
-      </c>
-      <c r="D21" t="s">
-        <v>308</v>
-      </c>
-      <c r="E21" t="s">
-        <v>309</v>
-      </c>
-      <c r="F21" t="s">
-        <v>348</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -4153,16 +4158,16 @@
         <v>33</v>
       </c>
       <c r="C22" t="s">
+        <v>348</v>
+      </c>
+      <c r="D22" t="s">
+        <v>307</v>
+      </c>
+      <c r="E22" t="s">
+        <v>308</v>
+      </c>
+      <c r="F22" t="s">
         <v>349</v>
-      </c>
-      <c r="D22" t="s">
-        <v>308</v>
-      </c>
-      <c r="E22" t="s">
-        <v>309</v>
-      </c>
-      <c r="F22" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -4173,16 +4178,16 @@
         <v>33</v>
       </c>
       <c r="C23" t="s">
+        <v>350</v>
+      </c>
+      <c r="D23" t="s">
+        <v>307</v>
+      </c>
+      <c r="E23" t="s">
+        <v>308</v>
+      </c>
+      <c r="F23" t="s">
         <v>351</v>
-      </c>
-      <c r="D23" t="s">
-        <v>308</v>
-      </c>
-      <c r="E23" t="s">
-        <v>309</v>
-      </c>
-      <c r="F23" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
@@ -4193,16 +4198,16 @@
         <v>33</v>
       </c>
       <c r="C24" t="s">
+        <v>352</v>
+      </c>
+      <c r="D24" t="s">
         <v>353</v>
-      </c>
-      <c r="D24" t="s">
-        <v>354</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
@@ -4210,19 +4215,19 @@
         <v>214</v>
       </c>
       <c r="B25" t="s">
+        <v>355</v>
+      </c>
+      <c r="C25" t="s">
         <v>356</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>357</v>
-      </c>
-      <c r="D25" t="s">
-        <v>358</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
@@ -4230,19 +4235,19 @@
         <v>155</v>
       </c>
       <c r="B26" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C26" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D26" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
@@ -4250,19 +4255,19 @@
         <v>160</v>
       </c>
       <c r="B27" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C27" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D27" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
@@ -4270,19 +4275,19 @@
         <v>200</v>
       </c>
       <c r="B28" t="s">
+        <v>363</v>
+      </c>
+      <c r="C28" t="s">
         <v>364</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
         <v>365</v>
-      </c>
-      <c r="D28" t="s">
-        <v>366</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
@@ -4290,19 +4295,19 @@
         <v>184</v>
       </c>
       <c r="B29" t="s">
+        <v>367</v>
+      </c>
+      <c r="C29" t="s">
         <v>368</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>369</v>
-      </c>
-      <c r="D29" t="s">
-        <v>370</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
@@ -4310,19 +4315,19 @@
         <v>169</v>
       </c>
       <c r="B30" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C30" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D30" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
@@ -4330,19 +4335,19 @@
         <v>196</v>
       </c>
       <c r="B31" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C31" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D31" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
@@ -4350,19 +4355,19 @@
         <v>188</v>
       </c>
       <c r="B32" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C32" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D32" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
@@ -4370,19 +4375,19 @@
         <v>179</v>
       </c>
       <c r="B33" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C33" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D33" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -4390,19 +4395,19 @@
         <v>150</v>
       </c>
       <c r="B34" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C34" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D34" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
@@ -4410,19 +4415,19 @@
         <v>205</v>
       </c>
       <c r="B35" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C35" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D35" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
@@ -4430,19 +4435,19 @@
         <v>165</v>
       </c>
       <c r="B36" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C36" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D36" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
@@ -4450,19 +4455,19 @@
         <v>209</v>
       </c>
       <c r="B37" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C37" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D37" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
@@ -4470,19 +4475,19 @@
         <v>174</v>
       </c>
       <c r="B38" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C38" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="D38" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
@@ -4490,19 +4495,19 @@
         <v>192</v>
       </c>
       <c r="B39" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C39" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D39" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
@@ -4510,19 +4515,19 @@
         <v>220</v>
       </c>
       <c r="B40" t="s">
+        <v>386</v>
+      </c>
+      <c r="C40" t="s">
         <v>387</v>
       </c>
-      <c r="C40" t="s">
+      <c r="D40" t="s">
         <v>388</v>
-      </c>
-      <c r="D40" t="s">
-        <v>389</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
@@ -4530,19 +4535,19 @@
         <v>224</v>
       </c>
       <c r="B41" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C41" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="D41" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
@@ -4550,19 +4555,19 @@
         <v>228</v>
       </c>
       <c r="B42" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C42" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D42" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E42">
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -4570,19 +4575,19 @@
         <v>233</v>
       </c>
       <c r="B43" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C43" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D43" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
@@ -4590,19 +4595,19 @@
         <v>236</v>
       </c>
       <c r="B44" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C44" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D44" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E44">
         <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
@@ -4610,19 +4615,19 @@
         <v>240</v>
       </c>
       <c r="B45" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C45" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D45" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E45">
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
@@ -4633,16 +4638,16 @@
         <v>33</v>
       </c>
       <c r="C46" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D46" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E46" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F46" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
@@ -4650,19 +4655,19 @@
         <v>244</v>
       </c>
       <c r="B47" t="s">
+        <v>399</v>
+      </c>
+      <c r="C47" t="s">
         <v>400</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>401</v>
-      </c>
-      <c r="D47" t="s">
-        <v>402</v>
       </c>
       <c r="E47">
         <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -4673,16 +4678,16 @@
         <v>33</v>
       </c>
       <c r="C48" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D48" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
@@ -4693,16 +4698,16 @@
         <v>33</v>
       </c>
       <c r="C49" t="s">
+        <v>404</v>
+      </c>
+      <c r="D49" t="s">
+        <v>404</v>
+      </c>
+      <c r="E49" t="s">
+        <v>308</v>
+      </c>
+      <c r="F49" t="s">
         <v>405</v>
-      </c>
-      <c r="D49" t="s">
-        <v>405</v>
-      </c>
-      <c r="E49" t="s">
-        <v>309</v>
-      </c>
-      <c r="F49" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
@@ -4713,16 +4718,16 @@
         <v>33</v>
       </c>
       <c r="C50" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="D50" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
@@ -4733,16 +4738,16 @@
         <v>33</v>
       </c>
       <c r="C51" t="s">
+        <v>408</v>
+      </c>
+      <c r="D51" t="s">
         <v>409</v>
-      </c>
-      <c r="D51" t="s">
-        <v>410</v>
       </c>
       <c r="E51">
         <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
@@ -4750,19 +4755,19 @@
         <v>271</v>
       </c>
       <c r="B52" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C52" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="D52" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>
@@ -4784,7 +4789,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C1" t="s">
         <v>5</v>
@@ -4793,22 +4798,22 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>413</v>
+      </c>
+      <c r="F1" t="s">
         <v>414</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>415</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>416</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>417</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>418</v>
-      </c>
-      <c r="J1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -4816,22 +4821,22 @@
         <v>238</v>
       </c>
       <c r="B2" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C2" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D2" t="s">
         <v>261</v>
       </c>
       <c r="E2" t="s">
+        <v>420</v>
+      </c>
+      <c r="F2" t="s">
         <v>421</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>422</v>
-      </c>
-      <c r="G2" t="s">
-        <v>423</v>
       </c>
       <c r="H2">
         <v>600</v>
@@ -4848,22 +4853,22 @@
         <v>216</v>
       </c>
       <c r="B3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D3" t="s">
         <v>261</v>
       </c>
       <c r="E3" t="s">
+        <v>424</v>
+      </c>
+      <c r="F3" t="s">
         <v>425</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>426</v>
-      </c>
-      <c r="G3" t="s">
-        <v>427</v>
       </c>
       <c r="H3">
         <v>665</v>
@@ -4880,22 +4885,22 @@
         <v>222</v>
       </c>
       <c r="B4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C4" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D4" t="s">
         <v>261</v>
       </c>
       <c r="E4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F4" t="s">
         <v>429</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>430</v>
-      </c>
-      <c r="G4" t="s">
-        <v>431</v>
       </c>
       <c r="H4">
         <v>730</v>
@@ -4912,22 +4917,22 @@
         <v>230</v>
       </c>
       <c r="B5" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C5" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D5" t="s">
         <v>261</v>
       </c>
       <c r="E5" t="s">
+        <v>432</v>
+      </c>
+      <c r="F5" t="s">
         <v>433</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>434</v>
-      </c>
-      <c r="G5" t="s">
-        <v>435</v>
       </c>
       <c r="H5">
         <v>795</v>
@@ -4944,22 +4949,22 @@
         <v>234</v>
       </c>
       <c r="B6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C6" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D6" t="s">
         <v>261</v>
       </c>
       <c r="E6" t="s">
+        <v>436</v>
+      </c>
+      <c r="F6" t="s">
         <v>437</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>438</v>
-      </c>
-      <c r="G6" t="s">
-        <v>439</v>
       </c>
       <c r="H6">
         <v>860</v>
@@ -4976,22 +4981,22 @@
         <v>226</v>
       </c>
       <c r="B7" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D7" t="s">
         <v>261</v>
       </c>
       <c r="E7" t="s">
+        <v>440</v>
+      </c>
+      <c r="F7" t="s">
         <v>441</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>442</v>
-      </c>
-      <c r="G7" t="s">
-        <v>443</v>
       </c>
       <c r="H7">
         <v>925</v>
@@ -5008,22 +5013,22 @@
         <v>258</v>
       </c>
       <c r="B8" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C8" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D8" t="s">
         <v>261</v>
       </c>
       <c r="E8" t="s">
+        <v>444</v>
+      </c>
+      <c r="F8" t="s">
         <v>445</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>446</v>
-      </c>
-      <c r="G8" t="s">
-        <v>447</v>
       </c>
       <c r="H8">
         <v>990</v>
@@ -5040,22 +5045,22 @@
         <v>242</v>
       </c>
       <c r="B9" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C9" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D9" t="s">
         <v>244</v>
       </c>
       <c r="E9" t="s">
+        <v>448</v>
+      </c>
+      <c r="F9" t="s">
         <v>449</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>450</v>
-      </c>
-      <c r="G9" t="s">
-        <v>451</v>
       </c>
       <c r="H9">
         <v>660</v>
@@ -5072,22 +5077,22 @@
         <v>246</v>
       </c>
       <c r="B10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C10" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D10" t="s">
         <v>244</v>
       </c>
       <c r="E10" t="s">
+        <v>452</v>
+      </c>
+      <c r="F10" t="s">
         <v>453</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>454</v>
-      </c>
-      <c r="G10" t="s">
-        <v>455</v>
       </c>
       <c r="H10">
         <v>705</v>
@@ -5104,22 +5109,22 @@
         <v>250</v>
       </c>
       <c r="B11" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C11" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D11" t="s">
         <v>244</v>
       </c>
       <c r="E11" t="s">
+        <v>456</v>
+      </c>
+      <c r="F11" t="s">
+        <v>430</v>
+      </c>
+      <c r="G11" t="s">
         <v>457</v>
-      </c>
-      <c r="F11" t="s">
-        <v>431</v>
-      </c>
-      <c r="G11" t="s">
-        <v>458</v>
       </c>
       <c r="H11">
         <v>780</v>
@@ -5136,22 +5141,22 @@
         <v>254</v>
       </c>
       <c r="B12" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C12" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D12" t="s">
         <v>244</v>
       </c>
       <c r="E12" t="s">
+        <v>459</v>
+      </c>
+      <c r="F12" t="s">
         <v>460</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>461</v>
-      </c>
-      <c r="G12" t="s">
-        <v>462</v>
       </c>
       <c r="H12">
         <v>835</v>
@@ -5168,22 +5173,22 @@
         <v>278</v>
       </c>
       <c r="B13" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C13" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D13" t="s">
         <v>281</v>
       </c>
       <c r="E13" t="s">
+        <v>463</v>
+      </c>
+      <c r="F13" t="s">
+        <v>421</v>
+      </c>
+      <c r="G13" t="s">
         <v>464</v>
-      </c>
-      <c r="F13" t="s">
-        <v>422</v>
-      </c>
-      <c r="G13" t="s">
-        <v>465</v>
       </c>
       <c r="H13">
         <v>600</v>
@@ -5200,22 +5205,22 @@
         <v>273</v>
       </c>
       <c r="B14" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C14" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D14" t="s">
         <v>276</v>
       </c>
       <c r="E14" t="s">
+        <v>466</v>
+      </c>
+      <c r="F14" t="s">
+        <v>430</v>
+      </c>
+      <c r="G14" t="s">
         <v>467</v>
-      </c>
-      <c r="F14" t="s">
-        <v>431</v>
-      </c>
-      <c r="G14" t="s">
-        <v>468</v>
       </c>
       <c r="H14">
         <v>780</v>
@@ -5232,22 +5237,22 @@
         <v>283</v>
       </c>
       <c r="B15" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C15" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D15" t="s">
         <v>286</v>
       </c>
       <c r="E15" t="s">
+        <v>469</v>
+      </c>
+      <c r="F15" t="s">
         <v>470</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>471</v>
-      </c>
-      <c r="G15" t="s">
-        <v>472</v>
       </c>
       <c r="H15">
         <v>810</v>
@@ -5264,22 +5269,22 @@
         <v>283</v>
       </c>
       <c r="B16" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C16" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D16" t="s">
         <v>286</v>
       </c>
       <c r="E16" t="s">
+        <v>473</v>
+      </c>
+      <c r="F16" t="s">
+        <v>467</v>
+      </c>
+      <c r="G16" t="s">
         <v>474</v>
-      </c>
-      <c r="F16" t="s">
-        <v>468</v>
-      </c>
-      <c r="G16" t="s">
-        <v>475</v>
       </c>
       <c r="H16">
         <v>840</v>
@@ -5296,22 +5301,22 @@
         <v>288</v>
       </c>
       <c r="B17" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C17" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D17" t="s">
         <v>286</v>
       </c>
       <c r="E17" t="s">
+        <v>476</v>
+      </c>
+      <c r="F17" t="s">
         <v>477</v>
       </c>
-      <c r="F17" t="s">
+      <c r="G17" t="s">
         <v>478</v>
-      </c>
-      <c r="G17" t="s">
-        <v>479</v>
       </c>
       <c r="H17">
         <v>885</v>
@@ -5328,22 +5333,22 @@
         <v>290</v>
       </c>
       <c r="B18" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C18" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="D18" t="s">
         <v>286</v>
       </c>
       <c r="E18" t="s">
+        <v>480</v>
+      </c>
+      <c r="F18" t="s">
         <v>481</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>482</v>
-      </c>
-      <c r="G18" t="s">
-        <v>483</v>
       </c>
       <c r="H18">
         <v>915</v>
@@ -5360,22 +5365,22 @@
         <v>238</v>
       </c>
       <c r="B19" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C19" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D19" t="s">
         <v>261</v>
       </c>
       <c r="E19" t="s">
+        <v>484</v>
+      </c>
+      <c r="F19" t="s">
+        <v>421</v>
+      </c>
+      <c r="G19" t="s">
         <v>485</v>
-      </c>
-      <c r="F19" t="s">
-        <v>422</v>
-      </c>
-      <c r="G19" t="s">
-        <v>486</v>
       </c>
       <c r="H19">
         <v>600</v>
@@ -5392,22 +5397,22 @@
         <v>216</v>
       </c>
       <c r="B20" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C20" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D20" t="s">
         <v>261</v>
       </c>
       <c r="E20" t="s">
+        <v>487</v>
+      </c>
+      <c r="F20" t="s">
         <v>488</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>489</v>
-      </c>
-      <c r="G20" t="s">
-        <v>490</v>
       </c>
       <c r="H20">
         <v>645</v>
@@ -5424,22 +5429,22 @@
         <v>222</v>
       </c>
       <c r="B21" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C21" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D21" t="s">
         <v>261</v>
       </c>
       <c r="E21" t="s">
+        <v>491</v>
+      </c>
+      <c r="F21" t="s">
+        <v>450</v>
+      </c>
+      <c r="G21" t="s">
         <v>492</v>
-      </c>
-      <c r="F21" t="s">
-        <v>451</v>
-      </c>
-      <c r="G21" t="s">
-        <v>493</v>
       </c>
       <c r="H21">
         <v>690</v>
@@ -5456,22 +5461,22 @@
         <v>230</v>
       </c>
       <c r="B22" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="C22" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D22" t="s">
         <v>261</v>
       </c>
       <c r="E22" t="s">
+        <v>494</v>
+      </c>
+      <c r="F22" t="s">
         <v>495</v>
       </c>
-      <c r="F22" t="s">
-        <v>496</v>
-      </c>
       <c r="G22" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H22">
         <v>735</v>
@@ -5488,22 +5493,22 @@
         <v>234</v>
       </c>
       <c r="B23" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D23" t="s">
         <v>261</v>
       </c>
       <c r="E23" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F23" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G23" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H23">
         <v>780</v>
@@ -5520,22 +5525,22 @@
         <v>226</v>
       </c>
       <c r="B24" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C24" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D24" t="s">
         <v>261</v>
       </c>
       <c r="E24" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F24" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G24" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H24">
         <v>825</v>
@@ -5552,22 +5557,22 @@
         <v>258</v>
       </c>
       <c r="B25" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C25" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D25" t="s">
         <v>261</v>
       </c>
       <c r="E25" t="s">
+        <v>501</v>
+      </c>
+      <c r="F25" t="s">
+        <v>477</v>
+      </c>
+      <c r="G25" t="s">
         <v>502</v>
-      </c>
-      <c r="F25" t="s">
-        <v>478</v>
-      </c>
-      <c r="G25" t="s">
-        <v>503</v>
       </c>
       <c r="H25">
         <v>885</v>
@@ -5584,22 +5589,22 @@
         <v>263</v>
       </c>
       <c r="B26" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C26" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D26" t="s">
         <v>261</v>
       </c>
       <c r="E26" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F26" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="G26" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H26">
         <v>960</v>
@@ -5616,22 +5621,22 @@
         <v>242</v>
       </c>
       <c r="B27" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C27" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D27" t="s">
         <v>244</v>
       </c>
       <c r="E27" t="s">
+        <v>506</v>
+      </c>
+      <c r="F27" t="s">
+        <v>492</v>
+      </c>
+      <c r="G27" t="s">
         <v>507</v>
-      </c>
-      <c r="F27" t="s">
-        <v>493</v>
-      </c>
-      <c r="G27" t="s">
-        <v>508</v>
       </c>
       <c r="H27">
         <v>720</v>
@@ -5648,22 +5653,22 @@
         <v>254</v>
       </c>
       <c r="B28" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C28" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D28" t="s">
         <v>244</v>
       </c>
       <c r="E28" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F28" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G28" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H28">
         <v>780</v>
@@ -5680,22 +5685,22 @@
         <v>298</v>
       </c>
       <c r="B29" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C29" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D29" t="s">
         <v>244</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="F29" s="3">
         <v>0.64583333333333337</v>
       </c>
       <c r="G29" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H29">
         <v>930</v>
@@ -5712,22 +5717,22 @@
         <v>278</v>
       </c>
       <c r="B30" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C30" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D30" t="s">
         <v>281</v>
       </c>
       <c r="E30" t="s">
+        <v>463</v>
+      </c>
+      <c r="F30" t="s">
+        <v>421</v>
+      </c>
+      <c r="G30" t="s">
         <v>464</v>
-      </c>
-      <c r="F30" t="s">
-        <v>422</v>
-      </c>
-      <c r="G30" t="s">
-        <v>465</v>
       </c>
       <c r="H30">
         <v>600</v>
@@ -5744,22 +5749,22 @@
         <v>294</v>
       </c>
       <c r="B31" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="C31" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D31" t="s">
         <v>286</v>
       </c>
       <c r="E31" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F31" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="G31" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H31">
         <v>780</v>
@@ -5776,22 +5781,22 @@
         <v>294</v>
       </c>
       <c r="B32" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="C32" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D32" t="s">
         <v>286</v>
       </c>
       <c r="E32" t="s">
+        <v>469</v>
+      </c>
+      <c r="F32" t="s">
         <v>470</v>
       </c>
-      <c r="F32" t="s">
+      <c r="G32" t="s">
         <v>471</v>
-      </c>
-      <c r="G32" t="s">
-        <v>472</v>
       </c>
       <c r="H32">
         <v>810</v>
@@ -5808,22 +5813,22 @@
         <v>296</v>
       </c>
       <c r="B33" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="C33" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D33" t="s">
         <v>286</v>
       </c>
       <c r="E33" t="s">
+        <v>473</v>
+      </c>
+      <c r="F33" t="s">
+        <v>467</v>
+      </c>
+      <c r="G33" t="s">
         <v>474</v>
-      </c>
-      <c r="F33" t="s">
-        <v>468</v>
-      </c>
-      <c r="G33" t="s">
-        <v>475</v>
       </c>
       <c r="H33">
         <v>840</v>
@@ -5840,22 +5845,22 @@
         <v>296</v>
       </c>
       <c r="B34" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C34" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="D34" t="s">
         <v>286</v>
       </c>
       <c r="E34" t="s">
+        <v>517</v>
+      </c>
+      <c r="F34" t="s">
         <v>518</v>
       </c>
-      <c r="F34" t="s">
-        <v>519</v>
-      </c>
       <c r="G34" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H34">
         <v>870</v>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkytw\Desktop\GitHub\Home-Page\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4556A40-1A16-4524-A707-43EF2FB5C386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B18C5F9-F4EF-4565-B9BB-34E92ABD0E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8376" yWindow="2676" windowWidth="12648" windowHeight="11004" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mogiten" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,11 @@
     <sheet name="timetable" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="550">
   <si>
     <t>id</t>
   </si>
@@ -91,10 +90,11 @@
     <t>day1</t>
   </si>
   <si>
-    <t>いちご_x000D__x000D_
-ブルーベリー_x000D__x000D_
-ちょこ_x000D__x000D_
-キャラメル　　※値段は未定</t>
+    <t>いちご
+ブルーベリー
+チョコ
+キャラメル
+パンケーキ1つ 350円</t>
   </si>
   <si>
     <t>おいしいパンケーキ屋さん！1年生だけの有志団体です！可愛くて美味しいパンケーキをぜひ食べに来てください♡</t>
@@ -118,9 +118,6 @@
     <t>写真部では今年も棒餃子を販売します！平潟祭はこれ食えば間違いナシ！</t>
   </si>
   <si>
-    <t>food-oystars</t>
-  </si>
-  <si>
     <t>筋肉巻き</t>
   </si>
   <si>
@@ -130,7 +127,7 @@
     <t>loc-tent-04</t>
   </si>
   <si>
-    <t/>
+    <t>サンドイッチ　一つ300円</t>
   </si>
   <si>
     <t>food-compass</t>
@@ -178,13 +175,16 @@
     <t>loc-tent-07</t>
   </si>
   <si>
-    <t>food-mogi-shutten</t>
+    <t>フランクフルト　1本 250円</t>
+  </si>
+  <si>
+    <t>ジューシーで香ばしい絶品フランクフルトを販売！パリッと弾ける食感と熱々の肉汁がたまりません。食べ歩きに最適ですので、ぜひお立ち寄りください！</t>
   </si>
   <si>
     <t>やきそば</t>
   </si>
   <si>
-    <t>模擬店出店</t>
+    <t>平潟祭実行委員会</t>
   </si>
   <si>
     <t>loc-tent-08</t>
@@ -251,10 +251,23 @@
     <t>皆様ごきげんよう！KGUのFABULOUSなお嬢様が作るドリンクはいかが？抽選もあるから是非いらして頂戴！</t>
   </si>
   <si>
-    <t>food-ojosama-circle2</t>
+    <t>food-ojyosama-select</t>
+  </si>
+  <si>
+    <t>アパレル</t>
+  </si>
+  <si>
+    <t>OJYOSAMA SELECT</t>
   </si>
   <si>
     <t>loc-tent-12</t>
+  </si>
+  <si>
+    <t>服やグッズの販売
+2,499円（税込）～7,499円（税込）</t>
+  </si>
+  <si>
+    <t>皆様ごきげんよう。お嬢様セレクトのアパレルで、上品な毎日をお過ごしまくりあげてちょうだい！</t>
   </si>
   <si>
     <t>food-kashiwazaki-semi</t>
@@ -315,6 +328,9 @@
 缶ビール 1本 400円</t>
   </si>
   <si>
+    <t>子どもから大人までだいすき お得にたくさん食べられる5本セットがおすすめ おいしい焼き鳥食べに来てね</t>
+  </si>
+  <si>
     <t>food-tecky</t>
   </si>
   <si>
@@ -484,6 +500,18 @@
     <t>茶道部です！8号館横の茶室で抹茶とお菓子をご用意しています。ぜひお気軽にお越しください！</t>
   </si>
   <si>
+    <t>food-hanahaku</t>
+  </si>
+  <si>
+    <t>ワークショップ</t>
+  </si>
+  <si>
+    <t>花博（Expo部）</t>
+  </si>
+  <si>
+    <t>loc-3-zakuro</t>
+  </si>
+  <si>
     <t>culture-wandervogel-bu</t>
   </si>
   <si>
@@ -520,9 +548,6 @@
     <t>culture-meag</t>
   </si>
   <si>
-    <t>ワークショップ</t>
-  </si>
-  <si>
     <t>MEAG</t>
   </si>
   <si>
@@ -589,9 +614,6 @@
     <t>放送研究会KGUBでは放送にまつわる機材の展示・体験や仕掛けをご用意しています！ぜひお越しください！</t>
   </si>
   <si>
-    <t>culture-shinsengumi</t>
-  </si>
-  <si>
     <t>公演</t>
   </si>
   <si>
@@ -652,9 +674,6 @@
     <t>自作プラネタリウムで本物のような星空を再現！天文部スバルが皆さんを宇宙の世界へご案内します。</t>
   </si>
   <si>
-    <t>culture-tetsudo-bu</t>
-  </si>
-  <si>
     <t>作品展示・体験展示</t>
   </si>
   <si>
@@ -667,9 +686,6 @@
     <t>鉄道研究部です。部員自慢のNゲージコレクションや沢山のプラレール達が走り回るジオラマ展示がございます！他にも鉄道に関する様々な 展示を行います。大人の方もお子様も、是非ご来場下さい！</t>
   </si>
   <si>
-    <t>culture-oystars</t>
-  </si>
-  <si>
     <t>マッスルコンテスト</t>
   </si>
   <si>
@@ -706,7 +722,7 @@
     <t>音楽館</t>
   </si>
   <si>
-    <t>loc-7-201</t>
+    <t>loc-7-402</t>
   </si>
   <si>
     <t>アルティメット軽音部です 私たちは色んなジャンルの音楽を楽しんでいます！ぜひ気軽に見に来てください♪</t>
@@ -718,21 +734,21 @@
     <t>軽音楽部</t>
   </si>
   <si>
+    <t>loc-7-302</t>
+  </si>
+  <si>
+    <t>部員が全力で演奏！熱いライブをお楽しみください！</t>
+  </si>
+  <si>
+    <t>music-dendenmushi-bu</t>
+  </si>
+  <si>
+    <t>でんでんむ詩部</t>
+  </si>
+  <si>
     <t>loc-7-203</t>
   </si>
   <si>
-    <t>部員が全力で演奏！熱いライブをお楽しみください！</t>
-  </si>
-  <si>
-    <t>music-dendenmushi-bu</t>
-  </si>
-  <si>
-    <t>でんでんむ詩部</t>
-  </si>
-  <si>
-    <t>loc-7-301</t>
-  </si>
-  <si>
     <t>私たちはジャンル問わず様々なバンドを演奏します！みんなで作る最高のライブをぜひ見に来てください！</t>
   </si>
   <si>
@@ -754,7 +770,7 @@
     <t>ウエスタン部</t>
   </si>
   <si>
-    <t>loc-7-401</t>
+    <t>loc-7-202</t>
   </si>
   <si>
     <t>こんにちはウエスタン部です!! 私達は主に洋楽をメインとした軽音楽部です! 普段洋楽を聞かない人でもめちゃくちゃ楽しめるのでぜひ遊びに来てください！！</t>
@@ -900,9 +916,6 @@
     <t>music-pipe-organ-fujishiro</t>
   </si>
   <si>
-    <t>パイプオルガン特別演奏</t>
-  </si>
-  <si>
     <t>パイプオルガン：藤城眞美</t>
   </si>
   <si>
@@ -948,661 +961,10 @@
     <t>宮世琉弥トークショー × 平潟祭</t>
   </si>
   <si>
+    <t>平潟祭実行委員会 芸能</t>
+  </si>
+  <si>
     <t>芸能</t>
-  </si>
-  <si>
-    <t>buildingId</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>building</t>
-  </si>
-  <si>
-    <t>floor</t>
-  </si>
-  <si>
-    <t>room</t>
-  </si>
-  <si>
-    <t>テントNo.1</t>
-  </si>
-  <si>
-    <t>テント</t>
-  </si>
-  <si>
-    <t>屋外</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>テントNo.2</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>テントNo.3</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>テントNo.4</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>テントNo.5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>テントNo.6</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>テントNo.7</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>テントNo.8</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>テントNo.9</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>テントNo.10</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>テントNo.11</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>テントNo.12</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>テントNo.13</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>テントNo.14</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>テントNo.15</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>テントNo.16</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>テントNo.17</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>テントNo.18</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>テントNo.19</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>テントNo.20</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>テントNo.21</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>テントNo.22</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>8号館横 茶室</t>
-  </si>
-  <si>
-    <t>茶室</t>
-  </si>
-  <si>
-    <t>茶室（専用個室）</t>
-  </si>
-  <si>
-    <t>no3</t>
-  </si>
-  <si>
-    <t>3-204</t>
-  </si>
-  <si>
-    <t>3号館</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>3-205</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>3-206</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>no6</t>
-  </si>
-  <si>
-    <t>6-101</t>
-  </si>
-  <si>
-    <t>6号館</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>no8</t>
-  </si>
-  <si>
-    <t>8-101</t>
-  </si>
-  <si>
-    <t>8号館</t>
-  </si>
-  <si>
-    <t>8-102</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>8-103・105</t>
-  </si>
-  <si>
-    <t>103・105</t>
-  </si>
-  <si>
-    <t>8-201</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>8-203</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>8-204</t>
-  </si>
-  <si>
-    <t>8-205</t>
-  </si>
-  <si>
-    <t>8-206</t>
-  </si>
-  <si>
-    <t>8-305</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>8-306</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>カフェポンド前</t>
-  </si>
-  <si>
-    <t>no7</t>
-  </si>
-  <si>
-    <t>7-201</t>
-  </si>
-  <si>
-    <t>7号館</t>
-  </si>
-  <si>
-    <t>7-203</t>
-  </si>
-  <si>
-    <t>7-301</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>7-303</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>7-401</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>7-403</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>屋外ステージ</t>
-  </si>
-  <si>
-    <t>scc</t>
-  </si>
-  <si>
-    <t>SCC 4階 ベンネットホール</t>
-  </si>
-  <si>
-    <t>SCC棟</t>
-  </si>
-  <si>
-    <t>ベンネットホール（屋内ステージ）</t>
-  </si>
-  <si>
-    <t>体育館</t>
-  </si>
-  <si>
-    <t>1号館前（セブンイレブン前）</t>
-  </si>
-  <si>
-    <t>1号館前広場</t>
-  </si>
-  <si>
-    <t>チャペル</t>
-  </si>
-  <si>
-    <t>礼拝堂</t>
-  </si>
-  <si>
-    <t>クラブハウス626</t>
-  </si>
-  <si>
-    <t>クラブハウス棟</t>
-  </si>
-  <si>
-    <t>626室</t>
-  </si>
-  <si>
-    <t>学生支援室</t>
-  </si>
-  <si>
-    <t>slotId</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>startTime</t>
-  </si>
-  <si>
-    <t>endTime</t>
-  </si>
-  <si>
-    <t>startMinutes</t>
-  </si>
-  <si>
-    <t>endMinutes</t>
-  </si>
-  <si>
-    <t>durationMinutes</t>
-  </si>
-  <si>
-    <t>tt-d1-01</t>
-  </si>
-  <si>
-    <t>10:00～10:50</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>tt-d1-02</t>
-  </si>
-  <si>
-    <t>11:05～11:55</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>tt-d1-03</t>
-  </si>
-  <si>
-    <t>12:10～13:00</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>tt-d1-04</t>
-  </si>
-  <si>
-    <t>13:15～14:05</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>tt-d1-05</t>
-  </si>
-  <si>
-    <t>14:20～15:10</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>tt-d1-06</t>
-  </si>
-  <si>
-    <t>15:25～16:15</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>tt-d1-07</t>
-  </si>
-  <si>
-    <t>16:30～17:00</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>tt-d1-08</t>
-  </si>
-  <si>
-    <t>11:00～11:30</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>tt-d1-09</t>
-  </si>
-  <si>
-    <t>11:45～12:45</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>tt-d1-10</t>
-  </si>
-  <si>
-    <t>13:00～13:40</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>tt-d1-11</t>
-  </si>
-  <si>
-    <t>13:55～14:25</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>tt-d1-12</t>
-  </si>
-  <si>
-    <t>10:00～16:00</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>tt-d1-13</t>
-  </si>
-  <si>
-    <t>13:00～14:00</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>tt-d1-14</t>
-  </si>
-  <si>
-    <t>13:30～13:45</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>tt-d1-15</t>
-  </si>
-  <si>
-    <t>14:00～14:15</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>tt-d1-16</t>
-  </si>
-  <si>
-    <t>14:45～15:00</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>tt-d1-17</t>
-  </si>
-  <si>
-    <t>15:15～15:30</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>tt-d2-01</t>
-  </si>
-  <si>
-    <t>10:00～10:30</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>tt-d2-02</t>
-  </si>
-  <si>
-    <t>10:45～11:15</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>tt-d2-03</t>
-  </si>
-  <si>
-    <t>11:30～12:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>tt-d2-04</t>
-  </si>
-  <si>
-    <t>12:15～12:45</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>tt-d2-05</t>
-  </si>
-  <si>
-    <t>13:00～13:30</t>
-  </si>
-  <si>
-    <t>tt-d2-06</t>
-  </si>
-  <si>
-    <t>13:45～14:15</t>
-  </si>
-  <si>
-    <t>tt-d2-07</t>
-  </si>
-  <si>
-    <t>14:45～15:45</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>tt-d2-08</t>
-  </si>
-  <si>
-    <t>16:00～17:00</t>
-  </si>
-  <si>
-    <t>tt-d2-09</t>
-  </si>
-  <si>
-    <t>12:00～12:30</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>tt-d2-10</t>
-  </si>
-  <si>
-    <t>tt-d2-11</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>tt-d2-12</t>
-  </si>
-  <si>
-    <t>tt-d2-13</t>
-  </si>
-  <si>
-    <t>13:00～13:15</t>
-  </si>
-  <si>
-    <t>tt-d2-14</t>
-  </si>
-  <si>
-    <t>tt-d2-15</t>
-  </si>
-  <si>
-    <t>tt-d2-16</t>
-  </si>
-  <si>
-    <t>14:30～14:45</t>
-  </si>
-  <si>
-    <t>14:30</t>
   </si>
   <si>
     <t>① 10/1(木) 12:30～17:00
@@ -1622,7 +984,6 @@
 ●3歳以下のお子様はご入場いただけません。4歳以上のお客様はチケットが必 要になります。
 ●車椅子をご利用のお客様1名につき、付き添いの方1名までご入場いただけます。車椅子をご利用のお客様、付き添いの方ともにチケットが必要となります。車椅子席は5席となります。以下までお問い合わせください。
 問い合わせ先：hirakata.geinou@gmail.com</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>宮世琉弥トークショー（全席指定・有料チケット制）開場15:30 開演16:30
@@ -1634,76 +995,759 @@
 ※ 転売が確認されたチケットは無効となり、ご入場をお断りいたします。その際の返金には応じかねます。
 ※ 公式以外のルートで購入されたチケットに関するトラブルについて、当学園祭実行委員会は一切の責任を負いません。
 ※ 出演者への直接のプレゼント、差し入れはできません。プレゼントボックスを設置いたします。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>day1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>day2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF79C0FF"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>開場</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF79C0FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">15:30 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF79C0FF"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>開演</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF79C0FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>16:30</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>平潟祭実行委員会 芸能</t>
-    <rPh sb="9" eb="11">
-      <t>ゲイノウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>buildingId</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>building</t>
+  </si>
+  <si>
+    <t>floor</t>
+  </si>
+  <si>
+    <t>room</t>
+  </si>
+  <si>
+    <t>テントNo.1</t>
+  </si>
+  <si>
+    <t>テント</t>
+  </si>
+  <si>
+    <t>屋外</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>テントNo.2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>テントNo.3</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>テントNo.4</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>テントNo.5</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>テントNo.6</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>テントNo.7</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>テントNo.8</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>テントNo.9</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>テントNo.10</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>テントNo.11</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>テントNo.12</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>テントNo.13</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>テントNo.14</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>テントNo.15</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>テントNo.16</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>テントNo.17</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>テントNo.18</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>テントNo.19</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>テントNo.20</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>テントNo.21</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>テントNo.22</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>8号館横 茶室</t>
+  </si>
+  <si>
+    <t>茶室</t>
+  </si>
+  <si>
+    <t>茶室（専用個室）</t>
+  </si>
+  <si>
+    <t>no3</t>
+  </si>
+  <si>
+    <t>3-204</t>
+  </si>
+  <si>
+    <t>3号館</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>3-205</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>3-206</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>no6</t>
+  </si>
+  <si>
+    <t>6-101</t>
+  </si>
+  <si>
+    <t>6号館</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>no8</t>
+  </si>
+  <si>
+    <t>8-101</t>
+  </si>
+  <si>
+    <t>8号館</t>
+  </si>
+  <si>
+    <t>8-102</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>8-103・105</t>
+  </si>
+  <si>
+    <t>103・105</t>
+  </si>
+  <si>
+    <t>8-201</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>8-203</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>8-204</t>
+  </si>
+  <si>
+    <t>8-205</t>
+  </si>
+  <si>
+    <t>8-206</t>
+  </si>
+  <si>
+    <t>8-305</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>8-306</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>カフェポンド前</t>
+  </si>
+  <si>
+    <t>loc-7-201</t>
+  </si>
+  <si>
+    <t>no7</t>
+  </si>
+  <si>
+    <t>7-201</t>
+  </si>
+  <si>
+    <t>7号館</t>
+  </si>
+  <si>
+    <t>7-203</t>
+  </si>
+  <si>
+    <t>loc-7-301</t>
+  </si>
+  <si>
+    <t>7-301</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>7-303</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>loc-7-401</t>
+  </si>
+  <si>
+    <t>7-401</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>7-403</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>屋外ステージ</t>
+  </si>
+  <si>
+    <t>scc</t>
+  </si>
+  <si>
+    <t>SCC 4階 ベンネットホール</t>
+  </si>
+  <si>
+    <t>SCC棟</t>
+  </si>
+  <si>
+    <t>ベンネットホール（屋内ステージ）</t>
+  </si>
+  <si>
+    <t>体育館</t>
+  </si>
+  <si>
+    <t>1号館前（セブンイレブン前）</t>
+  </si>
+  <si>
+    <t>1号館前広場</t>
+  </si>
+  <si>
+    <t>チャペル</t>
+  </si>
+  <si>
+    <t>礼拝堂</t>
+  </si>
+  <si>
+    <t>クラブハウス626</t>
+  </si>
+  <si>
+    <t>クラブハウス棟</t>
+  </si>
+  <si>
+    <t>626室</t>
+  </si>
+  <si>
+    <t>学生支援室</t>
+  </si>
+  <si>
+    <t>3号館食堂ザクロ</t>
+  </si>
+  <si>
+    <t>食堂ザクロ</t>
+  </si>
+  <si>
+    <t>7-202</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>7-402</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>7-302</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>slotId</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>startTime</t>
+  </si>
+  <si>
+    <t>endTime</t>
+  </si>
+  <si>
+    <t>startMinutes</t>
+  </si>
+  <si>
+    <t>endMinutes</t>
+  </si>
+  <si>
+    <t>durationMinutes</t>
+  </si>
+  <si>
+    <t>tt-d1-01</t>
+  </si>
+  <si>
+    <t>10:00～10:50</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>tt-d1-02</t>
+  </si>
+  <si>
+    <t>11:05～11:55</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>tt-d1-03</t>
+  </si>
+  <si>
+    <t>12:10～13:00</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>tt-d1-04</t>
+  </si>
+  <si>
+    <t>13:15～14:05</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>tt-d1-05</t>
+  </si>
+  <si>
+    <t>14:20～15:10</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>tt-d1-06</t>
+  </si>
+  <si>
+    <t>15:25～16:15</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>tt-d1-07</t>
+  </si>
+  <si>
+    <t>16:30～17:00</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>tt-d1-08</t>
+  </si>
+  <si>
+    <t>11:00～11:30</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>tt-d1-09</t>
+  </si>
+  <si>
+    <t>11:45～12:45</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>tt-d1-10</t>
+  </si>
+  <si>
+    <t>13:00～13:40</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>tt-d1-11</t>
+  </si>
+  <si>
+    <t>13:55～14:25</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>tt-d1-12</t>
+  </si>
+  <si>
+    <t>10:00～16:00</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>tt-d1-13</t>
+  </si>
+  <si>
+    <t>13:00～14:00</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>tt-d1-14</t>
+  </si>
+  <si>
+    <t>13:30～13:45</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>tt-d1-15</t>
+  </si>
+  <si>
+    <t>14:00～14:15</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>tt-d1-16</t>
+  </si>
+  <si>
+    <t>14:45～15:00</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>tt-d1-17</t>
+  </si>
+  <si>
+    <t>15:15～15:30</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>tt-d2-01</t>
+  </si>
+  <si>
+    <t>10:00～10:35</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>tt-d2-02</t>
+  </si>
+  <si>
+    <t>10:50～11:25</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>tt-d2-03</t>
+  </si>
+  <si>
+    <t>11:40～12:15</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>tt-d2-04</t>
+  </si>
+  <si>
+    <t>12:30～13:05</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>tt-d2-05</t>
+  </si>
+  <si>
+    <t>13:20～13:55</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>tt-d2-06</t>
+  </si>
+  <si>
+    <t>14:10～14:45</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>tt-d2-07</t>
+  </si>
+  <si>
+    <t>15:15～15:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>tt-d2-08</t>
+  </si>
+  <si>
+    <t>16:00～17:00</t>
+  </si>
+  <si>
+    <t>tt-d2-09</t>
+  </si>
+  <si>
+    <t>12:00～12:30</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>tt-d2-10</t>
+  </si>
+  <si>
+    <t>13:00～13:30</t>
+  </si>
+  <si>
+    <t>tt-d2-11</t>
+  </si>
+  <si>
+    <t>開場15:30 開演16:30</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>tt-d2-12</t>
+  </si>
+  <si>
+    <t>tt-d2-13</t>
+  </si>
+  <si>
+    <t>13:00～13:15</t>
+  </si>
+  <si>
+    <t>tt-d2-14</t>
+  </si>
+  <si>
+    <t>tt-d2-15</t>
+  </si>
+  <si>
+    <t>tt-d2-16</t>
+  </si>
+  <si>
+    <t>14:30～14:45</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>food-oystars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>culture-oystars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>food-mogi-shutten</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>culture-shinsengumi</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>culture-tetsudo-bu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>music-jazz-bu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チャペルコンサート</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="6"/>
@@ -1711,26 +1755,6 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF79C0FF"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF79C0FF"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF79C0FF"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1741,7 +1765,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1749,25 +1773,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1854,7 +1889,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1889,7 +1923,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1924,16 +1957,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -2055,78 +2092,49 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="74.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="255.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2210,111 +2218,108 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>543</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" t="s">
         <v>38</v>
-      </c>
-      <c r="H6" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" t="s">
         <v>40</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
         <v>44</v>
-      </c>
-      <c r="H7" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
         <v>46</v>
-      </c>
-      <c r="B8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" t="s">
-        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>545</v>
       </c>
       <c r="B9" t="s">
         <v>50</v>
@@ -2421,296 +2426,296 @@
         <v>73</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="H16" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="H17" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H18" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H19" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="H20" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="H21" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="H22" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="H23" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
@@ -2719,2124 +2724,2127 @@
         <v>58</v>
       </c>
       <c r="F24" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G24" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="H24" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C25" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="H25" t="s">
-        <v>145</v>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B26" t="s">
+        <v>152</v>
+      </c>
+      <c r="C26" t="s">
+        <v>153</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>154</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:H25" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="198.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
       <c r="B4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D4" t="s">
         <v>158</v>
       </c>
-      <c r="C4" t="s">
-        <v>159</v>
-      </c>
-      <c r="D4" t="s">
-        <v>149</v>
-      </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E6" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E8" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>181</v>
+        <v>546</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E9" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E10" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B11" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E11" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C12" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E12" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="B13" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C13" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E13" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>547</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E14" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>544</v>
       </c>
       <c r="B15" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E15" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B16" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C16" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="E16" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:G16" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="145.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>227</v>
+      </c>
+      <c r="B3" t="s">
         <v>222</v>
       </c>
-      <c r="B3" t="s">
-        <v>217</v>
-      </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="D3" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D4" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>548</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D5" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E5" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D6" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E6" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B7" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D7" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B8" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E8" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B9" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="C9" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D9" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E9" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B10" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="C10" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D10" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E10" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B11" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C11" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="D11" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B12" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C12" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D12" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E12" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B13" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C13" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="D13" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E13" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="F13" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G13" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B14" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="C14" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="D14" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E14" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B15" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C15" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D15" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E15" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B16" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="C16" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="D16" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E16" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B17" t="s">
-        <v>284</v>
+        <v>549</v>
       </c>
       <c r="C17" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="D17" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E17" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B18" t="s">
-        <v>284</v>
+        <v>549</v>
       </c>
       <c r="C18" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E18" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>294</v>
+      </c>
+      <c r="B19" t="s">
+        <v>295</v>
+      </c>
+      <c r="C19" t="s">
+        <v>296</v>
+      </c>
+      <c r="D19" t="s">
+        <v>224</v>
+      </c>
+      <c r="E19" t="s">
         <v>290</v>
-      </c>
-      <c r="B19" t="s">
-        <v>291</v>
-      </c>
-      <c r="C19" t="s">
-        <v>292</v>
-      </c>
-      <c r="D19" t="s">
-        <v>219</v>
-      </c>
-      <c r="E19" t="s">
-        <v>286</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B20" t="s">
-        <v>284</v>
+        <v>549</v>
       </c>
       <c r="C20" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D20" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E20" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F20" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G20" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B21" t="s">
-        <v>284</v>
+        <v>549</v>
       </c>
       <c r="C21" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="D21" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="E21" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="F21" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="G21" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:G21" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="5.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.09765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="64.5" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="316.8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C2" t="s">
-        <v>524</v>
+        <v>304</v>
       </c>
       <c r="D2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="E2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="F2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>520</v>
+        <v>142</v>
+      </c>
+      <c r="G2" t="s">
+        <v>306</v>
+      </c>
+      <c r="H2" t="s">
+        <v>307</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:H1 A2:B2 D2:F2" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="25.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F1" t="s">
-        <v>305</v>
+      <c r="B1" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
-        <v>33</v>
-      </c>
       <c r="C2" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="D2" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E2" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F2" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
       <c r="C3" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D3" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E3" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F3" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>26</v>
       </c>
-      <c r="B4" t="s">
-        <v>33</v>
-      </c>
       <c r="C4" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="D4" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E4" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F4" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
+        <v>321</v>
+      </c>
+      <c r="D5" t="s">
         <v>314</v>
       </c>
-      <c r="D5" t="s">
-        <v>307</v>
-      </c>
       <c r="E5" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F5" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="D6" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E6" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F6" t="s">
-        <v>317</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="D7" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E7" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F7" t="s">
-        <v>319</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="D8" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E8" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F8" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>52</v>
       </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
       <c r="C9" t="s">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="D9" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E9" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F9" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>58</v>
       </c>
-      <c r="B10" t="s">
-        <v>33</v>
-      </c>
       <c r="C10" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D10" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E10" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F10" t="s">
-        <v>325</v>
+        <v>332</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>64</v>
       </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
       <c r="C11" t="s">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="D11" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E11" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F11" t="s">
-        <v>327</v>
+        <v>334</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>70</v>
       </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
       <c r="C12" t="s">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="D12" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E12" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F12" t="s">
-        <v>329</v>
+        <v>336</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B13" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="D13" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E13" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F13" t="s">
-        <v>331</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="D14" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E14" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F14" t="s">
-        <v>333</v>
+        <v>340</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="D15" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E15" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F15" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="D16" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E16" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F16" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="D17" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E17" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F17" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="D18" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E18" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F18" t="s">
-        <v>341</v>
+        <v>348</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="D19" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E19" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F19" t="s">
-        <v>343</v>
+        <v>350</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" t="s">
-        <v>33</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="D20" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E20" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F20" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>119</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="D21" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E21" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F21" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="C22" t="s">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="D22" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E22" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F22" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="D23" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="E23" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F23" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B24" t="s">
-        <v>33</v>
+        <v>148</v>
       </c>
       <c r="C24" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="D24" t="s">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="B25" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C25" t="s">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="D25" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="B26" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C26" t="s">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="D26" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B27" t="s">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="C27" t="s">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="D27" t="s">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="B28" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C28" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="D28" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B29" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C29" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="D29" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B30" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C30" t="s">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="D30" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B31" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C31" t="s">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="D31" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>373</v>
+        <v>380</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B32" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C32" t="s">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="D32" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="B33" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C33" t="s">
+        <v>383</v>
+      </c>
+      <c r="D33" t="s">
         <v>376</v>
-      </c>
-      <c r="D33" t="s">
-        <v>369</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="B34" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C34" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="D34" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>358</v>
+        <v>365</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B35" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C35" t="s">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="D35" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>360</v>
+        <v>367</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B36" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C36" t="s">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="D36" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="B37" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C37" t="s">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="D37" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>382</v>
+        <v>389</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B38" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="C38" t="s">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="D38" t="s">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="C39" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="D39" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>220</v>
+        <v>393</v>
       </c>
       <c r="B40" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C40" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D40" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="B41" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C41" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="D41" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>377</v>
+        <v>384</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>228</v>
+        <v>398</v>
       </c>
       <c r="B42" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C42" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="D42" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E42">
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B43" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C43" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="D43" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>403</v>
       </c>
       <c r="B44" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C44" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="D44" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E44">
         <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B45" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C45" t="s">
+        <v>406</v>
+      </c>
+      <c r="D45" t="s">
         <v>396</v>
-      </c>
-      <c r="D45" t="s">
-        <v>388</v>
       </c>
       <c r="E45">
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>261</v>
-      </c>
-      <c r="B46" t="s">
-        <v>33</v>
+        <v>266</v>
       </c>
       <c r="C46" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="D46" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="E46" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F46" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="B47" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="C47" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="D47" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="E47">
         <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>281</v>
-      </c>
-      <c r="B48" t="s">
-        <v>33</v>
+        <v>286</v>
       </c>
       <c r="C48" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="D48" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>276</v>
-      </c>
-      <c r="B49" t="s">
-        <v>33</v>
+        <v>281</v>
       </c>
       <c r="C49" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="D49" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="E49" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="F49" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>286</v>
-      </c>
-      <c r="B50" t="s">
-        <v>33</v>
+        <v>290</v>
       </c>
       <c r="C50" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="D50" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>266</v>
-      </c>
-      <c r="B51" t="s">
-        <v>33</v>
+        <v>271</v>
       </c>
       <c r="C51" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="D51" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="E51">
         <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B52" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C52" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="D52" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>411</v>
+        <v>421</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>154</v>
+      </c>
+      <c r="B53" t="s">
+        <v>362</v>
+      </c>
+      <c r="C53" t="s">
+        <v>422</v>
+      </c>
+      <c r="D53" t="s">
+        <v>364</v>
+      </c>
+      <c r="E53" t="s">
+        <v>316</v>
+      </c>
+      <c r="F53" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>241</v>
+      </c>
+      <c r="B54" t="s">
+        <v>394</v>
+      </c>
+      <c r="C54" t="s">
+        <v>424</v>
+      </c>
+      <c r="D54" t="s">
+        <v>396</v>
+      </c>
+      <c r="E54" t="s">
+        <v>318</v>
+      </c>
+      <c r="F54" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>225</v>
+      </c>
+      <c r="B55" t="s">
+        <v>394</v>
+      </c>
+      <c r="C55" t="s">
+        <v>426</v>
+      </c>
+      <c r="D55" t="s">
+        <v>396</v>
+      </c>
+      <c r="E55" t="s">
+        <v>322</v>
+      </c>
+      <c r="F55" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>229</v>
+      </c>
+      <c r="B56" t="s">
+        <v>394</v>
+      </c>
+      <c r="C56" t="s">
+        <v>428</v>
+      </c>
+      <c r="D56" t="s">
+        <v>396</v>
+      </c>
+      <c r="E56" t="s">
+        <v>320</v>
+      </c>
+      <c r="F56" t="s">
+        <v>429</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:F52" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
-        <v>413</v>
-      </c>
-      <c r="F1" t="s">
-        <v>414</v>
-      </c>
-      <c r="G1" t="s">
-        <v>415</v>
-      </c>
-      <c r="H1" t="s">
-        <v>416</v>
-      </c>
-      <c r="I1" t="s">
-        <v>417</v>
-      </c>
-      <c r="J1" t="s">
-        <v>418</v>
+      <c r="E1" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B2" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="C2" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E2" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="F2" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="G2" t="s">
-        <v>422</v>
+        <v>440</v>
       </c>
       <c r="H2">
         <v>600</v>
@@ -4850,25 +4858,25 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B3" t="s">
-        <v>423</v>
+        <v>441</v>
       </c>
       <c r="C3" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E3" t="s">
-        <v>424</v>
+        <v>442</v>
       </c>
       <c r="F3" t="s">
-        <v>425</v>
+        <v>443</v>
       </c>
       <c r="G3" t="s">
-        <v>426</v>
+        <v>444</v>
       </c>
       <c r="H3">
         <v>665</v>
@@ -4882,25 +4890,25 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
-        <v>427</v>
+        <v>445</v>
       </c>
       <c r="C4" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E4" t="s">
-        <v>428</v>
+        <v>446</v>
       </c>
       <c r="F4" t="s">
-        <v>429</v>
+        <v>447</v>
       </c>
       <c r="G4" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="H4">
         <v>730</v>
@@ -4914,25 +4922,25 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B5" t="s">
-        <v>431</v>
+        <v>449</v>
       </c>
       <c r="C5" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E5" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="F5" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="G5" t="s">
-        <v>434</v>
+        <v>452</v>
       </c>
       <c r="H5">
         <v>795</v>
@@ -4946,25 +4954,25 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B6" t="s">
-        <v>435</v>
+        <v>453</v>
       </c>
       <c r="C6" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E6" t="s">
-        <v>436</v>
+        <v>454</v>
       </c>
       <c r="F6" t="s">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="G6" t="s">
-        <v>438</v>
+        <v>456</v>
       </c>
       <c r="H6">
         <v>860</v>
@@ -4978,25 +4986,25 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B7" t="s">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C7" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E7" t="s">
-        <v>440</v>
+        <v>458</v>
       </c>
       <c r="F7" t="s">
-        <v>441</v>
+        <v>459</v>
       </c>
       <c r="G7" t="s">
-        <v>442</v>
+        <v>460</v>
       </c>
       <c r="H7">
         <v>925</v>
@@ -5010,25 +5018,25 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B8" t="s">
-        <v>443</v>
+        <v>461</v>
       </c>
       <c r="C8" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E8" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="F8" t="s">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="G8" t="s">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="H8">
         <v>990</v>
@@ -5042,25 +5050,25 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B9" t="s">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="C9" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E9" t="s">
-        <v>448</v>
+        <v>466</v>
       </c>
       <c r="F9" t="s">
-        <v>449</v>
+        <v>467</v>
       </c>
       <c r="G9" t="s">
-        <v>450</v>
+        <v>468</v>
       </c>
       <c r="H9">
         <v>660</v>
@@ -5074,25 +5082,25 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="B10" t="s">
-        <v>451</v>
+        <v>469</v>
       </c>
       <c r="C10" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E10" t="s">
-        <v>452</v>
+        <v>470</v>
       </c>
       <c r="F10" t="s">
-        <v>453</v>
+        <v>471</v>
       </c>
       <c r="G10" t="s">
-        <v>454</v>
+        <v>472</v>
       </c>
       <c r="H10">
         <v>705</v>
@@ -5106,25 +5114,25 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="B11" t="s">
-        <v>455</v>
+        <v>473</v>
       </c>
       <c r="C11" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E11" t="s">
-        <v>456</v>
+        <v>474</v>
       </c>
       <c r="F11" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="G11" t="s">
-        <v>457</v>
+        <v>475</v>
       </c>
       <c r="H11">
         <v>780</v>
@@ -5138,25 +5146,25 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B12" t="s">
-        <v>458</v>
+        <v>476</v>
       </c>
       <c r="C12" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E12" t="s">
-        <v>459</v>
+        <v>477</v>
       </c>
       <c r="F12" t="s">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="G12" t="s">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="H12">
         <v>835</v>
@@ -5170,25 +5178,25 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B13" t="s">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="C13" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E13" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="F13" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="G13" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="H13">
         <v>600</v>
@@ -5202,25 +5210,25 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B14" t="s">
-        <v>465</v>
+        <v>483</v>
       </c>
       <c r="C14" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E14" t="s">
-        <v>466</v>
+        <v>484</v>
       </c>
       <c r="F14" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="G14" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="H14">
         <v>780</v>
@@ -5234,25 +5242,25 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B15" t="s">
-        <v>468</v>
+        <v>486</v>
       </c>
       <c r="C15" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E15" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="F15" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="G15" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="H15">
         <v>810</v>
@@ -5266,25 +5274,25 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="B16" t="s">
-        <v>472</v>
+        <v>490</v>
       </c>
       <c r="C16" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E16" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="F16" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="G16" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="H16">
         <v>840</v>
@@ -5298,25 +5306,25 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B17" t="s">
-        <v>475</v>
+        <v>493</v>
       </c>
       <c r="C17" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E17" t="s">
-        <v>476</v>
+        <v>494</v>
       </c>
       <c r="F17" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="G17" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="H17">
         <v>885</v>
@@ -5330,25 +5338,25 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>294</v>
+      </c>
+      <c r="B18" t="s">
+        <v>497</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
         <v>290</v>
       </c>
-      <c r="B18" t="s">
-        <v>479</v>
-      </c>
-      <c r="C18" t="s">
-        <v>521</v>
-      </c>
-      <c r="D18" t="s">
-        <v>286</v>
-      </c>
       <c r="E18" t="s">
-        <v>480</v>
+        <v>498</v>
       </c>
       <c r="F18" t="s">
-        <v>481</v>
+        <v>499</v>
       </c>
       <c r="G18" t="s">
-        <v>482</v>
+        <v>500</v>
       </c>
       <c r="H18">
         <v>915</v>
@@ -5362,249 +5370,249 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B19" t="s">
-        <v>483</v>
+        <v>501</v>
       </c>
       <c r="C19" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D19" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E19" t="s">
-        <v>484</v>
+        <v>502</v>
       </c>
       <c r="F19" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="G19" t="s">
-        <v>485</v>
+        <v>503</v>
       </c>
       <c r="H19">
         <v>600</v>
       </c>
       <c r="I19">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="J19">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B20" t="s">
-        <v>486</v>
+        <v>504</v>
       </c>
       <c r="C20" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D20" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E20" t="s">
-        <v>487</v>
+        <v>505</v>
       </c>
       <c r="F20" t="s">
-        <v>488</v>
+        <v>440</v>
       </c>
       <c r="G20" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="H20">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="I20">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="J20">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B21" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="C21" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D21" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E21" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="F21" t="s">
-        <v>450</v>
+        <v>509</v>
       </c>
       <c r="G21" t="s">
-        <v>492</v>
+        <v>510</v>
       </c>
       <c r="H21">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="I21">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="J21">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="C22" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D22" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E22" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="F22" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="G22" t="s">
-        <v>454</v>
+        <v>514</v>
       </c>
       <c r="H22">
-        <v>735</v>
+        <v>750</v>
       </c>
       <c r="I22">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="J22">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s">
-        <v>496</v>
+        <v>515</v>
       </c>
       <c r="C23" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D23" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E23" t="s">
-        <v>497</v>
+        <v>516</v>
       </c>
       <c r="F23" t="s">
-        <v>430</v>
+        <v>517</v>
       </c>
       <c r="G23" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="H23">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="I23">
-        <v>810</v>
+        <v>835</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s">
-        <v>498</v>
+        <v>518</v>
       </c>
       <c r="C24" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D24" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E24" t="s">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="F24" t="s">
-        <v>471</v>
+        <v>520</v>
       </c>
       <c r="G24" t="s">
-        <v>474</v>
+        <v>495</v>
       </c>
       <c r="H24">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="I24">
-        <v>855</v>
+        <v>885</v>
       </c>
       <c r="J24">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B25" t="s">
-        <v>500</v>
+        <v>521</v>
       </c>
       <c r="C25" t="s">
+        <v>142</v>
+      </c>
+      <c r="D25" t="s">
+        <v>266</v>
+      </c>
+      <c r="E25" t="s">
         <v>522</v>
       </c>
-      <c r="D25" t="s">
-        <v>261</v>
-      </c>
-      <c r="E25" t="s">
-        <v>501</v>
-      </c>
       <c r="F25" t="s">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="G25" t="s">
-        <v>502</v>
+        <v>523</v>
       </c>
       <c r="H25">
-        <v>885</v>
+        <v>915</v>
       </c>
       <c r="I25">
         <v>945</v>
       </c>
       <c r="J25">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="B26" t="s">
-        <v>503</v>
+        <v>524</v>
       </c>
       <c r="C26" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D26" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="E26" t="s">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="F26" t="s">
+        <v>482</v>
+      </c>
+      <c r="G26" t="s">
         <v>464</v>
-      </c>
-      <c r="G26" t="s">
-        <v>446</v>
       </c>
       <c r="H26">
         <v>960</v>
@@ -5618,25 +5626,25 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B27" t="s">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="C27" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D27" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E27" t="s">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="F27" t="s">
-        <v>492</v>
+        <v>528</v>
       </c>
       <c r="G27" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="H27">
         <v>720</v>
@@ -5650,25 +5658,25 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B28" t="s">
-        <v>508</v>
+        <v>529</v>
       </c>
       <c r="C28" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D28" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="E28" t="s">
-        <v>497</v>
+        <v>530</v>
       </c>
       <c r="F28" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="G28" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="H28">
         <v>780</v>
@@ -5682,25 +5690,25 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B29" t="s">
-        <v>509</v>
+        <v>531</v>
       </c>
       <c r="C29" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D29" t="s">
-        <v>244</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0.64583333333333337</v>
+        <v>249</v>
+      </c>
+      <c r="E29" t="s">
+        <v>532</v>
+      </c>
+      <c r="F29" t="s">
+        <v>533</v>
       </c>
       <c r="G29" t="s">
-        <v>510</v>
+        <v>534</v>
       </c>
       <c r="H29">
         <v>930</v>
@@ -5714,25 +5722,25 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="B30" t="s">
-        <v>511</v>
+        <v>535</v>
       </c>
       <c r="C30" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D30" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E30" t="s">
-        <v>463</v>
+        <v>481</v>
       </c>
       <c r="F30" t="s">
-        <v>421</v>
+        <v>439</v>
       </c>
       <c r="G30" t="s">
-        <v>464</v>
+        <v>482</v>
       </c>
       <c r="H30">
         <v>600</v>
@@ -5746,25 +5754,25 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B31" t="s">
-        <v>512</v>
+        <v>536</v>
       </c>
       <c r="C31" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D31" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E31" t="s">
-        <v>513</v>
+        <v>537</v>
       </c>
       <c r="F31" t="s">
-        <v>430</v>
+        <v>448</v>
       </c>
       <c r="G31" t="s">
-        <v>433</v>
+        <v>451</v>
       </c>
       <c r="H31">
         <v>780</v>
@@ -5778,25 +5786,25 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="B32" t="s">
-        <v>514</v>
+        <v>538</v>
       </c>
       <c r="C32" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D32" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E32" t="s">
-        <v>469</v>
+        <v>487</v>
       </c>
       <c r="F32" t="s">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="G32" t="s">
-        <v>471</v>
+        <v>489</v>
       </c>
       <c r="H32">
         <v>810</v>
@@ -5810,25 +5818,25 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B33" t="s">
-        <v>515</v>
+        <v>539</v>
       </c>
       <c r="C33" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D33" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E33" t="s">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="F33" t="s">
-        <v>467</v>
+        <v>485</v>
       </c>
       <c r="G33" t="s">
-        <v>474</v>
+        <v>492</v>
       </c>
       <c r="H33">
         <v>840</v>
@@ -5842,25 +5850,25 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="B34" t="s">
-        <v>516</v>
+        <v>540</v>
       </c>
       <c r="C34" t="s">
-        <v>522</v>
+        <v>142</v>
       </c>
       <c r="D34" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E34" t="s">
-        <v>517</v>
+        <v>541</v>
       </c>
       <c r="F34" t="s">
-        <v>518</v>
+        <v>542</v>
       </c>
       <c r="G34" t="s">
-        <v>477</v>
+        <v>495</v>
       </c>
       <c r="H34">
         <v>870</v>
@@ -5873,10 +5881,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:J1 A7:B7 A2:B2 D2:J2 A3:B3 D3:J3 A4:B4 D4:J4 A5:B5 D5:J5 A6:B6 D6:J6 A34:B34 A8:B8 D8:J8 D7:J7 A9:B9 D9:J9 A10:B10 D10:J10 A11:B11 D11:J11 A12:B12 D12:J12 A13:B13 D13:J13 A14:B14 D14:J14 A15:B15 D15:J15 A16:B16 D16:J16 A17:B17 D17:J17 A18:B18 D18:J18 A19:B19 D19:J19 A20:B20 D20:J20 A21:B21 D21:J21 A22:B22 D22:J22 A23:B23 D23:J23 A24:B24 D24:J24 A25:B25 D25:J25 A26:B26 D26:J26 A27:B27 D27:J27 A28:B28 D28:J28 A29:B29 D29 A30:B30 D30:J30 A31:B31 D31:J31 A32:B32 D32:J32 A33:B33 D33:J33 D34:J34 G29 I29" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkytw\Desktop\GitHub\Home-Page\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B18C5F9-F4EF-4565-B9BB-34E92ABD0E80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A64E29-3654-4352-BE58-95A3A944CD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mogiten" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="544">
   <si>
     <t>id</t>
   </si>
@@ -100,9 +100,6 @@
     <t>おいしいパンケーキ屋さん！1年生だけの有志団体です！可愛くて美味しいパンケーキをぜひ食べに来てください♡</t>
   </si>
   <si>
-    <t>food-shashin-bu</t>
-  </si>
-  <si>
     <t>棒餃子</t>
   </si>
   <si>
@@ -249,9 +246,6 @@
   </si>
   <si>
     <t>皆様ごきげんよう！KGUのFABULOUSなお嬢様が作るドリンクはいかが？抽選もあるから是非いらして頂戴！</t>
-  </si>
-  <si>
-    <t>food-ojyosama-select</t>
   </si>
   <si>
     <t>アパレル</t>
@@ -481,9 +475,6 @@
     <t>なおちゃんズではホットドッグを販売しています。一つひとつ真心込めて作りました！ぜひご賞味あれ！</t>
   </si>
   <si>
-    <t>food-sado-bu</t>
-  </si>
-  <si>
     <t>抹茶・和菓子</t>
   </si>
   <si>
@@ -713,9 +704,6 @@
     <t>music-ultimate-keion-bu</t>
   </si>
   <si>
-    <t>バンドライブ</t>
-  </si>
-  <si>
     <t>アルティメット軽音部</t>
   </si>
   <si>
@@ -755,9 +743,6 @@
     <t>music-jazz-bu</t>
   </si>
   <si>
-    <t>ジャズライブ</t>
-  </si>
-  <si>
     <t>JAZZ研究部</t>
   </si>
   <si>
@@ -789,9 +774,6 @@
   </si>
   <si>
     <t>music-kannai-sukayutopia</t>
-  </si>
-  <si>
-    <t>オーケストラ演奏</t>
   </si>
   <si>
     <t>loc-scc-bennett</t>
@@ -805,9 +787,6 @@
     <t>music-kangen-gakudan-bu</t>
   </si>
   <si>
-    <t>管弦楽演奏</t>
-  </si>
-  <si>
     <t>管弦楽団部</t>
   </si>
   <si>
@@ -817,9 +796,6 @@
     <t>music-suisogaku-bu</t>
   </si>
   <si>
-    <t>吹奏楽演奏</t>
-  </si>
-  <si>
     <t>吹奏楽部</t>
   </si>
   <si>
@@ -829,9 +805,6 @@
     <t>music-konsei-gassho-bu</t>
   </si>
   <si>
-    <t>アカペラ合唱</t>
-  </si>
-  <si>
     <t>混声合唱団部</t>
   </si>
   <si>
@@ -841,9 +814,6 @@
     <t>music-hn-entertainment</t>
   </si>
   <si>
-    <t>ライブ・実演</t>
-  </si>
-  <si>
     <t>HN entertainment</t>
   </si>
   <si>
@@ -856,9 +826,6 @@
     <t>music-bep-hop</t>
   </si>
   <si>
-    <t>ダンスパフォーマンス</t>
-  </si>
-  <si>
     <t>ストリートダンス部 BEP-HOP</t>
   </si>
   <si>
@@ -932,9 +899,6 @@
   </si>
   <si>
     <t>music-soprano-koyama</t>
-  </si>
-  <si>
-    <t>ソプラノ独唱</t>
   </si>
   <si>
     <t>ソプラノ：小山晴江</t>
@@ -1727,6 +1691,33 @@
   </si>
   <si>
     <t>チャペルコンサート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ソプラノ演奏</t>
+    <rPh sb="4" eb="6">
+      <t>エンソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>music-hn-entertainment</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>music-kannai-sukayutopia</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>food-sado-bu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>food-ojosama-select</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>food-shashin-bu</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2192,588 +2183,588 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>543</v>
+        <v>531</v>
       </c>
       <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
         <v>29</v>
-      </c>
-      <c r="C5" t="s">
-        <v>30</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
         <v>37</v>
-      </c>
-      <c r="H6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
         <v>39</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>40</v>
-      </c>
-      <c r="C7" t="s">
-        <v>41</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" t="s">
         <v>43</v>
-      </c>
-      <c r="H7" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" t="s">
         <v>45</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>46</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" t="s">
         <v>48</v>
-      </c>
-      <c r="H8" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>545</v>
+        <v>533</v>
       </c>
       <c r="B9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" t="s">
         <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
         <v>53</v>
-      </c>
-      <c r="H9" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
         <v>55</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>56</v>
-      </c>
-      <c r="C10" t="s">
-        <v>57</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
         <v>59</v>
-      </c>
-      <c r="H10" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
         <v>61</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>63</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" t="s">
         <v>65</v>
-      </c>
-      <c r="H11" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
         <v>67</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" t="s">
         <v>71</v>
-      </c>
-      <c r="H12" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>542</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
         <v>73</v>
-      </c>
-      <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
+        <v>77</v>
+      </c>
+      <c r="B14" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" t="s">
         <v>79</v>
-      </c>
-      <c r="B14" t="s">
-        <v>80</v>
-      </c>
-      <c r="C14" t="s">
-        <v>81</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C15" t="s">
         <v>85</v>
-      </c>
-      <c r="B15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" t="s">
-        <v>87</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B16" t="s">
+        <v>90</v>
+      </c>
+      <c r="C16" t="s">
         <v>91</v>
-      </c>
-      <c r="B16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" t="s">
-        <v>93</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
+        <v>95</v>
+      </c>
+      <c r="B17" t="s">
+        <v>96</v>
+      </c>
+      <c r="C17" t="s">
         <v>97</v>
-      </c>
-      <c r="B17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" t="s">
-        <v>99</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="H17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C18" t="s">
         <v>103</v>
-      </c>
-      <c r="B18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" t="s">
-        <v>105</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="H18" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
+        <v>107</v>
+      </c>
+      <c r="B19" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" t="s">
         <v>109</v>
-      </c>
-      <c r="B19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" t="s">
-        <v>111</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" t="s">
+        <v>114</v>
+      </c>
+      <c r="C20" t="s">
         <v>115</v>
-      </c>
-      <c r="B20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" t="s">
-        <v>117</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="H20" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
+        <v>119</v>
+      </c>
+      <c r="B21" t="s">
+        <v>120</v>
+      </c>
+      <c r="C21" t="s">
         <v>121</v>
-      </c>
-      <c r="B21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" t="s">
-        <v>123</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="H21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" t="s">
         <v>127</v>
-      </c>
-      <c r="B22" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" t="s">
-        <v>129</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="H22" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
+        <v>131</v>
+      </c>
+      <c r="B23" t="s">
+        <v>132</v>
+      </c>
+      <c r="C23" t="s">
         <v>133</v>
-      </c>
-      <c r="B23" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23" t="s">
-        <v>135</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="H23" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
+        <v>137</v>
+      </c>
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+      <c r="C24" t="s">
         <v>139</v>
-      </c>
-      <c r="B24" t="s">
-        <v>140</v>
-      </c>
-      <c r="C24" t="s">
-        <v>141</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
+        <v>140</v>
+      </c>
+      <c r="G24" t="s">
+        <v>141</v>
+      </c>
+      <c r="H24" t="s">
         <v>142</v>
-      </c>
-      <c r="G24" t="s">
-        <v>143</v>
-      </c>
-      <c r="H24" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>145</v>
+        <v>541</v>
       </c>
       <c r="B25" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="H25" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B26" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C26" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -2824,180 +2815,180 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" t="s">
+        <v>154</v>
+      </c>
+      <c r="D2" t="s">
         <v>155</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>156</v>
-      </c>
-      <c r="C2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E2" t="s">
-        <v>159</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D3" t="s">
+        <v>155</v>
+      </c>
+      <c r="E3" t="s">
         <v>161</v>
-      </c>
-      <c r="B3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E3" t="s">
-        <v>164</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E4" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C5" t="s">
+        <v>169</v>
+      </c>
+      <c r="D5" t="s">
+        <v>155</v>
+      </c>
+      <c r="E5" t="s">
         <v>170</v>
-      </c>
-      <c r="B5" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5" t="s">
-        <v>158</v>
-      </c>
-      <c r="E5" t="s">
-        <v>173</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D6" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>176</v>
+      </c>
+      <c r="B7" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E7" t="s">
         <v>179</v>
-      </c>
-      <c r="B7" t="s">
-        <v>180</v>
-      </c>
-      <c r="C7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E7" t="s">
-        <v>182</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
+        <v>181</v>
+      </c>
+      <c r="B8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" t="s">
+        <v>183</v>
+      </c>
+      <c r="D8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E8" t="s">
         <v>184</v>
-      </c>
-      <c r="B8" t="s">
-        <v>185</v>
-      </c>
-      <c r="C8" t="s">
-        <v>186</v>
-      </c>
-      <c r="D8" t="s">
-        <v>158</v>
-      </c>
-      <c r="E8" t="s">
-        <v>187</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
@@ -3005,163 +2996,163 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>189</v>
+      </c>
+      <c r="B10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" t="s">
+        <v>155</v>
+      </c>
+      <c r="E10" t="s">
         <v>192</v>
-      </c>
-      <c r="B10" t="s">
-        <v>193</v>
-      </c>
-      <c r="C10" t="s">
-        <v>194</v>
-      </c>
-      <c r="D10" t="s">
-        <v>158</v>
-      </c>
-      <c r="E10" t="s">
-        <v>195</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B12" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D12" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="B13" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D13" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E13" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>547</v>
+        <v>535</v>
       </c>
       <c r="B14" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D14" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E14" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>544</v>
+        <v>532</v>
       </c>
       <c r="B15" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E15" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
+        <v>213</v>
+      </c>
+      <c r="B16" t="s">
+        <v>214</v>
+      </c>
+      <c r="C16" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" t="s">
+        <v>155</v>
+      </c>
+      <c r="E16" t="s">
         <v>216</v>
-      </c>
-      <c r="B16" t="s">
-        <v>217</v>
-      </c>
-      <c r="C16" t="s">
-        <v>218</v>
-      </c>
-      <c r="D16" t="s">
-        <v>158</v>
-      </c>
-      <c r="E16" t="s">
-        <v>219</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -3209,88 +3200,88 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E2" t="s">
         <v>221</v>
-      </c>
-      <c r="B2" t="s">
-        <v>222</v>
-      </c>
-      <c r="C2" t="s">
-        <v>223</v>
-      </c>
-      <c r="D2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E2" t="s">
-        <v>225</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B3" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C3" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D3" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E3" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="C4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D4" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E4" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>548</v>
+        <v>536</v>
       </c>
       <c r="B5" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D5" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E5" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -3298,370 +3289,370 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B6" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D6" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E6" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B7" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="C7" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D7" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E7" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>247</v>
+        <v>540</v>
       </c>
       <c r="B8" t="s">
-        <v>248</v>
+        <v>91</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D8" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E8" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B9" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C9" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="D9" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E9" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B10" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C10" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="D10" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E10" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B11" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="C11" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="D11" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E11" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>263</v>
+        <v>539</v>
       </c>
       <c r="B12" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="C12" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="D12" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E12" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="B13" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E13" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="F13" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G13" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="B14" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="C14" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E14" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B15" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="C15" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="D15" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B16" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="C16" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="D16" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E16" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B17" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C17" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="D17" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E17" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="B18" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C18" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="D18" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E18" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B19" t="s">
-        <v>295</v>
+        <v>538</v>
       </c>
       <c r="C19" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="D19" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E19" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>297</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B20" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C20" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="D20" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E20" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G20" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B21" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C21" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="D21" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="E21" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="F21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G21" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -3703,28 +3694,28 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="B2" t="s">
-        <v>303</v>
+        <v>291</v>
       </c>
       <c r="C2" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="D2" t="s">
-        <v>305</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="F2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G2" t="s">
-        <v>306</v>
+        <v>294</v>
       </c>
       <c r="H2" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -3750,19 +3741,19 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>308</v>
+        <v>296</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>312</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -3770,16 +3761,16 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="D2" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E2" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F2" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
@@ -3787,998 +3778,998 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>317</v>
+        <v>305</v>
       </c>
       <c r="D3" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E3" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F3" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="D4" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E4" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F4" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="D5" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E5" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F5" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="D6" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E6" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F6" t="s">
-        <v>324</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="D7" t="s">
+        <v>302</v>
+      </c>
+      <c r="E7" t="s">
+        <v>303</v>
+      </c>
+      <c r="F7" t="s">
         <v>314</v>
-      </c>
-      <c r="E7" t="s">
-        <v>315</v>
-      </c>
-      <c r="F7" t="s">
-        <v>326</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="D8" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E8" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F8" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="D9" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E9" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F9" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>331</v>
+        <v>319</v>
       </c>
       <c r="D10" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E10" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F10" t="s">
-        <v>332</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>333</v>
+        <v>321</v>
       </c>
       <c r="D11" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E11" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F11" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>335</v>
+        <v>323</v>
       </c>
       <c r="D12" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E12" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F12" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C13" t="s">
-        <v>337</v>
+        <v>325</v>
       </c>
       <c r="D13" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E13" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F13" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="D14" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E14" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F14" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="D15" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E15" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F15" t="s">
-        <v>342</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>343</v>
+        <v>331</v>
       </c>
       <c r="D16" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E16" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F16" t="s">
-        <v>344</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>345</v>
+        <v>333</v>
       </c>
       <c r="D17" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E17" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F17" t="s">
-        <v>346</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>347</v>
+        <v>335</v>
       </c>
       <c r="D18" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E18" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F18" t="s">
-        <v>348</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="D19" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E19" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F19" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="D20" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E20" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F20" t="s">
-        <v>352</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>353</v>
+        <v>341</v>
       </c>
       <c r="D21" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E21" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F21" t="s">
-        <v>354</v>
+        <v>342</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C22" t="s">
-        <v>355</v>
+        <v>343</v>
       </c>
       <c r="D22" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E22" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F22" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C23" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="D23" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="E23" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F23" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="C24" t="s">
-        <v>359</v>
+        <v>347</v>
       </c>
       <c r="D24" t="s">
-        <v>360</v>
+        <v>348</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>361</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C25" t="s">
-        <v>363</v>
+        <v>351</v>
       </c>
       <c r="D25" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C26" t="s">
-        <v>366</v>
+        <v>354</v>
       </c>
       <c r="D26" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="B27" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C27" t="s">
-        <v>368</v>
+        <v>356</v>
       </c>
       <c r="D27" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C28" t="s">
-        <v>371</v>
+        <v>359</v>
       </c>
       <c r="D28" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B29" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C29" t="s">
-        <v>375</v>
+        <v>363</v>
       </c>
       <c r="D29" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>373</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B30" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C30" t="s">
-        <v>377</v>
+        <v>365</v>
       </c>
       <c r="D30" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>378</v>
+        <v>366</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B31" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C31" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="D31" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>380</v>
+        <v>368</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B32" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C32" t="s">
-        <v>381</v>
+        <v>369</v>
       </c>
       <c r="D32" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C33" t="s">
-        <v>383</v>
+        <v>371</v>
       </c>
       <c r="D33" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="B34" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C34" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="D34" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>365</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B35" t="s">
+        <v>362</v>
+      </c>
+      <c r="C35" t="s">
         <v>374</v>
       </c>
-      <c r="C35" t="s">
-        <v>386</v>
-      </c>
       <c r="D35" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C36" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="D36" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C37" t="s">
-        <v>388</v>
+        <v>376</v>
       </c>
       <c r="D37" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>389</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s">
-        <v>374</v>
+        <v>362</v>
       </c>
       <c r="C38" t="s">
-        <v>390</v>
+        <v>378</v>
       </c>
       <c r="D38" t="s">
-        <v>376</v>
+        <v>364</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s">
-        <v>370</v>
+        <v>358</v>
       </c>
       <c r="C39" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="D39" t="s">
-        <v>372</v>
+        <v>360</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="B40" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C40" t="s">
-        <v>395</v>
+        <v>383</v>
       </c>
       <c r="D40" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>382</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B41" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C41" t="s">
-        <v>397</v>
+        <v>385</v>
       </c>
       <c r="D41" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>384</v>
+        <v>372</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>398</v>
+        <v>386</v>
       </c>
       <c r="B42" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C42" t="s">
-        <v>399</v>
+        <v>387</v>
       </c>
       <c r="D42" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E42">
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>400</v>
+        <v>388</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="B43" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C43" t="s">
-        <v>401</v>
+        <v>389</v>
       </c>
       <c r="D43" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>402</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>403</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C44" t="s">
-        <v>404</v>
+        <v>392</v>
       </c>
       <c r="D44" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E44">
         <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>405</v>
+        <v>393</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="B45" t="s">
+        <v>382</v>
+      </c>
+      <c r="C45" t="s">
         <v>394</v>
       </c>
-      <c r="C45" t="s">
-        <v>406</v>
-      </c>
       <c r="D45" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E45">
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>407</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="C46" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="D46" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="E46" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F46" t="s">
-        <v>408</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="B47" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="C47" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="D47" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="E47">
         <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="C48" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="D48" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="C49" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="D49" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="E49" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="F49" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="C50" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="D50" t="s">
-        <v>416</v>
+        <v>404</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>417</v>
+        <v>405</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="C51" t="s">
-        <v>418</v>
+        <v>406</v>
       </c>
       <c r="D51" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="E51">
         <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="B52" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C52" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="D52" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="B53" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="C53" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="D53" t="s">
-        <v>364</v>
+        <v>352</v>
       </c>
       <c r="E53" t="s">
-        <v>316</v>
+        <v>304</v>
       </c>
       <c r="F53" t="s">
-        <v>423</v>
+        <v>411</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="B54" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C54" t="s">
-        <v>424</v>
+        <v>412</v>
       </c>
       <c r="D54" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E54" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="F54" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B55" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C55" t="s">
-        <v>426</v>
+        <v>414</v>
       </c>
       <c r="D55" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E55" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="F55" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B56" t="s">
-        <v>394</v>
+        <v>382</v>
       </c>
       <c r="C56" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="D56" t="s">
-        <v>396</v>
+        <v>384</v>
       </c>
       <c r="E56" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="F56" t="s">
-        <v>429</v>
+        <v>417</v>
       </c>
     </row>
   </sheetData>
@@ -4797,7 +4788,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>430</v>
+        <v>418</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -4806,45 +4797,45 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>431</v>
+        <v>419</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>432</v>
+        <v>420</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>435</v>
+        <v>423</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>436</v>
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B2" t="s">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E2" t="s">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="F2" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="G2" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="H2">
         <v>600</v>
@@ -4858,25 +4849,25 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B3" t="s">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E3" t="s">
-        <v>442</v>
+        <v>430</v>
       </c>
       <c r="F3" t="s">
-        <v>443</v>
+        <v>431</v>
       </c>
       <c r="G3" t="s">
-        <v>444</v>
+        <v>432</v>
       </c>
       <c r="H3">
         <v>665</v>
@@ -4890,25 +4881,25 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B4" t="s">
-        <v>445</v>
+        <v>433</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E4" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="F4" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="G4" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="H4">
         <v>730</v>
@@ -4922,25 +4913,25 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B5" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E5" t="s">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="F5" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="G5" t="s">
-        <v>452</v>
+        <v>440</v>
       </c>
       <c r="H5">
         <v>795</v>
@@ -4954,25 +4945,25 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B6" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E6" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="F6" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="G6" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="H6">
         <v>860</v>
@@ -4986,25 +4977,25 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B7" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E7" t="s">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="F7" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
       <c r="G7" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
       <c r="H7">
         <v>925</v>
@@ -5018,25 +5009,25 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B8" t="s">
-        <v>461</v>
+        <v>449</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E8" t="s">
-        <v>462</v>
+        <v>450</v>
       </c>
       <c r="F8" t="s">
-        <v>463</v>
+        <v>451</v>
       </c>
       <c r="G8" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="H8">
         <v>990</v>
@@ -5050,25 +5041,25 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B9" t="s">
-        <v>465</v>
+        <v>453</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>466</v>
+        <v>454</v>
       </c>
       <c r="F9" t="s">
-        <v>467</v>
+        <v>455</v>
       </c>
       <c r="G9" t="s">
-        <v>468</v>
+        <v>456</v>
       </c>
       <c r="H9">
         <v>660</v>
@@ -5082,25 +5073,25 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="B10" t="s">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="F10" t="s">
-        <v>471</v>
+        <v>459</v>
       </c>
       <c r="G10" t="s">
-        <v>472</v>
+        <v>460</v>
       </c>
       <c r="H10">
         <v>705</v>
@@ -5114,25 +5105,25 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B11" t="s">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="F11" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="G11" t="s">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="H11">
         <v>780</v>
@@ -5146,25 +5137,25 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B12" t="s">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="F12" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="G12" t="s">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="H12">
         <v>835</v>
@@ -5178,25 +5169,25 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B13" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E13" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="F13" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="G13" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="H13">
         <v>600</v>
@@ -5210,25 +5201,25 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B14" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="E14" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="F14" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="G14" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="H14">
         <v>780</v>
@@ -5242,25 +5233,25 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B15" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="E15" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="F15" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="G15" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="H15">
         <v>810</v>
@@ -5274,25 +5265,25 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="B16" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="E16" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="F16" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="G16" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="H16">
         <v>840</v>
@@ -5306,25 +5297,25 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="B17" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="E17" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="F17" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="G17" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="H17">
         <v>885</v>
@@ -5338,25 +5329,25 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="B18" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="E18" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="F18" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="G18" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="H18">
         <v>915</v>
@@ -5370,25 +5361,25 @@
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="B19" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="C19" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D19" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E19" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="F19" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="G19" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="H19">
         <v>600</v>
@@ -5402,25 +5393,25 @@
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="C20" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E20" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="F20" t="s">
-        <v>440</v>
+        <v>428</v>
       </c>
       <c r="G20" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="H20">
         <v>650</v>
@@ -5434,25 +5425,25 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="C21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E21" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="F21" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="G21" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="H21">
         <v>700</v>
@@ -5466,25 +5457,25 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="C22" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D22" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E22" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="F22" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="G22" t="s">
-        <v>514</v>
+        <v>502</v>
       </c>
       <c r="H22">
         <v>750</v>
@@ -5498,25 +5489,25 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B23" t="s">
-        <v>515</v>
+        <v>503</v>
       </c>
       <c r="C23" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E23" t="s">
-        <v>516</v>
+        <v>504</v>
       </c>
       <c r="F23" t="s">
-        <v>517</v>
+        <v>505</v>
       </c>
       <c r="G23" t="s">
-        <v>478</v>
+        <v>466</v>
       </c>
       <c r="H23">
         <v>800</v>
@@ -5530,25 +5521,25 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s">
-        <v>518</v>
+        <v>506</v>
       </c>
       <c r="C24" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E24" t="s">
-        <v>519</v>
+        <v>507</v>
       </c>
       <c r="F24" t="s">
-        <v>520</v>
+        <v>508</v>
       </c>
       <c r="G24" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="H24">
         <v>850</v>
@@ -5562,25 +5553,25 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s">
-        <v>521</v>
+        <v>509</v>
       </c>
       <c r="C25" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E25" t="s">
-        <v>522</v>
+        <v>510</v>
       </c>
       <c r="F25" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="G25" t="s">
-        <v>523</v>
+        <v>511</v>
       </c>
       <c r="H25">
         <v>915</v>
@@ -5594,25 +5585,25 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s">
-        <v>524</v>
+        <v>512</v>
       </c>
       <c r="C26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="E26" t="s">
-        <v>525</v>
+        <v>513</v>
       </c>
       <c r="F26" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="G26" t="s">
-        <v>464</v>
+        <v>452</v>
       </c>
       <c r="H26">
         <v>960</v>
@@ -5626,25 +5617,25 @@
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="B27" t="s">
-        <v>526</v>
+        <v>514</v>
       </c>
       <c r="C27" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>527</v>
+        <v>515</v>
       </c>
       <c r="F27" t="s">
-        <v>528</v>
+        <v>516</v>
       </c>
       <c r="G27" t="s">
-        <v>513</v>
+        <v>501</v>
       </c>
       <c r="H27">
         <v>720</v>
@@ -5658,25 +5649,25 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s">
-        <v>529</v>
+        <v>517</v>
       </c>
       <c r="C28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D28" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>530</v>
+        <v>518</v>
       </c>
       <c r="F28" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="G28" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="H28">
         <v>780</v>
@@ -5690,25 +5681,25 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>302</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s">
-        <v>531</v>
+        <v>519</v>
       </c>
       <c r="C29" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D29" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>532</v>
+        <v>520</v>
       </c>
       <c r="F29" t="s">
-        <v>533</v>
+        <v>521</v>
       </c>
       <c r="G29" t="s">
-        <v>534</v>
+        <v>522</v>
       </c>
       <c r="H29">
         <v>930</v>
@@ -5722,25 +5713,25 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s">
-        <v>535</v>
+        <v>523</v>
       </c>
       <c r="C30" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D30" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="E30" t="s">
-        <v>481</v>
+        <v>469</v>
       </c>
       <c r="F30" t="s">
-        <v>439</v>
+        <v>427</v>
       </c>
       <c r="G30" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="H30">
         <v>600</v>
@@ -5754,25 +5745,25 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s">
-        <v>536</v>
+        <v>524</v>
       </c>
       <c r="C31" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="E31" t="s">
-        <v>537</v>
+        <v>525</v>
       </c>
       <c r="F31" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="G31" t="s">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="H31">
         <v>780</v>
@@ -5786,25 +5777,25 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s">
-        <v>538</v>
+        <v>526</v>
       </c>
       <c r="C32" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="E32" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="F32" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="G32" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="H32">
         <v>810</v>
@@ -5818,25 +5809,25 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s">
-        <v>539</v>
+        <v>527</v>
       </c>
       <c r="C33" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="E33" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="F33" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="G33" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="H33">
         <v>840</v>
@@ -5850,25 +5841,25 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>300</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s">
-        <v>540</v>
+        <v>528</v>
       </c>
       <c r="C34" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="E34" t="s">
-        <v>541</v>
+        <v>529</v>
       </c>
       <c r="F34" t="s">
-        <v>542</v>
+        <v>530</v>
       </c>
       <c r="G34" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="H34">
         <v>870</v>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkytw\Desktop\GitHub\Home-Page\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4556A40-1A16-4524-A707-43EF2FB5C386}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A64E29-3654-4352-BE58-95A3A944CD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8376" yWindow="2676" windowWidth="12648" windowHeight="11004" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mogiten" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,11 @@
     <sheet name="timetable" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="525">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="544">
   <si>
     <t>id</t>
   </si>
@@ -91,18 +90,16 @@
     <t>day1</t>
   </si>
   <si>
-    <t>いちご_x000D__x000D_
-ブルーベリー_x000D__x000D_
-ちょこ_x000D__x000D_
-キャラメル　　※値段は未定</t>
+    <t>いちご
+ブルーベリー
+チョコ
+キャラメル
+パンケーキ1つ 350円</t>
   </si>
   <si>
     <t>おいしいパンケーキ屋さん！1年生だけの有志団体です！可愛くて美味しいパンケーキをぜひ食べに来てください♡</t>
   </si>
   <si>
-    <t>food-shashin-bu</t>
-  </si>
-  <si>
     <t>棒餃子</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>写真部では今年も棒餃子を販売します！平潟祭はこれ食えば間違いナシ！</t>
   </si>
   <si>
-    <t>food-oystars</t>
-  </si>
-  <si>
     <t>筋肉巻き</t>
   </si>
   <si>
@@ -130,7 +124,7 @@
     <t>loc-tent-04</t>
   </si>
   <si>
-    <t/>
+    <t>サンドイッチ　一つ300円</t>
   </si>
   <si>
     <t>food-compass</t>
@@ -178,13 +172,16 @@
     <t>loc-tent-07</t>
   </si>
   <si>
-    <t>food-mogi-shutten</t>
+    <t>フランクフルト　1本 250円</t>
+  </si>
+  <si>
+    <t>ジューシーで香ばしい絶品フランクフルトを販売！パリッと弾ける食感と熱々の肉汁がたまりません。食べ歩きに最適ですので、ぜひお立ち寄りください！</t>
   </si>
   <si>
     <t>やきそば</t>
   </si>
   <si>
-    <t>模擬店出店</t>
+    <t>平潟祭実行委員会</t>
   </si>
   <si>
     <t>loc-tent-08</t>
@@ -251,10 +248,20 @@
     <t>皆様ごきげんよう！KGUのFABULOUSなお嬢様が作るドリンクはいかが？抽選もあるから是非いらして頂戴！</t>
   </si>
   <si>
-    <t>food-ojosama-circle2</t>
+    <t>アパレル</t>
+  </si>
+  <si>
+    <t>OJYOSAMA SELECT</t>
   </si>
   <si>
     <t>loc-tent-12</t>
+  </si>
+  <si>
+    <t>服やグッズの販売
+2,499円（税込）～7,499円（税込）</t>
+  </si>
+  <si>
+    <t>皆様ごきげんよう。お嬢様セレクトのアパレルで、上品な毎日をお過ごしまくりあげてちょうだい！</t>
   </si>
   <si>
     <t>food-kashiwazaki-semi</t>
@@ -315,6 +322,9 @@
 缶ビール 1本 400円</t>
   </si>
   <si>
+    <t>子どもから大人までだいすき お得にたくさん食べられる5本セットがおすすめ おいしい焼き鳥食べに来てね</t>
+  </si>
+  <si>
     <t>food-tecky</t>
   </si>
   <si>
@@ -465,9 +475,6 @@
     <t>なおちゃんズではホットドッグを販売しています。一つひとつ真心込めて作りました！ぜひご賞味あれ！</t>
   </si>
   <si>
-    <t>food-sado-bu</t>
-  </si>
-  <si>
     <t>抹茶・和菓子</t>
   </si>
   <si>
@@ -484,6 +491,18 @@
     <t>茶道部です！8号館横の茶室で抹茶とお菓子をご用意しています。ぜひお気軽にお越しください！</t>
   </si>
   <si>
+    <t>food-hanahaku</t>
+  </si>
+  <si>
+    <t>ワークショップ</t>
+  </si>
+  <si>
+    <t>花博（Expo部）</t>
+  </si>
+  <si>
+    <t>loc-3-zakuro</t>
+  </si>
+  <si>
     <t>culture-wandervogel-bu</t>
   </si>
   <si>
@@ -520,9 +539,6 @@
     <t>culture-meag</t>
   </si>
   <si>
-    <t>ワークショップ</t>
-  </si>
-  <si>
     <t>MEAG</t>
   </si>
   <si>
@@ -589,9 +605,6 @@
     <t>放送研究会KGUBでは放送にまつわる機材の展示・体験や仕掛けをご用意しています！ぜひお越しください！</t>
   </si>
   <si>
-    <t>culture-shinsengumi</t>
-  </si>
-  <si>
     <t>公演</t>
   </si>
   <si>
@@ -652,9 +665,6 @@
     <t>自作プラネタリウムで本物のような星空を再現！天文部スバルが皆さんを宇宙の世界へご案内します。</t>
   </si>
   <si>
-    <t>culture-tetsudo-bu</t>
-  </si>
-  <si>
     <t>作品展示・体験展示</t>
   </si>
   <si>
@@ -667,9 +677,6 @@
     <t>鉄道研究部です。部員自慢のNゲージコレクションや沢山のプラレール達が走り回るジオラマ展示がございます！他にも鉄道に関する様々な 展示を行います。大人の方もお子様も、是非ご来場下さい！</t>
   </si>
   <si>
-    <t>culture-oystars</t>
-  </si>
-  <si>
     <t>マッスルコンテスト</t>
   </si>
   <si>
@@ -697,16 +704,13 @@
     <t>music-ultimate-keion-bu</t>
   </si>
   <si>
-    <t>バンドライブ</t>
-  </si>
-  <si>
     <t>アルティメット軽音部</t>
   </si>
   <si>
     <t>音楽館</t>
   </si>
   <si>
-    <t>loc-7-201</t>
+    <t>loc-7-402</t>
   </si>
   <si>
     <t>アルティメット軽音部です 私たちは色んなジャンルの音楽を楽しんでいます！ぜひ気軽に見に来てください♪</t>
@@ -718,30 +722,27 @@
     <t>軽音楽部</t>
   </si>
   <si>
+    <t>loc-7-302</t>
+  </si>
+  <si>
+    <t>部員が全力で演奏！熱いライブをお楽しみください！</t>
+  </si>
+  <si>
+    <t>music-dendenmushi-bu</t>
+  </si>
+  <si>
+    <t>でんでんむ詩部</t>
+  </si>
+  <si>
     <t>loc-7-203</t>
   </si>
   <si>
-    <t>部員が全力で演奏！熱いライブをお楽しみください！</t>
-  </si>
-  <si>
-    <t>music-dendenmushi-bu</t>
-  </si>
-  <si>
-    <t>でんでんむ詩部</t>
-  </si>
-  <si>
-    <t>loc-7-301</t>
-  </si>
-  <si>
     <t>私たちはジャンル問わず様々なバンドを演奏します！みんなで作る最高のライブをぜひ見に来てください！</t>
   </si>
   <si>
     <t>music-jazz-bu</t>
   </si>
   <si>
-    <t>ジャズライブ</t>
-  </si>
-  <si>
     <t>JAZZ研究部</t>
   </si>
   <si>
@@ -754,7 +755,7 @@
     <t>ウエスタン部</t>
   </si>
   <si>
-    <t>loc-7-401</t>
+    <t>loc-7-202</t>
   </si>
   <si>
     <t>こんにちはウエスタン部です!! 私達は主に洋楽をメインとした軽音楽部です! 普段洋楽を聞かない人でもめちゃくちゃ楽しめるのでぜひ遊びに来てください！！</t>
@@ -773,9 +774,6 @@
   </si>
   <si>
     <t>music-kannai-sukayutopia</t>
-  </si>
-  <si>
-    <t>オーケストラ演奏</t>
   </si>
   <si>
     <t>loc-scc-bennett</t>
@@ -789,9 +787,6 @@
     <t>music-kangen-gakudan-bu</t>
   </si>
   <si>
-    <t>管弦楽演奏</t>
-  </si>
-  <si>
     <t>管弦楽団部</t>
   </si>
   <si>
@@ -801,9 +796,6 @@
     <t>music-suisogaku-bu</t>
   </si>
   <si>
-    <t>吹奏楽演奏</t>
-  </si>
-  <si>
     <t>吹奏楽部</t>
   </si>
   <si>
@@ -813,9 +805,6 @@
     <t>music-konsei-gassho-bu</t>
   </si>
   <si>
-    <t>アカペラ合唱</t>
-  </si>
-  <si>
     <t>混声合唱団部</t>
   </si>
   <si>
@@ -825,9 +814,6 @@
     <t>music-hn-entertainment</t>
   </si>
   <si>
-    <t>ライブ・実演</t>
-  </si>
-  <si>
     <t>HN entertainment</t>
   </si>
   <si>
@@ -840,9 +826,6 @@
     <t>music-bep-hop</t>
   </si>
   <si>
-    <t>ダンスパフォーマンス</t>
-  </si>
-  <si>
     <t>ストリートダンス部 BEP-HOP</t>
   </si>
   <si>
@@ -900,9 +883,6 @@
     <t>music-pipe-organ-fujishiro</t>
   </si>
   <si>
-    <t>パイプオルガン特別演奏</t>
-  </si>
-  <si>
     <t>パイプオルガン：藤城眞美</t>
   </si>
   <si>
@@ -921,9 +901,6 @@
     <t>music-soprano-koyama</t>
   </si>
   <si>
-    <t>ソプラノ独唱</t>
-  </si>
-  <si>
     <t>ソプラノ：小山晴江</t>
   </si>
   <si>
@@ -948,661 +925,10 @@
     <t>宮世琉弥トークショー × 平潟祭</t>
   </si>
   <si>
+    <t>平潟祭実行委員会 芸能</t>
+  </si>
+  <si>
     <t>芸能</t>
-  </si>
-  <si>
-    <t>buildingId</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>building</t>
-  </si>
-  <si>
-    <t>floor</t>
-  </si>
-  <si>
-    <t>room</t>
-  </si>
-  <si>
-    <t>テントNo.1</t>
-  </si>
-  <si>
-    <t>テント</t>
-  </si>
-  <si>
-    <t>屋外</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>テントNo.2</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>テントNo.3</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>テントNo.4</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>テントNo.5</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>テントNo.6</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>テントNo.7</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>テントNo.8</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>テントNo.9</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>テントNo.10</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>テントNo.11</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>テントNo.12</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>テントNo.13</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>テントNo.14</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>テントNo.15</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>テントNo.16</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>テントNo.17</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>テントNo.18</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>テントNo.19</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>テントNo.20</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>テントNo.21</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>テントNo.22</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>8号館横 茶室</t>
-  </si>
-  <si>
-    <t>茶室</t>
-  </si>
-  <si>
-    <t>茶室（専用個室）</t>
-  </si>
-  <si>
-    <t>no3</t>
-  </si>
-  <si>
-    <t>3-204</t>
-  </si>
-  <si>
-    <t>3号館</t>
-  </si>
-  <si>
-    <t>204</t>
-  </si>
-  <si>
-    <t>3-205</t>
-  </si>
-  <si>
-    <t>205</t>
-  </si>
-  <si>
-    <t>3-206</t>
-  </si>
-  <si>
-    <t>206</t>
-  </si>
-  <si>
-    <t>no6</t>
-  </si>
-  <si>
-    <t>6-101</t>
-  </si>
-  <si>
-    <t>6号館</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>no8</t>
-  </si>
-  <si>
-    <t>8-101</t>
-  </si>
-  <si>
-    <t>8号館</t>
-  </si>
-  <si>
-    <t>8-102</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>8-103・105</t>
-  </si>
-  <si>
-    <t>103・105</t>
-  </si>
-  <si>
-    <t>8-201</t>
-  </si>
-  <si>
-    <t>201</t>
-  </si>
-  <si>
-    <t>8-203</t>
-  </si>
-  <si>
-    <t>203</t>
-  </si>
-  <si>
-    <t>8-204</t>
-  </si>
-  <si>
-    <t>8-205</t>
-  </si>
-  <si>
-    <t>8-206</t>
-  </si>
-  <si>
-    <t>8-305</t>
-  </si>
-  <si>
-    <t>305</t>
-  </si>
-  <si>
-    <t>8-306</t>
-  </si>
-  <si>
-    <t>306</t>
-  </si>
-  <si>
-    <t>カフェポンド前</t>
-  </si>
-  <si>
-    <t>no7</t>
-  </si>
-  <si>
-    <t>7-201</t>
-  </si>
-  <si>
-    <t>7号館</t>
-  </si>
-  <si>
-    <t>7-203</t>
-  </si>
-  <si>
-    <t>7-301</t>
-  </si>
-  <si>
-    <t>301</t>
-  </si>
-  <si>
-    <t>7-303</t>
-  </si>
-  <si>
-    <t>303</t>
-  </si>
-  <si>
-    <t>7-401</t>
-  </si>
-  <si>
-    <t>401</t>
-  </si>
-  <si>
-    <t>7-403</t>
-  </si>
-  <si>
-    <t>403</t>
-  </si>
-  <si>
-    <t>屋外ステージ</t>
-  </si>
-  <si>
-    <t>scc</t>
-  </si>
-  <si>
-    <t>SCC 4階 ベンネットホール</t>
-  </si>
-  <si>
-    <t>SCC棟</t>
-  </si>
-  <si>
-    <t>ベンネットホール（屋内ステージ）</t>
-  </si>
-  <si>
-    <t>体育館</t>
-  </si>
-  <si>
-    <t>1号館前（セブンイレブン前）</t>
-  </si>
-  <si>
-    <t>1号館前広場</t>
-  </si>
-  <si>
-    <t>チャペル</t>
-  </si>
-  <si>
-    <t>礼拝堂</t>
-  </si>
-  <si>
-    <t>クラブハウス626</t>
-  </si>
-  <si>
-    <t>クラブハウス棟</t>
-  </si>
-  <si>
-    <t>626室</t>
-  </si>
-  <si>
-    <t>学生支援室</t>
-  </si>
-  <si>
-    <t>slotId</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>startTime</t>
-  </si>
-  <si>
-    <t>endTime</t>
-  </si>
-  <si>
-    <t>startMinutes</t>
-  </si>
-  <si>
-    <t>endMinutes</t>
-  </si>
-  <si>
-    <t>durationMinutes</t>
-  </si>
-  <si>
-    <t>tt-d1-01</t>
-  </si>
-  <si>
-    <t>10:00～10:50</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>tt-d1-02</t>
-  </si>
-  <si>
-    <t>11:05～11:55</t>
-  </si>
-  <si>
-    <t>11:05</t>
-  </si>
-  <si>
-    <t>11:55</t>
-  </si>
-  <si>
-    <t>tt-d1-03</t>
-  </si>
-  <si>
-    <t>12:10～13:00</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>13:00</t>
-  </si>
-  <si>
-    <t>tt-d1-04</t>
-  </si>
-  <si>
-    <t>13:15～14:05</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>tt-d1-05</t>
-  </si>
-  <si>
-    <t>14:20～15:10</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>tt-d1-06</t>
-  </si>
-  <si>
-    <t>15:25～16:15</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>tt-d1-07</t>
-  </si>
-  <si>
-    <t>16:30～17:00</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>tt-d1-08</t>
-  </si>
-  <si>
-    <t>11:00～11:30</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>tt-d1-09</t>
-  </si>
-  <si>
-    <t>11:45～12:45</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>tt-d1-10</t>
-  </si>
-  <si>
-    <t>13:00～13:40</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>tt-d1-11</t>
-  </si>
-  <si>
-    <t>13:55～14:25</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>tt-d1-12</t>
-  </si>
-  <si>
-    <t>10:00～16:00</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>tt-d1-13</t>
-  </si>
-  <si>
-    <t>13:00～14:00</t>
-  </si>
-  <si>
-    <t>14:00</t>
-  </si>
-  <si>
-    <t>tt-d1-14</t>
-  </si>
-  <si>
-    <t>13:30～13:45</t>
-  </si>
-  <si>
-    <t>13:30</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>tt-d1-15</t>
-  </si>
-  <si>
-    <t>14:00～14:15</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>tt-d1-16</t>
-  </si>
-  <si>
-    <t>14:45～15:00</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>tt-d1-17</t>
-  </si>
-  <si>
-    <t>15:15～15:30</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>tt-d2-01</t>
-  </si>
-  <si>
-    <t>10:00～10:30</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>tt-d2-02</t>
-  </si>
-  <si>
-    <t>10:45～11:15</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>tt-d2-03</t>
-  </si>
-  <si>
-    <t>11:30～12:00</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>tt-d2-04</t>
-  </si>
-  <si>
-    <t>12:15～12:45</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>tt-d2-05</t>
-  </si>
-  <si>
-    <t>13:00～13:30</t>
-  </si>
-  <si>
-    <t>tt-d2-06</t>
-  </si>
-  <si>
-    <t>13:45～14:15</t>
-  </si>
-  <si>
-    <t>tt-d2-07</t>
-  </si>
-  <si>
-    <t>14:45～15:45</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>tt-d2-08</t>
-  </si>
-  <si>
-    <t>16:00～17:00</t>
-  </si>
-  <si>
-    <t>tt-d2-09</t>
-  </si>
-  <si>
-    <t>12:00～12:30</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>tt-d2-10</t>
-  </si>
-  <si>
-    <t>tt-d2-11</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>tt-d2-12</t>
-  </si>
-  <si>
-    <t>tt-d2-13</t>
-  </si>
-  <si>
-    <t>13:00～13:15</t>
-  </si>
-  <si>
-    <t>tt-d2-14</t>
-  </si>
-  <si>
-    <t>tt-d2-15</t>
-  </si>
-  <si>
-    <t>tt-d2-16</t>
-  </si>
-  <si>
-    <t>14:30～14:45</t>
-  </si>
-  <si>
-    <t>14:30</t>
   </si>
   <si>
     <t>① 10/1(木) 12:30～17:00
@@ -1622,7 +948,6 @@
 ●3歳以下のお子様はご入場いただけません。4歳以上のお客様はチケットが必 要になります。
 ●車椅子をご利用のお客様1名につき、付き添いの方1名までご入場いただけます。車椅子をご利用のお客様、付き添いの方ともにチケットが必要となります。車椅子席は5席となります。以下までお問い合わせください。
 問い合わせ先：hirakata.geinou@gmail.com</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>宮世琉弥トークショー（全席指定・有料チケット制）開場15:30 開演16:30
@@ -1634,76 +959,786 @@
 ※ 転売が確認されたチケットは無効となり、ご入場をお断りいたします。その際の返金には応じかねます。
 ※ 公式以外のルートで購入されたチケットに関するトラブルについて、当学園祭実行委員会は一切の責任を負いません。
 ※ 出演者への直接のプレゼント、差し入れはできません。プレゼントボックスを設置いたします。</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>day1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>day2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF79C0FF"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>開場</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF79C0FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">15:30 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF79C0FF"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>開演</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF79C0FF"/>
-        <rFont val="Consolas"/>
-        <family val="3"/>
-      </rPr>
-      <t>16:30</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>平潟祭実行委員会 芸能</t>
-    <rPh sb="9" eb="11">
-      <t>ゲイノウ</t>
+  </si>
+  <si>
+    <t>buildingId</t>
+  </si>
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>building</t>
+  </si>
+  <si>
+    <t>floor</t>
+  </si>
+  <si>
+    <t>room</t>
+  </si>
+  <si>
+    <t>テントNo.1</t>
+  </si>
+  <si>
+    <t>テント</t>
+  </si>
+  <si>
+    <t>屋外</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>テントNo.2</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>テントNo.3</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>テントNo.4</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>テントNo.5</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>テントNo.6</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>テントNo.7</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>テントNo.8</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>テントNo.9</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>テントNo.10</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>テントNo.11</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>テントNo.12</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>テントNo.13</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>テントNo.14</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>テントNo.15</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>テントNo.16</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>テントNo.17</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>テントNo.18</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>テントNo.19</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>テントNo.20</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>テントNo.21</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>テントNo.22</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>8号館横 茶室</t>
+  </si>
+  <si>
+    <t>茶室</t>
+  </si>
+  <si>
+    <t>茶室（専用個室）</t>
+  </si>
+  <si>
+    <t>no3</t>
+  </si>
+  <si>
+    <t>3-204</t>
+  </si>
+  <si>
+    <t>3号館</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>3-205</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>3-206</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>no6</t>
+  </si>
+  <si>
+    <t>6-101</t>
+  </si>
+  <si>
+    <t>6号館</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>no8</t>
+  </si>
+  <si>
+    <t>8-101</t>
+  </si>
+  <si>
+    <t>8号館</t>
+  </si>
+  <si>
+    <t>8-102</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>8-103・105</t>
+  </si>
+  <si>
+    <t>103・105</t>
+  </si>
+  <si>
+    <t>8-201</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>8-203</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>8-204</t>
+  </si>
+  <si>
+    <t>8-205</t>
+  </si>
+  <si>
+    <t>8-206</t>
+  </si>
+  <si>
+    <t>8-305</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>8-306</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>カフェポンド前</t>
+  </si>
+  <si>
+    <t>loc-7-201</t>
+  </si>
+  <si>
+    <t>no7</t>
+  </si>
+  <si>
+    <t>7-201</t>
+  </si>
+  <si>
+    <t>7号館</t>
+  </si>
+  <si>
+    <t>7-203</t>
+  </si>
+  <si>
+    <t>loc-7-301</t>
+  </si>
+  <si>
+    <t>7-301</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>7-303</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>loc-7-401</t>
+  </si>
+  <si>
+    <t>7-401</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>7-403</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>屋外ステージ</t>
+  </si>
+  <si>
+    <t>scc</t>
+  </si>
+  <si>
+    <t>SCC 4階 ベンネットホール</t>
+  </si>
+  <si>
+    <t>SCC棟</t>
+  </si>
+  <si>
+    <t>ベンネットホール（屋内ステージ）</t>
+  </si>
+  <si>
+    <t>体育館</t>
+  </si>
+  <si>
+    <t>1号館前（セブンイレブン前）</t>
+  </si>
+  <si>
+    <t>1号館前広場</t>
+  </si>
+  <si>
+    <t>チャペル</t>
+  </si>
+  <si>
+    <t>礼拝堂</t>
+  </si>
+  <si>
+    <t>クラブハウス626</t>
+  </si>
+  <si>
+    <t>クラブハウス棟</t>
+  </si>
+  <si>
+    <t>626室</t>
+  </si>
+  <si>
+    <t>学生支援室</t>
+  </si>
+  <si>
+    <t>3号館食堂ザクロ</t>
+  </si>
+  <si>
+    <t>食堂ザクロ</t>
+  </si>
+  <si>
+    <t>7-202</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>7-402</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>7-302</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>slotId</t>
+  </si>
+  <si>
+    <t>time</t>
+  </si>
+  <si>
+    <t>startTime</t>
+  </si>
+  <si>
+    <t>endTime</t>
+  </si>
+  <si>
+    <t>startMinutes</t>
+  </si>
+  <si>
+    <t>endMinutes</t>
+  </si>
+  <si>
+    <t>durationMinutes</t>
+  </si>
+  <si>
+    <t>tt-d1-01</t>
+  </si>
+  <si>
+    <t>10:00～10:50</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>tt-d1-02</t>
+  </si>
+  <si>
+    <t>11:05～11:55</t>
+  </si>
+  <si>
+    <t>11:05</t>
+  </si>
+  <si>
+    <t>11:55</t>
+  </si>
+  <si>
+    <t>tt-d1-03</t>
+  </si>
+  <si>
+    <t>12:10～13:00</t>
+  </si>
+  <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>13:00</t>
+  </si>
+  <si>
+    <t>tt-d1-04</t>
+  </si>
+  <si>
+    <t>13:15～14:05</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>tt-d1-05</t>
+  </si>
+  <si>
+    <t>14:20～15:10</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>tt-d1-06</t>
+  </si>
+  <si>
+    <t>15:25～16:15</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>tt-d1-07</t>
+  </si>
+  <si>
+    <t>16:30～17:00</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>tt-d1-08</t>
+  </si>
+  <si>
+    <t>11:00～11:30</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>tt-d1-09</t>
+  </si>
+  <si>
+    <t>11:45～12:45</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>tt-d1-10</t>
+  </si>
+  <si>
+    <t>13:00～13:40</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>tt-d1-11</t>
+  </si>
+  <si>
+    <t>13:55～14:25</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>tt-d1-12</t>
+  </si>
+  <si>
+    <t>10:00～16:00</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>tt-d1-13</t>
+  </si>
+  <si>
+    <t>13:00～14:00</t>
+  </si>
+  <si>
+    <t>14:00</t>
+  </si>
+  <si>
+    <t>tt-d1-14</t>
+  </si>
+  <si>
+    <t>13:30～13:45</t>
+  </si>
+  <si>
+    <t>13:30</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>tt-d1-15</t>
+  </si>
+  <si>
+    <t>14:00～14:15</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>tt-d1-16</t>
+  </si>
+  <si>
+    <t>14:45～15:00</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>tt-d1-17</t>
+  </si>
+  <si>
+    <t>15:15～15:30</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>tt-d2-01</t>
+  </si>
+  <si>
+    <t>10:00～10:35</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>tt-d2-02</t>
+  </si>
+  <si>
+    <t>10:50～11:25</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>tt-d2-03</t>
+  </si>
+  <si>
+    <t>11:40～12:15</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>tt-d2-04</t>
+  </si>
+  <si>
+    <t>12:30～13:05</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>tt-d2-05</t>
+  </si>
+  <si>
+    <t>13:20～13:55</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>tt-d2-06</t>
+  </si>
+  <si>
+    <t>14:10～14:45</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
+    <t>tt-d2-07</t>
+  </si>
+  <si>
+    <t>15:15～15:45</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>tt-d2-08</t>
+  </si>
+  <si>
+    <t>16:00～17:00</t>
+  </si>
+  <si>
+    <t>tt-d2-09</t>
+  </si>
+  <si>
+    <t>12:00～12:30</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>tt-d2-10</t>
+  </si>
+  <si>
+    <t>13:00～13:30</t>
+  </si>
+  <si>
+    <t>tt-d2-11</t>
+  </si>
+  <si>
+    <t>開場15:30 開演16:30</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>tt-d2-12</t>
+  </si>
+  <si>
+    <t>tt-d2-13</t>
+  </si>
+  <si>
+    <t>13:00～13:15</t>
+  </si>
+  <si>
+    <t>tt-d2-14</t>
+  </si>
+  <si>
+    <t>tt-d2-15</t>
+  </si>
+  <si>
+    <t>tt-d2-16</t>
+  </si>
+  <si>
+    <t>14:30～14:45</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>food-oystars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>culture-oystars</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>food-mogi-shutten</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>culture-shinsengumi</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>culture-tetsudo-bu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>music-jazz-bu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>チャペルコンサート</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>ソプラノ演奏</t>
+    <rPh sb="4" eb="6">
+      <t>エンソウ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>music-hn-entertainment</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>music-kannai-sukayutopia</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>food-sado-bu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>food-ojosama-select</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>food-shashin-bu</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
       <sz val="6"/>
@@ -1711,26 +1746,6 @@
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF79C0FF"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF79C0FF"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF79C0FF"/>
-      <name val="Consolas"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1741,7 +1756,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1749,25 +1764,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1854,7 +1880,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1889,7 +1914,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1924,16 +1948,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -2055,78 +2083,49 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="23.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="74.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="255.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2184,247 +2183,244 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
+        <v>543</v>
+      </c>
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
         <v>27</v>
-      </c>
-      <c r="H4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
+        <v>531</v>
+      </c>
+      <c r="B5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
-      </c>
-      <c r="H5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>34</v>
-      </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7" t="s">
         <v>40</v>
-      </c>
-      <c r="B7" t="s">
-        <v>41</v>
-      </c>
-      <c r="C7" t="s">
-        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="H8" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>533</v>
+      </c>
+      <c r="B9" t="s">
         <v>49</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>50</v>
-      </c>
-      <c r="C9" t="s">
-        <v>51</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" t="s">
         <v>53</v>
-      </c>
-      <c r="H9" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
+        <v>54</v>
+      </c>
+      <c r="B10" t="s">
         <v>55</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>56</v>
-      </c>
-      <c r="C10" t="s">
-        <v>57</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" t="s">
         <v>59</v>
-      </c>
-      <c r="H10" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" t="s">
         <v>61</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>62</v>
-      </c>
-      <c r="C11" t="s">
-        <v>63</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
+        <v>64</v>
+      </c>
+      <c r="H11" t="s">
         <v>65</v>
-      </c>
-      <c r="H11" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B12" t="s">
         <v>67</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>68</v>
-      </c>
-      <c r="C12" t="s">
-        <v>69</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" t="s">
         <v>71</v>
-      </c>
-      <c r="H12" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>542</v>
+      </c>
+      <c r="B13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C13" t="s">
         <v>73</v>
-      </c>
-      <c r="B13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C13" t="s">
-        <v>69</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
@@ -2436,833 +2432,859 @@
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H14" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H16" t="s">
-        <v>33</v>
+        <v>94</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H17" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B18" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H18" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C19" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="H19" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="C20" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="H20" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B21" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C21" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="H21" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B22" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C22" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H22" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B23" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="H23" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B24" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C24" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F24" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G24" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="H24" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>541</v>
       </c>
       <c r="B25" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C25" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H25" t="s">
-        <v>145</v>
+        <v>147</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" t="s">
+        <v>149</v>
+      </c>
+      <c r="C26" t="s">
+        <v>150</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>151</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:H25" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="198.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="D2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="D3" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E3" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B4" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="C4" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="D4" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E4" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E5" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B6" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D6" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B7" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="C7" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E7" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B8" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="C8" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E8" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>181</v>
+        <v>534</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
-      <c r="G9" t="s">
-        <v>33</v>
-      </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D10" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B11" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E11" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C12" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E12" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B13" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C13" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E13" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>202</v>
+        <v>535</v>
       </c>
       <c r="B14" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="C14" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E14" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>207</v>
+        <v>532</v>
       </c>
       <c r="B15" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E15" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C16" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D16" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E16" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:G16" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="27.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="145.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D3" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="C4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>536</v>
       </c>
       <c r="B5" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C5" t="s">
         <v>232</v>
       </c>
       <c r="D5" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E5" t="s">
         <v>233</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
-      </c>
-      <c r="G5" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
@@ -3270,13 +3292,13 @@
         <v>234</v>
       </c>
       <c r="B6" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C6" t="s">
         <v>235</v>
       </c>
       <c r="D6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E6" t="s">
         <v>236</v>
@@ -3293,13 +3315,13 @@
         <v>238</v>
       </c>
       <c r="B7" t="s">
-        <v>217</v>
+        <v>239</v>
       </c>
       <c r="C7" t="s">
         <v>239</v>
       </c>
       <c r="D7" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E7" t="s">
         <v>240</v>
@@ -3313,1261 +3335,1176 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>242</v>
+        <v>540</v>
       </c>
       <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" t="s">
         <v>243</v>
-      </c>
-      <c r="C8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" t="s">
-        <v>219</v>
-      </c>
-      <c r="E8" t="s">
-        <v>244</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
+        <v>245</v>
+      </c>
+      <c r="B9" t="s">
         <v>246</v>
       </c>
-      <c r="B9" t="s">
-        <v>247</v>
-      </c>
       <c r="C9" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B10" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="C10" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C11" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="D11" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>258</v>
+        <v>539</v>
       </c>
       <c r="B12" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="C12" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D12" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E12" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B13" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C13" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E13" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="F13" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G13" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B14" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C14" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E14" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B15" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C15" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="D15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E15" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B16" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C16" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D16" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E16" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B17" t="s">
-        <v>284</v>
+        <v>537</v>
       </c>
       <c r="C17" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="D17" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E17" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B18" t="s">
-        <v>284</v>
+        <v>537</v>
       </c>
       <c r="C18" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="D18" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E18" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B19" t="s">
-        <v>291</v>
+        <v>538</v>
       </c>
       <c r="C19" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="D19" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E19" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B20" t="s">
-        <v>284</v>
+        <v>537</v>
       </c>
       <c r="C20" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="D20" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E20" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F20" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G20" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B21" t="s">
-        <v>284</v>
+        <v>537</v>
       </c>
       <c r="C21" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="D21" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="E21" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="F21" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G21" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:G21" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="5.796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.09765625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.69921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="55.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="64.5" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="316.8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B2" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C2" t="s">
-        <v>524</v>
+        <v>292</v>
       </c>
       <c r="D2" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="E2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>520</v>
+        <v>140</v>
+      </c>
+      <c r="G2" t="s">
+        <v>294</v>
+      </c>
+      <c r="H2" t="s">
+        <v>295</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:H1 A2:B2 D2:F2" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F52"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F56"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="19.09765625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="25.796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="26.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" t="s">
-        <v>301</v>
-      </c>
-      <c r="C1" t="s">
-        <v>302</v>
-      </c>
-      <c r="D1" t="s">
-        <v>303</v>
-      </c>
-      <c r="E1" t="s">
-        <v>304</v>
-      </c>
-      <c r="F1" t="s">
-        <v>305</v>
+      <c r="B1" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
-        <v>33</v>
-      </c>
       <c r="C2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>19</v>
       </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
       <c r="C3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D3" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E3" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F3" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D4" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E4" t="s">
+        <v>303</v>
+      </c>
+      <c r="F4" t="s">
         <v>308</v>
-      </c>
-      <c r="F4" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>32</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D5" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E5" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F5" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="D6" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E6" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F6" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D7" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E7" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F7" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>48</v>
-      </c>
-      <c r="B8" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C8" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="D8" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E8" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F8" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D9" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E9" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F9" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>58</v>
-      </c>
-      <c r="B10" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="D10" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E10" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F10" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>64</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C11" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="D11" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E11" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F11" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="D12" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E12" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F12" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>74</v>
       </c>
-      <c r="B13" t="s">
-        <v>33</v>
-      </c>
       <c r="C13" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="D13" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E13" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F13" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" t="s">
-        <v>33</v>
+        <v>80</v>
       </c>
       <c r="C14" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D14" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E14" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F14" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>84</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="C15" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="D15" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E15" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F15" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>90</v>
-      </c>
-      <c r="B16" t="s">
-        <v>33</v>
+        <v>92</v>
       </c>
       <c r="C16" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="D16" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E16" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F16" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>95</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="C17" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D17" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E17" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F17" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>101</v>
-      </c>
-      <c r="B18" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="C18" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="D18" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E18" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F18" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="C19" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="D19" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E19" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F19" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B20" t="s">
-        <v>33</v>
+        <v>116</v>
       </c>
       <c r="C20" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D20" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E20" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F20" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>119</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="C21" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="D21" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E21" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F21" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>125</v>
-      </c>
-      <c r="B22" t="s">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="C22" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="D22" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E22" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F22" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>131</v>
-      </c>
-      <c r="B23" t="s">
-        <v>33</v>
+        <v>134</v>
       </c>
       <c r="C23" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D23" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E23" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F23" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>143</v>
-      </c>
-      <c r="B24" t="s">
-        <v>33</v>
+        <v>145</v>
       </c>
       <c r="C24" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D24" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B25" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C25" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D25" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
       <c r="F25" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C26" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="D26" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
       <c r="F26" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="B27" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="C27" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="D27" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B28" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C28" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="D28" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B29" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C29" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="D29" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="B30" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C30" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="D30" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B31" t="s">
+        <v>362</v>
+      </c>
+      <c r="C31" t="s">
         <v>367</v>
       </c>
-      <c r="C31" t="s">
-        <v>372</v>
-      </c>
       <c r="D31" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B32" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C32" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="D32" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
       <c r="F32" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="B33" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C33" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="D33" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
       <c r="F33" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="B34" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C34" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="D34" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="B35" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C35" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D35" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C36" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="D36" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B37" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C37" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="D37" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
       <c r="F37" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B38" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C38" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D38" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
       <c r="F38" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C39" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="D39" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>220</v>
+        <v>381</v>
       </c>
       <c r="B40" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C40" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="D40" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
       <c r="F40" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B41" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C41" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D41" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
       <c r="F41" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>228</v>
+        <v>386</v>
       </c>
       <c r="B42" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C42" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D42" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E42">
         <v>3</v>
       </c>
       <c r="F42" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.2">
@@ -4575,39 +4512,39 @@
         <v>233</v>
       </c>
       <c r="B43" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C43" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D43" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
       <c r="F43" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>236</v>
+        <v>391</v>
       </c>
       <c r="B44" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C44" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D44" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E44">
         <v>4</v>
       </c>
       <c r="F44" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
@@ -4615,205 +4552,267 @@
         <v>240</v>
       </c>
       <c r="B45" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C45" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="D45" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E45">
         <v>4</v>
       </c>
       <c r="F45" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>261</v>
-      </c>
-      <c r="B46" t="s">
-        <v>33</v>
+        <v>256</v>
       </c>
       <c r="C46" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D46" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E46" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F46" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B47" t="s">
+        <v>397</v>
+      </c>
+      <c r="C47" t="s">
+        <v>398</v>
+      </c>
+      <c r="D47" t="s">
         <v>399</v>
-      </c>
-      <c r="C47" t="s">
-        <v>400</v>
-      </c>
-      <c r="D47" t="s">
-        <v>401</v>
       </c>
       <c r="E47">
         <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>281</v>
-      </c>
-      <c r="B48" t="s">
-        <v>33</v>
+        <v>275</v>
       </c>
       <c r="C48" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="D48" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>276</v>
-      </c>
-      <c r="B49" t="s">
-        <v>33</v>
+        <v>270</v>
       </c>
       <c r="C49" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="D49" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E49" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F49" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>286</v>
-      </c>
-      <c r="B50" t="s">
-        <v>33</v>
+        <v>279</v>
       </c>
       <c r="C50" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D50" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>266</v>
-      </c>
-      <c r="B51" t="s">
-        <v>33</v>
+        <v>260</v>
       </c>
       <c r="C51" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="D51" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="E51">
         <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="B52" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="C52" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D52" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>151</v>
+      </c>
+      <c r="B53" t="s">
+        <v>350</v>
+      </c>
+      <c r="C53" t="s">
+        <v>410</v>
+      </c>
+      <c r="D53" t="s">
+        <v>352</v>
+      </c>
+      <c r="E53" t="s">
+        <v>304</v>
+      </c>
+      <c r="F53" t="s">
         <v>411</v>
       </c>
     </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>236</v>
+      </c>
+      <c r="B54" t="s">
+        <v>382</v>
+      </c>
+      <c r="C54" t="s">
+        <v>412</v>
+      </c>
+      <c r="D54" t="s">
+        <v>384</v>
+      </c>
+      <c r="E54" t="s">
+        <v>306</v>
+      </c>
+      <c r="F54" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>221</v>
+      </c>
+      <c r="B55" t="s">
+        <v>382</v>
+      </c>
+      <c r="C55" t="s">
+        <v>414</v>
+      </c>
+      <c r="D55" t="s">
+        <v>384</v>
+      </c>
+      <c r="E55" t="s">
+        <v>310</v>
+      </c>
+      <c r="F55" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>225</v>
+      </c>
+      <c r="B56" t="s">
+        <v>382</v>
+      </c>
+      <c r="C56" t="s">
+        <v>416</v>
+      </c>
+      <c r="D56" t="s">
+        <v>384</v>
+      </c>
+      <c r="E56" t="s">
+        <v>308</v>
+      </c>
+      <c r="F56" t="s">
+        <v>417</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:F52" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
-        <v>413</v>
-      </c>
-      <c r="F1" t="s">
-        <v>414</v>
-      </c>
-      <c r="G1" t="s">
-        <v>415</v>
-      </c>
-      <c r="H1" t="s">
-        <v>416</v>
-      </c>
-      <c r="I1" t="s">
-        <v>417</v>
-      </c>
-      <c r="J1" t="s">
-        <v>418</v>
+      <c r="E1" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.2">
@@ -4821,22 +4820,22 @@
         <v>238</v>
       </c>
       <c r="B2" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="C2" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E2" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="F2" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="G2" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="H2">
         <v>600</v>
@@ -4850,25 +4849,25 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B3" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="C3" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E3" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="F3" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="G3" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="H3">
         <v>665</v>
@@ -4882,25 +4881,25 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B4" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="C4" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E4" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="F4" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="G4" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="H4">
         <v>730</v>
@@ -4914,25 +4913,25 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B5" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C5" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E5" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="F5" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="G5" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="H5">
         <v>795</v>
@@ -4949,22 +4948,22 @@
         <v>234</v>
       </c>
       <c r="B6" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="C6" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E6" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="F6" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="G6" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="H6">
         <v>860</v>
@@ -4978,25 +4977,25 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B7" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="C7" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E7" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="F7" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="G7" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="H7">
         <v>925</v>
@@ -5010,25 +5009,25 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B8" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C8" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E8" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="F8" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="G8" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="H8">
         <v>990</v>
@@ -5045,22 +5044,22 @@
         <v>242</v>
       </c>
       <c r="B9" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="C9" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="F9" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="G9" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="H9">
         <v>660</v>
@@ -5074,25 +5073,25 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B10" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="C10" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="F10" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="G10" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="H10">
         <v>705</v>
@@ -5106,25 +5105,25 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B11" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C11" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="F11" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G11" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="H11">
         <v>780</v>
@@ -5138,25 +5137,25 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B12" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C12" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F12" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="G12" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="H12">
         <v>835</v>
@@ -5170,25 +5169,25 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B13" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C13" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E13" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="F13" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="G13" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="H13">
         <v>600</v>
@@ -5202,25 +5201,25 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="B14" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="C14" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E14" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="F14" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G14" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="H14">
         <v>780</v>
@@ -5234,25 +5233,25 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B15" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C15" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E15" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F15" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="G15" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="H15">
         <v>810</v>
@@ -5266,25 +5265,25 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="B16" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C16" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E16" t="s">
+        <v>479</v>
+      </c>
+      <c r="F16" t="s">
         <v>473</v>
       </c>
-      <c r="F16" t="s">
-        <v>467</v>
-      </c>
       <c r="G16" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="H16">
         <v>840</v>
@@ -5298,25 +5297,25 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="B17" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C17" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E17" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F17" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="G17" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="H17">
         <v>885</v>
@@ -5330,25 +5329,25 @@
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B18" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C18" t="s">
-        <v>521</v>
+        <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E18" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="F18" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="G18" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="H18">
         <v>915</v>
@@ -5365,127 +5364,127 @@
         <v>238</v>
       </c>
       <c r="B19" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="C19" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D19" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E19" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="F19" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="G19" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="H19">
         <v>600</v>
       </c>
       <c r="I19">
-        <v>630</v>
+        <v>635</v>
       </c>
       <c r="J19">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B20" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="C20" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D20" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E20" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="F20" t="s">
-        <v>488</v>
+        <v>428</v>
       </c>
       <c r="G20" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="H20">
-        <v>645</v>
+        <v>650</v>
       </c>
       <c r="I20">
-        <v>675</v>
+        <v>685</v>
       </c>
       <c r="J20">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B21" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C21" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D21" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E21" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="F21" t="s">
-        <v>450</v>
+        <v>497</v>
       </c>
       <c r="G21" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="H21">
-        <v>690</v>
+        <v>700</v>
       </c>
       <c r="I21">
-        <v>720</v>
+        <v>735</v>
       </c>
       <c r="J21">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B22" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="C22" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D22" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E22" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="F22" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="G22" t="s">
-        <v>454</v>
+        <v>502</v>
       </c>
       <c r="H22">
-        <v>735</v>
+        <v>750</v>
       </c>
       <c r="I22">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="J22">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.2">
@@ -5493,118 +5492,118 @@
         <v>234</v>
       </c>
       <c r="B23" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="C23" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D23" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E23" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="F23" t="s">
-        <v>430</v>
+        <v>505</v>
       </c>
       <c r="G23" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="H23">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="I23">
-        <v>810</v>
+        <v>835</v>
       </c>
       <c r="J23">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B24" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C24" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D24" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E24" t="s">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="F24" t="s">
-        <v>471</v>
+        <v>508</v>
       </c>
       <c r="G24" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="H24">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="I24">
-        <v>855</v>
+        <v>885</v>
       </c>
       <c r="J24">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="C25" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D25" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E25" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="F25" t="s">
-        <v>477</v>
+        <v>487</v>
       </c>
       <c r="G25" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="H25">
-        <v>885</v>
+        <v>915</v>
       </c>
       <c r="I25">
         <v>945</v>
       </c>
       <c r="J25">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="C26" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D26" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="E26" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="F26" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="G26" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="H26">
         <v>960</v>
@@ -5621,22 +5620,22 @@
         <v>242</v>
       </c>
       <c r="B27" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C27" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D27" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="F27" t="s">
-        <v>492</v>
+        <v>516</v>
       </c>
       <c r="G27" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
       <c r="H27">
         <v>720</v>
@@ -5650,25 +5649,25 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C28" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D28" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>497</v>
+        <v>518</v>
       </c>
       <c r="F28" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G28" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="H28">
         <v>780</v>
@@ -5682,25 +5681,25 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B29" t="s">
-        <v>509</v>
+        <v>519</v>
       </c>
       <c r="C29" t="s">
+        <v>140</v>
+      </c>
+      <c r="D29" t="s">
+        <v>243</v>
+      </c>
+      <c r="E29" t="s">
+        <v>520</v>
+      </c>
+      <c r="F29" t="s">
+        <v>521</v>
+      </c>
+      <c r="G29" t="s">
         <v>522</v>
-      </c>
-      <c r="D29" t="s">
-        <v>244</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0.64583333333333337</v>
-      </c>
-      <c r="G29" t="s">
-        <v>510</v>
       </c>
       <c r="H29">
         <v>930</v>
@@ -5714,25 +5713,25 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="C30" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D30" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="E30" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="F30" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="G30" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="H30">
         <v>600</v>
@@ -5746,25 +5745,25 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B31" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
       <c r="C31" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D31" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E31" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="F31" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G31" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="H31">
         <v>780</v>
@@ -5778,25 +5777,25 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="C32" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D32" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E32" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F32" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="G32" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="H32">
         <v>810</v>
@@ -5810,25 +5809,25 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="C33" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D33" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E33" t="s">
+        <v>479</v>
+      </c>
+      <c r="F33" t="s">
         <v>473</v>
       </c>
-      <c r="F33" t="s">
-        <v>467</v>
-      </c>
       <c r="G33" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="H33">
         <v>840</v>
@@ -5842,25 +5841,25 @@
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="B34" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="C34" t="s">
-        <v>522</v>
+        <v>140</v>
       </c>
       <c r="D34" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="E34" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="F34" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="G34" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="H34">
         <v>870</v>
@@ -5873,10 +5872,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:J1 A7:B7 A2:B2 D2:J2 A3:B3 D3:J3 A4:B4 D4:J4 A5:B5 D5:J5 A6:B6 D6:J6 A34:B34 A8:B8 D8:J8 D7:J7 A9:B9 D9:J9 A10:B10 D10:J10 A11:B11 D11:J11 A12:B12 D12:J12 A13:B13 D13:J13 A14:B14 D14:J14 A15:B15 D15:J15 A16:B16 D16:J16 A17:B17 D17:J17 A18:B18 D18:J18 A19:B19 D19:J19 A20:B20 D20:J20 A21:B21 D21:J21 A22:B22 D22:J22 A23:B23 D23:J23 A24:B24 D24:J24 A25:B25 D25:J25 A26:B26 D26:J26 A27:B27 D27:J27 A28:B28 D28:J28 A29:B29 D29 A30:B30 D30:J30 A31:B31 D31:J31 A32:B32 D32:J32 A33:B33 D33:J33 D34:J34 G29 I29" numberStoredAsText="1"/>
-  </ignoredErrors>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkytw\Desktop\GitHub\Home-Page\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3A64E29-3654-4352-BE58-95A3A944CD5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCDCEE3-E4E4-4968-8F48-ED0CB339CFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mogiten" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="544">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="543">
   <si>
     <t>id</t>
   </si>
@@ -1691,13 +1691,6 @@
   </si>
   <si>
     <t>チャペルコンサート</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>ソプラノ演奏</t>
-    <rPh sb="4" eb="6">
-      <t>エンソウ</t>
-    </rPh>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2183,7 +2176,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -2414,7 +2407,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B13" t="s">
         <v>72</v>
@@ -2726,7 +2719,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B25" t="s">
         <v>143</v>
@@ -3335,7 +3328,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B8" t="s">
         <v>91</v>
@@ -3427,7 +3420,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B12" t="s">
         <v>255</v>
@@ -3591,7 +3584,7 @@
         <v>283</v>
       </c>
       <c r="B19" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C19" t="s">
         <v>284</v>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkytw\Desktop\GitHub\Home-Page\app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BCDCEE3-E4E4-4968-8F48-ED0CB339CFD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A58DB29-A7F7-4FB9-B929-58BE8BE5F57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="mogiten" sheetId="1" r:id="rId1"/>
     <sheet name="culture" sheetId="2" r:id="rId2"/>
     <sheet name="music" sheetId="3" r:id="rId3"/>
-    <sheet name="geinou" sheetId="4" r:id="rId4"/>
+    <sheet name="other" sheetId="4" r:id="rId4"/>
     <sheet name="location" sheetId="5" r:id="rId5"/>
     <sheet name="timetable" sheetId="6" r:id="rId6"/>
   </sheets>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1000" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="552">
   <si>
     <t>id</t>
   </si>
@@ -1339,15 +1339,6 @@
     <t>endTime</t>
   </si>
   <si>
-    <t>startMinutes</t>
-  </si>
-  <si>
-    <t>endMinutes</t>
-  </si>
-  <si>
-    <t>durationMinutes</t>
-  </si>
-  <si>
     <t>tt-d1-01</t>
   </si>
   <si>
@@ -1711,6 +1702,61 @@
   </si>
   <si>
     <t>food-shashin-bu</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>id</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>soccer</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>JR東日本カップ2026 第100回関東大学サッカーリーグ戦</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>その他</t>
+    <rPh sb="2" eb="3">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>loc-ground</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>入場無料</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>第19節関東学院大学vs立教大学
+10/31 (土)14:00キックオフ、ぜひご観戦ください！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>tt-d1-18</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>day1</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>14:00キックオフ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>グラウンド</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>屋外</t>
+    <rPh sb="0" eb="2">
+      <t>オクガイ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1776,11 +1822,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2176,7 +2226,7 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
@@ -2202,7 +2252,7 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="B5" t="s">
         <v>28</v>
@@ -2303,7 +2353,7 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="B9" t="s">
         <v>49</v>
@@ -2407,7 +2457,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="B13" t="s">
         <v>72</v>
@@ -2719,7 +2769,7 @@
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="B25" t="s">
         <v>143</v>
@@ -2969,7 +3019,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="B9" t="s">
         <v>186</v>
@@ -3081,7 +3131,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="B14" t="s">
         <v>206</v>
@@ -3104,7 +3154,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B15" t="s">
         <v>210</v>
@@ -3262,7 +3312,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="B5" t="s">
         <v>232</v>
@@ -3328,7 +3378,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="B8" t="s">
         <v>91</v>
@@ -3420,7 +3470,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B12" t="s">
         <v>255</v>
@@ -3538,7 +3588,7 @@
         <v>277</v>
       </c>
       <c r="B17" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C17" t="s">
         <v>278</v>
@@ -3561,7 +3611,7 @@
         <v>281</v>
       </c>
       <c r="B18" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C18" t="s">
         <v>282</v>
@@ -3584,7 +3634,7 @@
         <v>283</v>
       </c>
       <c r="B19" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C19" t="s">
         <v>284</v>
@@ -3607,7 +3657,7 @@
         <v>286</v>
       </c>
       <c r="B20" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C20" t="s">
         <v>287</v>
@@ -3630,7 +3680,7 @@
         <v>288</v>
       </c>
       <c r="B21" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="C21" t="s">
         <v>289</v>
@@ -3656,12 +3706,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="255.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -3709,6 +3768,29 @@
       </c>
       <c r="H2" t="s">
         <v>295</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="26.4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B3" t="s">
+        <v>542</v>
+      </c>
+      <c r="D3" t="s">
+        <v>543</v>
+      </c>
+      <c r="E3" t="s">
+        <v>544</v>
+      </c>
+      <c r="F3" t="s">
+        <v>548</v>
+      </c>
+      <c r="G3" t="s">
+        <v>545</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>546</v>
       </c>
     </row>
   </sheetData>
@@ -3719,7 +3801,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
@@ -4765,6 +4847,23 @@
         <v>417</v>
       </c>
     </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>544</v>
+      </c>
+      <c r="C57" t="s">
+        <v>550</v>
+      </c>
+      <c r="D57" t="s">
+        <v>550</v>
+      </c>
+      <c r="E57" t="s">
+        <v>551</v>
+      </c>
+      <c r="F57" t="s">
+        <v>550</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4773,10 +4872,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4798,22 +4897,13 @@
       <c r="G1" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>422</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>238</v>
       </c>
       <c r="B2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -4822,30 +4912,21 @@
         <v>256</v>
       </c>
       <c r="E2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="G2" t="s">
-        <v>428</v>
-      </c>
-      <c r="H2">
-        <v>600</v>
-      </c>
-      <c r="I2">
-        <v>650</v>
-      </c>
-      <c r="J2">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>218</v>
       </c>
       <c r="B3" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -4854,30 +4935,21 @@
         <v>256</v>
       </c>
       <c r="E3" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="F3" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="G3" t="s">
-        <v>432</v>
-      </c>
-      <c r="H3">
-        <v>665</v>
-      </c>
-      <c r="I3">
-        <v>715</v>
-      </c>
-      <c r="J3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>223</v>
       </c>
       <c r="B4" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -4886,30 +4958,21 @@
         <v>256</v>
       </c>
       <c r="E4" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="F4" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="G4" t="s">
-        <v>436</v>
-      </c>
-      <c r="H4">
-        <v>730</v>
-      </c>
-      <c r="I4">
-        <v>780</v>
-      </c>
-      <c r="J4">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>231</v>
       </c>
       <c r="B5" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -4918,30 +4981,21 @@
         <v>256</v>
       </c>
       <c r="E5" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F5" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="G5" t="s">
-        <v>440</v>
-      </c>
-      <c r="H5">
-        <v>795</v>
-      </c>
-      <c r="I5">
-        <v>845</v>
-      </c>
-      <c r="J5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>234</v>
       </c>
       <c r="B6" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -4950,30 +5004,21 @@
         <v>256</v>
       </c>
       <c r="E6" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="F6" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="G6" t="s">
-        <v>444</v>
-      </c>
-      <c r="H6">
-        <v>860</v>
-      </c>
-      <c r="I6">
-        <v>910</v>
-      </c>
-      <c r="J6">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>227</v>
       </c>
       <c r="B7" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
@@ -4982,30 +5027,21 @@
         <v>256</v>
       </c>
       <c r="E7" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F7" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="G7" t="s">
-        <v>448</v>
-      </c>
-      <c r="H7">
-        <v>925</v>
-      </c>
-      <c r="I7">
-        <v>975</v>
-      </c>
-      <c r="J7">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>254</v>
       </c>
       <c r="B8" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
@@ -5014,30 +5050,21 @@
         <v>256</v>
       </c>
       <c r="E8" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="F8" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="G8" t="s">
-        <v>452</v>
-      </c>
-      <c r="H8">
-        <v>990</v>
-      </c>
-      <c r="I8">
-        <v>1020</v>
-      </c>
-      <c r="J8">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>242</v>
       </c>
       <c r="B9" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -5046,30 +5073,21 @@
         <v>243</v>
       </c>
       <c r="E9" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="F9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G9" t="s">
-        <v>456</v>
-      </c>
-      <c r="H9">
-        <v>660</v>
-      </c>
-      <c r="I9">
-        <v>690</v>
-      </c>
-      <c r="J9">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>245</v>
       </c>
       <c r="B10" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -5078,30 +5096,21 @@
         <v>243</v>
       </c>
       <c r="E10" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F10" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G10" t="s">
-        <v>460</v>
-      </c>
-      <c r="H10">
-        <v>705</v>
-      </c>
-      <c r="I10">
-        <v>765</v>
-      </c>
-      <c r="J10">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>248</v>
       </c>
       <c r="B11" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -5110,30 +5119,21 @@
         <v>243</v>
       </c>
       <c r="E11" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="F11" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G11" t="s">
-        <v>463</v>
-      </c>
-      <c r="H11">
-        <v>780</v>
-      </c>
-      <c r="I11">
-        <v>820</v>
-      </c>
-      <c r="J11">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>251</v>
       </c>
       <c r="B12" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -5142,30 +5142,21 @@
         <v>243</v>
       </c>
       <c r="E12" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="F12" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="G12" t="s">
-        <v>467</v>
-      </c>
-      <c r="H12">
-        <v>835</v>
-      </c>
-      <c r="I12">
-        <v>865</v>
-      </c>
-      <c r="J12">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>272</v>
       </c>
       <c r="B13" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
@@ -5174,30 +5165,21 @@
         <v>275</v>
       </c>
       <c r="E13" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F13" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="G13" t="s">
-        <v>470</v>
-      </c>
-      <c r="H13">
-        <v>600</v>
-      </c>
-      <c r="I13">
-        <v>960</v>
-      </c>
-      <c r="J13">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>267</v>
       </c>
       <c r="B14" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
@@ -5206,30 +5188,21 @@
         <v>270</v>
       </c>
       <c r="E14" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="F14" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G14" t="s">
-        <v>473</v>
-      </c>
-      <c r="H14">
-        <v>780</v>
-      </c>
-      <c r="I14">
-        <v>840</v>
-      </c>
-      <c r="J14">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>277</v>
       </c>
       <c r="B15" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -5238,30 +5211,21 @@
         <v>279</v>
       </c>
       <c r="E15" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F15" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="G15" t="s">
-        <v>477</v>
-      </c>
-      <c r="H15">
-        <v>810</v>
-      </c>
-      <c r="I15">
-        <v>825</v>
-      </c>
-      <c r="J15">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>277</v>
       </c>
       <c r="B16" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
@@ -5270,30 +5234,21 @@
         <v>279</v>
       </c>
       <c r="E16" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F16" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="G16" t="s">
-        <v>480</v>
-      </c>
-      <c r="H16">
-        <v>840</v>
-      </c>
-      <c r="I16">
-        <v>855</v>
-      </c>
-      <c r="J16">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>281</v>
       </c>
       <c r="B17" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
@@ -5302,30 +5257,21 @@
         <v>279</v>
       </c>
       <c r="E17" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="F17" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="G17" t="s">
-        <v>484</v>
-      </c>
-      <c r="H17">
-        <v>885</v>
-      </c>
-      <c r="I17">
-        <v>900</v>
-      </c>
-      <c r="J17">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>283</v>
       </c>
       <c r="B18" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -5334,30 +5280,21 @@
         <v>279</v>
       </c>
       <c r="E18" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F18" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="G18" t="s">
-        <v>488</v>
-      </c>
-      <c r="H18">
-        <v>915</v>
-      </c>
-      <c r="I18">
-        <v>930</v>
-      </c>
-      <c r="J18">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.2">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>238</v>
       </c>
       <c r="B19" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C19" t="s">
         <v>140</v>
@@ -5366,30 +5303,21 @@
         <v>256</v>
       </c>
       <c r="E19" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F19" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="G19" t="s">
-        <v>491</v>
-      </c>
-      <c r="H19">
-        <v>600</v>
-      </c>
-      <c r="I19">
-        <v>635</v>
-      </c>
-      <c r="J19">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>218</v>
       </c>
       <c r="B20" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="C20" t="s">
         <v>140</v>
@@ -5398,30 +5326,21 @@
         <v>256</v>
       </c>
       <c r="E20" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="F20" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="G20" t="s">
-        <v>494</v>
-      </c>
-      <c r="H20">
-        <v>650</v>
-      </c>
-      <c r="I20">
-        <v>685</v>
-      </c>
-      <c r="J20">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.2">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>223</v>
       </c>
       <c r="B21" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="C21" t="s">
         <v>140</v>
@@ -5430,30 +5349,21 @@
         <v>256</v>
       </c>
       <c r="E21" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="F21" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="G21" t="s">
-        <v>498</v>
-      </c>
-      <c r="H21">
-        <v>700</v>
-      </c>
-      <c r="I21">
-        <v>735</v>
-      </c>
-      <c r="J21">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.2">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>231</v>
       </c>
       <c r="B22" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="C22" t="s">
         <v>140</v>
@@ -5462,30 +5372,21 @@
         <v>256</v>
       </c>
       <c r="E22" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F22" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="G22" t="s">
-        <v>502</v>
-      </c>
-      <c r="H22">
-        <v>750</v>
-      </c>
-      <c r="I22">
-        <v>785</v>
-      </c>
-      <c r="J22">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>234</v>
       </c>
       <c r="B23" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="C23" t="s">
         <v>140</v>
@@ -5494,30 +5395,21 @@
         <v>256</v>
       </c>
       <c r="E23" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="F23" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="G23" t="s">
-        <v>466</v>
-      </c>
-      <c r="H23">
-        <v>800</v>
-      </c>
-      <c r="I23">
-        <v>835</v>
-      </c>
-      <c r="J23">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.2">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>227</v>
       </c>
       <c r="B24" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C24" t="s">
         <v>140</v>
@@ -5526,30 +5418,21 @@
         <v>256</v>
       </c>
       <c r="E24" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="F24" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="G24" t="s">
-        <v>483</v>
-      </c>
-      <c r="H24">
-        <v>850</v>
-      </c>
-      <c r="I24">
-        <v>885</v>
-      </c>
-      <c r="J24">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>254</v>
       </c>
       <c r="B25" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="C25" t="s">
         <v>140</v>
@@ -5558,30 +5441,21 @@
         <v>256</v>
       </c>
       <c r="E25" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="F25" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="G25" t="s">
-        <v>511</v>
-      </c>
-      <c r="H25">
-        <v>915</v>
-      </c>
-      <c r="I25">
-        <v>945</v>
-      </c>
-      <c r="J25">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.2">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>258</v>
       </c>
       <c r="B26" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="C26" t="s">
         <v>140</v>
@@ -5590,30 +5464,21 @@
         <v>256</v>
       </c>
       <c r="E26" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="F26" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="G26" t="s">
-        <v>452</v>
-      </c>
-      <c r="H26">
-        <v>960</v>
-      </c>
-      <c r="I26">
-        <v>1020</v>
-      </c>
-      <c r="J26">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.2">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>242</v>
       </c>
       <c r="B27" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="C27" t="s">
         <v>140</v>
@@ -5622,30 +5487,21 @@
         <v>243</v>
       </c>
       <c r="E27" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F27" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="G27" t="s">
-        <v>501</v>
-      </c>
-      <c r="H27">
-        <v>720</v>
-      </c>
-      <c r="I27">
-        <v>750</v>
-      </c>
-      <c r="J27">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>251</v>
       </c>
       <c r="B28" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="C28" t="s">
         <v>140</v>
@@ -5654,30 +5510,21 @@
         <v>243</v>
       </c>
       <c r="E28" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F28" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G28" t="s">
-        <v>476</v>
-      </c>
-      <c r="H28">
-        <v>780</v>
-      </c>
-      <c r="I28">
-        <v>810</v>
-      </c>
-      <c r="J28">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.2">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>290</v>
       </c>
       <c r="B29" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="C29" t="s">
         <v>140</v>
@@ -5686,30 +5533,21 @@
         <v>243</v>
       </c>
       <c r="E29" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="F29" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="G29" t="s">
-        <v>522</v>
-      </c>
-      <c r="H29">
-        <v>930</v>
-      </c>
-      <c r="I29">
-        <v>1050</v>
-      </c>
-      <c r="J29">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>272</v>
       </c>
       <c r="B30" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="C30" t="s">
         <v>140</v>
@@ -5718,30 +5556,21 @@
         <v>275</v>
       </c>
       <c r="E30" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="F30" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="G30" t="s">
-        <v>470</v>
-      </c>
-      <c r="H30">
-        <v>600</v>
-      </c>
-      <c r="I30">
-        <v>960</v>
-      </c>
-      <c r="J30">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.2">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>286</v>
       </c>
       <c r="B31" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="C31" t="s">
         <v>140</v>
@@ -5750,30 +5579,21 @@
         <v>279</v>
       </c>
       <c r="E31" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="F31" t="s">
+        <v>433</v>
+      </c>
+      <c r="G31" t="s">
         <v>436</v>
       </c>
-      <c r="G31" t="s">
-        <v>439</v>
-      </c>
-      <c r="H31">
-        <v>780</v>
-      </c>
-      <c r="I31">
-        <v>795</v>
-      </c>
-      <c r="J31">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>286</v>
       </c>
       <c r="B32" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C32" t="s">
         <v>140</v>
@@ -5782,30 +5602,21 @@
         <v>279</v>
       </c>
       <c r="E32" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="F32" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="G32" t="s">
-        <v>477</v>
-      </c>
-      <c r="H32">
-        <v>810</v>
-      </c>
-      <c r="I32">
-        <v>825</v>
-      </c>
-      <c r="J32">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>288</v>
       </c>
       <c r="B33" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="C33" t="s">
         <v>140</v>
@@ -5814,30 +5625,21 @@
         <v>279</v>
       </c>
       <c r="E33" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="F33" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="G33" t="s">
-        <v>480</v>
-      </c>
-      <c r="H33">
-        <v>840</v>
-      </c>
-      <c r="I33">
-        <v>855</v>
-      </c>
-      <c r="J33">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>288</v>
       </c>
       <c r="B34" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="C34" t="s">
         <v>140</v>
@@ -5846,22 +5648,36 @@
         <v>279</v>
       </c>
       <c r="E34" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="F34" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="G34" t="s">
-        <v>483</v>
-      </c>
-      <c r="H34">
-        <v>870</v>
-      </c>
-      <c r="I34">
-        <v>885</v>
-      </c>
-      <c r="J34">
-        <v>15</v>
+        <v>480</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>541</v>
+      </c>
+      <c r="B35" t="s">
+        <v>547</v>
+      </c>
+      <c r="C35" t="s">
+        <v>548</v>
+      </c>
+      <c r="D35" t="s">
+        <v>544</v>
+      </c>
+      <c r="E35" t="s">
+        <v>549</v>
+      </c>
+      <c r="F35" s="3">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="G35" s="3">
+        <v>0.66666666666666663</v>
       </c>
     </row>
   </sheetData>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -1,31 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkytw\Desktop\GitHub\Home-Page\app\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A58DB29-A7F7-4FB9-B929-58BE8BE5F57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="mogiten" sheetId="1" r:id="rId1"/>
-    <sheet name="culture" sheetId="2" r:id="rId2"/>
-    <sheet name="music" sheetId="3" r:id="rId3"/>
-    <sheet name="other" sheetId="4" r:id="rId4"/>
-    <sheet name="location" sheetId="5" r:id="rId5"/>
-    <sheet name="timetable" sheetId="6" r:id="rId6"/>
+    <sheet sheetId="1" name="mogiten" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="culture" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="music" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="other" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="location" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="timetable" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="968" uniqueCount="510">
   <si>
     <t>id</t>
   </si>
@@ -90,7 +81,7 @@
     <t>day1</t>
   </si>
   <si>
-    <t>いちご
+    <t xml:space="preserve">いちご
 ブルーベリー
 チョコ
 キャラメル
@@ -100,6 +91,9 @@
     <t>おいしいパンケーキ屋さん！1年生だけの有志団体です！可愛くて美味しいパンケーキをぜひ食べに来てください♡</t>
   </si>
   <si>
+    <t>food-shashin-bu</t>
+  </si>
+  <si>
     <t>棒餃子</t>
   </si>
   <si>
@@ -115,6 +109,9 @@
     <t>写真部では今年も棒餃子を販売します！平潟祭はこれ食えば間違いナシ！</t>
   </si>
   <si>
+    <t>food-oystars</t>
+  </si>
+  <si>
     <t>筋肉巻き</t>
   </si>
   <si>
@@ -178,6 +175,9 @@
     <t>ジューシーで香ばしい絶品フランクフルトを販売！パリッと弾ける食感と熱々の肉汁がたまりません。食べ歩きに最適ですので、ぜひお立ち寄りください！</t>
   </si>
   <si>
+    <t>food-mogi-shutten</t>
+  </si>
+  <si>
     <t>やきそば</t>
   </si>
   <si>
@@ -241,13 +241,16 @@
     <t>loc-tent-11</t>
   </si>
   <si>
-    <t>黒糖わらび餅抹茶ラテ 1杯 380円_x000D__x000D_
+    <t xml:space="preserve">黒糖わらび餅抹茶ラテ 1杯 380円
 黒糖わらび餅ミルクティー 1杯 380円</t>
   </si>
   <si>
     <t>皆様ごきげんよう！KGUのFABULOUSなお嬢様が作るドリンクはいかが？抽選もあるから是非いらして頂戴！</t>
   </si>
   <si>
+    <t>food-ojosama-select</t>
+  </si>
+  <si>
     <t>アパレル</t>
   </si>
   <si>
@@ -257,7 +260,7 @@
     <t>loc-tent-12</t>
   </si>
   <si>
-    <t>服やグッズの販売
+    <t xml:space="preserve">服やグッズの販売
 2,499円（税込）～7,499円（税込）</t>
   </si>
   <si>
@@ -276,9 +279,9 @@
     <t>loc-tent-13</t>
   </si>
   <si>
-    <t>ソーラーランタン_x000D__x000D_
-ウォーム 1個 4,400円_x000D__x000D_
-クール 1個 4,400円_x000D__x000D_
+    <t xml:space="preserve">ソーラーランタン
+ウォーム 1個 4,400円
+クール 1個 4,400円
 レインボー 1個 5,500円</t>
   </si>
   <si>
@@ -315,10 +318,10 @@
     <t>loc-tent-15</t>
   </si>
   <si>
-    <t>焼き鳥（塩orタレ）_x000D__x000D_
-1本 200円_x000D__x000D_
-3本 500円_x000D__x000D_
-5本 700円_x000D__x000D_
+    <t xml:space="preserve">焼き鳥（塩orタレ）
+1本 200円
+3本 500円
+5本 700円
 缶ビール 1本 400円</t>
   </si>
   <si>
@@ -355,10 +358,10 @@
     <t>loc-tent-17</t>
   </si>
   <si>
-    <t>ひとくちドーナツ_x000D__x000D_
-6個 300円_x000D__x000D_
-8個 350円_x000D__x000D_
-各種ソース ＋50円_x000D__x000D_
+    <t xml:space="preserve">ひとくちドーナツ
+6個 300円
+8個 350円
+各種ソース ＋50円
 ホイップ ＋50円</t>
   </si>
   <si>
@@ -377,8 +380,8 @@
     <t>loc-tent-18</t>
   </si>
   <si>
-    <t>ホットコーヒー 1杯 200円_x000D__x000D_
-アイスコーヒー 1杯 300円_x000D__x000D_
+    <t xml:space="preserve">ホットコーヒー 1杯 200円
+アイスコーヒー 1杯 300円
 おかわり 1杯 100円</t>
   </si>
   <si>
@@ -475,16 +478,19 @@
     <t>なおちゃんズではホットドッグを販売しています。一つひとつ真心込めて作りました！ぜひご賞味あれ！</t>
   </si>
   <si>
+    <t>food-sado-bu</t>
+  </si>
+  <si>
     <t>抹茶・和菓子</t>
   </si>
   <si>
     <t>茶道部</t>
   </si>
   <si>
-    <t>loc-sado-room</t>
-  </si>
-  <si>
-    <t>参加費　おひとり500円_x000D__x000D_
+    <t>loc-3-zakuro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">参加費　おひとり500円
 (抹茶＋和菓子)</t>
   </si>
   <si>
@@ -500,9 +506,6 @@
     <t>花博（Expo部）</t>
   </si>
   <si>
-    <t>loc-3-zakuro</t>
-  </si>
-  <si>
     <t>culture-wandervogel-bu</t>
   </si>
   <si>
@@ -605,6 +608,9 @@
     <t>放送研究会KGUBでは放送にまつわる機材の展示・体験や仕掛けをご用意しています！ぜひお越しください！</t>
   </si>
   <si>
+    <t>culture-shinsengumi</t>
+  </si>
+  <si>
     <t>公演</t>
   </si>
   <si>
@@ -665,6 +671,9 @@
     <t>自作プラネタリウムで本物のような星空を再現！天文部スバルが皆さんを宇宙の世界へご案内します。</t>
   </si>
   <si>
+    <t>culture-tetsudo-bu</t>
+  </si>
+  <si>
     <t>作品展示・体験展示</t>
   </si>
   <si>
@@ -677,6 +686,9 @@
     <t>鉄道研究部です。部員自慢のNゲージコレクションや沢山のプラレール達が走り回るジオラマ展示がございます！他にも鉄道に関する様々な 展示を行います。大人の方もお子様も、是非ご来場下さい！</t>
   </si>
   <si>
+    <t>culture-oystars</t>
+  </si>
+  <si>
     <t>マッスルコンテスト</t>
   </si>
   <si>
@@ -779,8 +791,8 @@
     <t>loc-scc-bennett</t>
   </si>
   <si>
-    <t>子どもから大人までだいすき_x000D__x000D_
-お得にたくさん食べられる5本セットがおすすめ_x000D__x000D_
+    <t xml:space="preserve">子どもから大人までだいすき
+お得にたくさん食べられる5本セットがおすすめ
 おいしい焼き鳥食べに来てね</t>
   </si>
   <si>
@@ -883,6 +895,9 @@
     <t>music-pipe-organ-fujishiro</t>
   </si>
   <si>
+    <t>チャペルコンサート</t>
+  </si>
+  <si>
     <t>パイプオルガン：藤城眞美</t>
   </si>
   <si>
@@ -931,7 +946,7 @@
     <t>芸能</t>
   </si>
   <si>
-    <t>① 10/1(木) 12:30～17:00
+    <t xml:space="preserve">① 10/1(木) 12:30～17:00
 SCC1 階
 ② 10/2(金) 12:30～17:00
 SCC1 階
@@ -950,7 +965,7 @@
 問い合わせ先：hirakata.geinou@gmail.com</t>
   </si>
   <si>
-    <t>宮世琉弥トークショー（全席指定・有料チケット制）開場15:30 開演16:30
+    <t xml:space="preserve">宮世琉弥トークショー（全席指定・有料チケット制）開場15:30 開演16:30
 注意事項
 ※ 会場内および会場周辺では、他のお客様や近隣の方のご迷惑となる行為はおやめください。
 ※ スマートフォン、カメラ等、いかなる機器による写真・動画の撮影および録音は禁止いたします。
@@ -961,6 +976,25 @@
 ※ 出演者への直接のプレゼント、差し入れはできません。プレゼントボックスを設置いたします。</t>
   </si>
   <si>
+    <t>soccer</t>
+  </si>
+  <si>
+    <t>JR東日本カップ2026 第100回関東大学サッカーリーグ戦</t>
+  </si>
+  <si>
+    <t>その他</t>
+  </si>
+  <si>
+    <t>loc-ground</t>
+  </si>
+  <si>
+    <t>入場無料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第19節関東学院大学vs立教大学
+10/31 (土)14:00キックオフ、ぜひご観戦ください！</t>
+  </si>
+  <si>
     <t>buildingId</t>
   </si>
   <si>
@@ -985,133 +1019,70 @@
     <t>屋外</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>テントNo.2</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>テントNo.3</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>テントNo.4</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>テントNo.5</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>テントNo.6</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>テントNo.7</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>テントNo.8</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>テントNo.9</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>テントNo.10</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>テントNo.11</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>テントNo.12</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>テントNo.13</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>テントNo.14</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>テントNo.15</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>テントNo.16</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>テントNo.17</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>テントNo.18</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>テントNo.19</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>テントNo.20</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>テントNo.21</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>テントNo.22</t>
   </si>
   <si>
-    <t>22</t>
+    <t>loc-sado-room</t>
   </si>
   <si>
     <t>8号館横 茶室</t>
@@ -1132,21 +1103,12 @@
     <t>3号館</t>
   </si>
   <si>
-    <t>204</t>
-  </si>
-  <si>
     <t>3-205</t>
   </si>
   <si>
-    <t>205</t>
-  </si>
-  <si>
     <t>3-206</t>
   </si>
   <si>
-    <t>206</t>
-  </si>
-  <si>
     <t>no6</t>
   </si>
   <si>
@@ -1156,9 +1118,6 @@
     <t>6号館</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>no8</t>
   </si>
   <si>
@@ -1171,9 +1130,6 @@
     <t>8-102</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
     <t>8-103・105</t>
   </si>
   <si>
@@ -1183,15 +1139,9 @@
     <t>8-201</t>
   </si>
   <si>
-    <t>201</t>
-  </si>
-  <si>
     <t>8-203</t>
   </si>
   <si>
-    <t>203</t>
-  </si>
-  <si>
     <t>8-204</t>
   </si>
   <si>
@@ -1204,15 +1154,9 @@
     <t>8-305</t>
   </si>
   <si>
-    <t>305</t>
-  </si>
-  <si>
     <t>8-306</t>
   </si>
   <si>
-    <t>306</t>
-  </si>
-  <si>
     <t>カフェポンド前</t>
   </si>
   <si>
@@ -1237,30 +1181,18 @@
     <t>7-301</t>
   </si>
   <si>
-    <t>301</t>
-  </si>
-  <si>
     <t>7-303</t>
   </si>
   <si>
-    <t>303</t>
-  </si>
-  <si>
     <t>loc-7-401</t>
   </si>
   <si>
     <t>7-401</t>
   </si>
   <si>
-    <t>401</t>
-  </si>
-  <si>
     <t>7-403</t>
   </si>
   <si>
-    <t>403</t>
-  </si>
-  <si>
     <t>屋外ステージ</t>
   </si>
   <si>
@@ -1312,19 +1244,13 @@
     <t>7-202</t>
   </si>
   <si>
-    <t>202</t>
-  </si>
-  <si>
     <t>7-402</t>
   </si>
   <si>
-    <t>402</t>
-  </si>
-  <si>
     <t>7-302</t>
   </si>
   <si>
-    <t>302</t>
+    <t>グラウンド</t>
   </si>
   <si>
     <t>slotId</t>
@@ -1657,134 +1583,38 @@
     <t>14:30</t>
   </si>
   <si>
-    <t>food-oystars</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>culture-oystars</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>food-mogi-shutten</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>culture-shinsengumi</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>culture-tetsudo-bu</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>music-jazz-bu</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>チャペルコンサート</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>music-hn-entertainment</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>music-kannai-sukayutopia</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>food-sado-bu</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>food-ojosama-select</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>food-shashin-bu</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>soccer</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>JR東日本カップ2026 第100回関東大学サッカーリーグ戦</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>その他</t>
-    <rPh sb="2" eb="3">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>loc-ground</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>入場無料</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>第19節関東学院大学vs立教大学
-10/31 (土)14:00キックオフ、ぜひご観戦ください！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>tt-d1-18</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>day1</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>14:00キックオフ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>グラウンド</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>屋外</t>
-    <rPh sb="0" eb="2">
-      <t>オクガイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Sat Dec 30 1899 23:00:00 GMT+0900 (日本標準時)</t>
+  </si>
+  <si>
+    <t>Sun Dec 31 1899 01:00:00 GMT+0900 (日本標準時)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
-      <sz val="6"/>
+      <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1805,16 +1635,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1827,16 +1657,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1923,6 +1753,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1957,6 +1788,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1991,20 +1823,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -2126,27 +1954,66 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="74.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.571428571428573" customWidth="1"/>
+    <col min="2" max="2" width="22.857142857142858" customWidth="1"/>
+    <col min="3" max="3" width="33.142857142857146" customWidth="1"/>
+    <col min="4" max="4" width="9.714285714285714" customWidth="1"/>
+    <col min="5" max="5" width="14.285714285714286" customWidth="1"/>
+    <col min="6" max="6" width="9.285714285714286" customWidth="1"/>
+    <col min="7" max="8" width="42.142857142857146" customWidth="1"/>
+    <col min="9" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2172,7 +2039,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2198,7 +2065,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2224,616 +2091,617 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>539</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>528</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>530</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>538</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H19" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H20" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H21" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H22" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B23" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F24" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H24" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>537</v>
+        <v>147</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H25" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D26" t="s">
         <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="198.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.714285714285715" customWidth="1"/>
+    <col min="2" max="2" width="34.285714285714285" customWidth="1"/>
+    <col min="3" max="3" width="24.857142857142858" customWidth="1"/>
+    <col min="4" max="4" width="9.714285714285714" customWidth="1"/>
+    <col min="5" max="5" width="14.285714285714286" customWidth="1"/>
+    <col min="6" max="6" width="9.285714285714286" customWidth="1"/>
+    <col min="7" max="7" width="42.142857142857146" customWidth="1"/>
+    <col min="8" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2856,369 +2724,370 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C2" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D3" t="s">
         <v>159</v>
       </c>
-      <c r="C3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D3" t="s">
-        <v>155</v>
-      </c>
       <c r="E3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E5" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" t="s">
         <v>172</v>
       </c>
-      <c r="B6" t="s">
-        <v>168</v>
-      </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C7" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E7" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E8" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>531</v>
+        <v>190</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B11" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B12" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E12" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C13" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E13" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>532</v>
+        <v>211</v>
       </c>
       <c r="B14" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="C14" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E14" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>529</v>
+        <v>216</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E15" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B16" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="C16" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="D16" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="E16" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="145.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.142857142857142" customWidth="1"/>
+    <col min="2" max="2" width="23.714285714285715" customWidth="1"/>
+    <col min="3" max="3" width="32.714285714285715" customWidth="1"/>
+    <col min="4" max="4" width="9.714285714285714" customWidth="1"/>
+    <col min="5" max="5" width="19.285714285714285" customWidth="1"/>
+    <col min="6" max="6" width="9.285714285714286" customWidth="1"/>
+    <col min="7" max="7" width="42.142857142857146" customWidth="1"/>
+    <col min="8" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3241,486 +3110,487 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="D2" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E2" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
       <c r="D3" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>234</v>
+      </c>
+      <c r="B4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D4" t="s">
         <v>227</v>
       </c>
-      <c r="B4" t="s">
-        <v>228</v>
-      </c>
-      <c r="C4" t="s">
-        <v>228</v>
-      </c>
-      <c r="D4" t="s">
-        <v>220</v>
-      </c>
       <c r="E4" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>533</v>
+        <v>238</v>
       </c>
       <c r="B5" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E5" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="D6" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E6" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>536</v>
+        <v>249</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E8" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B9" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="D9" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E9" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B10" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C10" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="D10" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E10" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>258</v>
+      </c>
+      <c r="B11" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" t="s">
+        <v>259</v>
+      </c>
+      <c r="D11" t="s">
+        <v>227</v>
+      </c>
+      <c r="E11" t="s">
         <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>251</v>
-      </c>
-      <c r="B11" t="s">
-        <v>252</v>
-      </c>
-      <c r="C11" t="s">
-        <v>252</v>
-      </c>
-      <c r="D11" t="s">
-        <v>220</v>
-      </c>
-      <c r="E11" t="s">
-        <v>243</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>535</v>
+        <v>261</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="C12" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="D12" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E12" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B13" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="C13" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E13" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="F13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G13" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B14" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="C14" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="D14" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E14" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B15" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="C15" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E15" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B16" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C16" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="D16" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E16" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B17" t="s">
-        <v>534</v>
+        <v>285</v>
       </c>
       <c r="C17" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E17" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B18" t="s">
-        <v>534</v>
+        <v>285</v>
       </c>
       <c r="C18" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="D18" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E18" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B19" t="s">
-        <v>534</v>
+        <v>285</v>
       </c>
       <c r="C19" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="E19" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
       </c>
       <c r="G19" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>294</v>
+      </c>
+      <c r="B20" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>286</v>
-      </c>
-      <c r="B20" t="s">
-        <v>534</v>
-      </c>
       <c r="C20" t="s">
+        <v>295</v>
+      </c>
+      <c r="D20" t="s">
+        <v>227</v>
+      </c>
+      <c r="E20" t="s">
         <v>287</v>
       </c>
-      <c r="D20" t="s">
-        <v>220</v>
-      </c>
-      <c r="E20" t="s">
-        <v>279</v>
-      </c>
       <c r="F20" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G20" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>296</v>
+      </c>
+      <c r="B21" t="s">
+        <v>285</v>
+      </c>
+      <c r="C21" t="s">
+        <v>297</v>
+      </c>
+      <c r="D21" t="s">
+        <v>227</v>
+      </c>
+      <c r="E21" t="s">
+        <v>287</v>
+      </c>
+      <c r="F21" t="s">
+        <v>144</v>
+      </c>
+      <c r="G21" t="s">
         <v>288</v>
       </c>
-      <c r="B21" t="s">
-        <v>534</v>
-      </c>
-      <c r="C21" t="s">
-        <v>289</v>
-      </c>
-      <c r="D21" t="s">
-        <v>220</v>
-      </c>
-      <c r="E21" t="s">
-        <v>279</v>
-      </c>
-      <c r="F21" t="s">
-        <v>140</v>
-      </c>
-      <c r="G21" t="s">
-        <v>280</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
+    <col min="2" max="2" width="42.142857142857146" customWidth="1"/>
+    <col min="3" max="3" width="23.285714285714285" customWidth="1"/>
+    <col min="4" max="4" width="9.714285714285714" customWidth="1"/>
+    <col min="5" max="5" width="15.714285714285714" customWidth="1"/>
+    <col min="6" max="6" width="9.285714285714286" customWidth="1"/>
+    <col min="7" max="8" width="42.142857142857146" customWidth="1"/>
+    <col min="9" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -3744,1143 +3614,1147 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C2" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="D2" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="E2" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="F2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G2" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="H2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="26.4" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>541</v>
+        <v>304</v>
       </c>
       <c r="B3" t="s">
-        <v>542</v>
+        <v>305</v>
       </c>
       <c r="D3" t="s">
-        <v>543</v>
+        <v>306</v>
       </c>
       <c r="E3" t="s">
-        <v>544</v>
+        <v>307</v>
       </c>
       <c r="F3" t="s">
-        <v>548</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>545</v>
+        <v>308</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>546</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F57"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.285714285714285" customWidth="1"/>
+    <col min="2" max="2" width="10.285714285714286" customWidth="1"/>
+    <col min="3" max="4" width="26.285714285714285" customWidth="1"/>
+    <col min="5" max="5" width="9.285714285714286" customWidth="1"/>
+    <col min="6" max="6" width="30.714285714285715" customWidth="1"/>
+    <col min="7" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>315</v>
       </c>
       <c r="D2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>305</v>
+        <v>318</v>
       </c>
       <c r="D3" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D4" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E4" t="s">
-        <v>303</v>
-      </c>
-      <c r="F4" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="D5" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
-      </c>
-      <c r="F5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="D6" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
-      </c>
-      <c r="F6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D7" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E7" t="s">
-        <v>303</v>
-      </c>
-      <c r="F7" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="D8" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E8" t="s">
-        <v>303</v>
-      </c>
-      <c r="F8" t="s">
+        <v>317</v>
+      </c>
+      <c r="F8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>324</v>
+      </c>
+      <c r="D9" t="s">
         <v>316</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>317</v>
       </c>
-      <c r="D9" t="s">
-        <v>302</v>
-      </c>
-      <c r="E9" t="s">
-        <v>303</v>
-      </c>
-      <c r="F9" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="D10" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E10" t="s">
-        <v>303</v>
-      </c>
-      <c r="F10" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="D11" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E11" t="s">
-        <v>303</v>
-      </c>
-      <c r="F11" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="D12" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E12" t="s">
-        <v>303</v>
-      </c>
-      <c r="F12" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="D13" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E13" t="s">
-        <v>303</v>
-      </c>
-      <c r="F13" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="D14" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E14" t="s">
-        <v>303</v>
-      </c>
-      <c r="F14" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="D15" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E15" t="s">
-        <v>303</v>
-      </c>
-      <c r="F15" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+        <v>317</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
         <v>331</v>
       </c>
       <c r="D16" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="E16" t="s">
-        <v>303</v>
-      </c>
-      <c r="F16" t="s">
+        <v>317</v>
+      </c>
+      <c r="F16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
+        <v>316</v>
+      </c>
+      <c r="E17" t="s">
+        <v>317</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" t="s">
         <v>333</v>
       </c>
-      <c r="D17" t="s">
-        <v>302</v>
-      </c>
-      <c r="E17" t="s">
-        <v>303</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="D18" t="s">
+        <v>316</v>
+      </c>
+      <c r="E18" t="s">
+        <v>317</v>
+      </c>
+      <c r="F18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="D19" t="s">
+        <v>316</v>
+      </c>
+      <c r="E19" t="s">
+        <v>317</v>
+      </c>
+      <c r="F19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" t="s">
         <v>335</v>
       </c>
-      <c r="D18" t="s">
-        <v>302</v>
-      </c>
-      <c r="E18" t="s">
-        <v>303</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="D20" t="s">
+        <v>316</v>
+      </c>
+      <c r="E20" t="s">
+        <v>317</v>
+      </c>
+      <c r="F20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D21" t="s">
+        <v>316</v>
+      </c>
+      <c r="E21" t="s">
+        <v>317</v>
+      </c>
+      <c r="F21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" t="s">
         <v>337</v>
       </c>
-      <c r="D19" t="s">
-        <v>302</v>
-      </c>
-      <c r="E19" t="s">
-        <v>303</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="D22" t="s">
+        <v>316</v>
+      </c>
+      <c r="E22" t="s">
+        <v>317</v>
+      </c>
+      <c r="F22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="D23" t="s">
+        <v>316</v>
+      </c>
+      <c r="E23" t="s">
+        <v>317</v>
+      </c>
+      <c r="F23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>339</v>
       </c>
-      <c r="D20" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" t="s">
-        <v>303</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="C24" t="s">
         <v>340</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="D24" t="s">
         <v>341</v>
-      </c>
-      <c r="D21" t="s">
-        <v>302</v>
-      </c>
-      <c r="E21" t="s">
-        <v>303</v>
-      </c>
-      <c r="F21" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" t="s">
-        <v>343</v>
-      </c>
-      <c r="D22" t="s">
-        <v>302</v>
-      </c>
-      <c r="E22" t="s">
-        <v>303</v>
-      </c>
-      <c r="F22" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23" t="s">
-        <v>345</v>
-      </c>
-      <c r="D23" t="s">
-        <v>302</v>
-      </c>
-      <c r="E23" t="s">
-        <v>303</v>
-      </c>
-      <c r="F23" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" t="s">
-        <v>347</v>
-      </c>
-      <c r="D24" t="s">
-        <v>348</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="B25" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C25" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="D25" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
-      <c r="F25" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B26" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C26" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="D26" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
-      <c r="F26" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B27" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C27" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D27" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
-      <c r="F27" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B28" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C28" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="D28" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
-      <c r="F28" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B29" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C29" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="D29" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="F29" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F29">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B30" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C30" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="D30" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F30">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B31" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C31" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="D31" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B32" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C32" t="s">
-        <v>369</v>
+        <v>357</v>
       </c>
       <c r="D32" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
-      <c r="F32" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F32">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B33" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C33" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="D33" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
-      <c r="F33" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F33">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B34" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C34" t="s">
-        <v>373</v>
+        <v>359</v>
       </c>
       <c r="D34" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F34">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>214</v>
+      </c>
+      <c r="B35" t="s">
+        <v>351</v>
+      </c>
+      <c r="C35" t="s">
+        <v>360</v>
+      </c>
+      <c r="D35" t="s">
         <v>353</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>208</v>
-      </c>
-      <c r="B35" t="s">
-        <v>362</v>
-      </c>
-      <c r="C35" t="s">
-        <v>374</v>
-      </c>
-      <c r="D35" t="s">
-        <v>364</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
-      <c r="F35" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C36" t="s">
-        <v>375</v>
+        <v>361</v>
       </c>
       <c r="D36" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
-      <c r="F36" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F36">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B37" t="s">
+        <v>351</v>
+      </c>
+      <c r="C37" t="s">
         <v>362</v>
       </c>
-      <c r="C37" t="s">
-        <v>376</v>
-      </c>
       <c r="D37" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
-      <c r="F37" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F37">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="C38" t="s">
-        <v>378</v>
+        <v>363</v>
       </c>
       <c r="D38" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
-      <c r="F38" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F38">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B39" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="C39" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="D39" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="B40" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C40" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="D40" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
-      <c r="F40" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F40">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="B41" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C41" t="s">
-        <v>385</v>
+        <v>369</v>
       </c>
       <c r="D41" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
-      <c r="F41" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F41">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>386</v>
+        <v>370</v>
       </c>
       <c r="B42" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C42" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="D42" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="E42">
         <v>3</v>
       </c>
-      <c r="F42" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F42">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="B43" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C43" t="s">
-        <v>389</v>
+        <v>372</v>
       </c>
       <c r="D43" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
-      <c r="F43" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F43">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>391</v>
+        <v>373</v>
       </c>
       <c r="B44" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C44" t="s">
-        <v>392</v>
+        <v>374</v>
       </c>
       <c r="D44" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="E44">
         <v>4</v>
       </c>
-      <c r="F44" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F44">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B45" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C45" t="s">
-        <v>394</v>
+        <v>375</v>
       </c>
       <c r="D45" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="E45">
         <v>4</v>
       </c>
-      <c r="F45" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="C46" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="D46" t="s">
-        <v>396</v>
+        <v>376</v>
       </c>
       <c r="E46" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="F46" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B47" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="C47" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="D47" t="s">
-        <v>399</v>
+        <v>379</v>
       </c>
       <c r="E47">
         <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="C48" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="D48" t="s">
-        <v>401</v>
+        <v>381</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="C49" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="D49" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="E49" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="F49" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="C50" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="D50" t="s">
-        <v>404</v>
+        <v>384</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="C51" t="s">
-        <v>406</v>
+        <v>386</v>
       </c>
       <c r="D51" t="s">
-        <v>407</v>
+        <v>387</v>
       </c>
       <c r="E51">
         <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B52" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C52" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="D52" t="s">
-        <v>384</v>
+        <v>368</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B53" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C53" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="D53" t="s">
-        <v>352</v>
-      </c>
-      <c r="E53" t="s">
-        <v>304</v>
+        <v>345</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B54" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C54" t="s">
-        <v>412</v>
+        <v>392</v>
       </c>
       <c r="D54" t="s">
-        <v>384</v>
-      </c>
-      <c r="E54" t="s">
-        <v>306</v>
-      </c>
-      <c r="F54" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="B55" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C55" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="D55" t="s">
-        <v>384</v>
-      </c>
-      <c r="E55" t="s">
-        <v>310</v>
-      </c>
-      <c r="F55" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B56" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C56" t="s">
-        <v>416</v>
+        <v>394</v>
       </c>
       <c r="D56" t="s">
-        <v>384</v>
-      </c>
-      <c r="E56" t="s">
-        <v>308</v>
-      </c>
-      <c r="F56" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>544</v>
+        <v>307</v>
       </c>
       <c r="C57" t="s">
-        <v>550</v>
+        <v>395</v>
       </c>
       <c r="D57" t="s">
-        <v>550</v>
+        <v>395</v>
       </c>
       <c r="E57" t="s">
-        <v>551</v>
+        <v>317</v>
       </c>
       <c r="F57" t="s">
-        <v>550</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>418</v>
+        <v>396</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -4889,799 +4763,799 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>419</v>
+        <v>397</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>420</v>
+        <v>398</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>422</v>
+        <v>400</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E2" t="s">
-        <v>423</v>
+        <v>401</v>
       </c>
       <c r="F2" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
       <c r="G2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B3" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E3" t="s">
-        <v>427</v>
+        <v>405</v>
       </c>
       <c r="F3" t="s">
-        <v>428</v>
+        <v>406</v>
       </c>
       <c r="G3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="B4" t="s">
-        <v>430</v>
+        <v>408</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E4" t="s">
-        <v>431</v>
+        <v>409</v>
       </c>
       <c r="F4" t="s">
-        <v>432</v>
+        <v>410</v>
       </c>
       <c r="G4" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B5" t="s">
-        <v>434</v>
+        <v>412</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E5" t="s">
-        <v>435</v>
+        <v>413</v>
       </c>
       <c r="F5" t="s">
-        <v>436</v>
+        <v>414</v>
       </c>
       <c r="G5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B6" t="s">
-        <v>438</v>
+        <v>416</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E6" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="F6" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="G6" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="B7" t="s">
-        <v>442</v>
+        <v>420</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E7" t="s">
-        <v>443</v>
+        <v>421</v>
       </c>
       <c r="F7" t="s">
-        <v>444</v>
+        <v>422</v>
       </c>
       <c r="G7" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B8" t="s">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="E8" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="F8" t="s">
-        <v>448</v>
+        <v>426</v>
       </c>
       <c r="G8" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="B9" t="s">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E9" t="s">
-        <v>451</v>
+        <v>429</v>
       </c>
       <c r="F9" t="s">
-        <v>452</v>
+        <v>430</v>
       </c>
       <c r="G9" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="B10" t="s">
-        <v>454</v>
+        <v>432</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E10" t="s">
-        <v>455</v>
+        <v>433</v>
       </c>
       <c r="F10" t="s">
-        <v>456</v>
+        <v>434</v>
       </c>
       <c r="G10" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B11" t="s">
-        <v>458</v>
+        <v>436</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E11" t="s">
-        <v>459</v>
+        <v>437</v>
       </c>
       <c r="F11" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="G11" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B12" t="s">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E12" t="s">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="F12" t="s">
-        <v>463</v>
+        <v>441</v>
       </c>
       <c r="G12" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="B13" t="s">
-        <v>465</v>
+        <v>443</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="E13" t="s">
-        <v>466</v>
+        <v>444</v>
       </c>
       <c r="F13" t="s">
-        <v>424</v>
+        <v>402</v>
       </c>
       <c r="G13" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="B14" t="s">
-        <v>468</v>
+        <v>446</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="E14" t="s">
-        <v>469</v>
+        <v>447</v>
       </c>
       <c r="F14" t="s">
-        <v>433</v>
+        <v>411</v>
       </c>
       <c r="G14" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B15" t="s">
-        <v>471</v>
+        <v>449</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E15" t="s">
-        <v>472</v>
+        <v>450</v>
       </c>
       <c r="F15" t="s">
-        <v>473</v>
+        <v>451</v>
       </c>
       <c r="G15" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="B16" t="s">
-        <v>475</v>
+        <v>453</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E16" t="s">
-        <v>476</v>
+        <v>454</v>
       </c>
       <c r="F16" t="s">
-        <v>470</v>
+        <v>448</v>
       </c>
       <c r="G16" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="B17" t="s">
-        <v>478</v>
+        <v>456</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="E17" t="s">
-        <v>479</v>
+        <v>457</v>
       </c>
       <c r="F17" t="s">
-        <v>480</v>
+        <v>458</v>
       </c>
       <c r="G17" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B18" t="s">
-        <v>482</v>
+        <v>460</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" t="s">
+        <v>287</v>
+      </c>
+      <c r="E18" t="s">
+        <v>461</v>
+      </c>
+      <c r="F18" t="s">
+        <v>462</v>
+      </c>
+      <c r="G18" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>245</v>
+      </c>
+      <c r="B19" t="s">
+        <v>464</v>
+      </c>
+      <c r="C19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" t="s">
+        <v>263</v>
+      </c>
+      <c r="E19" t="s">
+        <v>465</v>
+      </c>
+      <c r="F19" t="s">
+        <v>402</v>
+      </c>
+      <c r="G19" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>225</v>
+      </c>
+      <c r="B20" t="s">
+        <v>467</v>
+      </c>
+      <c r="C20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" t="s">
+        <v>263</v>
+      </c>
+      <c r="E20" t="s">
+        <v>468</v>
+      </c>
+      <c r="F20" t="s">
+        <v>403</v>
+      </c>
+      <c r="G20" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>230</v>
+      </c>
+      <c r="B21" t="s">
+        <v>470</v>
+      </c>
+      <c r="C21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" t="s">
+        <v>263</v>
+      </c>
+      <c r="E21" t="s">
+        <v>471</v>
+      </c>
+      <c r="F21" t="s">
+        <v>472</v>
+      </c>
+      <c r="G21" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>238</v>
+      </c>
+      <c r="B22" t="s">
+        <v>474</v>
+      </c>
+      <c r="C22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" t="s">
+        <v>263</v>
+      </c>
+      <c r="E22" t="s">
+        <v>475</v>
+      </c>
+      <c r="F22" t="s">
+        <v>476</v>
+      </c>
+      <c r="G22" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>241</v>
+      </c>
+      <c r="B23" t="s">
+        <v>478</v>
+      </c>
+      <c r="C23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" t="s">
+        <v>263</v>
+      </c>
+      <c r="E23" t="s">
+        <v>479</v>
+      </c>
+      <c r="F23" t="s">
+        <v>480</v>
+      </c>
+      <c r="G23" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>234</v>
+      </c>
+      <c r="B24" t="s">
+        <v>481</v>
+      </c>
+      <c r="C24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>263</v>
+      </c>
+      <c r="E24" t="s">
+        <v>482</v>
+      </c>
+      <c r="F24" t="s">
+        <v>483</v>
+      </c>
+      <c r="G24" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>261</v>
+      </c>
+      <c r="B25" t="s">
+        <v>484</v>
+      </c>
+      <c r="C25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" t="s">
+        <v>263</v>
+      </c>
+      <c r="E25" t="s">
+        <v>485</v>
+      </c>
+      <c r="F25" t="s">
+        <v>462</v>
+      </c>
+      <c r="G25" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>265</v>
+      </c>
+      <c r="B26" t="s">
+        <v>487</v>
+      </c>
+      <c r="C26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" t="s">
+        <v>263</v>
+      </c>
+      <c r="E26" t="s">
+        <v>488</v>
+      </c>
+      <c r="F26" t="s">
+        <v>445</v>
+      </c>
+      <c r="G26" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>249</v>
+      </c>
+      <c r="B27" t="s">
+        <v>489</v>
+      </c>
+      <c r="C27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" t="s">
+        <v>250</v>
+      </c>
+      <c r="E27" t="s">
+        <v>490</v>
+      </c>
+      <c r="F27" t="s">
+        <v>491</v>
+      </c>
+      <c r="G27" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>258</v>
+      </c>
+      <c r="B28" t="s">
+        <v>492</v>
+      </c>
+      <c r="C28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" t="s">
+        <v>250</v>
+      </c>
+      <c r="E28" t="s">
+        <v>493</v>
+      </c>
+      <c r="F28" t="s">
+        <v>411</v>
+      </c>
+      <c r="G28" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>298</v>
+      </c>
+      <c r="B29" t="s">
+        <v>494</v>
+      </c>
+      <c r="C29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" t="s">
+        <v>250</v>
+      </c>
+      <c r="E29" t="s">
+        <v>495</v>
+      </c>
+      <c r="F29" t="s">
+        <v>496</v>
+      </c>
+      <c r="G29" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>279</v>
       </c>
-      <c r="E18" t="s">
-        <v>483</v>
-      </c>
-      <c r="F18" t="s">
-        <v>484</v>
-      </c>
-      <c r="G18" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B19" t="s">
-        <v>486</v>
-      </c>
-      <c r="C19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D19" t="s">
-        <v>256</v>
-      </c>
-      <c r="E19" t="s">
-        <v>487</v>
-      </c>
-      <c r="F19" t="s">
-        <v>424</v>
-      </c>
-      <c r="G19" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>218</v>
-      </c>
-      <c r="B20" t="s">
-        <v>489</v>
-      </c>
-      <c r="C20" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" t="s">
-        <v>256</v>
-      </c>
-      <c r="E20" t="s">
-        <v>490</v>
-      </c>
-      <c r="F20" t="s">
-        <v>425</v>
-      </c>
-      <c r="G20" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>223</v>
-      </c>
-      <c r="B21" t="s">
-        <v>492</v>
-      </c>
-      <c r="C21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D21" t="s">
-        <v>256</v>
-      </c>
-      <c r="E21" t="s">
-        <v>493</v>
-      </c>
-      <c r="F21" t="s">
-        <v>494</v>
-      </c>
-      <c r="G21" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>231</v>
-      </c>
-      <c r="B22" t="s">
-        <v>496</v>
-      </c>
-      <c r="C22" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" t="s">
-        <v>256</v>
-      </c>
-      <c r="E22" t="s">
-        <v>497</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="B30" t="s">
         <v>498</v>
       </c>
-      <c r="G22" t="s">
+      <c r="C30" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" t="s">
+        <v>282</v>
+      </c>
+      <c r="E30" t="s">
+        <v>444</v>
+      </c>
+      <c r="F30" t="s">
+        <v>402</v>
+      </c>
+      <c r="G30" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>294</v>
+      </c>
+      <c r="B31" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>234</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" t="s">
+        <v>287</v>
+      </c>
+      <c r="E31" t="s">
         <v>500</v>
       </c>
-      <c r="C23" t="s">
-        <v>140</v>
-      </c>
-      <c r="D23" t="s">
-        <v>256</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="F31" t="s">
+        <v>411</v>
+      </c>
+      <c r="G31" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>294</v>
+      </c>
+      <c r="B32" t="s">
         <v>501</v>
       </c>
-      <c r="F23" t="s">
+      <c r="C32" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" t="s">
+        <v>287</v>
+      </c>
+      <c r="E32" t="s">
+        <v>450</v>
+      </c>
+      <c r="F32" t="s">
+        <v>451</v>
+      </c>
+      <c r="G32" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>296</v>
+      </c>
+      <c r="B33" t="s">
         <v>502</v>
       </c>
-      <c r="G23" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>227</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" t="s">
+        <v>287</v>
+      </c>
+      <c r="E33" t="s">
+        <v>454</v>
+      </c>
+      <c r="F33" t="s">
+        <v>448</v>
+      </c>
+      <c r="G33" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>296</v>
+      </c>
+      <c r="B34" t="s">
         <v>503</v>
       </c>
-      <c r="C24" t="s">
-        <v>140</v>
-      </c>
-      <c r="D24" t="s">
-        <v>256</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="C34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" t="s">
+        <v>287</v>
+      </c>
+      <c r="E34" t="s">
         <v>504</v>
       </c>
-      <c r="F24" t="s">
+      <c r="F34" t="s">
         <v>505</v>
       </c>
-      <c r="G24" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>254</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="G34" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>304</v>
+      </c>
+      <c r="B35" t="s">
         <v>506</v>
       </c>
-      <c r="C25" t="s">
-        <v>140</v>
-      </c>
-      <c r="D25" t="s">
-        <v>256</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" t="s">
+        <v>307</v>
+      </c>
+      <c r="E35" t="s">
         <v>507</v>
       </c>
-      <c r="F25" t="s">
-        <v>484</v>
-      </c>
-      <c r="G25" t="s">
+      <c r="F35" s="3" t="s">
         <v>508</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>258</v>
-      </c>
-      <c r="B26" t="s">
+      <c r="G35" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="C26" t="s">
-        <v>140</v>
-      </c>
-      <c r="D26" t="s">
-        <v>256</v>
-      </c>
-      <c r="E26" t="s">
-        <v>510</v>
-      </c>
-      <c r="F26" t="s">
-        <v>467</v>
-      </c>
-      <c r="G26" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>242</v>
-      </c>
-      <c r="B27" t="s">
-        <v>511</v>
-      </c>
-      <c r="C27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D27" t="s">
-        <v>243</v>
-      </c>
-      <c r="E27" t="s">
-        <v>512</v>
-      </c>
-      <c r="F27" t="s">
-        <v>513</v>
-      </c>
-      <c r="G27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>251</v>
-      </c>
-      <c r="B28" t="s">
-        <v>514</v>
-      </c>
-      <c r="C28" t="s">
-        <v>140</v>
-      </c>
-      <c r="D28" t="s">
-        <v>243</v>
-      </c>
-      <c r="E28" t="s">
-        <v>515</v>
-      </c>
-      <c r="F28" t="s">
-        <v>433</v>
-      </c>
-      <c r="G28" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>290</v>
-      </c>
-      <c r="B29" t="s">
-        <v>516</v>
-      </c>
-      <c r="C29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" t="s">
-        <v>243</v>
-      </c>
-      <c r="E29" t="s">
-        <v>517</v>
-      </c>
-      <c r="F29" t="s">
-        <v>518</v>
-      </c>
-      <c r="G29" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>272</v>
-      </c>
-      <c r="B30" t="s">
-        <v>520</v>
-      </c>
-      <c r="C30" t="s">
-        <v>140</v>
-      </c>
-      <c r="D30" t="s">
-        <v>275</v>
-      </c>
-      <c r="E30" t="s">
-        <v>466</v>
-      </c>
-      <c r="F30" t="s">
-        <v>424</v>
-      </c>
-      <c r="G30" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>286</v>
-      </c>
-      <c r="B31" t="s">
-        <v>521</v>
-      </c>
-      <c r="C31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D31" t="s">
-        <v>279</v>
-      </c>
-      <c r="E31" t="s">
-        <v>522</v>
-      </c>
-      <c r="F31" t="s">
-        <v>433</v>
-      </c>
-      <c r="G31" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>286</v>
-      </c>
-      <c r="B32" t="s">
-        <v>523</v>
-      </c>
-      <c r="C32" t="s">
-        <v>140</v>
-      </c>
-      <c r="D32" t="s">
-        <v>279</v>
-      </c>
-      <c r="E32" t="s">
-        <v>472</v>
-      </c>
-      <c r="F32" t="s">
-        <v>473</v>
-      </c>
-      <c r="G32" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>288</v>
-      </c>
-      <c r="B33" t="s">
-        <v>524</v>
-      </c>
-      <c r="C33" t="s">
-        <v>140</v>
-      </c>
-      <c r="D33" t="s">
-        <v>279</v>
-      </c>
-      <c r="E33" t="s">
-        <v>476</v>
-      </c>
-      <c r="F33" t="s">
-        <v>470</v>
-      </c>
-      <c r="G33" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>288</v>
-      </c>
-      <c r="B34" t="s">
-        <v>525</v>
-      </c>
-      <c r="C34" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" t="s">
-        <v>279</v>
-      </c>
-      <c r="E34" t="s">
-        <v>526</v>
-      </c>
-      <c r="F34" t="s">
-        <v>527</v>
-      </c>
-      <c r="G34" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>541</v>
-      </c>
-      <c r="B35" t="s">
-        <v>547</v>
-      </c>
-      <c r="C35" t="s">
-        <v>548</v>
-      </c>
-      <c r="D35" t="s">
-        <v>544</v>
-      </c>
-      <c r="E35" t="s">
-        <v>549</v>
-      </c>
-      <c r="F35" s="3">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0.66666666666666663</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -1,31 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tkytw\Desktop\GitHub\Home-Page\app\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A58DB29-A7F7-4FB9-B929-58BE8BE5F57B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet name="mogiten" sheetId="1" r:id="rId1"/>
-    <sheet name="culture" sheetId="2" r:id="rId2"/>
-    <sheet name="music" sheetId="3" r:id="rId3"/>
-    <sheet name="other" sheetId="4" r:id="rId4"/>
-    <sheet name="location" sheetId="5" r:id="rId5"/>
-    <sheet name="timetable" sheetId="6" r:id="rId6"/>
+    <sheet sheetId="1" name="mogiten" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="culture" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="music" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="other" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="location" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="timetable" state="visible" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1014" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="508">
   <si>
     <t>id</t>
   </si>
@@ -90,7 +81,7 @@
     <t>day1</t>
   </si>
   <si>
-    <t>いちご
+    <t xml:space="preserve">いちご
 ブルーベリー
 チョコ
 キャラメル
@@ -100,6 +91,9 @@
     <t>おいしいパンケーキ屋さん！1年生だけの有志団体です！可愛くて美味しいパンケーキをぜひ食べに来てください♡</t>
   </si>
   <si>
+    <t>food-shashin-bu</t>
+  </si>
+  <si>
     <t>棒餃子</t>
   </si>
   <si>
@@ -115,6 +109,9 @@
     <t>写真部では今年も棒餃子を販売します！平潟祭はこれ食えば間違いナシ！</t>
   </si>
   <si>
+    <t>food-oystars</t>
+  </si>
+  <si>
     <t>筋肉巻き</t>
   </si>
   <si>
@@ -178,6 +175,9 @@
     <t>ジューシーで香ばしい絶品フランクフルトを販売！パリッと弾ける食感と熱々の肉汁がたまりません。食べ歩きに最適ですので、ぜひお立ち寄りください！</t>
   </si>
   <si>
+    <t>food-mogi-shutten</t>
+  </si>
+  <si>
     <t>やきそば</t>
   </si>
   <si>
@@ -241,13 +241,16 @@
     <t>loc-tent-11</t>
   </si>
   <si>
-    <t>黒糖わらび餅抹茶ラテ 1杯 380円_x000D__x000D_
+    <t xml:space="preserve">黒糖わらび餅抹茶ラテ 1杯 380円
 黒糖わらび餅ミルクティー 1杯 380円</t>
   </si>
   <si>
     <t>皆様ごきげんよう！KGUのFABULOUSなお嬢様が作るドリンクはいかが？抽選もあるから是非いらして頂戴！</t>
   </si>
   <si>
+    <t>food-ojosama-select</t>
+  </si>
+  <si>
     <t>アパレル</t>
   </si>
   <si>
@@ -257,7 +260,7 @@
     <t>loc-tent-12</t>
   </si>
   <si>
-    <t>服やグッズの販売
+    <t xml:space="preserve">服やグッズの販売
 2,499円（税込）～7,499円（税込）</t>
   </si>
   <si>
@@ -276,9 +279,9 @@
     <t>loc-tent-13</t>
   </si>
   <si>
-    <t>ソーラーランタン_x000D__x000D_
-ウォーム 1個 4,400円_x000D__x000D_
-クール 1個 4,400円_x000D__x000D_
+    <t xml:space="preserve">ソーラーランタン
+ウォーム 1個 4,400円
+クール 1個 4,400円
 レインボー 1個 5,500円</t>
   </si>
   <si>
@@ -315,10 +318,10 @@
     <t>loc-tent-15</t>
   </si>
   <si>
-    <t>焼き鳥（塩orタレ）_x000D__x000D_
-1本 200円_x000D__x000D_
-3本 500円_x000D__x000D_
-5本 700円_x000D__x000D_
+    <t xml:space="preserve">焼き鳥（塩orタレ）
+1本 200円
+3本 500円
+5本 700円
 缶ビール 1本 400円</t>
   </si>
   <si>
@@ -355,10 +358,10 @@
     <t>loc-tent-17</t>
   </si>
   <si>
-    <t>ひとくちドーナツ_x000D__x000D_
-6個 300円_x000D__x000D_
-8個 350円_x000D__x000D_
-各種ソース ＋50円_x000D__x000D_
+    <t xml:space="preserve">ひとくちドーナツ
+6個 300円
+8個 350円
+各種ソース ＋50円
 ホイップ ＋50円</t>
   </si>
   <si>
@@ -377,8 +380,8 @@
     <t>loc-tent-18</t>
   </si>
   <si>
-    <t>ホットコーヒー 1杯 200円_x000D__x000D_
-アイスコーヒー 1杯 300円_x000D__x000D_
+    <t xml:space="preserve">ホットコーヒー 1杯 200円
+アイスコーヒー 1杯 300円
 おかわり 1杯 100円</t>
   </si>
   <si>
@@ -475,6 +478,9 @@
     <t>なおちゃんズではホットドッグを販売しています。一つひとつ真心込めて作りました！ぜひご賞味あれ！</t>
   </si>
   <si>
+    <t>food-sado-bu</t>
+  </si>
+  <si>
     <t>抹茶・和菓子</t>
   </si>
   <si>
@@ -484,61 +490,52 @@
     <t>loc-sado-room</t>
   </si>
   <si>
-    <t>参加費　おひとり500円_x000D__x000D_
+    <t xml:space="preserve">参加費　おひとり500円
 (抹茶＋和菓子)</t>
   </si>
   <si>
     <t>茶道部です！8号館横の茶室で抹茶とお菓子をご用意しています。ぜひお気軽にお越しください！</t>
   </si>
   <si>
-    <t>food-hanahaku</t>
+    <t>culture-wandervogel-bu</t>
+  </si>
+  <si>
+    <t>コンペ兼活動報告</t>
+  </si>
+  <si>
+    <t>ワンダーフォーゲル部</t>
+  </si>
+  <si>
+    <t>文化館</t>
+  </si>
+  <si>
+    <t>loc-8-204</t>
+  </si>
+  <si>
+    <t>ワンダーフォーゲル部では、山行記録の映像上映や登山道具を展示中！自然の魅力を部員がお届けします！ぜひお越しください。</t>
+  </si>
+  <si>
+    <t>culture-su-bu</t>
+  </si>
+  <si>
+    <t>数学に関するポスター展示</t>
+  </si>
+  <si>
+    <t>すーぶ（数理・物理コース）</t>
+  </si>
+  <si>
+    <t>loc-3-205</t>
+  </si>
+  <si>
+    <t>すーぶ（数理物理コース）（兼子研究室）は数学の面白さ、奥深さを楽しく感じ取ってもらえるようMEAGと協力して展示会を開きます！難しく感じてしまう数学も見方を変えれば簡単に感じるかもしれないですよ！</t>
+  </si>
+  <si>
+    <t>culture-meag</t>
   </si>
   <si>
     <t>ワークショップ</t>
   </si>
   <si>
-    <t>花博（Expo部）</t>
-  </si>
-  <si>
-    <t>loc-3-zakuro</t>
-  </si>
-  <si>
-    <t>culture-wandervogel-bu</t>
-  </si>
-  <si>
-    <t>コンペ兼活動報告</t>
-  </si>
-  <si>
-    <t>ワンダーフォーゲル部</t>
-  </si>
-  <si>
-    <t>文化館</t>
-  </si>
-  <si>
-    <t>loc-8-204</t>
-  </si>
-  <si>
-    <t>ワンダーフォーゲル部では、山行記録の映像上映や登山道具を展示中！自然の魅力を部員がお届けします！ぜひお越しください。</t>
-  </si>
-  <si>
-    <t>culture-su-bu</t>
-  </si>
-  <si>
-    <t>数学に関するポスター展示</t>
-  </si>
-  <si>
-    <t>すーぶ（数理・物理コース）</t>
-  </si>
-  <si>
-    <t>loc-3-205</t>
-  </si>
-  <si>
-    <t>すーぶ（数理物理コース）（兼子研究室）は数学の面白さ、奥深さを楽しく感じ取ってもらえるようMEAGと協力して展示会を開きます！難しく感じてしまう数学も見方を変えれば簡単に感じるかもしれないですよ！</t>
-  </si>
-  <si>
-    <t>culture-meag</t>
-  </si>
-  <si>
     <t>MEAG</t>
   </si>
   <si>
@@ -605,6 +602,9 @@
     <t>放送研究会KGUBでは放送にまつわる機材の展示・体験や仕掛けをご用意しています！ぜひお越しください！</t>
   </si>
   <si>
+    <t>culture-shinsengumi</t>
+  </si>
+  <si>
     <t>公演</t>
   </si>
   <si>
@@ -665,6 +665,9 @@
     <t>自作プラネタリウムで本物のような星空を再現！天文部スバルが皆さんを宇宙の世界へご案内します。</t>
   </si>
   <si>
+    <t>culture-tetsudo-bu</t>
+  </si>
+  <si>
     <t>作品展示・体験展示</t>
   </si>
   <si>
@@ -677,6 +680,9 @@
     <t>鉄道研究部です。部員自慢のNゲージコレクションや沢山のプラレール達が走り回るジオラマ展示がございます！他にも鉄道に関する様々な 展示を行います。大人の方もお子様も、是非ご来場下さい！</t>
   </si>
   <si>
+    <t>culture-oystars</t>
+  </si>
+  <si>
     <t>マッスルコンテスト</t>
   </si>
   <si>
@@ -779,8 +785,8 @@
     <t>loc-scc-bennett</t>
   </si>
   <si>
-    <t>子どもから大人までだいすき_x000D__x000D_
-お得にたくさん食べられる5本セットがおすすめ_x000D__x000D_
+    <t xml:space="preserve">子どもから大人までだいすき
+お得にたくさん食べられる5本セットがおすすめ
 おいしい焼き鳥食べに来てね</t>
   </si>
   <si>
@@ -883,6 +889,9 @@
     <t>music-pipe-organ-fujishiro</t>
   </si>
   <si>
+    <t>チャペルコンサート</t>
+  </si>
+  <si>
     <t>パイプオルガン：藤城眞美</t>
   </si>
   <si>
@@ -931,7 +940,7 @@
     <t>芸能</t>
   </si>
   <si>
-    <t>① 10/1(木) 12:30～17:00
+    <t xml:space="preserve">① 10/1(木) 12:30～17:00
 SCC1 階
 ② 10/2(金) 12:30～17:00
 SCC1 階
@@ -950,7 +959,7 @@
 問い合わせ先：hirakata.geinou@gmail.com</t>
   </si>
   <si>
-    <t>宮世琉弥トークショー（全席指定・有料チケット制）開場15:30 開演16:30
+    <t xml:space="preserve">宮世琉弥トークショー（全席指定・有料チケット制）開場15:30 開演16:30
 注意事項
 ※ 会場内および会場周辺では、他のお客様や近隣の方のご迷惑となる行為はおやめください。
 ※ スマートフォン、カメラ等、いかなる機器による写真・動画の撮影および録音は禁止いたします。
@@ -961,6 +970,25 @@
 ※ 出演者への直接のプレゼント、差し入れはできません。プレゼントボックスを設置いたします。</t>
   </si>
   <si>
+    <t>soccer</t>
+  </si>
+  <si>
+    <t>JR東日本カップ2026 第100回関東大学サッカーリーグ戦</t>
+  </si>
+  <si>
+    <t>その他</t>
+  </si>
+  <si>
+    <t>loc-ground</t>
+  </si>
+  <si>
+    <t>入場無料</t>
+  </si>
+  <si>
+    <t xml:space="preserve">第19節関東学院大学vs立教大学
+10/31 (土)14:00キックオフ、ぜひご観戦ください！</t>
+  </si>
+  <si>
     <t>buildingId</t>
   </si>
   <si>
@@ -985,135 +1013,69 @@
     <t>屋外</t>
   </si>
   <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>テントNo.2</t>
   </si>
   <si>
-    <t>2</t>
-  </si>
-  <si>
     <t>テントNo.3</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>テントNo.4</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
     <t>テントNo.5</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>テントNo.6</t>
   </si>
   <si>
-    <t>6</t>
-  </si>
-  <si>
     <t>テントNo.7</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
     <t>テントNo.8</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>テントNo.9</t>
   </si>
   <si>
-    <t>9</t>
-  </si>
-  <si>
     <t>テントNo.10</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>テントNo.11</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
     <t>テントNo.12</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>テントNo.13</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
     <t>テントNo.14</t>
   </si>
   <si>
-    <t>14</t>
-  </si>
-  <si>
     <t>テントNo.15</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>テントNo.16</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
     <t>テントNo.17</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>テントNo.18</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
     <t>テントNo.19</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
     <t>テントNo.20</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
     <t>テントNo.21</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>テントNo.22</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>8号館横 茶室</t>
   </si>
   <si>
@@ -1132,21 +1094,12 @@
     <t>3号館</t>
   </si>
   <si>
-    <t>204</t>
-  </si>
-  <si>
     <t>3-205</t>
   </si>
   <si>
-    <t>205</t>
-  </si>
-  <si>
     <t>3-206</t>
   </si>
   <si>
-    <t>206</t>
-  </si>
-  <si>
     <t>no6</t>
   </si>
   <si>
@@ -1156,9 +1109,6 @@
     <t>6号館</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>no8</t>
   </si>
   <si>
@@ -1171,9 +1121,6 @@
     <t>8-102</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
     <t>8-103・105</t>
   </si>
   <si>
@@ -1183,15 +1130,9 @@
     <t>8-201</t>
   </si>
   <si>
-    <t>201</t>
-  </si>
-  <si>
     <t>8-203</t>
   </si>
   <si>
-    <t>203</t>
-  </si>
-  <si>
     <t>8-204</t>
   </si>
   <si>
@@ -1204,15 +1145,9 @@
     <t>8-305</t>
   </si>
   <si>
-    <t>305</t>
-  </si>
-  <si>
     <t>8-306</t>
   </si>
   <si>
-    <t>306</t>
-  </si>
-  <si>
     <t>カフェポンド前</t>
   </si>
   <si>
@@ -1237,30 +1172,18 @@
     <t>7-301</t>
   </si>
   <si>
-    <t>301</t>
-  </si>
-  <si>
     <t>7-303</t>
   </si>
   <si>
-    <t>303</t>
-  </si>
-  <si>
     <t>loc-7-401</t>
   </si>
   <si>
     <t>7-401</t>
   </si>
   <si>
-    <t>401</t>
-  </si>
-  <si>
     <t>7-403</t>
   </si>
   <si>
-    <t>403</t>
-  </si>
-  <si>
     <t>屋外ステージ</t>
   </si>
   <si>
@@ -1303,6 +1226,9 @@
     <t>学生支援室</t>
   </si>
   <si>
+    <t>loc-3-zakuro</t>
+  </si>
+  <si>
     <t>3号館食堂ザクロ</t>
   </si>
   <si>
@@ -1312,19 +1238,13 @@
     <t>7-202</t>
   </si>
   <si>
-    <t>202</t>
-  </si>
-  <si>
     <t>7-402</t>
   </si>
   <si>
-    <t>402</t>
-  </si>
-  <si>
     <t>7-302</t>
   </si>
   <si>
-    <t>302</t>
+    <t>グラウンド</t>
   </si>
   <si>
     <t>slotId</t>
@@ -1657,134 +1577,38 @@
     <t>14:30</t>
   </si>
   <si>
-    <t>food-oystars</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>culture-oystars</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>food-mogi-shutten</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>culture-shinsengumi</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>culture-tetsudo-bu</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>music-jazz-bu</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>チャペルコンサート</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>music-hn-entertainment</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>music-kannai-sukayutopia</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>food-sado-bu</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>food-ojosama-select</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>food-shashin-bu</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>soccer</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>JR東日本カップ2026 第100回関東大学サッカーリーグ戦</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>その他</t>
-    <rPh sb="2" eb="3">
-      <t>タ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>loc-ground</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>入場無料</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>第19節関東学院大学vs立教大学
-10/31 (土)14:00キックオフ、ぜひご観戦ください！</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>tt-d1-18</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>day1</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>14:00キックオフ</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>グラウンド</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>屋外</t>
-    <rPh sb="0" eb="2">
-      <t>オクガイ</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Sat Dec 30 1899 23:00:00 GMT+0900 (日本標準時)</t>
+  </si>
+  <si>
+    <t>Sun Dec 31 1899 01:00:00 GMT+0900 (日本標準時)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
     </font>
     <font>
-      <sz val="6"/>
+      <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1805,16 +1629,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1827,16 +1651,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="21" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1923,6 +1747,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1957,6 +1782,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1991,20 +1817,16 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="80000">
-              <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="100000"/>
+                <a:shade val="100000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:tint val="50000"/>
+                <a:shade val="100000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -2126,27 +1948,66 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:spDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </a:style>
+    </a:spDef>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="23.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="74.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.571428571428573" customWidth="1"/>
+    <col min="2" max="2" width="22.857142857142858" customWidth="1"/>
+    <col min="3" max="3" width="33.142857142857146" customWidth="1"/>
+    <col min="4" max="4" width="9.714285714285714" customWidth="1"/>
+    <col min="5" max="5" width="14.285714285714286" customWidth="1"/>
+    <col min="6" max="6" width="9.285714285714286" customWidth="1"/>
+    <col min="7" max="8" width="42.142857142857146" customWidth="1"/>
+    <col min="9" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2172,7 +2033,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2198,7 +2059,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>16</v>
       </c>
@@ -2224,616 +2085,598 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>539</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>528</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
         <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D7" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D8" t="s">
         <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H8" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>530</v>
+        <v>51</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
         <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="D10" t="s">
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
         <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C12" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H12" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>538</v>
+        <v>75</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D13" t="s">
         <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B14" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D14" t="s">
         <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="H14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="D15" t="s">
         <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="H15" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D16" t="s">
         <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="H16" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
         <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H17" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B18" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="D18" t="s">
         <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="H18" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B19" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
         <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="H19" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B20" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D20" t="s">
         <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H20" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B21" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
         <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="H21" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B22" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C22" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D22" t="s">
         <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="H22" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B23" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C23" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="D23" t="s">
         <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B24" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C24" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D24" t="s">
         <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="F24" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G24" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="H24" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>537</v>
+        <v>147</v>
       </c>
       <c r="B25" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C25" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="D25" t="s">
         <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="H25" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>148</v>
-      </c>
-      <c r="B26" t="s">
-        <v>149</v>
-      </c>
-      <c r="C26" t="s">
-        <v>150</v>
-      </c>
-      <c r="D26" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" t="s">
-        <v>151</v>
-      </c>
-      <c r="F26" t="s">
-        <v>13</v>
-      </c>
-    </row>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="22.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="34.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="198.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.714285714285715" customWidth="1"/>
+    <col min="2" max="2" width="34.285714285714285" customWidth="1"/>
+    <col min="3" max="3" width="24.857142857142858" customWidth="1"/>
+    <col min="4" max="4" width="9.714285714285714" customWidth="1"/>
+    <col min="5" max="5" width="14.285714285714286" customWidth="1"/>
+    <col min="6" max="6" width="9.285714285714286" customWidth="1"/>
+    <col min="7" max="7" width="42.142857142857146" customWidth="1"/>
+    <col min="8" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2856,369 +2699,370 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B5" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C7" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D7" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C8" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E8" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>531</v>
+        <v>188</v>
       </c>
       <c r="B9" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E9" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="B10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="D10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B11" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E11" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="B12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C12" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E12" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="B13" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E13" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>532</v>
+        <v>209</v>
       </c>
       <c r="B14" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C14" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E14" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>529</v>
+        <v>214</v>
       </c>
       <c r="B15" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E15" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B16" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C16" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E16" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="27.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="23.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="32.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="145.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="27.142857142857142" customWidth="1"/>
+    <col min="2" max="2" width="23.714285714285715" customWidth="1"/>
+    <col min="3" max="3" width="32.714285714285715" customWidth="1"/>
+    <col min="4" max="4" width="9.714285714285714" customWidth="1"/>
+    <col min="5" max="5" width="19.285714285714285" customWidth="1"/>
+    <col min="6" max="6" width="9.285714285714286" customWidth="1"/>
+    <col min="7" max="7" width="42.142857142857146" customWidth="1"/>
+    <col min="8" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3241,486 +3085,487 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="D2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="C4" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E4" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>533</v>
+        <v>236</v>
       </c>
       <c r="B5" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="C5" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="D5" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E5" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="D6" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E6" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="C7" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D7" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E7" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>536</v>
+        <v>247</v>
       </c>
       <c r="B8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E8" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B9" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="C9" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="D9" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E9" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>253</v>
+      </c>
+      <c r="B10" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" t="s">
+        <v>254</v>
+      </c>
+      <c r="D10" t="s">
+        <v>225</v>
+      </c>
+      <c r="E10" t="s">
         <v>248</v>
-      </c>
-      <c r="B10" t="s">
-        <v>249</v>
-      </c>
-      <c r="C10" t="s">
-        <v>249</v>
-      </c>
-      <c r="D10" t="s">
-        <v>220</v>
-      </c>
-      <c r="E10" t="s">
-        <v>243</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B11" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="C11" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D11" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E11" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>535</v>
+        <v>259</v>
       </c>
       <c r="B12" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="C12" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="D12" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E12" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="B13" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="C13" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D13" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E13" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="F13" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G13" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B14" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="C14" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="D14" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E14" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B15" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="C15" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D15" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E15" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B16" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="C16" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="D16" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E16" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B17" t="s">
-        <v>534</v>
+        <v>283</v>
       </c>
       <c r="C17" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D17" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E17" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B18" t="s">
-        <v>534</v>
+        <v>283</v>
       </c>
       <c r="C18" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="D18" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E18" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>289</v>
+      </c>
+      <c r="B19" t="s">
         <v>283</v>
       </c>
-      <c r="B19" t="s">
-        <v>534</v>
-      </c>
       <c r="C19" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D19" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E19" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
       </c>
       <c r="G19" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>292</v>
+      </c>
+      <c r="B20" t="s">
+        <v>283</v>
+      </c>
+      <c r="C20" t="s">
+        <v>293</v>
+      </c>
+      <c r="D20" t="s">
+        <v>225</v>
+      </c>
+      <c r="E20" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+      <c r="F20" t="s">
+        <v>144</v>
+      </c>
+      <c r="G20" t="s">
         <v>286</v>
       </c>
-      <c r="B20" t="s">
-        <v>534</v>
-      </c>
-      <c r="C20" t="s">
-        <v>287</v>
-      </c>
-      <c r="D20" t="s">
-        <v>220</v>
-      </c>
-      <c r="E20" t="s">
-        <v>279</v>
-      </c>
-      <c r="F20" t="s">
-        <v>140</v>
-      </c>
-      <c r="G20" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B21" t="s">
-        <v>534</v>
+        <v>283</v>
       </c>
       <c r="C21" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="D21" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="E21" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="F21" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G21" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="52.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="255.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
+    <col min="2" max="2" width="42.142857142857146" customWidth="1"/>
+    <col min="3" max="3" width="23.285714285714285" customWidth="1"/>
+    <col min="4" max="4" width="9.714285714285714" customWidth="1"/>
+    <col min="5" max="5" width="15.714285714285714" customWidth="1"/>
+    <col min="6" max="6" width="9.285714285714286" customWidth="1"/>
+    <col min="7" max="8" width="42.142857142857146" customWidth="1"/>
+    <col min="9" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>540</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -3744,1143 +3589,1147 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C2" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="D2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="E2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="G2" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="26.4" x14ac:dyDescent="0.2">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>541</v>
+        <v>302</v>
       </c>
       <c r="B3" t="s">
-        <v>542</v>
+        <v>303</v>
       </c>
       <c r="D3" t="s">
-        <v>543</v>
+        <v>304</v>
       </c>
       <c r="E3" t="s">
-        <v>544</v>
+        <v>305</v>
       </c>
       <c r="F3" t="s">
-        <v>548</v>
+        <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>545</v>
+        <v>306</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>546</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F57"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="26.21875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="30.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.285714285714285" customWidth="1"/>
+    <col min="2" max="2" width="10.285714285714286" customWidth="1"/>
+    <col min="3" max="4" width="26.285714285714285" customWidth="1"/>
+    <col min="5" max="5" width="9.285714285714286" customWidth="1"/>
+    <col min="6" max="6" width="30.714285714285715" customWidth="1"/>
+    <col min="7" max="24" width="13.571428571428571" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="D2" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E2" t="s">
-        <v>303</v>
-      </c>
-      <c r="F2" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="D3" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F3" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="F3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="D4" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E4" t="s">
-        <v>303</v>
-      </c>
-      <c r="F4" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="F4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D5" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E5" t="s">
-        <v>303</v>
-      </c>
-      <c r="F5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="F5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="D6" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E6" t="s">
-        <v>303</v>
-      </c>
-      <c r="F6" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="F6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D7" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E7" t="s">
-        <v>303</v>
-      </c>
-      <c r="F7" t="s">
+        <v>315</v>
+      </c>
+      <c r="F7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>321</v>
+      </c>
+      <c r="D8" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>315</v>
       </c>
-      <c r="D8" t="s">
-        <v>302</v>
-      </c>
-      <c r="E8" t="s">
-        <v>303</v>
-      </c>
-      <c r="F8" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D9" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E9" t="s">
-        <v>303</v>
-      </c>
-      <c r="F9" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="F9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D10" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E10" t="s">
-        <v>303</v>
-      </c>
-      <c r="F10" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="F10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D11" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E11" t="s">
-        <v>303</v>
-      </c>
-      <c r="F11" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D12" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E12" t="s">
-        <v>303</v>
-      </c>
-      <c r="F12" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="F12">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D13" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E13" t="s">
-        <v>303</v>
-      </c>
-      <c r="F13" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+        <v>315</v>
+      </c>
+      <c r="F13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
         <v>327</v>
       </c>
       <c r="D14" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="E14" t="s">
-        <v>303</v>
-      </c>
-      <c r="F14" t="s">
+        <v>315</v>
+      </c>
+      <c r="F14">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C15" t="s">
         <v>328</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
+        <v>314</v>
+      </c>
+      <c r="E15" t="s">
+        <v>315</v>
+      </c>
+      <c r="F15">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="C16" t="s">
         <v>329</v>
       </c>
-      <c r="D15" t="s">
-        <v>302</v>
-      </c>
-      <c r="E15" t="s">
-        <v>303</v>
-      </c>
-      <c r="F15" t="s">
+      <c r="D16" t="s">
+        <v>314</v>
+      </c>
+      <c r="E16" t="s">
+        <v>315</v>
+      </c>
+      <c r="F16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C17" t="s">
         <v>330</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="D17" t="s">
+        <v>314</v>
+      </c>
+      <c r="E17" t="s">
+        <v>315</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" t="s">
         <v>331</v>
       </c>
-      <c r="D16" t="s">
-        <v>302</v>
-      </c>
-      <c r="E16" t="s">
-        <v>303</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="D18" t="s">
+        <v>314</v>
+      </c>
+      <c r="E18" t="s">
+        <v>315</v>
+      </c>
+      <c r="F18">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>114</v>
+      </c>
+      <c r="C19" t="s">
         <v>332</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A17" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" t="s">
+      <c r="D19" t="s">
+        <v>314</v>
+      </c>
+      <c r="E19" t="s">
+        <v>315</v>
+      </c>
+      <c r="F19">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>120</v>
+      </c>
+      <c r="C20" t="s">
         <v>333</v>
       </c>
-      <c r="D17" t="s">
-        <v>302</v>
-      </c>
-      <c r="E17" t="s">
-        <v>303</v>
-      </c>
-      <c r="F17" t="s">
+      <c r="D20" t="s">
+        <v>314</v>
+      </c>
+      <c r="E20" t="s">
+        <v>315</v>
+      </c>
+      <c r="F20">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>126</v>
+      </c>
+      <c r="C21" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
-        <v>104</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="D21" t="s">
+        <v>314</v>
+      </c>
+      <c r="E21" t="s">
+        <v>315</v>
+      </c>
+      <c r="F21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>132</v>
+      </c>
+      <c r="C22" t="s">
         <v>335</v>
       </c>
-      <c r="D18" t="s">
-        <v>302</v>
-      </c>
-      <c r="E18" t="s">
-        <v>303</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="D22" t="s">
+        <v>314</v>
+      </c>
+      <c r="E22" t="s">
+        <v>315</v>
+      </c>
+      <c r="F22">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" t="s">
         <v>336</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>110</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D23" t="s">
+        <v>314</v>
+      </c>
+      <c r="E23" t="s">
+        <v>315</v>
+      </c>
+      <c r="F23">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" t="s">
         <v>337</v>
       </c>
-      <c r="D19" t="s">
-        <v>302</v>
-      </c>
-      <c r="E19" t="s">
-        <v>303</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="D24" t="s">
         <v>338</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>116</v>
-      </c>
-      <c r="C20" t="s">
-        <v>339</v>
-      </c>
-      <c r="D20" t="s">
-        <v>302</v>
-      </c>
-      <c r="E20" t="s">
-        <v>303</v>
-      </c>
-      <c r="F20" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>122</v>
-      </c>
-      <c r="C21" t="s">
-        <v>341</v>
-      </c>
-      <c r="D21" t="s">
-        <v>302</v>
-      </c>
-      <c r="E21" t="s">
-        <v>303</v>
-      </c>
-      <c r="F21" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>128</v>
-      </c>
-      <c r="C22" t="s">
-        <v>343</v>
-      </c>
-      <c r="D22" t="s">
-        <v>302</v>
-      </c>
-      <c r="E22" t="s">
-        <v>303</v>
-      </c>
-      <c r="F22" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>134</v>
-      </c>
-      <c r="C23" t="s">
-        <v>345</v>
-      </c>
-      <c r="D23" t="s">
-        <v>302</v>
-      </c>
-      <c r="E23" t="s">
-        <v>303</v>
-      </c>
-      <c r="F23" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" t="s">
-        <v>347</v>
-      </c>
-      <c r="D24" t="s">
-        <v>348</v>
       </c>
       <c r="E24">
         <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B25" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C25" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="D25" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E25">
         <v>2</v>
       </c>
-      <c r="F25" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F25">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B26" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C26" t="s">
-        <v>354</v>
+        <v>343</v>
       </c>
       <c r="D26" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E26">
         <v>2</v>
       </c>
-      <c r="F26" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F26">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C27" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="D27" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
-      <c r="F27" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F27">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B28" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="C28" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="D28" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="E28">
         <v>1</v>
       </c>
-      <c r="F28" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F28">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B29" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C29" t="s">
-        <v>363</v>
+        <v>349</v>
       </c>
       <c r="D29" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E29">
         <v>1</v>
       </c>
-      <c r="F29" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F29">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B30" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C30" t="s">
-        <v>365</v>
+        <v>351</v>
       </c>
       <c r="D30" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
-      <c r="F30" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F30">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="B31" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C31" t="s">
-        <v>367</v>
+        <v>352</v>
       </c>
       <c r="D31" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="B32" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C32" t="s">
-        <v>369</v>
+        <v>354</v>
       </c>
       <c r="D32" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E32">
         <v>2</v>
       </c>
-      <c r="F32" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F32">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B33" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C33" t="s">
-        <v>371</v>
+        <v>355</v>
       </c>
       <c r="D33" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E33">
         <v>2</v>
       </c>
-      <c r="F33" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F33">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B34" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C34" t="s">
-        <v>373</v>
+        <v>356</v>
       </c>
       <c r="D34" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
-      <c r="F34" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F34">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B35" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C35" t="s">
-        <v>374</v>
+        <v>357</v>
       </c>
       <c r="D35" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
-      <c r="F35" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F35">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B36" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C36" t="s">
-        <v>375</v>
+        <v>358</v>
       </c>
       <c r="D36" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
-      <c r="F36" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F36">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B37" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C37" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="D37" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E37">
         <v>3</v>
       </c>
-      <c r="F37" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F37">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B38" t="s">
-        <v>362</v>
+        <v>348</v>
       </c>
       <c r="C38" t="s">
-        <v>378</v>
+        <v>360</v>
       </c>
       <c r="D38" t="s">
-        <v>364</v>
+        <v>350</v>
       </c>
       <c r="E38">
         <v>3</v>
       </c>
-      <c r="F38" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F38">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="B39" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="C39" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="D39" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="E39">
         <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>381</v>
+        <v>362</v>
       </c>
       <c r="B40" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C40" t="s">
-        <v>383</v>
+        <v>364</v>
       </c>
       <c r="D40" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="E40">
         <v>2</v>
       </c>
-      <c r="F40" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F40">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B41" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C41" t="s">
-        <v>385</v>
+        <v>366</v>
       </c>
       <c r="D41" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="E41">
         <v>2</v>
       </c>
-      <c r="F41" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F41">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="B42" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C42" t="s">
-        <v>387</v>
+        <v>368</v>
       </c>
       <c r="D42" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="E42">
         <v>3</v>
       </c>
-      <c r="F42" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F42">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B43" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C43" t="s">
-        <v>389</v>
+        <v>369</v>
       </c>
       <c r="D43" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="E43">
         <v>3</v>
       </c>
-      <c r="F43" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F43">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>391</v>
+        <v>370</v>
       </c>
       <c r="B44" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C44" t="s">
-        <v>392</v>
+        <v>371</v>
       </c>
       <c r="D44" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="E44">
         <v>4</v>
       </c>
-      <c r="F44" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F44">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="B45" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C45" t="s">
-        <v>394</v>
+        <v>372</v>
       </c>
       <c r="D45" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="E45">
         <v>4</v>
       </c>
-      <c r="F45" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F45">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="C46" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
       <c r="D46" t="s">
-        <v>396</v>
+        <v>373</v>
       </c>
       <c r="E46" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F46" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="B47" t="s">
-        <v>397</v>
+        <v>374</v>
       </c>
       <c r="C47" t="s">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="D47" t="s">
-        <v>399</v>
+        <v>376</v>
       </c>
       <c r="E47">
         <v>4</v>
       </c>
       <c r="F47" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="C48" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="D48" t="s">
-        <v>401</v>
+        <v>378</v>
       </c>
       <c r="E48">
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="C49" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="D49" t="s">
-        <v>402</v>
+        <v>379</v>
       </c>
       <c r="E49" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
       <c r="F49" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C50" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="D50" t="s">
-        <v>404</v>
+        <v>381</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C51" t="s">
-        <v>406</v>
+        <v>383</v>
       </c>
       <c r="D51" t="s">
-        <v>407</v>
+        <v>384</v>
       </c>
       <c r="E51">
         <v>6</v>
       </c>
       <c r="F51" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B52" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C52" t="s">
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="D52" t="s">
-        <v>384</v>
+        <v>365</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>151</v>
+        <v>387</v>
       </c>
       <c r="B53" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="C53" t="s">
-        <v>410</v>
+        <v>388</v>
       </c>
       <c r="D53" t="s">
-        <v>352</v>
-      </c>
-      <c r="E53" t="s">
-        <v>304</v>
+        <v>342</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="B54" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C54" t="s">
-        <v>412</v>
+        <v>390</v>
       </c>
       <c r="D54" t="s">
-        <v>384</v>
-      </c>
-      <c r="E54" t="s">
-        <v>306</v>
-      </c>
-      <c r="F54" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
+        <v>365</v>
+      </c>
+      <c r="E54">
+        <v>2</v>
+      </c>
+      <c r="F54">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="B55" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C55" t="s">
-        <v>414</v>
+        <v>391</v>
       </c>
       <c r="D55" t="s">
-        <v>384</v>
-      </c>
-      <c r="E55" t="s">
-        <v>310</v>
-      </c>
-      <c r="F55" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
+        <v>365</v>
+      </c>
+      <c r="E55">
+        <v>4</v>
+      </c>
+      <c r="F55">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B56" t="s">
-        <v>382</v>
+        <v>363</v>
       </c>
       <c r="C56" t="s">
-        <v>416</v>
+        <v>392</v>
       </c>
       <c r="D56" t="s">
-        <v>384</v>
-      </c>
-      <c r="E56" t="s">
-        <v>308</v>
-      </c>
-      <c r="F56" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
+        <v>365</v>
+      </c>
+      <c r="E56">
+        <v>3</v>
+      </c>
+      <c r="F56">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>544</v>
+        <v>305</v>
       </c>
       <c r="C57" t="s">
-        <v>550</v>
+        <v>393</v>
       </c>
       <c r="D57" t="s">
-        <v>550</v>
+        <v>393</v>
       </c>
       <c r="E57" t="s">
-        <v>551</v>
+        <v>315</v>
       </c>
       <c r="F57" t="s">
-        <v>550</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G35"/>
-  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>418</v>
+        <v>394</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -4889,799 +4738,799 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>420</v>
+        <v>396</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B2" t="s">
-        <v>422</v>
+        <v>398</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E2" t="s">
-        <v>423</v>
+        <v>399</v>
       </c>
       <c r="F2" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="G2" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="B3" t="s">
-        <v>426</v>
+        <v>402</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E3" t="s">
-        <v>427</v>
+        <v>403</v>
       </c>
       <c r="F3" t="s">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="G3" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B4" t="s">
-        <v>430</v>
+        <v>406</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E4" t="s">
-        <v>431</v>
+        <v>407</v>
       </c>
       <c r="F4" t="s">
-        <v>432</v>
+        <v>408</v>
       </c>
       <c r="G4" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="B5" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E5" t="s">
-        <v>435</v>
+        <v>411</v>
       </c>
       <c r="F5" t="s">
-        <v>436</v>
+        <v>412</v>
       </c>
       <c r="G5" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B6" t="s">
-        <v>438</v>
+        <v>414</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E6" t="s">
-        <v>439</v>
+        <v>415</v>
       </c>
       <c r="F6" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="G6" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="B7" t="s">
-        <v>442</v>
+        <v>418</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E7" t="s">
-        <v>443</v>
+        <v>419</v>
       </c>
       <c r="F7" t="s">
-        <v>444</v>
+        <v>420</v>
       </c>
       <c r="G7" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B8" t="s">
-        <v>446</v>
+        <v>422</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="E8" t="s">
-        <v>447</v>
+        <v>423</v>
       </c>
       <c r="F8" t="s">
-        <v>448</v>
+        <v>424</v>
       </c>
       <c r="G8" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B9" t="s">
-        <v>450</v>
+        <v>426</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E9" t="s">
-        <v>451</v>
+        <v>427</v>
       </c>
       <c r="F9" t="s">
-        <v>452</v>
+        <v>428</v>
       </c>
       <c r="G9" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B10" t="s">
-        <v>454</v>
+        <v>430</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E10" t="s">
-        <v>455</v>
+        <v>431</v>
       </c>
       <c r="F10" t="s">
-        <v>456</v>
+        <v>432</v>
       </c>
       <c r="G10" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B11" t="s">
-        <v>458</v>
+        <v>434</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E11" t="s">
-        <v>459</v>
+        <v>435</v>
       </c>
       <c r="F11" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="G11" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B12" t="s">
-        <v>461</v>
+        <v>437</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E12" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="F12" t="s">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="G12" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="B13" t="s">
-        <v>465</v>
+        <v>441</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E13" t="s">
-        <v>466</v>
+        <v>442</v>
       </c>
       <c r="F13" t="s">
-        <v>424</v>
+        <v>400</v>
       </c>
       <c r="G13" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B14" t="s">
-        <v>468</v>
+        <v>444</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="E14" t="s">
-        <v>469</v>
+        <v>445</v>
       </c>
       <c r="F14" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="G14" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B15" t="s">
-        <v>471</v>
+        <v>447</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E15" t="s">
-        <v>472</v>
+        <v>448</v>
       </c>
       <c r="F15" t="s">
-        <v>473</v>
+        <v>449</v>
       </c>
       <c r="G15" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B16" t="s">
-        <v>475</v>
+        <v>451</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E16" t="s">
-        <v>476</v>
+        <v>452</v>
       </c>
       <c r="F16" t="s">
-        <v>470</v>
+        <v>446</v>
       </c>
       <c r="G16" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B17" t="s">
-        <v>478</v>
+        <v>454</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E17" t="s">
-        <v>479</v>
+        <v>455</v>
       </c>
       <c r="F17" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="G17" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B18" t="s">
-        <v>482</v>
+        <v>458</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E18" t="s">
+        <v>459</v>
+      </c>
+      <c r="F18" t="s">
+        <v>460</v>
+      </c>
+      <c r="G18" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>243</v>
+      </c>
+      <c r="B19" t="s">
+        <v>462</v>
+      </c>
+      <c r="C19" t="s">
+        <v>144</v>
+      </c>
+      <c r="D19" t="s">
+        <v>261</v>
+      </c>
+      <c r="E19" t="s">
+        <v>463</v>
+      </c>
+      <c r="F19" t="s">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>223</v>
+      </c>
+      <c r="B20" t="s">
+        <v>465</v>
+      </c>
+      <c r="C20" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" t="s">
+        <v>261</v>
+      </c>
+      <c r="E20" t="s">
+        <v>466</v>
+      </c>
+      <c r="F20" t="s">
+        <v>401</v>
+      </c>
+      <c r="G20" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>228</v>
+      </c>
+      <c r="B21" t="s">
+        <v>468</v>
+      </c>
+      <c r="C21" t="s">
+        <v>144</v>
+      </c>
+      <c r="D21" t="s">
+        <v>261</v>
+      </c>
+      <c r="E21" t="s">
+        <v>469</v>
+      </c>
+      <c r="F21" t="s">
+        <v>470</v>
+      </c>
+      <c r="G21" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>236</v>
+      </c>
+      <c r="B22" t="s">
+        <v>472</v>
+      </c>
+      <c r="C22" t="s">
+        <v>144</v>
+      </c>
+      <c r="D22" t="s">
+        <v>261</v>
+      </c>
+      <c r="E22" t="s">
+        <v>473</v>
+      </c>
+      <c r="F22" t="s">
+        <v>474</v>
+      </c>
+      <c r="G22" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>239</v>
+      </c>
+      <c r="B23" t="s">
+        <v>476</v>
+      </c>
+      <c r="C23" t="s">
+        <v>144</v>
+      </c>
+      <c r="D23" t="s">
+        <v>261</v>
+      </c>
+      <c r="E23" t="s">
+        <v>477</v>
+      </c>
+      <c r="F23" t="s">
+        <v>478</v>
+      </c>
+      <c r="G23" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>232</v>
+      </c>
+      <c r="B24" t="s">
+        <v>479</v>
+      </c>
+      <c r="C24" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" t="s">
+        <v>261</v>
+      </c>
+      <c r="E24" t="s">
+        <v>480</v>
+      </c>
+      <c r="F24" t="s">
+        <v>481</v>
+      </c>
+      <c r="G24" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>259</v>
+      </c>
+      <c r="B25" t="s">
+        <v>482</v>
+      </c>
+      <c r="C25" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" t="s">
+        <v>261</v>
+      </c>
+      <c r="E25" t="s">
         <v>483</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F25" t="s">
+        <v>460</v>
+      </c>
+      <c r="G25" t="s">
         <v>484</v>
       </c>
-      <c r="G18" t="s">
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>263</v>
+      </c>
+      <c r="B26" t="s">
         <v>485</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B19" t="s">
+      <c r="C26" t="s">
+        <v>144</v>
+      </c>
+      <c r="D26" t="s">
+        <v>261</v>
+      </c>
+      <c r="E26" t="s">
         <v>486</v>
       </c>
-      <c r="C19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="F26" t="s">
+        <v>443</v>
+      </c>
+      <c r="G26" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>247</v>
+      </c>
+      <c r="B27" t="s">
+        <v>487</v>
+      </c>
+      <c r="C27" t="s">
+        <v>144</v>
+      </c>
+      <c r="D27" t="s">
+        <v>248</v>
+      </c>
+      <c r="E27" t="s">
+        <v>488</v>
+      </c>
+      <c r="F27" t="s">
+        <v>489</v>
+      </c>
+      <c r="G27" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>256</v>
       </c>
-      <c r="E19" t="s">
-        <v>487</v>
-      </c>
-      <c r="F19" t="s">
-        <v>424</v>
-      </c>
-      <c r="G19" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
-        <v>218</v>
-      </c>
-      <c r="B20" t="s">
-        <v>489</v>
-      </c>
-      <c r="C20" t="s">
-        <v>140</v>
-      </c>
-      <c r="D20" t="s">
-        <v>256</v>
-      </c>
-      <c r="E20" t="s">
+      <c r="B28" t="s">
         <v>490</v>
       </c>
-      <c r="F20" t="s">
-        <v>425</v>
-      </c>
-      <c r="G20" t="s">
+      <c r="C28" t="s">
+        <v>144</v>
+      </c>
+      <c r="D28" t="s">
+        <v>248</v>
+      </c>
+      <c r="E28" t="s">
         <v>491</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
-        <v>223</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="F28" t="s">
+        <v>409</v>
+      </c>
+      <c r="G28" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>296</v>
+      </c>
+      <c r="B29" t="s">
         <v>492</v>
       </c>
-      <c r="C21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D21" t="s">
-        <v>256</v>
-      </c>
-      <c r="E21" t="s">
+      <c r="C29" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" t="s">
+        <v>248</v>
+      </c>
+      <c r="E29" t="s">
         <v>493</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F29" t="s">
         <v>494</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G29" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
-        <v>231</v>
-      </c>
-      <c r="B22" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>277</v>
+      </c>
+      <c r="B30" t="s">
         <v>496</v>
       </c>
-      <c r="C22" t="s">
-        <v>140</v>
-      </c>
-      <c r="D22" t="s">
-        <v>256</v>
-      </c>
-      <c r="E22" t="s">
+      <c r="C30" t="s">
+        <v>144</v>
+      </c>
+      <c r="D30" t="s">
+        <v>280</v>
+      </c>
+      <c r="E30" t="s">
+        <v>442</v>
+      </c>
+      <c r="F30" t="s">
+        <v>400</v>
+      </c>
+      <c r="G30" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>292</v>
+      </c>
+      <c r="B31" t="s">
         <v>497</v>
       </c>
-      <c r="F22" t="s">
+      <c r="C31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" t="s">
+        <v>285</v>
+      </c>
+      <c r="E31" t="s">
         <v>498</v>
       </c>
-      <c r="G22" t="s">
+      <c r="F31" t="s">
+        <v>409</v>
+      </c>
+      <c r="G31" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>292</v>
+      </c>
+      <c r="B32" t="s">
         <v>499</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
-        <v>234</v>
-      </c>
-      <c r="B23" t="s">
+      <c r="C32" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" t="s">
+        <v>285</v>
+      </c>
+      <c r="E32" t="s">
+        <v>448</v>
+      </c>
+      <c r="F32" t="s">
+        <v>449</v>
+      </c>
+      <c r="G32" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>294</v>
+      </c>
+      <c r="B33" t="s">
         <v>500</v>
       </c>
-      <c r="C23" t="s">
-        <v>140</v>
-      </c>
-      <c r="D23" t="s">
-        <v>256</v>
-      </c>
-      <c r="E23" t="s">
+      <c r="C33" t="s">
+        <v>144</v>
+      </c>
+      <c r="D33" t="s">
+        <v>285</v>
+      </c>
+      <c r="E33" t="s">
+        <v>452</v>
+      </c>
+      <c r="F33" t="s">
+        <v>446</v>
+      </c>
+      <c r="G33" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>294</v>
+      </c>
+      <c r="B34" t="s">
         <v>501</v>
       </c>
-      <c r="F23" t="s">
+      <c r="C34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D34" t="s">
+        <v>285</v>
+      </c>
+      <c r="E34" t="s">
         <v>502</v>
       </c>
-      <c r="G23" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
-        <v>227</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="F34" t="s">
         <v>503</v>
       </c>
-      <c r="C24" t="s">
-        <v>140</v>
-      </c>
-      <c r="D24" t="s">
-        <v>256</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="G34" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>302</v>
+      </c>
+      <c r="B35" t="s">
         <v>504</v>
       </c>
-      <c r="F24" t="s">
+      <c r="C35" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" t="s">
+        <v>305</v>
+      </c>
+      <c r="E35" t="s">
         <v>505</v>
       </c>
-      <c r="G24" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A25" t="s">
-        <v>254</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="F35" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="C25" t="s">
-        <v>140</v>
-      </c>
-      <c r="D25" t="s">
-        <v>256</v>
-      </c>
-      <c r="E25" t="s">
+      <c r="G35" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="F25" t="s">
-        <v>484</v>
-      </c>
-      <c r="G25" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
-        <v>258</v>
-      </c>
-      <c r="B26" t="s">
-        <v>509</v>
-      </c>
-      <c r="C26" t="s">
-        <v>140</v>
-      </c>
-      <c r="D26" t="s">
-        <v>256</v>
-      </c>
-      <c r="E26" t="s">
-        <v>510</v>
-      </c>
-      <c r="F26" t="s">
-        <v>467</v>
-      </c>
-      <c r="G26" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>242</v>
-      </c>
-      <c r="B27" t="s">
-        <v>511</v>
-      </c>
-      <c r="C27" t="s">
-        <v>140</v>
-      </c>
-      <c r="D27" t="s">
-        <v>243</v>
-      </c>
-      <c r="E27" t="s">
-        <v>512</v>
-      </c>
-      <c r="F27" t="s">
-        <v>513</v>
-      </c>
-      <c r="G27" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>251</v>
-      </c>
-      <c r="B28" t="s">
-        <v>514</v>
-      </c>
-      <c r="C28" t="s">
-        <v>140</v>
-      </c>
-      <c r="D28" t="s">
-        <v>243</v>
-      </c>
-      <c r="E28" t="s">
-        <v>515</v>
-      </c>
-      <c r="F28" t="s">
-        <v>433</v>
-      </c>
-      <c r="G28" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
-        <v>290</v>
-      </c>
-      <c r="B29" t="s">
-        <v>516</v>
-      </c>
-      <c r="C29" t="s">
-        <v>140</v>
-      </c>
-      <c r="D29" t="s">
-        <v>243</v>
-      </c>
-      <c r="E29" t="s">
-        <v>517</v>
-      </c>
-      <c r="F29" t="s">
-        <v>518</v>
-      </c>
-      <c r="G29" t="s">
-        <v>519</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
-        <v>272</v>
-      </c>
-      <c r="B30" t="s">
-        <v>520</v>
-      </c>
-      <c r="C30" t="s">
-        <v>140</v>
-      </c>
-      <c r="D30" t="s">
-        <v>275</v>
-      </c>
-      <c r="E30" t="s">
-        <v>466</v>
-      </c>
-      <c r="F30" t="s">
-        <v>424</v>
-      </c>
-      <c r="G30" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31" t="s">
-        <v>286</v>
-      </c>
-      <c r="B31" t="s">
-        <v>521</v>
-      </c>
-      <c r="C31" t="s">
-        <v>140</v>
-      </c>
-      <c r="D31" t="s">
-        <v>279</v>
-      </c>
-      <c r="E31" t="s">
-        <v>522</v>
-      </c>
-      <c r="F31" t="s">
-        <v>433</v>
-      </c>
-      <c r="G31" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
-        <v>286</v>
-      </c>
-      <c r="B32" t="s">
-        <v>523</v>
-      </c>
-      <c r="C32" t="s">
-        <v>140</v>
-      </c>
-      <c r="D32" t="s">
-        <v>279</v>
-      </c>
-      <c r="E32" t="s">
-        <v>472</v>
-      </c>
-      <c r="F32" t="s">
-        <v>473</v>
-      </c>
-      <c r="G32" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>288</v>
-      </c>
-      <c r="B33" t="s">
-        <v>524</v>
-      </c>
-      <c r="C33" t="s">
-        <v>140</v>
-      </c>
-      <c r="D33" t="s">
-        <v>279</v>
-      </c>
-      <c r="E33" t="s">
-        <v>476</v>
-      </c>
-      <c r="F33" t="s">
-        <v>470</v>
-      </c>
-      <c r="G33" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>288</v>
-      </c>
-      <c r="B34" t="s">
-        <v>525</v>
-      </c>
-      <c r="C34" t="s">
-        <v>140</v>
-      </c>
-      <c r="D34" t="s">
-        <v>279</v>
-      </c>
-      <c r="E34" t="s">
-        <v>526</v>
-      </c>
-      <c r="F34" t="s">
-        <v>527</v>
-      </c>
-      <c r="G34" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>541</v>
-      </c>
-      <c r="B35" t="s">
-        <v>547</v>
-      </c>
-      <c r="C35" t="s">
-        <v>548</v>
-      </c>
-      <c r="D35" t="s">
-        <v>544</v>
-      </c>
-      <c r="E35" t="s">
-        <v>549</v>
-      </c>
-      <c r="F35" s="3">
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="G35" s="3">
-        <v>0.66666666666666663</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>
--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="505">
   <si>
     <t>id</t>
   </si>
@@ -1547,9 +1547,6 @@
     <t>開場15:30 開演16:30</t>
   </si>
   <si>
-    <t>15:30:00</t>
-  </si>
-  <si>
     <t>17:30</t>
   </si>
   <si>
@@ -1581,12 +1578,6 @@
   </si>
   <si>
     <t>14:00キックオフ</t>
-  </si>
-  <si>
-    <t>Sat Dec 30 1899 23:00:00 GMT+0900 (日本標準時)</t>
-  </si>
-  <si>
-    <t>Sun Dec 31 1899 01:00:00 GMT+0900 (日本標準時)</t>
   </si>
 </sst>
 </file>
@@ -1654,7 +1645,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="21" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1994,7 +1985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="23.571428571428573" customWidth="1"/>
@@ -2654,7 +2645,6 @@
         <v>152</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5385,10 +5375,10 @@
         <v>493</v>
       </c>
       <c r="F29" t="s">
+        <v>461</v>
+      </c>
+      <c r="G29" t="s">
         <v>494</v>
-      </c>
-      <c r="G29" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -5396,7 +5386,7 @@
         <v>277</v>
       </c>
       <c r="B30" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C30" t="s">
         <v>144</v>
@@ -5419,7 +5409,7 @@
         <v>292</v>
       </c>
       <c r="B31" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="C31" t="s">
         <v>144</v>
@@ -5428,7 +5418,7 @@
         <v>285</v>
       </c>
       <c r="E31" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F31" t="s">
         <v>409</v>
@@ -5442,7 +5432,7 @@
         <v>292</v>
       </c>
       <c r="B32" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C32" t="s">
         <v>144</v>
@@ -5465,7 +5455,7 @@
         <v>294</v>
       </c>
       <c r="B33" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C33" t="s">
         <v>144</v>
@@ -5488,7 +5478,7 @@
         <v>294</v>
       </c>
       <c r="B34" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C34" t="s">
         <v>144</v>
@@ -5497,10 +5487,10 @@
         <v>285</v>
       </c>
       <c r="E34" t="s">
+        <v>501</v>
+      </c>
+      <c r="F34" t="s">
         <v>502</v>
-      </c>
-      <c r="F34" t="s">
-        <v>503</v>
       </c>
       <c r="G34" t="s">
         <v>456</v>
@@ -5511,7 +5501,7 @@
         <v>302</v>
       </c>
       <c r="B35" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C35" t="s">
         <v>20</v>
@@ -5520,13 +5510,13 @@
         <v>305</v>
       </c>
       <c r="E35" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>506</v>
+        <v>446</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>507</v>
+        <v>443</v>
       </c>
     </row>
   </sheetData>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="516">
   <si>
     <t>id</t>
   </si>
@@ -487,7 +487,7 @@
     <t>茶道部</t>
   </si>
   <si>
-    <t>loc-sado-room</t>
+    <t>loc-3-zakuro</t>
   </si>
   <si>
     <t xml:space="preserve">参加費　おひとり500円
@@ -495,6 +495,38 @@
   </si>
   <si>
     <t>茶道部です！8号館横の茶室で抹茶とお菓子をご用意しています。ぜひお気軽にお越しください！</t>
+  </si>
+  <si>
+    <t>food-kangaku-kyoukai</t>
+  </si>
+  <si>
+    <t>ミャンマーティー</t>
+  </si>
+  <si>
+    <t>関東学院教会</t>
+  </si>
+  <si>
+    <t>loc-company-tent-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">・２０２６年クリスマス礼拝の案内をお渡ししています。
+・チャリティでミャンマーティー（１杯１００円）、その他ミャンマーのグッズを販売しています。</t>
+  </si>
+  <si>
+    <t>金沢八景キャンパスのチャペルで毎週日曜日に礼拝を行っている教会です。どなたでもご来会ください。</t>
+  </si>
+  <si>
+    <t>docomo-cs</t>
+  </si>
+  <si>
+    <t>ドコモCS神奈川支店</t>
+  </si>
+  <si>
+    <t>loc-company-tent-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大人気ポインコも登場！
+毎年人気の握力王決定戦もたくさんノベルティを用意してお待ちしています。</t>
   </si>
   <si>
     <t>culture-wandervogel-bu</t>
@@ -1076,6 +1108,12 @@
     <t>テントNo.22</t>
   </si>
   <si>
+    <t>企業テントNo.1</t>
+  </si>
+  <si>
+    <t>loc-sado-room</t>
+  </si>
+  <si>
     <t>8号館横 茶室</t>
   </si>
   <si>
@@ -1224,9 +1262,6 @@
   </si>
   <si>
     <t>学生支援室</t>
-  </si>
-  <si>
-    <t>loc-3-zakuro</t>
   </si>
   <si>
     <t>3号館食堂ザクロ</t>
@@ -1985,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="23.571428571428573" customWidth="1"/>
@@ -2632,10 +2667,8 @@
       <c r="D25" t="s">
         <v>11</v>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>loc-3-zakuro</t>
-        </is>
+      <c r="E25" t="s">
+        <v>150</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -2645,6 +2678,55 @@
       </c>
       <c r="H25" t="s">
         <v>152</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>153</v>
+      </c>
+      <c r="B26" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" t="s">
+        <v>155</v>
+      </c>
+      <c r="D26" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" t="s">
+        <v>156</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26" t="s">
+        <v>157</v>
+      </c>
+      <c r="H26" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" ht="36" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" t="s">
+        <v>161</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" t="s">
+        <v>162</v>
       </c>
     </row>
   </sheetData>
@@ -2693,180 +2775,180 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="D3" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E3" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="B4" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="C4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D4" t="s">
         <v>166</v>
       </c>
-      <c r="D4" t="s">
-        <v>156</v>
-      </c>
       <c r="E4" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="D5" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E5" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="B6" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="D6" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E6" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="B7" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="C7" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="D7" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E7" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="B8" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="C8" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="D8" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E8" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="B9" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="C9" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="D9" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E9" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
@@ -2874,163 +2956,163 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="B10" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C10" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="D10" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E10" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B11" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E11" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="B12" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C12" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="D12" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E12" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="B13" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="C13" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E13" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="B14" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C14" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="D14" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E14" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="B15" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E15" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B16" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C16" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="D16" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="E16" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>
@@ -3079,88 +3161,88 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C2" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D2" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E2" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="C3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D3" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E3" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B4" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="C4" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D4" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E4" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B5" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="C5" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D5" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E5" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -3168,53 +3250,53 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B6" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C6" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D6" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E6" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C7" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="D7" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E7" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B8" t="s">
         <v>95</v>
@@ -3223,315 +3305,315 @@
         <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E8" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B9" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="C9" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="D9" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B10" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="C10" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="D10" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E10" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B11" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="C11" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="D11" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E11" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B12" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="C12" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="D12" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E12" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B13" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="C13" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="D13" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E13" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="F13" t="s">
         <v>144</v>
       </c>
       <c r="G13" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B14" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="C14" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="D14" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E14" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B15" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="C15" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="D15" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E15" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="F15" t="s">
         <v>20</v>
       </c>
       <c r="G15" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B16" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="C16" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="D16" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E16" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B17" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="C17" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="D17" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E17" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B18" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="C18" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="D18" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E18" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B19" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="C19" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="D19" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E19" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="F19" t="s">
         <v>20</v>
       </c>
       <c r="G19" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B20" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="C20" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="D20" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="E20" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="F20" t="s">
         <v>144</v>
       </c>
       <c r="G20" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B21" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="C21" t="s">
+        <v>305</v>
+      </c>
+      <c r="D21" t="s">
+        <v>235</v>
+      </c>
+      <c r="E21" t="s">
         <v>295</v>
-      </c>
-      <c r="D21" t="s">
-        <v>225</v>
-      </c>
-      <c r="E21" t="s">
-        <v>285</v>
       </c>
       <c r="F21" t="s">
         <v>144</v>
       </c>
       <c r="G21" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -3542,7 +3624,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
@@ -3583,51 +3665,74 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B2" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="C2" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="D2" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="E2" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="F2" t="s">
         <v>144</v>
       </c>
       <c r="G2" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="H2" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
     </row>
     <row r="3" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B3" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="D3" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="E3" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>307</v>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>277</v>
+      </c>
+      <c r="B4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C4" t="s">
+        <v>279</v>
+      </c>
+      <c r="D4" t="s">
+        <v>235</v>
+      </c>
+      <c r="E4" t="s">
+        <v>280</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H4" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
@@ -3638,7 +3743,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19.285714285714285" customWidth="1"/>
@@ -3654,19 +3759,19 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -3674,13 +3779,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="D2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E2" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -3691,13 +3796,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="D3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E3" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -3708,13 +3813,13 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="D4" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E4" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -3725,13 +3830,13 @@
         <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="D5" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E5" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -3742,13 +3847,13 @@
         <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="D6" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E6" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3759,13 +3864,13 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="D7" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E7" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -3776,13 +3881,13 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="D8" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E8" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -3793,13 +3898,13 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="D9" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E9" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -3810,13 +3915,13 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="D10" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E10" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -3827,13 +3932,13 @@
         <v>66</v>
       </c>
       <c r="C11" t="s">
+        <v>334</v>
+      </c>
+      <c r="D11" t="s">
         <v>324</v>
       </c>
-      <c r="D11" t="s">
-        <v>314</v>
-      </c>
       <c r="E11" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -3844,13 +3949,13 @@
         <v>72</v>
       </c>
       <c r="C12" t="s">
+        <v>335</v>
+      </c>
+      <c r="D12" t="s">
+        <v>324</v>
+      </c>
+      <c r="E12" t="s">
         <v>325</v>
-      </c>
-      <c r="D12" t="s">
-        <v>314</v>
-      </c>
-      <c r="E12" t="s">
-        <v>315</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -3861,13 +3966,13 @@
         <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="D13" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E13" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -3878,13 +3983,13 @@
         <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="D14" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E14" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -3895,13 +4000,13 @@
         <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="D15" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E15" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -3912,13 +4017,13 @@
         <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="D16" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E16" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -3929,13 +4034,13 @@
         <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="D17" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E17" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -3946,13 +4051,13 @@
         <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="D18" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E18" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -3963,13 +4068,13 @@
         <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="D19" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E19" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -3980,13 +4085,13 @@
         <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="D20" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E20" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -3997,13 +4102,13 @@
         <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="D21" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E21" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -4014,13 +4119,13 @@
         <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="D22" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E22" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -4031,13 +4136,13 @@
         <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="D23" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="E23" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -4045,661 +4150,697 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C24" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="D24" t="s">
-        <v>338</v>
-      </c>
-      <c r="E24">
+        <v>324</v>
+      </c>
+      <c r="E24" t="s">
+        <v>325</v>
+      </c>
+      <c r="F24">
         <v>1</v>
-      </c>
-      <c r="F24" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>221</v>
-      </c>
-      <c r="B25" t="s">
-        <v>340</v>
-      </c>
-      <c r="C25" t="s">
-        <v>341</v>
+        <v>156</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>企業テントNo.2</t>
+        </is>
       </c>
       <c r="D25" t="s">
-        <v>342</v>
-      </c>
-      <c r="E25">
+        <v>324</v>
+      </c>
+      <c r="E25" t="s">
+        <v>325</v>
+      </c>
+      <c r="F25">
         <v>2</v>
-      </c>
-      <c r="F25">
-        <v>204</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>162</v>
-      </c>
-      <c r="B26" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="C26" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="D26" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="E26">
-        <v>2</v>
-      </c>
-      <c r="F26">
-        <v>205</v>
+        <v>1</v>
+      </c>
+      <c r="F26" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>167</v>
+        <v>231</v>
       </c>
       <c r="B27" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="C27" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D27" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="E27">
         <v>2</v>
       </c>
       <c r="F27">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>207</v>
+        <v>172</v>
       </c>
       <c r="B28" t="s">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C28" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D28" t="s">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="E28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28">
-        <v>101</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="B29" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C29" t="s">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="D29" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E29">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F29">
-        <v>101</v>
+        <v>206</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="B30" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="C30" t="s">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="D30" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="E30">
         <v>1</v>
       </c>
       <c r="F30">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B31" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C31" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D31" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E31">
         <v>1</v>
       </c>
-      <c r="F31" t="s">
-        <v>353</v>
+      <c r="F31">
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="B32" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C32" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="D32" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>201</v>
+        <v>102</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="B33" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C33" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="D33" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E33">
-        <v>2</v>
-      </c>
-      <c r="F33">
-        <v>203</v>
+        <v>1</v>
+      </c>
+      <c r="F33" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>157</v>
+        <v>205</v>
       </c>
       <c r="B34" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C34" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="D34" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E34">
         <v>2</v>
       </c>
       <c r="F34">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="B35" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C35" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="D35" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E35">
         <v>2</v>
       </c>
       <c r="F35">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="B36" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C36" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="D36" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B37" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C37" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="D37" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E37">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F37">
-        <v>305</v>
+        <v>205</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B38" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="C38" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="D38" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="E38">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F38">
-        <v>306</v>
+        <v>206</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="B39" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="C39" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="D39" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="E39">
-        <v>1</v>
-      </c>
-      <c r="F39" t="s">
-        <v>361</v>
+        <v>3</v>
+      </c>
+      <c r="F39">
+        <v>305</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>191</v>
+      </c>
+      <c r="B40" t="s">
+        <v>360</v>
+      </c>
+      <c r="C40" t="s">
+        <v>372</v>
+      </c>
+      <c r="D40" t="s">
         <v>362</v>
       </c>
-      <c r="B40" t="s">
-        <v>363</v>
-      </c>
-      <c r="C40" t="s">
-        <v>364</v>
-      </c>
-      <c r="D40" t="s">
-        <v>365</v>
-      </c>
       <c r="E40">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40">
-        <v>201</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>234</v>
+        <v>209</v>
       </c>
       <c r="B41" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="C41" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="D41" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="E41">
-        <v>2</v>
-      </c>
-      <c r="F41">
-        <v>203</v>
+        <v>1</v>
+      </c>
+      <c r="F41" t="s">
+        <v>373</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C42" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="D42" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E42">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F42">
-        <v>301</v>
+        <v>201</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B43" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C43" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="D43" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E43">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F43">
-        <v>303</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="B44" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C44" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="D44" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E44">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F44">
-        <v>401</v>
+        <v>301</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B45" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C45" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="D45" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E45">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F45">
-        <v>403</v>
+        <v>303</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>261</v>
+        <v>382</v>
+      </c>
+      <c r="B46" t="s">
+        <v>375</v>
       </c>
       <c r="C46" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="D46" t="s">
-        <v>373</v>
-      </c>
-      <c r="E46" t="s">
-        <v>315</v>
-      </c>
-      <c r="F46" t="s">
-        <v>373</v>
+        <v>377</v>
+      </c>
+      <c r="E46">
+        <v>4</v>
+      </c>
+      <c r="F46">
+        <v>401</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B47" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C47" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="D47" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E47">
         <v>4</v>
       </c>
-      <c r="F47" t="s">
-        <v>377</v>
+      <c r="F47">
+        <v>403</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="C48" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="D48" t="s">
-        <v>378</v>
-      </c>
-      <c r="E48">
-        <v>1</v>
+        <v>385</v>
+      </c>
+      <c r="E48" t="s">
+        <v>325</v>
       </c>
       <c r="F48" t="s">
-        <v>378</v>
+        <v>385</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>275</v>
+        <v>258</v>
+      </c>
+      <c r="B49" t="s">
+        <v>386</v>
       </c>
       <c r="C49" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="D49" t="s">
-        <v>379</v>
-      </c>
-      <c r="E49" t="s">
-        <v>315</v>
+        <v>388</v>
+      </c>
+      <c r="E49">
+        <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="C50" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="D50" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="C51" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="D51" t="s">
-        <v>384</v>
-      </c>
-      <c r="E51">
-        <v>6</v>
+        <v>391</v>
+      </c>
+      <c r="E51" t="s">
+        <v>325</v>
       </c>
       <c r="F51" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>270</v>
-      </c>
-      <c r="B52" t="s">
-        <v>363</v>
+        <v>295</v>
       </c>
       <c r="C52" t="s">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="D52" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>387</v>
-      </c>
-      <c r="B53" t="s">
-        <v>340</v>
+        <v>275</v>
       </c>
       <c r="C53" t="s">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="D53" t="s">
-        <v>342</v>
+        <v>396</v>
       </c>
       <c r="E53">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F53" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>241</v>
+        <v>280</v>
       </c>
       <c r="B54" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C54" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="D54" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E54">
-        <v>2</v>
-      </c>
-      <c r="F54">
-        <v>202</v>
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>226</v>
+        <v>150</v>
       </c>
       <c r="B55" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="C55" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="D55" t="s">
-        <v>365</v>
+        <v>354</v>
       </c>
       <c r="E55">
-        <v>4</v>
-      </c>
-      <c r="F55">
-        <v>402</v>
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>400</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="B56" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="C56" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="D56" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="E56">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F56">
-        <v>302</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>305</v>
+        <v>236</v>
+      </c>
+      <c r="B57" t="s">
+        <v>375</v>
       </c>
       <c r="C57" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D57" t="s">
-        <v>393</v>
-      </c>
-      <c r="E57" t="s">
+        <v>377</v>
+      </c>
+      <c r="E57">
+        <v>4</v>
+      </c>
+      <c r="F57">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>240</v>
+      </c>
+      <c r="B58" t="s">
+        <v>375</v>
+      </c>
+      <c r="C58" t="s">
+        <v>403</v>
+      </c>
+      <c r="D58" t="s">
+        <v>377</v>
+      </c>
+      <c r="E58">
+        <v>3</v>
+      </c>
+      <c r="F58">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>315</v>
       </c>
-      <c r="F57" t="s">
-        <v>393</v>
+      <c r="C59" t="s">
+        <v>404</v>
+      </c>
+      <c r="D59" t="s">
+        <v>404</v>
+      </c>
+      <c r="E59" t="s">
+        <v>325</v>
+      </c>
+      <c r="F59" t="s">
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -4721,7 +4862,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -4730,795 +4871,795 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B2" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E2" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="F2" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="G2" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B3" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E3" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="F3" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="G3" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B4" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E4" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="F4" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="G4" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B5" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E5" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="F5" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="G5" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B6" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E6" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="F6" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="G6" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B7" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E7" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="F7" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="G7" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B8" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E8" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="F8" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="G8" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B9" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E9" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="F9" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
       <c r="G9" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="B10" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E10" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="F10" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="G10" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B11" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E11" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="F11" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="G11" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B12" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E12" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="F12" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="G12" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B13" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="E13" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="F13" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="G13" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B14" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="E14" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="F14" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="G14" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B15" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E15" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="F15" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="G15" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B16" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E16" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="F16" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="G16" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B17" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E17" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="F17" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="G17" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B18" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E18" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="F18" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="G18" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B19" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="C19" t="s">
         <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E19" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="F19" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="G19" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="B20" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="C20" t="s">
         <v>144</v>
       </c>
       <c r="D20" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E20" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="F20" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="G20" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="B21" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="C21" t="s">
         <v>144</v>
       </c>
       <c r="D21" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E21" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="F21" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="G21" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B22" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="C22" t="s">
         <v>144</v>
       </c>
       <c r="D22" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E22" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="F22" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="G22" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="C23" t="s">
         <v>144</v>
       </c>
       <c r="D23" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E23" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="F23" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="G23" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B24" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="C24" t="s">
         <v>144</v>
       </c>
       <c r="D24" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E24" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="F24" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="G24" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="C25" t="s">
         <v>144</v>
       </c>
       <c r="D25" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E25" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="F25" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="G25" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B26" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
       <c r="C26" t="s">
         <v>144</v>
       </c>
       <c r="D26" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="E26" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="F26" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="G26" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="C27" t="s">
         <v>144</v>
       </c>
       <c r="D27" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E27" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="F27" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="G27" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="C28" t="s">
         <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E28" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="F28" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="G28" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B29" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="C29" t="s">
         <v>144</v>
       </c>
       <c r="D29" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E29" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="F29" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="G29" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B30" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="C30" t="s">
         <v>144</v>
       </c>
       <c r="D30" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="E30" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="F30" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="G30" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B31" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="C31" t="s">
         <v>144</v>
       </c>
       <c r="D31" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E31" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="F31" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="G31" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B32" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="C32" t="s">
         <v>144</v>
       </c>
       <c r="D32" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E32" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="F32" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="G32" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B33" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="C33" t="s">
         <v>144</v>
       </c>
       <c r="D33" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E33" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="F33" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="G33" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="C34" t="s">
         <v>144</v>
       </c>
       <c r="D34" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="E34" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="F34" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="G34" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B35" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="C35" t="s">
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="E35" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -3123,7 +3123,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="27.142857142857142" customWidth="1"/>
@@ -3434,82 +3434,82 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B14" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="C14" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="D14" t="s">
         <v>235</v>
       </c>
       <c r="E14" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="B15" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="C15" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="D15" t="s">
         <v>235</v>
       </c>
       <c r="E15" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="F15" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="B16" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="C16" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="D16" t="s">
         <v>235</v>
       </c>
       <c r="E16" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="B17" t="s">
         <v>293</v>
       </c>
       <c r="C17" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="D17" t="s">
         <v>235</v>
@@ -3526,13 +3526,13 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B18" t="s">
         <v>293</v>
       </c>
       <c r="C18" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D18" t="s">
         <v>235</v>
@@ -3544,18 +3544,18 @@
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B19" t="s">
         <v>293</v>
       </c>
       <c r="C19" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="D19" t="s">
         <v>235</v>
@@ -3564,21 +3564,21 @@
         <v>295</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="G19" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B20" t="s">
         <v>293</v>
       </c>
       <c r="C20" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D20" t="s">
         <v>235</v>
@@ -3590,29 +3590,6 @@
         <v>144</v>
       </c>
       <c r="G20" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>304</v>
-      </c>
-      <c r="B21" t="s">
-        <v>293</v>
-      </c>
-      <c r="C21" t="s">
-        <v>305</v>
-      </c>
-      <c r="D21" t="s">
-        <v>235</v>
-      </c>
-      <c r="E21" t="s">
-        <v>295</v>
-      </c>
-      <c r="F21" t="s">
-        <v>144</v>
-      </c>
-      <c r="G21" t="s">
         <v>296</v>
       </c>
     </row>
@@ -3722,8 +3699,10 @@
       <c r="C4" t="s">
         <v>279</v>
       </c>
-      <c r="D4" t="s">
-        <v>235</v>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>その他</t>
+        </is>
       </c>
       <c r="E4" t="s">
         <v>280</v>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="992" uniqueCount="516">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="517">
   <si>
     <t>id</t>
   </si>
@@ -321,8 +321,7 @@
     <t xml:space="preserve">焼き鳥（塩orタレ）
 1本 200円
 3本 500円
-5本 700円
-缶ビール 1本 400円</t>
+5本 700円</t>
   </si>
   <si>
     <t>子どもから大人までだいすき お得にたくさん食べられる5本セットがおすすめ おいしい焼き鳥食べに来てね</t>
@@ -871,21 +870,6 @@
   </si>
   <si>
     <t>こんにちは！ ストリートダンス部BEP-HOPです！ 最っ高なステージをお届けできるように部員一同全力で頑張るのでみなさん瞬き厳禁でお楽しみください！！</t>
-  </si>
-  <si>
-    <t>music-gakusei-mentor</t>
-  </si>
-  <si>
-    <t>縁日企画</t>
-  </si>
-  <si>
-    <t>学生メンター</t>
-  </si>
-  <si>
-    <t>loc-student-support</t>
-  </si>
-  <si>
-    <t>縁日開催！射的、千本くじ、ボール転がしなど！子供から大人までみなさんお待ちしております！</t>
   </si>
   <si>
     <t>music-aiki-do</t>
@@ -1021,6 +1005,21 @@
 10/31 (土)14:00キックオフ、ぜひご観戦ください！</t>
   </si>
   <si>
+    <t>music-gakusei-mentor</t>
+  </si>
+  <si>
+    <t>縁日企画</t>
+  </si>
+  <si>
+    <t>学生メンター</t>
+  </si>
+  <si>
+    <t>loc-student-support</t>
+  </si>
+  <si>
+    <t>縁日開催！射的、千本くじ、ボール転がしなど！子供から大人までみなさんお待ちしております！</t>
+  </si>
+  <si>
     <t>buildingId</t>
   </si>
   <si>
@@ -1109,6 +1108,9 @@
   </si>
   <si>
     <t>企業テントNo.1</t>
+  </si>
+  <si>
+    <t>企業テントNo.2</t>
   </si>
   <si>
     <t>loc-sado-room</t>
@@ -3434,163 +3436,163 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B14" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="C14" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D14" t="s">
         <v>235</v>
       </c>
       <c r="E14" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F14" t="s">
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B15" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="C15" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D15" t="s">
         <v>235</v>
       </c>
       <c r="E15" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B16" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C16" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="D16" t="s">
         <v>235</v>
       </c>
       <c r="E16" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F16" t="s">
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B17" t="s">
+        <v>288</v>
+      </c>
+      <c r="C17" t="s">
         <v>293</v>
-      </c>
-      <c r="C17" t="s">
-        <v>298</v>
       </c>
       <c r="D17" t="s">
         <v>235</v>
       </c>
       <c r="E17" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B18" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C18" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="D18" t="s">
         <v>235</v>
       </c>
       <c r="E18" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B19" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C19" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D19" t="s">
         <v>235</v>
       </c>
       <c r="E19" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F19" t="s">
         <v>144</v>
       </c>
       <c r="G19" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B20" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="C20" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="D20" t="s">
         <v>235</v>
       </c>
       <c r="E20" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="F20" t="s">
         <v>144</v>
       </c>
       <c r="G20" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>
@@ -3642,16 +3644,16 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="C2" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="D2" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="E2" t="s">
         <v>258</v>
@@ -3660,58 +3662,56 @@
         <v>144</v>
       </c>
       <c r="G2" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="H2" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
     </row>
     <row r="3" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="D3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="E3" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>277</v>
+        <v>313</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>314</v>
       </c>
       <c r="C4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>その他</t>
-        </is>
+        <v>315</v>
+      </c>
+      <c r="D4" t="s">
+        <v>309</v>
       </c>
       <c r="E4" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>281</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>
@@ -4148,10 +4148,8 @@
       <c r="A25" t="s">
         <v>156</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>企業テントNo.2</t>
-        </is>
+      <c r="C25" t="s">
+        <v>348</v>
       </c>
       <c r="D25" t="s">
         <v>324</v>
@@ -4165,19 +4163,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C26" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="D26" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4185,13 +4183,13 @@
         <v>231</v>
       </c>
       <c r="B27" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C27" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D27" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E27">
         <v>2</v>
@@ -4205,13 +4203,13 @@
         <v>172</v>
       </c>
       <c r="B28" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C28" t="s">
+        <v>356</v>
+      </c>
+      <c r="D28" t="s">
         <v>355</v>
-      </c>
-      <c r="D28" t="s">
-        <v>354</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -4225,13 +4223,13 @@
         <v>177</v>
       </c>
       <c r="B29" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C29" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D29" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -4245,13 +4243,13 @@
         <v>217</v>
       </c>
       <c r="B30" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C30" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D30" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E30">
         <v>1</v>
@@ -4265,13 +4263,13 @@
         <v>201</v>
       </c>
       <c r="B31" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C31" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D31" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -4285,13 +4283,13 @@
         <v>186</v>
       </c>
       <c r="B32" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C32" t="s">
+        <v>364</v>
+      </c>
+      <c r="D32" t="s">
         <v>363</v>
-      </c>
-      <c r="D32" t="s">
-        <v>362</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -4305,19 +4303,19 @@
         <v>213</v>
       </c>
       <c r="B33" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C33" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D33" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -4325,13 +4323,13 @@
         <v>205</v>
       </c>
       <c r="B34" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C34" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D34" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E34">
         <v>2</v>
@@ -4345,13 +4343,13 @@
         <v>196</v>
       </c>
       <c r="B35" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C35" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D35" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E35">
         <v>2</v>
@@ -4365,13 +4363,13 @@
         <v>167</v>
       </c>
       <c r="B36" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C36" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D36" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -4385,13 +4383,13 @@
         <v>222</v>
       </c>
       <c r="B37" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C37" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D37" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E37">
         <v>2</v>
@@ -4405,13 +4403,13 @@
         <v>182</v>
       </c>
       <c r="B38" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C38" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D38" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -4425,13 +4423,13 @@
         <v>226</v>
       </c>
       <c r="B39" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C39" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D39" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E39">
         <v>3</v>
@@ -4445,13 +4443,13 @@
         <v>191</v>
       </c>
       <c r="B40" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C40" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D40" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E40">
         <v>3</v>
@@ -4465,33 +4463,33 @@
         <v>209</v>
       </c>
       <c r="B41" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C41" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D41" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E41">
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B42" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C42" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D42" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E42">
         <v>2</v>
@@ -4505,13 +4503,13 @@
         <v>244</v>
       </c>
       <c r="B43" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C43" t="s">
+        <v>379</v>
+      </c>
+      <c r="D43" t="s">
         <v>378</v>
-      </c>
-      <c r="D43" t="s">
-        <v>377</v>
       </c>
       <c r="E43">
         <v>2</v>
@@ -4522,16 +4520,16 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B44" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C44" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D44" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E44">
         <v>3</v>
@@ -4545,13 +4543,13 @@
         <v>248</v>
       </c>
       <c r="B45" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C45" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D45" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E45">
         <v>3</v>
@@ -4562,16 +4560,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B46" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C46" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="D46" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E46">
         <v>4</v>
@@ -4585,13 +4583,13 @@
         <v>255</v>
       </c>
       <c r="B47" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C47" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D47" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E47">
         <v>4</v>
@@ -4605,16 +4603,16 @@
         <v>271</v>
       </c>
       <c r="C48" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D48" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E48" t="s">
         <v>325</v>
       </c>
       <c r="F48" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -4622,70 +4620,70 @@
         <v>258</v>
       </c>
       <c r="B49" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C49" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D49" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E49">
         <v>4</v>
       </c>
       <c r="F49" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="C50" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D50" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E50">
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C51" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="D51" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E51" t="s">
         <v>325</v>
       </c>
       <c r="F51" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C52" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D52" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4693,36 +4691,36 @@
         <v>275</v>
       </c>
       <c r="C53" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D53" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E53">
         <v>6</v>
       </c>
       <c r="F53" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>280</v>
+        <v>316</v>
       </c>
       <c r="B54" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C54" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="D54" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4730,19 +4728,19 @@
         <v>150</v>
       </c>
       <c r="B55" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C55" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D55" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E55">
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4750,13 +4748,13 @@
         <v>251</v>
       </c>
       <c r="B56" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C56" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D56" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E56">
         <v>2</v>
@@ -4770,13 +4768,13 @@
         <v>236</v>
       </c>
       <c r="B57" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C57" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D57" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E57">
         <v>4</v>
@@ -4790,13 +4788,13 @@
         <v>240</v>
       </c>
       <c r="B58" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C58" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="D58" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E58">
         <v>3</v>
@@ -4807,19 +4805,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="C59" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D59" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E59" t="s">
         <v>325</v>
       </c>
       <c r="F59" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
   </sheetData>
@@ -4841,7 +4839,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -4850,13 +4848,13 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -4864,7 +4862,7 @@
         <v>253</v>
       </c>
       <c r="B2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -4873,13 +4871,13 @@
         <v>271</v>
       </c>
       <c r="E2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="F2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -4887,7 +4885,7 @@
         <v>233</v>
       </c>
       <c r="B3" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -4896,13 +4894,13 @@
         <v>271</v>
       </c>
       <c r="E3" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F3" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="G3" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -4910,7 +4908,7 @@
         <v>238</v>
       </c>
       <c r="B4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -4919,13 +4917,13 @@
         <v>271</v>
       </c>
       <c r="E4" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -4933,7 +4931,7 @@
         <v>246</v>
       </c>
       <c r="B5" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -4942,13 +4940,13 @@
         <v>271</v>
       </c>
       <c r="E5" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F5" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G5" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -4956,7 +4954,7 @@
         <v>249</v>
       </c>
       <c r="B6" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -4965,13 +4963,13 @@
         <v>271</v>
       </c>
       <c r="E6" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F6" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="G6" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -4979,7 +4977,7 @@
         <v>242</v>
       </c>
       <c r="B7" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
@@ -4988,13 +4986,13 @@
         <v>271</v>
       </c>
       <c r="E7" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F7" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G7" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5002,7 +5000,7 @@
         <v>269</v>
       </c>
       <c r="B8" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
@@ -5011,13 +5009,13 @@
         <v>271</v>
       </c>
       <c r="E8" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="F8" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="G8" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5025,7 +5023,7 @@
         <v>257</v>
       </c>
       <c r="B9" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -5034,13 +5032,13 @@
         <v>258</v>
       </c>
       <c r="E9" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="F9" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="G9" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5048,7 +5046,7 @@
         <v>260</v>
       </c>
       <c r="B10" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -5057,13 +5055,13 @@
         <v>258</v>
       </c>
       <c r="E10" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G10" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5071,7 +5069,7 @@
         <v>263</v>
       </c>
       <c r="B11" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -5080,13 +5078,13 @@
         <v>258</v>
       </c>
       <c r="E11" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="F11" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G11" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5094,7 +5092,7 @@
         <v>266</v>
       </c>
       <c r="B12" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -5103,151 +5101,151 @@
         <v>258</v>
       </c>
       <c r="E12" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="F12" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="G12" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B13" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E13" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F13" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G13" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B14" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E14" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F14" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G14" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B15" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E15" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F15" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G15" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="B16" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E16" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F16" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G16" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B17" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E17" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="F17" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="G17" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="B18" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E18" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F18" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G18" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5255,7 +5253,7 @@
         <v>253</v>
       </c>
       <c r="B19" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C19" t="s">
         <v>144</v>
@@ -5264,13 +5262,13 @@
         <v>271</v>
       </c>
       <c r="E19" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F19" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G19" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5278,7 +5276,7 @@
         <v>233</v>
       </c>
       <c r="B20" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C20" t="s">
         <v>144</v>
@@ -5287,13 +5285,13 @@
         <v>271</v>
       </c>
       <c r="E20" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F20" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="G20" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5301,7 +5299,7 @@
         <v>238</v>
       </c>
       <c r="B21" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C21" t="s">
         <v>144</v>
@@ -5310,13 +5308,13 @@
         <v>271</v>
       </c>
       <c r="E21" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="F21" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G21" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -5324,7 +5322,7 @@
         <v>246</v>
       </c>
       <c r="B22" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C22" t="s">
         <v>144</v>
@@ -5333,13 +5331,13 @@
         <v>271</v>
       </c>
       <c r="E22" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F22" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G22" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -5347,7 +5345,7 @@
         <v>249</v>
       </c>
       <c r="B23" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C23" t="s">
         <v>144</v>
@@ -5356,13 +5354,13 @@
         <v>271</v>
       </c>
       <c r="E23" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F23" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="G23" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -5370,7 +5368,7 @@
         <v>242</v>
       </c>
       <c r="B24" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C24" t="s">
         <v>144</v>
@@ -5379,13 +5377,13 @@
         <v>271</v>
       </c>
       <c r="E24" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F24" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G24" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -5393,7 +5391,7 @@
         <v>269</v>
       </c>
       <c r="B25" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C25" t="s">
         <v>144</v>
@@ -5402,13 +5400,13 @@
         <v>271</v>
       </c>
       <c r="E25" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F25" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="G25" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -5416,7 +5414,7 @@
         <v>273</v>
       </c>
       <c r="B26" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="C26" t="s">
         <v>144</v>
@@ -5425,13 +5423,13 @@
         <v>271</v>
       </c>
       <c r="E26" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="F26" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="G26" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -5439,7 +5437,7 @@
         <v>257</v>
       </c>
       <c r="B27" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C27" t="s">
         <v>144</v>
@@ -5448,13 +5446,13 @@
         <v>258</v>
       </c>
       <c r="E27" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F27" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="G27" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -5462,7 +5460,7 @@
         <v>266</v>
       </c>
       <c r="B28" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C28" t="s">
         <v>144</v>
@@ -5471,21 +5469,21 @@
         <v>258</v>
       </c>
       <c r="E28" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="F28" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G28" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C29" t="s">
         <v>144</v>
@@ -5494,151 +5492,151 @@
         <v>258</v>
       </c>
       <c r="E29" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F29" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G29" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B30" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C30" t="s">
         <v>144</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="E30" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="F30" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G30" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B31" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="C31" t="s">
         <v>144</v>
       </c>
       <c r="D31" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E31" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F31" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G31" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="B32" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C32" t="s">
         <v>144</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E32" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="F32" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="G32" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B33" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C33" t="s">
         <v>144</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E33" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="F33" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G33" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="B34" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C34" t="s">
         <v>144</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E34" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="F34" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="G34" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B35" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="C35" t="s">
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="E35" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
   </sheetData>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="534">
   <si>
     <t>id</t>
   </si>
@@ -526,6 +526,26 @@
   <si>
     <t xml:space="preserve">大人気ポインコも登場！
 毎年人気の握力王決定戦もたくさんノベルティを用意してお待ちしています。</t>
+  </si>
+  <si>
+    <t>expo-cafe</t>
+  </si>
+  <si>
+    <t>「もちっとぐりーんフレンズカフェ」 ～観葉植物を推すカフェ～</t>
+  </si>
+  <si>
+    <t>関東学院大学EXPO部</t>
+  </si>
+  <si>
+    <t>模擬店,EXPO部</t>
+  </si>
+  <si>
+    <t xml:space="preserve">コーヒー・紅茶：200円
+カフェラテ・カプチーノ：250円
+オリジナルキャラクターカラフルフロート：350円</t>
+  </si>
+  <si>
+    <t>犬カフェ、猫カフェ…色々なアニマルカフェに 次ぐ、新感覚！“観葉植物”を推すカフェを関東 学院大学EXPO部“初”？で開催します。 それぞれの観葉植物に会える？のはもちろんの こと、特徴にちなんだキャラクターも考案！ カフェをきっかけに、みなさんも植物推し活を 始めましょう！</t>
   </si>
   <si>
     <t>culture-wandervogel-bu</t>
@@ -1018,6 +1038,39 @@
   </si>
   <si>
     <t>縁日開催！射的、千本くじ、ボール転がしなど！子供から大人までみなさんお待ちしております！</t>
+  </si>
+  <si>
+    <t>expo-walk-rally</t>
+  </si>
+  <si>
+    <t>ウォークラリー</t>
+  </si>
+  <si>
+    <t>EXPO部</t>
+  </si>
+  <si>
+    <t>loc-3-1</t>
+  </si>
+  <si>
+    <t>人間共生学部共生デザイン学科の定國ゼミが、ウォークラリーを 企画！地球のこれからはみんなで考えていくもの、そんな環境に 関することを楽しくゲームで体験しながら、学んでいきましょう！ ラリー達成者にはグッズプレゼント！ぜひ気軽にご参加ください。</t>
+  </si>
+  <si>
+    <t>expo-tekken</t>
+  </si>
+  <si>
+    <t>横浜グリーンエクスポと交通</t>
+  </si>
+  <si>
+    <t>loc-3-203</t>
+  </si>
+  <si>
+    <t>い よい よ2027年3月から はじまる 横 浜 グリーン エ クス ポ！！ とはいうものの、会場までどうやっていけばいいの…横浜市在住 の方でも実は疑問に思っていませんか？そんな疑問に鉄道研究部 ならではの視点でお答えします！また、過去に開催されたEXPO についても、交通という切り口での展示も行います！</t>
+  </si>
+  <si>
+    <t>expo-photo-spot</t>
+  </si>
+  <si>
+    <t>関東学院大学 EXPO部 × 平潟祭実行委員会制作！ フォトスポット</t>
   </si>
   <si>
     <t>buildingId</t>
@@ -2022,7 +2075,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="23.571428571428573" customWidth="1"/>
@@ -2729,6 +2782,32 @@
       </c>
       <c r="H27" t="s">
         <v>162</v>
+      </c>
+    </row>
+    <row r="28" ht="54" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>163</v>
+      </c>
+      <c r="B28" t="s">
+        <v>164</v>
+      </c>
+      <c r="C28" t="s">
+        <v>165</v>
+      </c>
+      <c r="D28" t="s">
+        <v>166</v>
+      </c>
+      <c r="E28" t="s">
+        <v>150</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28" t="s">
+        <v>167</v>
+      </c>
+      <c r="H28" t="s">
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -2777,180 +2856,180 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="D2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="C3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E3" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="B4" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="C4" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="D4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="B5" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C5" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="D5" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E5" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B6" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C6" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D6" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E6" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B7" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="C7" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="D7" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E7" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B8" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="C8" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D8" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E8" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B9" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="C9" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="D9" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E9" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F9" t="s">
         <v>13</v>
@@ -2958,163 +3037,163 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="C10" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D10" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E10" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F10" t="s">
         <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B11" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="C11" t="s">
         <v>25</v>
       </c>
       <c r="D11" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E11" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B12" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C12" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="D12" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B13" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C13" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="D13" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E13" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F13" t="s">
         <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B14" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="C14" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="D14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E14" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B15" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="C15" t="s">
         <v>31</v>
       </c>
       <c r="D15" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E15" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B16" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="C16" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="D16" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="E16" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3163,88 +3242,88 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C2" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D2" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E2" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="F2" t="s">
         <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B3" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="C3" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="D3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E3" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F3" t="s">
         <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B4" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="C4" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D4" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="C5" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E5" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
@@ -3252,53 +3331,53 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="C6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D6" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E6" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B7" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="C7" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E7" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B8" t="s">
         <v>95</v>
@@ -3307,292 +3386,292 @@
         <v>95</v>
       </c>
       <c r="D8" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E8" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B9" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="C9" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F9" t="s">
         <v>20</v>
       </c>
       <c r="G9" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B10" t="s">
+        <v>270</v>
+      </c>
+      <c r="C10" t="s">
+        <v>270</v>
+      </c>
+      <c r="D10" t="s">
+        <v>241</v>
+      </c>
+      <c r="E10" t="s">
         <v>264</v>
-      </c>
-      <c r="C10" t="s">
-        <v>264</v>
-      </c>
-      <c r="D10" t="s">
-        <v>235</v>
-      </c>
-      <c r="E10" t="s">
-        <v>258</v>
       </c>
       <c r="F10" t="s">
         <v>20</v>
       </c>
       <c r="G10" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B11" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="C11" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="D11" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F11" t="s">
         <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B12" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="C12" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D12" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E12" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F12" t="s">
         <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B13" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="C13" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D13" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E13" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="F13" t="s">
         <v>144</v>
       </c>
       <c r="G13" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B14" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="C14" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="D14" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E14" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="F14" t="s">
         <v>20</v>
       </c>
       <c r="G14" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B15" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="C15" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="D15" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E15" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B16" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C16" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="D16" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E16" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F16" t="s">
         <v>20</v>
       </c>
       <c r="G16" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B17" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C17" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D17" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E17" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F17" t="s">
         <v>20</v>
       </c>
       <c r="G17" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>300</v>
+      </c>
+      <c r="B18" t="s">
         <v>294</v>
       </c>
-      <c r="B18" t="s">
-        <v>288</v>
-      </c>
       <c r="C18" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D18" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E18" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F18" t="s">
         <v>20</v>
       </c>
       <c r="G18" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B19" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C19" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="D19" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E19" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F19" t="s">
         <v>144</v>
       </c>
       <c r="G19" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B20" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="C20" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D20" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E20" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F20" t="s">
         <v>144</v>
       </c>
       <c r="G20" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
   </sheetData>
@@ -3603,7 +3682,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
@@ -3644,74 +3723,146 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B2" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="C2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="D2" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="E2" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F2" t="s">
         <v>144</v>
       </c>
       <c r="G2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="H2" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="3" ht="26.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B3" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="D3" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="E3" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="F3" t="s">
         <v>20</v>
       </c>
       <c r="G3" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B4" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="C4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" t="s">
         <v>315</v>
       </c>
-      <c r="D4" t="s">
-        <v>309</v>
-      </c>
       <c r="E4" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="F4" t="s">
         <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>317</v>
+        <v>323</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>324</v>
+      </c>
+      <c r="B5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>定國ゼミ</t>
+        </is>
+      </c>
+      <c r="D5" t="s">
+        <v>326</v>
+      </c>
+      <c r="E5" t="s">
+        <v>327</v>
+      </c>
+      <c r="F5" t="s">
+        <v>13</v>
+      </c>
+      <c r="H5" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>329</v>
+      </c>
+      <c r="B6" t="s">
+        <v>330</v>
+      </c>
+      <c r="C6" t="s">
+        <v>227</v>
+      </c>
+      <c r="D6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E6" t="s">
+        <v>331</v>
+      </c>
+      <c r="F6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B7" t="s">
+        <v>334</v>
+      </c>
+      <c r="C7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D7" t="s">
+        <v>326</v>
+      </c>
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -3722,7 +3873,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19.285714285714285" customWidth="1"/>
@@ -3738,19 +3889,19 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -3758,13 +3909,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="D2" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E2" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -3775,13 +3926,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="D3" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E3" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -3792,13 +3943,13 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="D4" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E4" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -3809,13 +3960,13 @@
         <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="D5" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E5" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -3826,13 +3977,13 @@
         <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="D6" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E6" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -3843,13 +3994,13 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="D7" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E7" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -3860,13 +4011,13 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="D8" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E8" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -3877,13 +4028,13 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="D9" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E9" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -3894,13 +4045,13 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="D10" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E10" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -3911,13 +4062,13 @@
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="D11" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E11" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -3928,13 +4079,13 @@
         <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="D12" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E12" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -3945,13 +4096,13 @@
         <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="D13" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E13" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -3962,13 +4113,13 @@
         <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="D14" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E14" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -3979,13 +4130,13 @@
         <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="D15" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E15" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -3996,13 +4147,13 @@
         <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="D16" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E16" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -4013,13 +4164,13 @@
         <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="D17" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E17" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -4030,13 +4181,13 @@
         <v>108</v>
       </c>
       <c r="C18" t="s">
+        <v>358</v>
+      </c>
+      <c r="D18" t="s">
         <v>341</v>
       </c>
-      <c r="D18" t="s">
-        <v>324</v>
-      </c>
       <c r="E18" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -4047,13 +4198,13 @@
         <v>114</v>
       </c>
       <c r="C19" t="s">
+        <v>359</v>
+      </c>
+      <c r="D19" t="s">
+        <v>341</v>
+      </c>
+      <c r="E19" t="s">
         <v>342</v>
-      </c>
-      <c r="D19" t="s">
-        <v>324</v>
-      </c>
-      <c r="E19" t="s">
-        <v>325</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -4064,13 +4215,13 @@
         <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="D20" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E20" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -4081,13 +4232,13 @@
         <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="D21" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E21" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -4098,13 +4249,13 @@
         <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="D22" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E22" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -4115,13 +4266,13 @@
         <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="D23" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E23" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -4132,13 +4283,13 @@
         <v>161</v>
       </c>
       <c r="C24" t="s">
-        <v>347</v>
+        <v>364</v>
       </c>
       <c r="D24" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E24" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -4149,13 +4300,13 @@
         <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="D25" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="E25" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -4163,661 +4314,725 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="C26" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="D26" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>231</v>
-      </c>
-      <c r="B27" t="s">
-        <v>353</v>
-      </c>
-      <c r="C27" t="s">
-        <v>354</v>
-      </c>
-      <c r="D27" t="s">
-        <v>355</v>
-      </c>
-      <c r="E27">
-        <v>2</v>
-      </c>
-      <c r="F27">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>172</v>
-      </c>
-      <c r="B28" t="s">
-        <v>353</v>
-      </c>
-      <c r="C28" t="s">
-        <v>356</v>
-      </c>
-      <c r="D28" t="s">
-        <v>355</v>
-      </c>
-      <c r="E28">
-        <v>2</v>
-      </c>
-      <c r="F28">
-        <v>205</v>
+        <v>369</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>loc-3-1</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>no3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3号館1階</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3号館</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>1階</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>loc-3-203</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>no3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3-203</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3号館</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>203</t>
+        </is>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>177</v>
+        <v>237</v>
       </c>
       <c r="B29" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="C29" t="s">
-        <v>357</v>
+        <v>371</v>
       </c>
       <c r="D29" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="E29">
         <v>2</v>
       </c>
       <c r="F29">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="B30" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
       <c r="C30" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="D30" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="E30">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30">
-        <v>101</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>201</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="C31" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="D31" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="E31">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F31">
-        <v>101</v>
+        <v>206</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>186</v>
+        <v>223</v>
       </c>
       <c r="B32" t="s">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="C32" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="D32" t="s">
-        <v>363</v>
+        <v>377</v>
       </c>
       <c r="E32">
         <v>1</v>
       </c>
       <c r="F32">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C33" t="s">
-        <v>365</v>
+        <v>379</v>
       </c>
       <c r="D33" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E33">
         <v>1</v>
       </c>
-      <c r="F33" t="s">
-        <v>366</v>
+      <c r="F33">
+        <v>101</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C34" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="D34" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F34">
-        <v>201</v>
+        <v>102</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>219</v>
       </c>
       <c r="B35" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C35" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="D35" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E35">
-        <v>2</v>
-      </c>
-      <c r="F35">
-        <v>203</v>
+        <v>1</v>
+      </c>
+      <c r="F35" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>167</v>
+        <v>211</v>
       </c>
       <c r="B36" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C36" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="D36" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E36">
         <v>2</v>
       </c>
       <c r="F36">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>222</v>
+        <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C37" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
       <c r="D37" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E37">
         <v>2</v>
       </c>
       <c r="F37">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C38" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="D38" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E38">
         <v>2</v>
       </c>
       <c r="F38">
-        <v>206</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B39" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C39" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="D39" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E39">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F39">
-        <v>305</v>
+        <v>205</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B40" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="C40" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="D40" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="E40">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F40">
-        <v>306</v>
+        <v>206</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="B41" t="s">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="C41" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="D41" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="E41">
-        <v>1</v>
-      </c>
-      <c r="F41" t="s">
-        <v>374</v>
+        <v>3</v>
+      </c>
+      <c r="F41">
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>375</v>
+        <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C42" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="D42" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E42">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F42">
-        <v>201</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="B43" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C43" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="D43" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E43">
-        <v>2</v>
-      </c>
-      <c r="F43">
-        <v>203</v>
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B44" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="C44" t="s">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="D44" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="E44">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44">
-        <v>301</v>
+        <v>201</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B45" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="C45" t="s">
-        <v>382</v>
+        <v>396</v>
       </c>
       <c r="D45" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="E45">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F45">
-        <v>303</v>
+        <v>203</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>383</v>
+        <v>397</v>
       </c>
       <c r="B46" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="C46" t="s">
-        <v>384</v>
+        <v>398</v>
       </c>
       <c r="D46" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="E46">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F46">
-        <v>401</v>
+        <v>301</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B47" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="C47" t="s">
-        <v>385</v>
+        <v>399</v>
       </c>
       <c r="D47" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="E47">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47">
-        <v>403</v>
+        <v>303</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>271</v>
+        <v>400</v>
+      </c>
+      <c r="B48" t="s">
+        <v>393</v>
       </c>
       <c r="C48" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
       <c r="D48" t="s">
-        <v>386</v>
-      </c>
-      <c r="E48" t="s">
-        <v>325</v>
-      </c>
-      <c r="F48" t="s">
-        <v>386</v>
+        <v>395</v>
+      </c>
+      <c r="E48">
+        <v>4</v>
+      </c>
+      <c r="F48">
+        <v>401</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B49" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C49" t="s">
-        <v>388</v>
+        <v>402</v>
       </c>
       <c r="D49" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="E49">
         <v>4</v>
       </c>
-      <c r="F49" t="s">
-        <v>390</v>
+      <c r="F49">
+        <v>403</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
       <c r="C50" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="D50" t="s">
-        <v>391</v>
-      </c>
-      <c r="E50">
-        <v>1</v>
+        <v>403</v>
+      </c>
+      <c r="E50" t="s">
+        <v>342</v>
       </c>
       <c r="F50" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>280</v>
+        <v>264</v>
+      </c>
+      <c r="B51" t="s">
+        <v>404</v>
       </c>
       <c r="C51" t="s">
-        <v>392</v>
+        <v>405</v>
       </c>
       <c r="D51" t="s">
-        <v>392</v>
-      </c>
-      <c r="E51" t="s">
-        <v>325</v>
+        <v>406</v>
+      </c>
+      <c r="E51">
+        <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>393</v>
+        <v>407</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C52" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="D52" t="s">
-        <v>394</v>
+        <v>408</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>395</v>
+        <v>408</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
       <c r="C53" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="D53" t="s">
-        <v>397</v>
-      </c>
-      <c r="E53">
-        <v>6</v>
+        <v>409</v>
+      </c>
+      <c r="E53" t="s">
+        <v>342</v>
       </c>
       <c r="F53" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>316</v>
-      </c>
-      <c r="B54" t="s">
-        <v>376</v>
+        <v>296</v>
       </c>
       <c r="C54" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="D54" t="s">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>399</v>
+        <v>412</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>150</v>
-      </c>
-      <c r="B55" t="s">
-        <v>353</v>
+        <v>281</v>
       </c>
       <c r="C55" t="s">
-        <v>400</v>
+        <v>413</v>
       </c>
       <c r="D55" t="s">
-        <v>355</v>
+        <v>414</v>
       </c>
       <c r="E55">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F55" t="s">
-        <v>401</v>
+        <v>415</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>251</v>
+        <v>322</v>
       </c>
       <c r="B56" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="C56" t="s">
-        <v>402</v>
+        <v>416</v>
       </c>
       <c r="D56" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="E56">
-        <v>2</v>
-      </c>
-      <c r="F56">
-        <v>202</v>
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>236</v>
+        <v>150</v>
       </c>
       <c r="B57" t="s">
-        <v>376</v>
+        <v>370</v>
       </c>
       <c r="C57" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="D57" t="s">
-        <v>378</v>
+        <v>372</v>
       </c>
       <c r="E57">
-        <v>4</v>
-      </c>
-      <c r="F57">
-        <v>402</v>
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="B58" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="C58" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="D58" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="E58">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F58">
-        <v>302</v>
+        <v>202</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>310</v>
+        <v>242</v>
+      </c>
+      <c r="B59" t="s">
+        <v>393</v>
       </c>
       <c r="C59" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="D59" t="s">
-        <v>405</v>
-      </c>
-      <c r="E59" t="s">
-        <v>325</v>
-      </c>
-      <c r="F59" t="s">
-        <v>405</v>
+        <v>395</v>
+      </c>
+      <c r="E59">
+        <v>4</v>
+      </c>
+      <c r="F59">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>246</v>
+      </c>
+      <c r="B60" t="s">
+        <v>393</v>
+      </c>
+      <c r="C60" t="s">
+        <v>421</v>
+      </c>
+      <c r="D60" t="s">
+        <v>395</v>
+      </c>
+      <c r="E60">
+        <v>3</v>
+      </c>
+      <c r="F60">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>316</v>
+      </c>
+      <c r="C61" t="s">
+        <v>422</v>
+      </c>
+      <c r="D61" t="s">
+        <v>422</v>
+      </c>
+      <c r="E61" t="s">
+        <v>342</v>
+      </c>
+      <c r="F61" t="s">
+        <v>422</v>
       </c>
     </row>
   </sheetData>
@@ -4839,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>406</v>
+        <v>423</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -4848,795 +5063,795 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>407</v>
+        <v>424</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>408</v>
+        <v>425</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>409</v>
+        <v>426</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B2" t="s">
-        <v>410</v>
+        <v>427</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
       </c>
       <c r="D2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E2" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="F2" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="G2" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B3" t="s">
-        <v>414</v>
+        <v>431</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
       </c>
       <c r="D3" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E3" t="s">
-        <v>415</v>
+        <v>432</v>
       </c>
       <c r="F3" t="s">
-        <v>416</v>
+        <v>433</v>
       </c>
       <c r="G3" t="s">
-        <v>417</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B4" t="s">
-        <v>418</v>
+        <v>435</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E4" t="s">
-        <v>419</v>
+        <v>436</v>
       </c>
       <c r="F4" t="s">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="G4" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>422</v>
+        <v>439</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
       </c>
       <c r="D5" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E5" t="s">
-        <v>423</v>
+        <v>440</v>
       </c>
       <c r="F5" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
       <c r="G5" t="s">
-        <v>425</v>
+        <v>442</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B6" t="s">
-        <v>426</v>
+        <v>443</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
       </c>
       <c r="D6" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E6" t="s">
-        <v>427</v>
+        <v>444</v>
       </c>
       <c r="F6" t="s">
-        <v>428</v>
+        <v>445</v>
       </c>
       <c r="G6" t="s">
-        <v>429</v>
+        <v>446</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B7" t="s">
-        <v>430</v>
+        <v>447</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E7" t="s">
-        <v>431</v>
+        <v>448</v>
       </c>
       <c r="F7" t="s">
-        <v>432</v>
+        <v>449</v>
       </c>
       <c r="G7" t="s">
-        <v>433</v>
+        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B8" t="s">
-        <v>434</v>
+        <v>451</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E8" t="s">
-        <v>435</v>
+        <v>452</v>
       </c>
       <c r="F8" t="s">
-        <v>436</v>
+        <v>453</v>
       </c>
       <c r="G8" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B9" t="s">
-        <v>438</v>
+        <v>455</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
       </c>
       <c r="D9" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E9" t="s">
-        <v>439</v>
+        <v>456</v>
       </c>
       <c r="F9" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="G9" t="s">
-        <v>441</v>
+        <v>458</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B10" t="s">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
       </c>
       <c r="D10" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E10" t="s">
-        <v>443</v>
+        <v>460</v>
       </c>
       <c r="F10" t="s">
-        <v>444</v>
+        <v>461</v>
       </c>
       <c r="G10" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B11" t="s">
-        <v>446</v>
+        <v>463</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
       </c>
       <c r="D11" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E11" t="s">
-        <v>447</v>
+        <v>464</v>
       </c>
       <c r="F11" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="G11" t="s">
-        <v>448</v>
+        <v>465</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B12" t="s">
-        <v>449</v>
+        <v>466</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E12" t="s">
-        <v>450</v>
+        <v>467</v>
       </c>
       <c r="F12" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
       <c r="G12" t="s">
-        <v>452</v>
+        <v>469</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B13" t="s">
-        <v>453</v>
+        <v>470</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E13" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="F13" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="G13" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B14" t="s">
-        <v>456</v>
+        <v>473</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
       </c>
       <c r="D14" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E14" t="s">
-        <v>457</v>
+        <v>474</v>
       </c>
       <c r="F14" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="G14" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B15" t="s">
-        <v>459</v>
+        <v>476</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E15" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="F15" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="G15" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B16" t="s">
-        <v>463</v>
+        <v>480</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
       </c>
       <c r="D16" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E16" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="F16" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="G16" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B17" t="s">
-        <v>466</v>
+        <v>483</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
       </c>
       <c r="D17" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E17" t="s">
-        <v>467</v>
+        <v>484</v>
       </c>
       <c r="F17" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
       <c r="G17" t="s">
-        <v>469</v>
+        <v>486</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B18" t="s">
-        <v>470</v>
+        <v>487</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
       </c>
       <c r="D18" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E18" t="s">
-        <v>471</v>
+        <v>488</v>
       </c>
       <c r="F18" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="G18" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B19" t="s">
-        <v>474</v>
+        <v>491</v>
       </c>
       <c r="C19" t="s">
         <v>144</v>
       </c>
       <c r="D19" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E19" t="s">
-        <v>475</v>
+        <v>492</v>
       </c>
       <c r="F19" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="G19" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B20" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
       <c r="C20" t="s">
         <v>144</v>
       </c>
       <c r="D20" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E20" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="F20" t="s">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="G20" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B21" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="C21" t="s">
         <v>144</v>
       </c>
       <c r="D21" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E21" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="F21" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="G21" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B22" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="C22" t="s">
         <v>144</v>
       </c>
       <c r="D22" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E22" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="F22" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="G22" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B23" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="C23" t="s">
         <v>144</v>
       </c>
       <c r="D23" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E23" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="F23" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="G23" t="s">
-        <v>451</v>
+        <v>468</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B24" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="C24" t="s">
         <v>144</v>
       </c>
       <c r="D24" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E24" t="s">
-        <v>492</v>
+        <v>509</v>
       </c>
       <c r="F24" t="s">
-        <v>493</v>
+        <v>510</v>
       </c>
       <c r="G24" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s">
-        <v>494</v>
+        <v>511</v>
       </c>
       <c r="C25" t="s">
         <v>144</v>
       </c>
       <c r="D25" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E25" t="s">
-        <v>495</v>
+        <v>512</v>
       </c>
       <c r="F25" t="s">
-        <v>472</v>
+        <v>489</v>
       </c>
       <c r="G25" t="s">
-        <v>496</v>
+        <v>513</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B26" t="s">
-        <v>497</v>
+        <v>514</v>
       </c>
       <c r="C26" t="s">
         <v>144</v>
       </c>
       <c r="D26" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E26" t="s">
-        <v>498</v>
+        <v>515</v>
       </c>
       <c r="F26" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
       <c r="G26" t="s">
-        <v>437</v>
+        <v>454</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s">
-        <v>499</v>
+        <v>516</v>
       </c>
       <c r="C27" t="s">
         <v>144</v>
       </c>
       <c r="D27" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E27" t="s">
-        <v>500</v>
+        <v>517</v>
       </c>
       <c r="F27" t="s">
-        <v>501</v>
+        <v>518</v>
       </c>
       <c r="G27" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B28" t="s">
-        <v>502</v>
+        <v>519</v>
       </c>
       <c r="C28" t="s">
         <v>144</v>
       </c>
       <c r="D28" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E28" t="s">
-        <v>503</v>
+        <v>520</v>
       </c>
       <c r="F28" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="G28" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B29" t="s">
-        <v>504</v>
+        <v>521</v>
       </c>
       <c r="C29" t="s">
         <v>144</v>
       </c>
       <c r="D29" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E29" t="s">
-        <v>505</v>
+        <v>522</v>
       </c>
       <c r="F29" t="s">
-        <v>473</v>
+        <v>490</v>
       </c>
       <c r="G29" t="s">
-        <v>506</v>
+        <v>523</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B30" t="s">
-        <v>507</v>
+        <v>524</v>
       </c>
       <c r="C30" t="s">
         <v>144</v>
       </c>
       <c r="D30" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E30" t="s">
-        <v>454</v>
+        <v>471</v>
       </c>
       <c r="F30" t="s">
-        <v>412</v>
+        <v>429</v>
       </c>
       <c r="G30" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s">
-        <v>508</v>
+        <v>525</v>
       </c>
       <c r="C31" t="s">
         <v>144</v>
       </c>
       <c r="D31" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E31" t="s">
-        <v>509</v>
+        <v>526</v>
       </c>
       <c r="F31" t="s">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="G31" t="s">
-        <v>424</v>
+        <v>441</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s">
-        <v>510</v>
+        <v>527</v>
       </c>
       <c r="C32" t="s">
         <v>144</v>
       </c>
       <c r="D32" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E32" t="s">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="F32" t="s">
-        <v>461</v>
+        <v>478</v>
       </c>
       <c r="G32" t="s">
-        <v>462</v>
+        <v>479</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B33" t="s">
-        <v>511</v>
+        <v>528</v>
       </c>
       <c r="C33" t="s">
         <v>144</v>
       </c>
       <c r="D33" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E33" t="s">
-        <v>464</v>
+        <v>481</v>
       </c>
       <c r="F33" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="G33" t="s">
-        <v>465</v>
+        <v>482</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s">
-        <v>512</v>
+        <v>529</v>
       </c>
       <c r="C34" t="s">
         <v>144</v>
       </c>
       <c r="D34" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="E34" t="s">
-        <v>513</v>
+        <v>530</v>
       </c>
       <c r="F34" t="s">
-        <v>514</v>
+        <v>531</v>
       </c>
       <c r="G34" t="s">
-        <v>468</v>
+        <v>485</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B35" t="s">
-        <v>515</v>
+        <v>532</v>
       </c>
       <c r="C35" t="s">
         <v>20</v>
       </c>
       <c r="D35" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="E35" t="s">
-        <v>516</v>
+        <v>533</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>458</v>
+        <v>475</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>455</v>
+        <v>472</v>
       </c>
     </row>
   </sheetData>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -3854,6 +3854,11 @@
       <c r="D7" t="s">
         <v>326</v>
       </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>loc-undecided</t>
+        </is>
+      </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
@@ -3861,7 +3866,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t/>
+          <t>expo-greeting</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>トゥンクトゥンク グリーティング</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EXPO部</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>loc-undecided</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>day1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>公式マスコット キャラクター トゥンクトゥンクが やって来る！</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3903,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19.285714285714285" customWidth="1"/>
@@ -5035,6 +5065,30 @@
         <v>422</v>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>loc-undecided</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>loc-private</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>非公開</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -5043,7 +5097,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
@@ -5854,6 +5908,43 @@
         <v>472</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>expo-greeting</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>tt-d1-19</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>day1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>loc-undecided</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>11:00～11:30頃</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="534">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="546">
   <si>
     <t>id</t>
   </si>
@@ -1046,6 +1046,9 @@
     <t>ウォークラリー</t>
   </si>
   <si>
+    <t>定國ゼミ</t>
+  </si>
+  <si>
     <t>EXPO部</t>
   </si>
   <si>
@@ -1073,6 +1076,12 @@
     <t>関東学院大学 EXPO部 × 平潟祭実行委員会制作！ フォトスポット</t>
   </si>
   <si>
+    <t xml:space="preserve">公式マスコット キャラクター トゥンクトゥンクが やって来る！
+グリーティングの日程は以下となります。
+10/31 (土) 11:00~11:30頃
+※フォトスポットはいつでも撮影できます。</t>
+  </si>
+  <si>
     <t>buildingId</t>
   </si>
   <si>
@@ -1181,12 +1190,21 @@
     <t>no3</t>
   </si>
   <si>
+    <t>3号館1階</t>
+  </si>
+  <si>
+    <t>3号館</t>
+  </si>
+  <si>
+    <t>1階</t>
+  </si>
+  <si>
+    <t>3-203</t>
+  </si>
+  <si>
     <t>3-204</t>
   </si>
   <si>
-    <t>3号館</t>
-  </si>
-  <si>
     <t>3-205</t>
   </si>
   <si>
@@ -1337,6 +1355,18 @@
     <t>グラウンド</t>
   </si>
   <si>
+    <t>loc-undecided</t>
+  </si>
+  <si>
+    <t>未定</t>
+  </si>
+  <si>
+    <t>loc-private</t>
+  </si>
+  <si>
+    <t>非公開</t>
+  </si>
+  <si>
     <t>slotId</t>
   </si>
   <si>
@@ -1668,6 +1698,15 @@
   </si>
   <si>
     <t>14:00キックオフ</t>
+  </si>
+  <si>
+    <t>expo-greeting</t>
+  </si>
+  <si>
+    <t>tt-d1-19</t>
+  </si>
+  <si>
+    <t>11:00～11:30頃</t>
   </si>
 </sst>
 </file>
@@ -3800,101 +3839,69 @@
       <c r="B5" t="s">
         <v>325</v>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>定國ゼミ</t>
-        </is>
+      <c r="C5" t="s">
+        <v>326</v>
       </c>
       <c r="D5" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F5" t="s">
         <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B6" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C6" t="s">
         <v>227</v>
       </c>
       <c r="D6" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="E6" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F6" t="s">
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="7" ht="50.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B7" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C7" t="s">
         <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>326</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>loc-undecided</t>
-        </is>
+        <v>327</v>
+      </c>
+      <c r="E7" t="s">
+        <v>328</v>
       </c>
       <c r="F7" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>expo-greeting</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>トゥンクトゥンク グリーティング</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>EXPO部</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>loc-undecided</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>day1</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>公式マスコット キャラクター トゥンクトゥンクが やって来る！</t>
-        </is>
-      </c>
-    </row>
+      <c r="H7" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3919,19 +3926,19 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -3939,13 +3946,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -3956,13 +3963,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D3" t="s">
         <v>343</v>
       </c>
-      <c r="D3" t="s">
-        <v>341</v>
-      </c>
       <c r="E3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -3973,13 +3980,13 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D4" t="s">
+        <v>343</v>
+      </c>
+      <c r="E4" t="s">
         <v>344</v>
-      </c>
-      <c r="D4" t="s">
-        <v>341</v>
-      </c>
-      <c r="E4" t="s">
-        <v>342</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -3990,13 +3997,13 @@
         <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="D5" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E5" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -4007,13 +4014,13 @@
         <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4024,13 +4031,13 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D7" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -4041,13 +4048,13 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="D8" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E8" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -4058,13 +4065,13 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -4075,13 +4082,13 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="D10" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E10" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -4092,13 +4099,13 @@
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D11" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E11" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -4109,13 +4116,13 @@
         <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D12" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E12" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -4126,13 +4133,13 @@
         <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D13" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E13" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -4143,13 +4150,13 @@
         <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="D14" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E14" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -4160,13 +4167,13 @@
         <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D15" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E15" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -4177,13 +4184,13 @@
         <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D16" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E16" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -4194,13 +4201,13 @@
         <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D17" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E17" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -4211,13 +4218,13 @@
         <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D18" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E18" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -4228,13 +4235,13 @@
         <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D19" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E19" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -4245,13 +4252,13 @@
         <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D20" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E20" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -4262,13 +4269,13 @@
         <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D21" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E21" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -4279,13 +4286,13 @@
         <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D22" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E22" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -4296,13 +4303,13 @@
         <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D23" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E23" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -4313,13 +4320,13 @@
         <v>161</v>
       </c>
       <c r="C24" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D24" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E24" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -4330,13 +4337,13 @@
         <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D25" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E25" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -4344,83 +4351,59 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C26" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D26" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>loc-3-1</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no3</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>3号館1階</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>3号館</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>1階</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>loc-3-203</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>no3</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>3-203</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>3号館</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>203</t>
-        </is>
+        <v>371</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>328</v>
+      </c>
+      <c r="B27" t="s">
+        <v>372</v>
+      </c>
+      <c r="C27" t="s">
+        <v>373</v>
+      </c>
+      <c r="D27" t="s">
+        <v>374</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+      <c r="F27" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>332</v>
+      </c>
+      <c r="B28" t="s">
+        <v>372</v>
+      </c>
+      <c r="C28" t="s">
+        <v>376</v>
+      </c>
+      <c r="D28" t="s">
+        <v>374</v>
+      </c>
+      <c r="E28">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>203</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -4428,13 +4411,13 @@
         <v>237</v>
       </c>
       <c r="B29" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C29" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="D29" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -4448,13 +4431,13 @@
         <v>178</v>
       </c>
       <c r="B30" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C30" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D30" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -4468,13 +4451,13 @@
         <v>183</v>
       </c>
       <c r="B31" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C31" t="s">
+        <v>379</v>
+      </c>
+      <c r="D31" t="s">
         <v>374</v>
-      </c>
-      <c r="D31" t="s">
-        <v>372</v>
       </c>
       <c r="E31">
         <v>2</v>
@@ -4488,13 +4471,13 @@
         <v>223</v>
       </c>
       <c r="B32" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C32" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D32" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -4508,13 +4491,13 @@
         <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C33" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="D33" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -4528,13 +4511,13 @@
         <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C34" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D34" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -4548,19 +4531,19 @@
         <v>219</v>
       </c>
       <c r="B35" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C35" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D35" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4568,13 +4551,13 @@
         <v>211</v>
       </c>
       <c r="B36" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C36" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D36" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -4588,13 +4571,13 @@
         <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C37" t="s">
+        <v>390</v>
+      </c>
+      <c r="D37" t="s">
         <v>385</v>
-      </c>
-      <c r="D37" t="s">
-        <v>380</v>
       </c>
       <c r="E37">
         <v>2</v>
@@ -4608,13 +4591,13 @@
         <v>173</v>
       </c>
       <c r="B38" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C38" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D38" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -4628,13 +4611,13 @@
         <v>228</v>
       </c>
       <c r="B39" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C39" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D39" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E39">
         <v>2</v>
@@ -4648,13 +4631,13 @@
         <v>188</v>
       </c>
       <c r="B40" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C40" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="D40" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E40">
         <v>2</v>
@@ -4668,13 +4651,13 @@
         <v>232</v>
       </c>
       <c r="B41" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C41" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D41" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -4688,13 +4671,13 @@
         <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="C42" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="D42" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -4708,33 +4691,33 @@
         <v>215</v>
       </c>
       <c r="B43" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="C43" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D43" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="B44" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C44" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D44" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -4748,13 +4731,13 @@
         <v>250</v>
       </c>
       <c r="B45" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C45" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D45" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E45">
         <v>2</v>
@@ -4765,16 +4748,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B46" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C46" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D46" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -4788,13 +4771,13 @@
         <v>254</v>
       </c>
       <c r="B47" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C47" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D47" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -4805,16 +4788,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>405</v>
+      </c>
+      <c r="B48" t="s">
+        <v>398</v>
+      </c>
+      <c r="C48" t="s">
+        <v>406</v>
+      </c>
+      <c r="D48" t="s">
         <v>400</v>
-      </c>
-      <c r="B48" t="s">
-        <v>393</v>
-      </c>
-      <c r="C48" t="s">
-        <v>401</v>
-      </c>
-      <c r="D48" t="s">
-        <v>395</v>
       </c>
       <c r="E48">
         <v>4</v>
@@ -4828,13 +4811,13 @@
         <v>261</v>
       </c>
       <c r="B49" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C49" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="D49" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E49">
         <v>4</v>
@@ -4848,16 +4831,16 @@
         <v>277</v>
       </c>
       <c r="C50" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D50" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="E50" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F50" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4865,19 +4848,19 @@
         <v>264</v>
       </c>
       <c r="B51" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="C51" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="D51" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="E51">
         <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4885,16 +4868,16 @@
         <v>291</v>
       </c>
       <c r="C52" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D52" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4902,16 +4885,16 @@
         <v>286</v>
       </c>
       <c r="C53" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D53" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E53" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F53" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4919,16 +4902,16 @@
         <v>296</v>
       </c>
       <c r="C54" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="D54" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4936,16 +4919,16 @@
         <v>281</v>
       </c>
       <c r="C55" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D55" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E55">
         <v>6</v>
       </c>
       <c r="F55" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4953,19 +4936,19 @@
         <v>322</v>
       </c>
       <c r="B56" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C56" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D56" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4973,19 +4956,19 @@
         <v>150</v>
       </c>
       <c r="B57" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C57" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D57" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4993,13 +4976,13 @@
         <v>257</v>
       </c>
       <c r="B58" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C58" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D58" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E58">
         <v>2</v>
@@ -5013,13 +4996,13 @@
         <v>242</v>
       </c>
       <c r="B59" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C59" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="D59" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E59">
         <v>4</v>
@@ -5033,13 +5016,13 @@
         <v>246</v>
       </c>
       <c r="B60" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="C60" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D60" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -5053,40 +5036,32 @@
         <v>316</v>
       </c>
       <c r="C61" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D61" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="E61" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F61" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>loc-undecided</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>未定</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>loc-private</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>非公開</t>
-        </is>
+        <v>427</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>428</v>
+      </c>
+      <c r="C62" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>430</v>
+      </c>
+      <c r="C63" t="s">
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -5108,7 +5083,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -5117,13 +5092,13 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -5131,7 +5106,7 @@
         <v>259</v>
       </c>
       <c r="B2" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -5140,13 +5115,13 @@
         <v>277</v>
       </c>
       <c r="E2" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="F2" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="G2" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5154,7 +5129,7 @@
         <v>239</v>
       </c>
       <c r="B3" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -5163,13 +5138,13 @@
         <v>277</v>
       </c>
       <c r="E3" t="s">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="F3" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="G3" t="s">
-        <v>434</v>
+        <v>443</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5177,7 +5152,7 @@
         <v>244</v>
       </c>
       <c r="B4" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -5186,13 +5161,13 @@
         <v>277</v>
       </c>
       <c r="E4" t="s">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="F4" t="s">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="G4" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5200,7 +5175,7 @@
         <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -5209,13 +5184,13 @@
         <v>277</v>
       </c>
       <c r="E5" t="s">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="F5" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="G5" t="s">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5223,7 +5198,7 @@
         <v>255</v>
       </c>
       <c r="B6" t="s">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -5232,13 +5207,13 @@
         <v>277</v>
       </c>
       <c r="E6" t="s">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="F6" t="s">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="G6" t="s">
-        <v>446</v>
+        <v>455</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5246,7 +5221,7 @@
         <v>248</v>
       </c>
       <c r="B7" t="s">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
@@ -5255,13 +5230,13 @@
         <v>277</v>
       </c>
       <c r="E7" t="s">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="F7" t="s">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="G7" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5269,7 +5244,7 @@
         <v>275</v>
       </c>
       <c r="B8" t="s">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
@@ -5278,13 +5253,13 @@
         <v>277</v>
       </c>
       <c r="E8" t="s">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="F8" t="s">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="G8" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5292,7 +5267,7 @@
         <v>263</v>
       </c>
       <c r="B9" t="s">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -5301,13 +5276,13 @@
         <v>264</v>
       </c>
       <c r="E9" t="s">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="F9" t="s">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="G9" t="s">
-        <v>458</v>
+        <v>467</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5315,7 +5290,7 @@
         <v>266</v>
       </c>
       <c r="B10" t="s">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -5324,13 +5299,13 @@
         <v>264</v>
       </c>
       <c r="E10" t="s">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="F10" t="s">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="G10" t="s">
-        <v>462</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5338,7 +5313,7 @@
         <v>269</v>
       </c>
       <c r="B11" t="s">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -5347,13 +5322,13 @@
         <v>264</v>
       </c>
       <c r="E11" t="s">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="F11" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="G11" t="s">
-        <v>465</v>
+        <v>474</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5361,7 +5336,7 @@
         <v>272</v>
       </c>
       <c r="B12" t="s">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -5370,13 +5345,13 @@
         <v>264</v>
       </c>
       <c r="E12" t="s">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="F12" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="G12" t="s">
-        <v>469</v>
+        <v>478</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5384,7 +5359,7 @@
         <v>288</v>
       </c>
       <c r="B13" t="s">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
@@ -5393,13 +5368,13 @@
         <v>291</v>
       </c>
       <c r="E13" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="F13" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="G13" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5407,7 +5382,7 @@
         <v>283</v>
       </c>
       <c r="B14" t="s">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
@@ -5416,13 +5391,13 @@
         <v>286</v>
       </c>
       <c r="E14" t="s">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="F14" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="G14" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5430,7 +5405,7 @@
         <v>293</v>
       </c>
       <c r="B15" t="s">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -5439,13 +5414,13 @@
         <v>296</v>
       </c>
       <c r="E15" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="F15" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="G15" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5453,7 +5428,7 @@
         <v>293</v>
       </c>
       <c r="B16" t="s">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
@@ -5462,13 +5437,13 @@
         <v>296</v>
       </c>
       <c r="E16" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F16" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="G16" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5476,7 +5451,7 @@
         <v>298</v>
       </c>
       <c r="B17" t="s">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
@@ -5485,13 +5460,13 @@
         <v>296</v>
       </c>
       <c r="E17" t="s">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="F17" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="G17" t="s">
-        <v>486</v>
+        <v>495</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5499,7 +5474,7 @@
         <v>300</v>
       </c>
       <c r="B18" t="s">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -5508,13 +5483,13 @@
         <v>296</v>
       </c>
       <c r="E18" t="s">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="F18" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="G18" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5522,7 +5497,7 @@
         <v>259</v>
       </c>
       <c r="B19" t="s">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="C19" t="s">
         <v>144</v>
@@ -5531,13 +5506,13 @@
         <v>277</v>
       </c>
       <c r="E19" t="s">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="F19" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="G19" t="s">
-        <v>493</v>
+        <v>502</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5545,7 +5520,7 @@
         <v>239</v>
       </c>
       <c r="B20" t="s">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="C20" t="s">
         <v>144</v>
@@ -5554,13 +5529,13 @@
         <v>277</v>
       </c>
       <c r="E20" t="s">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="F20" t="s">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="G20" t="s">
-        <v>496</v>
+        <v>505</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5568,7 +5543,7 @@
         <v>244</v>
       </c>
       <c r="B21" t="s">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="C21" t="s">
         <v>144</v>
@@ -5577,13 +5552,13 @@
         <v>277</v>
       </c>
       <c r="E21" t="s">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="F21" t="s">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="G21" t="s">
-        <v>500</v>
+        <v>509</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -5591,7 +5566,7 @@
         <v>252</v>
       </c>
       <c r="B22" t="s">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="C22" t="s">
         <v>144</v>
@@ -5600,13 +5575,13 @@
         <v>277</v>
       </c>
       <c r="E22" t="s">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="F22" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="G22" t="s">
-        <v>504</v>
+        <v>513</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -5614,7 +5589,7 @@
         <v>255</v>
       </c>
       <c r="B23" t="s">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="C23" t="s">
         <v>144</v>
@@ -5623,13 +5598,13 @@
         <v>277</v>
       </c>
       <c r="E23" t="s">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="F23" t="s">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="G23" t="s">
-        <v>468</v>
+        <v>477</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -5637,7 +5612,7 @@
         <v>248</v>
       </c>
       <c r="B24" t="s">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C24" t="s">
         <v>144</v>
@@ -5646,13 +5621,13 @@
         <v>277</v>
       </c>
       <c r="E24" t="s">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="F24" t="s">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="G24" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -5660,7 +5635,7 @@
         <v>275</v>
       </c>
       <c r="B25" t="s">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="C25" t="s">
         <v>144</v>
@@ -5669,13 +5644,13 @@
         <v>277</v>
       </c>
       <c r="E25" t="s">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="F25" t="s">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="G25" t="s">
-        <v>513</v>
+        <v>522</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -5683,7 +5658,7 @@
         <v>279</v>
       </c>
       <c r="B26" t="s">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="C26" t="s">
         <v>144</v>
@@ -5692,13 +5667,13 @@
         <v>277</v>
       </c>
       <c r="E26" t="s">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="F26" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="G26" t="s">
-        <v>454</v>
+        <v>463</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -5706,7 +5681,7 @@
         <v>263</v>
       </c>
       <c r="B27" t="s">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C27" t="s">
         <v>144</v>
@@ -5715,13 +5690,13 @@
         <v>264</v>
       </c>
       <c r="E27" t="s">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="F27" t="s">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="G27" t="s">
-        <v>503</v>
+        <v>512</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -5729,7 +5704,7 @@
         <v>272</v>
       </c>
       <c r="B28" t="s">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="C28" t="s">
         <v>144</v>
@@ -5738,13 +5713,13 @@
         <v>264</v>
       </c>
       <c r="E28" t="s">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="F28" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="G28" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -5752,7 +5727,7 @@
         <v>307</v>
       </c>
       <c r="B29" t="s">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="C29" t="s">
         <v>144</v>
@@ -5761,13 +5736,13 @@
         <v>264</v>
       </c>
       <c r="E29" t="s">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="F29" t="s">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="G29" t="s">
-        <v>523</v>
+        <v>532</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -5775,7 +5750,7 @@
         <v>288</v>
       </c>
       <c r="B30" t="s">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="C30" t="s">
         <v>144</v>
@@ -5784,13 +5759,13 @@
         <v>291</v>
       </c>
       <c r="E30" t="s">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="F30" t="s">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="G30" t="s">
-        <v>472</v>
+        <v>481</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -5798,7 +5773,7 @@
         <v>303</v>
       </c>
       <c r="B31" t="s">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C31" t="s">
         <v>144</v>
@@ -5807,13 +5782,13 @@
         <v>296</v>
       </c>
       <c r="E31" t="s">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="F31" t="s">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="G31" t="s">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -5821,7 +5796,7 @@
         <v>303</v>
       </c>
       <c r="B32" t="s">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="C32" t="s">
         <v>144</v>
@@ -5830,13 +5805,13 @@
         <v>296</v>
       </c>
       <c r="E32" t="s">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="F32" t="s">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="G32" t="s">
-        <v>479</v>
+        <v>488</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -5844,7 +5819,7 @@
         <v>305</v>
       </c>
       <c r="B33" t="s">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="C33" t="s">
         <v>144</v>
@@ -5853,13 +5828,13 @@
         <v>296</v>
       </c>
       <c r="E33" t="s">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="F33" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="G33" t="s">
-        <v>482</v>
+        <v>491</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -5867,7 +5842,7 @@
         <v>305</v>
       </c>
       <c r="B34" t="s">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="C34" t="s">
         <v>144</v>
@@ -5876,13 +5851,13 @@
         <v>296</v>
       </c>
       <c r="E34" t="s">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="F34" t="s">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="G34" t="s">
-        <v>485</v>
+        <v>494</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -5890,7 +5865,7 @@
         <v>313</v>
       </c>
       <c r="B35" t="s">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="C35" t="s">
         <v>20</v>
@@ -5899,50 +5874,36 @@
         <v>316</v>
       </c>
       <c r="E35" t="s">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>expo-greeting</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>tt-d1-19</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>day1</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>loc-undecided</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>11:00～11:30頃</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
+        <v>481</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>543</v>
+      </c>
+      <c r="B36" t="s">
+        <v>544</v>
+      </c>
+      <c r="C36" t="s">
+        <v>20</v>
+      </c>
+      <c r="D36" t="s">
+        <v>428</v>
+      </c>
+      <c r="E36" t="s">
+        <v>545</v>
+      </c>
+      <c r="F36" t="s">
+        <v>466</v>
+      </c>
+      <c r="G36" t="s">
+        <v>467</v>
       </c>
     </row>
   </sheetData>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -2833,8 +2833,10 @@
       <c r="C28" t="s">
         <v>165</v>
       </c>
-      <c r="D28" t="s">
-        <v>166</v>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>EXPO部,模擬店</t>
+        </is>
       </c>
       <c r="E28" t="s">
         <v>150</v>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -537,7 +537,7 @@
     <t>関東学院大学EXPO部</t>
   </si>
   <si>
-    <t>模擬店,EXPO部</t>
+    <t>EXPO部,模擬店</t>
   </si>
   <si>
     <t xml:space="preserve">コーヒー・紅茶：200円
@@ -1043,7 +1043,7 @@
     <t>expo-walk-rally</t>
   </si>
   <si>
-    <t>ウォークラリー</t>
+    <t>環境について考える「ミライノタネ」</t>
   </si>
   <si>
     <t>定國ゼミ</t>
@@ -2833,10 +2833,8 @@
       <c r="C28" t="s">
         <v>165</v>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>EXPO部,模擬店</t>
-        </is>
+      <c r="D28" t="s">
+        <v>166</v>
       </c>
       <c r="E28" t="s">
         <v>150</v>
@@ -3723,7 +3721,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
@@ -3903,7 +3901,8 @@
         <v>336</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="5:5" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="4:4" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1034" uniqueCount="546">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="554">
   <si>
     <t>id</t>
   </si>
@@ -1082,6 +1082,23 @@
 ※フォトスポットはいつでも撮影できます。</t>
   </si>
   <si>
+    <t>omikoshi</t>
+  </si>
+  <si>
+    <t>御神輿</t>
+  </si>
+  <si>
+    <t>横浜金沢みこし-まつり保存協会×平潟祭実行委員会</t>
+  </si>
+  <si>
+    <t>loc-entrance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">関東学院大学のキャンパスに、大きなお神輿がやってきます！
+構内を威勢よく進むその姿は、地域のみなさまとこれまで築いてきた絆の証。
+そして、これからもずっと手を取り合い、温かい関係が続いていくという未来への願いが込められています。お神輿の熱気とともに、地域との絆をもっともっと強く、そして深めていきます。</t>
+  </si>
+  <si>
     <t>buildingId</t>
   </si>
   <si>
@@ -1352,6 +1369,9 @@
     <t>7-302</t>
   </si>
   <si>
+    <t>エントランス広場</t>
+  </si>
+  <si>
     <t>グラウンド</t>
   </si>
   <si>
@@ -1707,6 +1727,12 @@
   </si>
   <si>
     <t>11:00～11:30頃</t>
+  </si>
+  <si>
+    <t>tt-d1-20</t>
+  </si>
+  <si>
+    <t>12:00頃~</t>
   </si>
 </sst>
 </file>
@@ -3721,7 +3747,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
@@ -3901,8 +3927,29 @@
         <v>336</v>
       </c>
     </row>
-    <row r="8" spans="5:5" x14ac:dyDescent="0.25"/>
-    <row r="9" spans="4:4" x14ac:dyDescent="0.25"/>
+    <row r="8" ht="89.25" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>337</v>
+      </c>
+      <c r="B8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C8" t="s">
+        <v>339</v>
+      </c>
+      <c r="D8" t="s">
+        <v>315</v>
+      </c>
+      <c r="E8" t="s">
+        <v>340</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s">
+        <v>341</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3911,7 +3958,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19.285714285714285" customWidth="1"/>
@@ -3927,19 +3974,19 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -3947,13 +3994,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="D2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -3964,13 +4011,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="D3" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -3981,13 +4028,13 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="D4" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E4" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -3998,13 +4045,13 @@
         <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D5" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E5" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -4015,13 +4062,13 @@
         <v>37</v>
       </c>
       <c r="C6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D6" t="s">
         <v>348</v>
       </c>
-      <c r="D6" t="s">
-        <v>343</v>
-      </c>
       <c r="E6" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4032,13 +4079,13 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
+        <v>354</v>
+      </c>
+      <c r="D7" t="s">
+        <v>348</v>
+      </c>
+      <c r="E7" t="s">
         <v>349</v>
-      </c>
-      <c r="D7" t="s">
-        <v>343</v>
-      </c>
-      <c r="E7" t="s">
-        <v>344</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -4049,13 +4096,13 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D8" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E8" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -4066,13 +4113,13 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D9" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E9" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -4083,13 +4130,13 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D10" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E10" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -4100,13 +4147,13 @@
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D11" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E11" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -4117,13 +4164,13 @@
         <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="D12" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E12" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -4134,13 +4181,13 @@
         <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D13" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E13" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -4151,13 +4198,13 @@
         <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D14" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E14" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -4168,13 +4215,13 @@
         <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D15" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E15" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -4185,13 +4232,13 @@
         <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="D16" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E16" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -4202,13 +4249,13 @@
         <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D17" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E17" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -4219,13 +4266,13 @@
         <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D18" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E18" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -4236,13 +4283,13 @@
         <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D19" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E19" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -4253,13 +4300,13 @@
         <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D20" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E20" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -4270,13 +4317,13 @@
         <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="D21" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E21" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -4287,13 +4334,13 @@
         <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D22" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E22" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -4304,13 +4351,13 @@
         <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="D23" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E23" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -4321,13 +4368,13 @@
         <v>161</v>
       </c>
       <c r="C24" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D24" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E24" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -4338,13 +4385,13 @@
         <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D25" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="E25" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -4352,19 +4399,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="C26" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D26" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4372,19 +4419,19 @@
         <v>328</v>
       </c>
       <c r="B27" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C27" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D27" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4392,13 +4439,13 @@
         <v>332</v>
       </c>
       <c r="B28" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C28" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="D28" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -4412,13 +4459,13 @@
         <v>237</v>
       </c>
       <c r="B29" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C29" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D29" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -4432,13 +4479,13 @@
         <v>178</v>
       </c>
       <c r="B30" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C30" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D30" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -4452,13 +4499,13 @@
         <v>183</v>
       </c>
       <c r="B31" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C31" t="s">
+        <v>384</v>
+      </c>
+      <c r="D31" t="s">
         <v>379</v>
-      </c>
-      <c r="D31" t="s">
-        <v>374</v>
       </c>
       <c r="E31">
         <v>2</v>
@@ -4472,13 +4519,13 @@
         <v>223</v>
       </c>
       <c r="B32" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C32" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D32" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -4492,13 +4539,13 @@
         <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C33" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="D33" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -4512,13 +4559,13 @@
         <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C34" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D34" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -4532,19 +4579,19 @@
         <v>219</v>
       </c>
       <c r="B35" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C35" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="D35" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4552,13 +4599,13 @@
         <v>211</v>
       </c>
       <c r="B36" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C36" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D36" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -4572,13 +4619,13 @@
         <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C37" t="s">
+        <v>395</v>
+      </c>
+      <c r="D37" t="s">
         <v>390</v>
-      </c>
-      <c r="D37" t="s">
-        <v>385</v>
       </c>
       <c r="E37">
         <v>2</v>
@@ -4592,13 +4639,13 @@
         <v>173</v>
       </c>
       <c r="B38" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C38" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D38" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -4612,13 +4659,13 @@
         <v>228</v>
       </c>
       <c r="B39" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C39" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D39" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E39">
         <v>2</v>
@@ -4632,13 +4679,13 @@
         <v>188</v>
       </c>
       <c r="B40" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C40" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
       <c r="D40" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E40">
         <v>2</v>
@@ -4652,13 +4699,13 @@
         <v>232</v>
       </c>
       <c r="B41" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C41" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D41" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -4672,13 +4719,13 @@
         <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="C42" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
       <c r="D42" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -4692,33 +4739,33 @@
         <v>215</v>
       </c>
       <c r="B43" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="C43" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D43" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="B44" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C44" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D44" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -4732,13 +4779,13 @@
         <v>250</v>
       </c>
       <c r="B45" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C45" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D45" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E45">
         <v>2</v>
@@ -4749,16 +4796,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B46" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C46" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="D46" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -4772,13 +4819,13 @@
         <v>254</v>
       </c>
       <c r="B47" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C47" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D47" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -4789,16 +4836,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>410</v>
+      </c>
+      <c r="B48" t="s">
+        <v>403</v>
+      </c>
+      <c r="C48" t="s">
+        <v>411</v>
+      </c>
+      <c r="D48" t="s">
         <v>405</v>
-      </c>
-      <c r="B48" t="s">
-        <v>398</v>
-      </c>
-      <c r="C48" t="s">
-        <v>406</v>
-      </c>
-      <c r="D48" t="s">
-        <v>400</v>
       </c>
       <c r="E48">
         <v>4</v>
@@ -4812,13 +4859,13 @@
         <v>261</v>
       </c>
       <c r="B49" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C49" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="D49" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E49">
         <v>4</v>
@@ -4832,16 +4879,16 @@
         <v>277</v>
       </c>
       <c r="C50" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D50" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="E50" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F50" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4849,19 +4896,19 @@
         <v>264</v>
       </c>
       <c r="B51" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="C51" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="D51" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="E51">
         <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4869,16 +4916,16 @@
         <v>291</v>
       </c>
       <c r="C52" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D52" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4886,16 +4933,16 @@
         <v>286</v>
       </c>
       <c r="C53" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="D53" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="E53" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="F53" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4903,16 +4950,16 @@
         <v>296</v>
       </c>
       <c r="C54" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D54" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4920,16 +4967,16 @@
         <v>281</v>
       </c>
       <c r="C55" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D55" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E55">
         <v>6</v>
       </c>
       <c r="F55" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4937,19 +4984,19 @@
         <v>322</v>
       </c>
       <c r="B56" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C56" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D56" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -4957,19 +5004,19 @@
         <v>150</v>
       </c>
       <c r="B57" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="C57" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="D57" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -4977,13 +5024,13 @@
         <v>257</v>
       </c>
       <c r="B58" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C58" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="D58" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E58">
         <v>2</v>
@@ -4997,13 +5044,13 @@
         <v>242</v>
       </c>
       <c r="B59" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C59" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
       <c r="D59" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E59">
         <v>4</v>
@@ -5017,13 +5064,13 @@
         <v>246</v>
       </c>
       <c r="B60" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="C60" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D60" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -5034,35 +5081,52 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>340</v>
+      </c>
+      <c r="C61" t="s">
+        <v>432</v>
+      </c>
+      <c r="D61" t="s">
+        <v>432</v>
+      </c>
+      <c r="E61" t="s">
+        <v>349</v>
+      </c>
+      <c r="F61" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
         <v>316</v>
       </c>
-      <c r="C61" t="s">
-        <v>427</v>
-      </c>
-      <c r="D61" t="s">
-        <v>427</v>
-      </c>
-      <c r="E61" t="s">
-        <v>344</v>
-      </c>
-      <c r="F61" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>428</v>
-      </c>
       <c r="C62" t="s">
-        <v>429</v>
+        <v>433</v>
+      </c>
+      <c r="D62" t="s">
+        <v>433</v>
+      </c>
+      <c r="E62" t="s">
+        <v>349</v>
+      </c>
+      <c r="F62" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C63" t="s">
-        <v>431</v>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>436</v>
+      </c>
+      <c r="C64" t="s">
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -5073,7 +5137,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
@@ -5084,7 +5148,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -5093,13 +5157,13 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -5107,7 +5171,7 @@
         <v>259</v>
       </c>
       <c r="B2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -5116,13 +5180,13 @@
         <v>277</v>
       </c>
       <c r="E2" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="F2" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="G2" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5130,7 +5194,7 @@
         <v>239</v>
       </c>
       <c r="B3" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -5139,13 +5203,13 @@
         <v>277</v>
       </c>
       <c r="E3" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="F3" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="G3" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5153,7 +5217,7 @@
         <v>244</v>
       </c>
       <c r="B4" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -5162,13 +5226,13 @@
         <v>277</v>
       </c>
       <c r="E4" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="F4" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="G4" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5176,7 +5240,7 @@
         <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -5185,13 +5249,13 @@
         <v>277</v>
       </c>
       <c r="E5" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="F5" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="G5" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5199,7 +5263,7 @@
         <v>255</v>
       </c>
       <c r="B6" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -5208,13 +5272,13 @@
         <v>277</v>
       </c>
       <c r="E6" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F6" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="G6" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5222,7 +5286,7 @@
         <v>248</v>
       </c>
       <c r="B7" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
@@ -5231,13 +5295,13 @@
         <v>277</v>
       </c>
       <c r="E7" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="F7" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="G7" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5245,7 +5309,7 @@
         <v>275</v>
       </c>
       <c r="B8" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
@@ -5254,13 +5318,13 @@
         <v>277</v>
       </c>
       <c r="E8" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="F8" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="G8" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5268,7 +5332,7 @@
         <v>263</v>
       </c>
       <c r="B9" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -5277,13 +5341,13 @@
         <v>264</v>
       </c>
       <c r="E9" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="F9" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="G9" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5291,7 +5355,7 @@
         <v>266</v>
       </c>
       <c r="B10" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -5300,13 +5364,13 @@
         <v>264</v>
       </c>
       <c r="E10" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="F10" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="G10" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5314,7 +5378,7 @@
         <v>269</v>
       </c>
       <c r="B11" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -5323,13 +5387,13 @@
         <v>264</v>
       </c>
       <c r="E11" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="F11" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="G11" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5337,7 +5401,7 @@
         <v>272</v>
       </c>
       <c r="B12" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -5346,13 +5410,13 @@
         <v>264</v>
       </c>
       <c r="E12" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="F12" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="G12" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5360,7 +5424,7 @@
         <v>288</v>
       </c>
       <c r="B13" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
@@ -5369,13 +5433,13 @@
         <v>291</v>
       </c>
       <c r="E13" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="F13" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="G13" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5383,7 +5447,7 @@
         <v>283</v>
       </c>
       <c r="B14" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
@@ -5392,13 +5456,13 @@
         <v>286</v>
       </c>
       <c r="E14" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="F14" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="G14" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5406,7 +5470,7 @@
         <v>293</v>
       </c>
       <c r="B15" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -5415,13 +5479,13 @@
         <v>296</v>
       </c>
       <c r="E15" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F15" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="G15" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5429,7 +5493,7 @@
         <v>293</v>
       </c>
       <c r="B16" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
@@ -5438,13 +5502,13 @@
         <v>296</v>
       </c>
       <c r="E16" t="s">
+        <v>496</v>
+      </c>
+      <c r="F16" t="s">
         <v>490</v>
       </c>
-      <c r="F16" t="s">
-        <v>484</v>
-      </c>
       <c r="G16" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5452,7 +5516,7 @@
         <v>298</v>
       </c>
       <c r="B17" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
@@ -5461,13 +5525,13 @@
         <v>296</v>
       </c>
       <c r="E17" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="F17" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
       <c r="G17" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5475,7 +5539,7 @@
         <v>300</v>
       </c>
       <c r="B18" t="s">
-        <v>496</v>
+        <v>502</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -5484,13 +5548,13 @@
         <v>296</v>
       </c>
       <c r="E18" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="F18" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G18" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5498,7 +5562,7 @@
         <v>259</v>
       </c>
       <c r="B19" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="C19" t="s">
         <v>144</v>
@@ -5507,13 +5571,13 @@
         <v>277</v>
       </c>
       <c r="E19" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="F19" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="G19" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5521,7 +5585,7 @@
         <v>239</v>
       </c>
       <c r="B20" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="C20" t="s">
         <v>144</v>
@@ -5530,13 +5594,13 @@
         <v>277</v>
       </c>
       <c r="E20" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="F20" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="G20" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5544,7 +5608,7 @@
         <v>244</v>
       </c>
       <c r="B21" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C21" t="s">
         <v>144</v>
@@ -5553,13 +5617,13 @@
         <v>277</v>
       </c>
       <c r="E21" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="F21" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="G21" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -5567,7 +5631,7 @@
         <v>252</v>
       </c>
       <c r="B22" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="C22" t="s">
         <v>144</v>
@@ -5576,13 +5640,13 @@
         <v>277</v>
       </c>
       <c r="E22" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
       <c r="F22" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="G22" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -5590,7 +5654,7 @@
         <v>255</v>
       </c>
       <c r="B23" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C23" t="s">
         <v>144</v>
@@ -5599,13 +5663,13 @@
         <v>277</v>
       </c>
       <c r="E23" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
       <c r="F23" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="G23" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -5613,7 +5677,7 @@
         <v>248</v>
       </c>
       <c r="B24" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C24" t="s">
         <v>144</v>
@@ -5622,13 +5686,13 @@
         <v>277</v>
       </c>
       <c r="E24" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="F24" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="G24" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -5636,7 +5700,7 @@
         <v>275</v>
       </c>
       <c r="B25" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C25" t="s">
         <v>144</v>
@@ -5645,13 +5709,13 @@
         <v>277</v>
       </c>
       <c r="E25" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="F25" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="G25" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -5659,7 +5723,7 @@
         <v>279</v>
       </c>
       <c r="B26" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C26" t="s">
         <v>144</v>
@@ -5668,13 +5732,13 @@
         <v>277</v>
       </c>
       <c r="E26" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="F26" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="G26" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -5682,7 +5746,7 @@
         <v>263</v>
       </c>
       <c r="B27" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="C27" t="s">
         <v>144</v>
@@ -5691,13 +5755,13 @@
         <v>264</v>
       </c>
       <c r="E27" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="F27" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="G27" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -5705,7 +5769,7 @@
         <v>272</v>
       </c>
       <c r="B28" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="C28" t="s">
         <v>144</v>
@@ -5714,13 +5778,13 @@
         <v>264</v>
       </c>
       <c r="E28" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="F28" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="G28" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -5728,7 +5792,7 @@
         <v>307</v>
       </c>
       <c r="B29" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="C29" t="s">
         <v>144</v>
@@ -5737,13 +5801,13 @@
         <v>264</v>
       </c>
       <c r="E29" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="F29" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="G29" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -5751,7 +5815,7 @@
         <v>288</v>
       </c>
       <c r="B30" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="C30" t="s">
         <v>144</v>
@@ -5760,13 +5824,13 @@
         <v>291</v>
       </c>
       <c r="E30" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="F30" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="G30" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -5774,7 +5838,7 @@
         <v>303</v>
       </c>
       <c r="B31" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C31" t="s">
         <v>144</v>
@@ -5783,13 +5847,13 @@
         <v>296</v>
       </c>
       <c r="E31" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F31" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="G31" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -5797,7 +5861,7 @@
         <v>303</v>
       </c>
       <c r="B32" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C32" t="s">
         <v>144</v>
@@ -5806,13 +5870,13 @@
         <v>296</v>
       </c>
       <c r="E32" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F32" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="G32" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -5820,7 +5884,7 @@
         <v>305</v>
       </c>
       <c r="B33" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="C33" t="s">
         <v>144</v>
@@ -5829,13 +5893,13 @@
         <v>296</v>
       </c>
       <c r="E33" t="s">
+        <v>496</v>
+      </c>
+      <c r="F33" t="s">
         <v>490</v>
       </c>
-      <c r="F33" t="s">
-        <v>484</v>
-      </c>
       <c r="G33" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -5843,7 +5907,7 @@
         <v>305</v>
       </c>
       <c r="B34" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="C34" t="s">
         <v>144</v>
@@ -5852,13 +5916,13 @@
         <v>296</v>
       </c>
       <c r="E34" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F34" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="G34" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -5866,7 +5930,7 @@
         <v>313</v>
       </c>
       <c r="B35" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="C35" t="s">
         <v>20</v>
@@ -5875,36 +5939,59 @@
         <v>316</v>
       </c>
       <c r="E35" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B36" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C36" t="s">
         <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="E36" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F36" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="G36" t="s">
-        <v>467</v>
+        <v>473</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>337</v>
+      </c>
+      <c r="B37" t="s">
+        <v>552</v>
+      </c>
+      <c r="C37" t="s">
+        <v>20</v>
+      </c>
+      <c r="D37" t="s">
+        <v>340</v>
+      </c>
+      <c r="E37" t="s">
+        <v>553</v>
+      </c>
+      <c r="F37" t="s">
+        <v>533</v>
+      </c>
+      <c r="G37" t="s">
+        <v>453</v>
       </c>
     </row>
   </sheetData>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1053" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1076" uniqueCount="563">
   <si>
     <t>id</t>
   </si>
@@ -1099,6 +1099,21 @@
 そして、これからもずっと手を取り合い、温かい関係が続いていくという未来への願いが込められています。お神輿の熱気とともに、地域との絆をもっともっと強く、そして深めていきます。</t>
   </si>
   <si>
+    <t>radio</t>
+  </si>
+  <si>
+    <t>ひらかたジャック2026！～学生が届ける、平潟祭の『今』!～</t>
+  </si>
+  <si>
+    <t>金沢シーサイドFM×平潟祭実行委員会</t>
+  </si>
+  <si>
+    <t>loc-around-campus</t>
+  </si>
+  <si>
+    <t>金沢区を元気にするメディア 金沢シーサイドFM 連携企画！</t>
+  </si>
+  <si>
     <t>buildingId</t>
   </si>
   <si>
@@ -1387,6 +1402,9 @@
     <t>非公開</t>
   </si>
   <si>
+    <t>学内各所</t>
+  </si>
+  <si>
     <t>slotId</t>
   </si>
   <si>
@@ -1733,6 +1751,15 @@
   </si>
   <si>
     <t>12:00頃~</t>
+  </si>
+  <si>
+    <t>tt-d1-21</t>
+  </si>
+  <si>
+    <t>11:30~</t>
+  </si>
+  <si>
+    <t>tt-d2-17</t>
   </si>
 </sst>
 </file>
@@ -3747,7 +3774,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="9.285714285714286" customWidth="1"/>
@@ -3950,6 +3977,29 @@
         <v>341</v>
       </c>
     </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>342</v>
+      </c>
+      <c r="B9" t="s">
+        <v>343</v>
+      </c>
+      <c r="C9" t="s">
+        <v>344</v>
+      </c>
+      <c r="D9" t="s">
+        <v>315</v>
+      </c>
+      <c r="E9" t="s">
+        <v>345</v>
+      </c>
+      <c r="F9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" t="s">
+        <v>346</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -3958,7 +4008,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="19.285714285714285" customWidth="1"/>
@@ -3974,19 +4024,19 @@
         <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -3994,13 +4044,13 @@
         <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F2">
         <v>1</v>
@@ -4011,13 +4061,13 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E3" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F3">
         <v>2</v>
@@ -4028,13 +4078,13 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="D4" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E4" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -4045,13 +4095,13 @@
         <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="D5" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E5" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F5">
         <v>4</v>
@@ -4062,13 +4112,13 @@
         <v>37</v>
       </c>
       <c r="C6" t="s">
+        <v>358</v>
+      </c>
+      <c r="D6" t="s">
         <v>353</v>
       </c>
-      <c r="D6" t="s">
-        <v>348</v>
-      </c>
       <c r="E6" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F6">
         <v>5</v>
@@ -4079,13 +4129,13 @@
         <v>43</v>
       </c>
       <c r="C7" t="s">
+        <v>359</v>
+      </c>
+      <c r="D7" t="s">
+        <v>353</v>
+      </c>
+      <c r="E7" t="s">
         <v>354</v>
-      </c>
-      <c r="D7" t="s">
-        <v>348</v>
-      </c>
-      <c r="E7" t="s">
-        <v>349</v>
       </c>
       <c r="F7">
         <v>6</v>
@@ -4096,13 +4146,13 @@
         <v>48</v>
       </c>
       <c r="C8" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="D8" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E8" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F8">
         <v>7</v>
@@ -4113,13 +4163,13 @@
         <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D9" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E9" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -4130,13 +4180,13 @@
         <v>60</v>
       </c>
       <c r="C10" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="D10" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E10" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F10">
         <v>9</v>
@@ -4147,13 +4197,13 @@
         <v>66</v>
       </c>
       <c r="C11" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="D11" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E11" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -4164,13 +4214,13 @@
         <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D12" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E12" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F12">
         <v>11</v>
@@ -4181,13 +4231,13 @@
         <v>78</v>
       </c>
       <c r="C13" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="D13" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E13" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F13">
         <v>12</v>
@@ -4198,13 +4248,13 @@
         <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="D14" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E14" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F14">
         <v>13</v>
@@ -4215,13 +4265,13 @@
         <v>90</v>
       </c>
       <c r="C15" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D15" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E15" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F15">
         <v>14</v>
@@ -4232,13 +4282,13 @@
         <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="D16" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E16" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F16">
         <v>15</v>
@@ -4249,13 +4299,13 @@
         <v>102</v>
       </c>
       <c r="C17" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="D17" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E17" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -4266,13 +4316,13 @@
         <v>108</v>
       </c>
       <c r="C18" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="D18" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E18" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F18">
         <v>17</v>
@@ -4283,13 +4333,13 @@
         <v>114</v>
       </c>
       <c r="C19" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="D19" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E19" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F19">
         <v>18</v>
@@ -4300,13 +4350,13 @@
         <v>120</v>
       </c>
       <c r="C20" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="D20" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E20" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F20">
         <v>19</v>
@@ -4317,13 +4367,13 @@
         <v>126</v>
       </c>
       <c r="C21" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D21" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E21" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F21">
         <v>20</v>
@@ -4334,13 +4384,13 @@
         <v>132</v>
       </c>
       <c r="C22" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="D22" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E22" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F22">
         <v>21</v>
@@ -4351,13 +4401,13 @@
         <v>138</v>
       </c>
       <c r="C23" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="D23" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E23" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F23">
         <v>22</v>
@@ -4368,13 +4418,13 @@
         <v>161</v>
       </c>
       <c r="C24" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="D24" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E24" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -4385,13 +4435,13 @@
         <v>156</v>
       </c>
       <c r="C25" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="D25" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="E25" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F25">
         <v>2</v>
@@ -4399,19 +4449,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="C26" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="D26" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="E26">
         <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -4419,19 +4469,19 @@
         <v>328</v>
       </c>
       <c r="B27" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C27" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D27" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E27">
         <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -4439,13 +4489,13 @@
         <v>332</v>
       </c>
       <c r="B28" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C28" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="D28" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E28">
         <v>2</v>
@@ -4459,13 +4509,13 @@
         <v>237</v>
       </c>
       <c r="B29" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C29" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="D29" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E29">
         <v>2</v>
@@ -4479,13 +4529,13 @@
         <v>178</v>
       </c>
       <c r="B30" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C30" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="D30" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E30">
         <v>2</v>
@@ -4499,13 +4549,13 @@
         <v>183</v>
       </c>
       <c r="B31" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C31" t="s">
+        <v>389</v>
+      </c>
+      <c r="D31" t="s">
         <v>384</v>
-      </c>
-      <c r="D31" t="s">
-        <v>379</v>
       </c>
       <c r="E31">
         <v>2</v>
@@ -4519,13 +4569,13 @@
         <v>223</v>
       </c>
       <c r="B32" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C32" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
       <c r="D32" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E32">
         <v>1</v>
@@ -4539,13 +4589,13 @@
         <v>207</v>
       </c>
       <c r="B33" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C33" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="D33" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E33">
         <v>1</v>
@@ -4559,13 +4609,13 @@
         <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C34" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
       <c r="D34" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E34">
         <v>1</v>
@@ -4579,19 +4629,19 @@
         <v>219</v>
       </c>
       <c r="B35" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C35" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="D35" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E35">
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -4599,13 +4649,13 @@
         <v>211</v>
       </c>
       <c r="B36" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C36" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
       <c r="D36" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E36">
         <v>2</v>
@@ -4619,13 +4669,13 @@
         <v>202</v>
       </c>
       <c r="B37" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C37" t="s">
+        <v>400</v>
+      </c>
+      <c r="D37" t="s">
         <v>395</v>
-      </c>
-      <c r="D37" t="s">
-        <v>390</v>
       </c>
       <c r="E37">
         <v>2</v>
@@ -4639,13 +4689,13 @@
         <v>173</v>
       </c>
       <c r="B38" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C38" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="D38" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E38">
         <v>2</v>
@@ -4659,13 +4709,13 @@
         <v>228</v>
       </c>
       <c r="B39" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C39" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
       <c r="D39" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E39">
         <v>2</v>
@@ -4679,13 +4729,13 @@
         <v>188</v>
       </c>
       <c r="B40" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C40" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="D40" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E40">
         <v>2</v>
@@ -4699,13 +4749,13 @@
         <v>232</v>
       </c>
       <c r="B41" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C41" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
       <c r="D41" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E41">
         <v>3</v>
@@ -4719,13 +4769,13 @@
         <v>197</v>
       </c>
       <c r="B42" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="C42" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
       <c r="D42" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="E42">
         <v>3</v>
@@ -4739,33 +4789,33 @@
         <v>215</v>
       </c>
       <c r="B43" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="C43" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="D43" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="E43">
         <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="B44" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C44" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
       <c r="D44" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E44">
         <v>2</v>
@@ -4779,13 +4829,13 @@
         <v>250</v>
       </c>
       <c r="B45" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C45" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="D45" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E45">
         <v>2</v>
@@ -4796,16 +4846,16 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
       <c r="B46" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C46" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="D46" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E46">
         <v>3</v>
@@ -4819,13 +4869,13 @@
         <v>254</v>
       </c>
       <c r="B47" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C47" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="D47" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E47">
         <v>3</v>
@@ -4836,16 +4886,16 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>415</v>
+      </c>
+      <c r="B48" t="s">
+        <v>408</v>
+      </c>
+      <c r="C48" t="s">
+        <v>416</v>
+      </c>
+      <c r="D48" t="s">
         <v>410</v>
-      </c>
-      <c r="B48" t="s">
-        <v>403</v>
-      </c>
-      <c r="C48" t="s">
-        <v>411</v>
-      </c>
-      <c r="D48" t="s">
-        <v>405</v>
       </c>
       <c r="E48">
         <v>4</v>
@@ -4859,13 +4909,13 @@
         <v>261</v>
       </c>
       <c r="B49" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C49" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D49" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E49">
         <v>4</v>
@@ -4879,16 +4929,16 @@
         <v>277</v>
       </c>
       <c r="C50" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="D50" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E50" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F50" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -4896,19 +4946,19 @@
         <v>264</v>
       </c>
       <c r="B51" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="C51" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="D51" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E51">
         <v>4</v>
       </c>
       <c r="F51" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -4916,16 +4966,16 @@
         <v>291</v>
       </c>
       <c r="C52" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="D52" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E52">
         <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -4933,16 +4983,16 @@
         <v>286</v>
       </c>
       <c r="C53" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="D53" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="E53" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F53" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -4950,16 +5000,16 @@
         <v>296</v>
       </c>
       <c r="C54" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="D54" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="E54">
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -4967,16 +5017,16 @@
         <v>281</v>
       </c>
       <c r="C55" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="D55" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
       <c r="E55">
         <v>6</v>
       </c>
       <c r="F55" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -4984,19 +5034,19 @@
         <v>322</v>
       </c>
       <c r="B56" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C56" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
       <c r="D56" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E56">
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -5004,19 +5054,19 @@
         <v>150</v>
       </c>
       <c r="B57" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="C57" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="D57" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E57">
         <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -5024,13 +5074,13 @@
         <v>257</v>
       </c>
       <c r="B58" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C58" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="D58" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E58">
         <v>2</v>
@@ -5044,13 +5094,13 @@
         <v>242</v>
       </c>
       <c r="B59" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C59" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="D59" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E59">
         <v>4</v>
@@ -5064,13 +5114,13 @@
         <v>246</v>
       </c>
       <c r="B60" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="C60" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="D60" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
       <c r="E60">
         <v>3</v>
@@ -5084,16 +5134,16 @@
         <v>340</v>
       </c>
       <c r="C61" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D61" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="E61" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F61" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -5101,32 +5151,40 @@
         <v>316</v>
       </c>
       <c r="C62" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="D62" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E62" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="F62" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C63" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="C64" t="s">
-        <v>437</v>
+        <v>442</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>345</v>
+      </c>
+      <c r="C65" t="s">
+        <v>443</v>
       </c>
     </row>
   </sheetData>
@@ -5137,7 +5195,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
@@ -5148,7 +5206,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>5</v>
@@ -5157,13 +5215,13 @@
         <v>4</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -5171,7 +5229,7 @@
         <v>259</v>
       </c>
       <c r="B2" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="C2" t="s">
         <v>20</v>
@@ -5180,13 +5238,13 @@
         <v>277</v>
       </c>
       <c r="E2" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="F2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="G2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
@@ -5194,7 +5252,7 @@
         <v>239</v>
       </c>
       <c r="B3" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -5203,13 +5261,13 @@
         <v>277</v>
       </c>
       <c r="E3" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="F3" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="G3" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -5217,7 +5275,7 @@
         <v>244</v>
       </c>
       <c r="B4" t="s">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -5226,13 +5284,13 @@
         <v>277</v>
       </c>
       <c r="E4" t="s">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c r="F4" t="s">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="G4" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -5240,7 +5298,7 @@
         <v>252</v>
       </c>
       <c r="B5" t="s">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -5249,13 +5307,13 @@
         <v>277</v>
       </c>
       <c r="E5" t="s">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="F5" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="G5" t="s">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -5263,7 +5321,7 @@
         <v>255</v>
       </c>
       <c r="B6" t="s">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -5272,13 +5330,13 @@
         <v>277</v>
       </c>
       <c r="E6" t="s">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="F6" t="s">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="G6" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
@@ -5286,7 +5344,7 @@
         <v>248</v>
       </c>
       <c r="B7" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="C7" t="s">
         <v>20</v>
@@ -5295,13 +5353,13 @@
         <v>277</v>
       </c>
       <c r="E7" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="F7" t="s">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="G7" t="s">
-        <v>465</v>
+        <v>471</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
@@ -5309,7 +5367,7 @@
         <v>275</v>
       </c>
       <c r="B8" t="s">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="C8" t="s">
         <v>20</v>
@@ -5318,13 +5376,13 @@
         <v>277</v>
       </c>
       <c r="E8" t="s">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="F8" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="G8" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -5332,7 +5390,7 @@
         <v>263</v>
       </c>
       <c r="B9" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="C9" t="s">
         <v>20</v>
@@ -5341,13 +5399,13 @@
         <v>264</v>
       </c>
       <c r="E9" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="F9" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G9" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
@@ -5355,7 +5413,7 @@
         <v>266</v>
       </c>
       <c r="B10" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
       <c r="C10" t="s">
         <v>20</v>
@@ -5364,13 +5422,13 @@
         <v>264</v>
       </c>
       <c r="E10" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="F10" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
       <c r="G10" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
@@ -5378,7 +5436,7 @@
         <v>269</v>
       </c>
       <c r="B11" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
       <c r="C11" t="s">
         <v>20</v>
@@ -5387,13 +5445,13 @@
         <v>264</v>
       </c>
       <c r="E11" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="F11" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="G11" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
@@ -5401,7 +5459,7 @@
         <v>272</v>
       </c>
       <c r="B12" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="C12" t="s">
         <v>20</v>
@@ -5410,13 +5468,13 @@
         <v>264</v>
       </c>
       <c r="E12" t="s">
-        <v>482</v>
+        <v>488</v>
       </c>
       <c r="F12" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="G12" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
@@ -5424,7 +5482,7 @@
         <v>288</v>
       </c>
       <c r="B13" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="C13" t="s">
         <v>20</v>
@@ -5433,13 +5491,13 @@
         <v>291</v>
       </c>
       <c r="E13" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F13" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="G13" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
@@ -5447,7 +5505,7 @@
         <v>283</v>
       </c>
       <c r="B14" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
@@ -5456,13 +5514,13 @@
         <v>286</v>
       </c>
       <c r="E14" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="F14" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="G14" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
@@ -5470,7 +5528,7 @@
         <v>293</v>
       </c>
       <c r="B15" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
@@ -5479,13 +5537,13 @@
         <v>296</v>
       </c>
       <c r="E15" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F15" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="G15" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
@@ -5493,7 +5551,7 @@
         <v>293</v>
       </c>
       <c r="B16" t="s">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="C16" t="s">
         <v>20</v>
@@ -5502,13 +5560,13 @@
         <v>296</v>
       </c>
       <c r="E16" t="s">
+        <v>502</v>
+      </c>
+      <c r="F16" t="s">
         <v>496</v>
       </c>
-      <c r="F16" t="s">
-        <v>490</v>
-      </c>
       <c r="G16" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
@@ -5516,7 +5574,7 @@
         <v>298</v>
       </c>
       <c r="B17" t="s">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="C17" t="s">
         <v>20</v>
@@ -5525,13 +5583,13 @@
         <v>296</v>
       </c>
       <c r="E17" t="s">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="F17" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="G17" t="s">
-        <v>501</v>
+        <v>507</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
@@ -5539,7 +5597,7 @@
         <v>300</v>
       </c>
       <c r="B18" t="s">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="C18" t="s">
         <v>20</v>
@@ -5548,13 +5606,13 @@
         <v>296</v>
       </c>
       <c r="E18" t="s">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="F18" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="G18" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
@@ -5562,7 +5620,7 @@
         <v>259</v>
       </c>
       <c r="B19" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="C19" t="s">
         <v>144</v>
@@ -5571,13 +5629,13 @@
         <v>277</v>
       </c>
       <c r="E19" t="s">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="F19" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="G19" t="s">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -5585,7 +5643,7 @@
         <v>239</v>
       </c>
       <c r="B20" t="s">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="C20" t="s">
         <v>144</v>
@@ -5594,13 +5652,13 @@
         <v>277</v>
       </c>
       <c r="E20" t="s">
-        <v>510</v>
+        <v>516</v>
       </c>
       <c r="F20" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="G20" t="s">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
@@ -5608,7 +5666,7 @@
         <v>244</v>
       </c>
       <c r="B21" t="s">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="C21" t="s">
         <v>144</v>
@@ -5617,13 +5675,13 @@
         <v>277</v>
       </c>
       <c r="E21" t="s">
-        <v>513</v>
+        <v>519</v>
       </c>
       <c r="F21" t="s">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="G21" t="s">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
@@ -5631,7 +5689,7 @@
         <v>252</v>
       </c>
       <c r="B22" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="C22" t="s">
         <v>144</v>
@@ -5640,13 +5698,13 @@
         <v>277</v>
       </c>
       <c r="E22" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="F22" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
       <c r="G22" t="s">
-        <v>519</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
@@ -5654,7 +5712,7 @@
         <v>255</v>
       </c>
       <c r="B23" t="s">
-        <v>520</v>
+        <v>526</v>
       </c>
       <c r="C23" t="s">
         <v>144</v>
@@ -5663,13 +5721,13 @@
         <v>277</v>
       </c>
       <c r="E23" t="s">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="F23" t="s">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="G23" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
@@ -5677,7 +5735,7 @@
         <v>248</v>
       </c>
       <c r="B24" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C24" t="s">
         <v>144</v>
@@ -5686,13 +5744,13 @@
         <v>277</v>
       </c>
       <c r="E24" t="s">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="F24" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="G24" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
@@ -5700,7 +5758,7 @@
         <v>275</v>
       </c>
       <c r="B25" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="C25" t="s">
         <v>144</v>
@@ -5709,13 +5767,13 @@
         <v>277</v>
       </c>
       <c r="E25" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="F25" t="s">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="G25" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
@@ -5723,7 +5781,7 @@
         <v>279</v>
       </c>
       <c r="B26" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="C26" t="s">
         <v>144</v>
@@ -5732,13 +5790,13 @@
         <v>277</v>
       </c>
       <c r="E26" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="F26" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="G26" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
@@ -5746,7 +5804,7 @@
         <v>263</v>
       </c>
       <c r="B27" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C27" t="s">
         <v>144</v>
@@ -5755,13 +5813,13 @@
         <v>264</v>
       </c>
       <c r="E27" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="F27" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="G27" t="s">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
@@ -5769,7 +5827,7 @@
         <v>272</v>
       </c>
       <c r="B28" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="C28" t="s">
         <v>144</v>
@@ -5778,13 +5836,13 @@
         <v>264</v>
       </c>
       <c r="E28" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="F28" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="G28" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
@@ -5792,7 +5850,7 @@
         <v>307</v>
       </c>
       <c r="B29" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="C29" t="s">
         <v>144</v>
@@ -5801,13 +5859,13 @@
         <v>264</v>
       </c>
       <c r="E29" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="F29" t="s">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="G29" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
@@ -5815,7 +5873,7 @@
         <v>288</v>
       </c>
       <c r="B30" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="C30" t="s">
         <v>144</v>
@@ -5824,13 +5882,13 @@
         <v>291</v>
       </c>
       <c r="E30" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
       <c r="F30" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="G30" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
@@ -5838,7 +5896,7 @@
         <v>303</v>
       </c>
       <c r="B31" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="C31" t="s">
         <v>144</v>
@@ -5847,13 +5905,13 @@
         <v>296</v>
       </c>
       <c r="E31" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="F31" t="s">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="G31" t="s">
-        <v>456</v>
+        <v>462</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
@@ -5861,7 +5919,7 @@
         <v>303</v>
       </c>
       <c r="B32" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="C32" t="s">
         <v>144</v>
@@ -5870,13 +5928,13 @@
         <v>296</v>
       </c>
       <c r="E32" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
       <c r="F32" t="s">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="G32" t="s">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
@@ -5884,7 +5942,7 @@
         <v>305</v>
       </c>
       <c r="B33" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="C33" t="s">
         <v>144</v>
@@ -5893,13 +5951,13 @@
         <v>296</v>
       </c>
       <c r="E33" t="s">
+        <v>502</v>
+      </c>
+      <c r="F33" t="s">
         <v>496</v>
       </c>
-      <c r="F33" t="s">
-        <v>490</v>
-      </c>
       <c r="G33" t="s">
-        <v>497</v>
+        <v>503</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
@@ -5907,7 +5965,7 @@
         <v>305</v>
       </c>
       <c r="B34" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C34" t="s">
         <v>144</v>
@@ -5916,13 +5974,13 @@
         <v>296</v>
       </c>
       <c r="E34" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F34" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="G34" t="s">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
@@ -5930,7 +5988,7 @@
         <v>313</v>
       </c>
       <c r="B35" t="s">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="C35" t="s">
         <v>20</v>
@@ -5939,36 +5997,36 @@
         <v>316</v>
       </c>
       <c r="E35" t="s">
-        <v>548</v>
+        <v>554</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B36" t="s">
-        <v>550</v>
+        <v>556</v>
       </c>
       <c r="C36" t="s">
         <v>20</v>
       </c>
       <c r="D36" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="E36" t="s">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="F36" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="G36" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
@@ -5976,7 +6034,7 @@
         <v>337</v>
       </c>
       <c r="B37" t="s">
-        <v>552</v>
+        <v>558</v>
       </c>
       <c r="C37" t="s">
         <v>20</v>
@@ -5985,13 +6043,59 @@
         <v>340</v>
       </c>
       <c r="E37" t="s">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="F37" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="G37" t="s">
-        <v>453</v>
+        <v>459</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>342</v>
+      </c>
+      <c r="B38" t="s">
+        <v>560</v>
+      </c>
+      <c r="C38" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" t="s">
+        <v>345</v>
+      </c>
+      <c r="E38" t="s">
+        <v>561</v>
+      </c>
+      <c r="F38" t="s">
+        <v>479</v>
+      </c>
+      <c r="G38" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>342</v>
+      </c>
+      <c r="B39" t="s">
+        <v>562</v>
+      </c>
+      <c r="C39" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" t="s">
+        <v>345</v>
+      </c>
+      <c r="E39" t="s">
+        <v>561</v>
+      </c>
+      <c r="F39" t="s">
+        <v>479</v>
+      </c>
+      <c r="G39" t="s">
+        <v>524</v>
       </c>
     </row>
   </sheetData>

--- a/app/data/hirakata_festival_data.xlsx
+++ b/app/data/hirakata_festival_data.xlsx
@@ -3379,8 +3379,10 @@
       <c r="D2" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>293</v>
+      <c r="E2" t="inlineStr" s="2">
+        <is>
+          <t>loc-7-402,loc-outdoor-stage</t>
+        </is>
       </c>
       <c r="F2" s="2" t="s">
         <v>320</v>
@@ -3402,8 +3404,10 @@
       <c r="D3" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>295</v>
+      <c r="E3" t="inlineStr" s="2">
+        <is>
+          <t>loc-7-302,loc-outdoor-stage</t>
+        </is>
       </c>
       <c r="F3" s="2" t="s">
         <v>320</v>
@@ -3425,8 +3429,10 @@
       <c r="D4" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>262</v>
+      <c r="E4" t="inlineStr" s="2">
+        <is>
+          <t>loc-7-202,loc-outdoor-stage</t>
+        </is>
       </c>
       <c r="F4" s="2" t="s">
         <v>320</v>
@@ -3448,8 +3454,10 @@
       <c r="D5" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>266</v>
+      <c r="E5" t="inlineStr" s="2">
+        <is>
+          <t>loc-7-303,loc-outdoor-stage</t>
+        </is>
       </c>
       <c r="F5" s="2" t="s">
         <v>320</v>
@@ -3469,8 +3477,10 @@
       <c r="D6" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>262</v>
+      <c r="E6" t="inlineStr" s="2">
+        <is>
+          <t>loc-7-203,loc-outdoor-stage</t>
+        </is>
       </c>
       <c r="F6" s="2" t="s">
         <v>320</v>
@@ -3492,8 +3502,10 @@
       <c r="D7" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>270</v>
+      <c r="E7" t="inlineStr" s="2">
+        <is>
+          <t>loc-7-403,loc-outdoor-stage</t>
+        </is>
       </c>
       <c r="F7" s="2" t="s">
         <v>320</v>
@@ -3515,8 +3527,10 @@
       <c r="D8" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>354</v>
+      <c r="E8" t="inlineStr" s="2">
+        <is>
+          <t>loc-7-107,loc-scc-bennett</t>
+        </is>
       </c>
       <c r="F8" s="2" t="s">
         <v>320</v>
@@ -5146,8 +5160,10 @@
       <c r="B55" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>274</v>
+      <c r="C55" t="inlineStr" s="2">
+        <is>
+          <t>屋内ステージ</t>
+        </is>
       </c>
       <c r="D55" s="2" t="s">
         <v>275</v>
